--- a/productos_mercadolibre.xlsx
+++ b/productos_mercadolibre.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="almacenamiento" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monitores" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,71 +430,276 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>categoria</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>titulo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>precio</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>precio_anterior</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>descuento</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>envio</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>envio_gratis</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>rating</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>total_reviews</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>imagen</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>fecha_actualizacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ssd Nvme Disco Duro Solido 512 Gb M2 2280 Laptop Computacion</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=ee0j4wvh3eoimsVzRTuAIAVGZRhEh39tccNpGmJsQsTUTvaZtOkuMFEVDCpA1wo7L9E1Qcv4mZQjQW4t0%2BpzVZGZ02sRp9HovJI4gnDsJ57b2KbH2A97ga%2FuHfWF98KKSMI78U9iYOyiJc45zf26KS%2B7VFk0dbFL4PrNuBCoaKkLh%2FWuYqqohEj70HEkOey5n%2FlaNCLBf%2BRjNL9HCjnYIDnfJTp5SLOsupH6LYnRR5PObE2tTdhe%2BPLZyj4JNYaDPjhaw%2BfcxUA%2FjA0yyCdr%2Be5yiFe8ljZcO356%2Bx5%2FQuvehjUTrO2lYmJyL0y4jwwVa79L7wbm%2FOx9BkmPoIiscJx5IwCMBXfsDNxiphyxc02mDpvf1SenSh0CeCeOE4GDQvb6cW8hx9WKKgHtI6lNQ%2F7bYaQlym%2FANBX%2FJAuRJFe1appHjiOU3N8xz2jGJh5ZSokVbB0rnJOy1d7JPFZAxZ4Ub50%2FHR%2FIAXNxW7ZV7oOnBDrK4vRK8WOQfDCMSJGuBqIdQsplAbZToNITHwKtS9VrPvfiMMEAqbwYrqNjNR%2FgL5dhCy1BTCiXGh4%2FkThcWUcoCQqOtOUm2m1Rp2%2B7COiH4u5D3CmY%2BUEU8iwY9RmHq4zdxGXnifZE9qQohxhpMf0fXo1qFAz1NblBF%2BdWDmRw2A68Bi%2F%2B8mCUqG1XYyuCO9Mjmkxrrz9pnxGEXB10EfDRNjbF7jjGGRNecoDH%2BT5R4nWK2XgCDCo9gX1qyoDgt%2Bgbor0Yy1rHD9GCCmTfZIZvNyOCKaJkxtEz2RxWUwrkO1bQN7vpO%2F5Hbg%3D%3D&amp;highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=eb85adee-7abb-4fdd-ab55-264cf6b14e7e&amp;wid=MCO2742971682&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>176560</v>
+      </c>
+      <c r="E2" t="n">
+        <v>296500</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>40% OFF</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J2" t="n">
+        <v>14</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_764117-MCO83036481287_032025-V.webp</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>45809.63719189815</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Disco Solido Ssd Interno 120gb (128gb) Sata Premium Seguro</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=t80usphhHp4v1mI6O87K82wGWIJ3bYXyjr3NaWgzhLEiq75tvWqauIq6Ycr%2BVjLTRyjU4H9F%2BqKKM3EOLQC2mhzWa1e6tlTDXqzGXLEOCpzxC6gwqvTrjHKkVyigls4VW9hvoUR%2FnVM7Tjvp0obKB3o61fK4EIgx0IdJKVuPpU0fhXocfiy6C6uXXpAqHM8OBUwBurVGvO7K%2FY5dNrQZ4%2FTVKslVDBx%2F7LlLcIXc9LwbXjdXpzPml6rNxP1ksjouCirVNSscccUrNItopUGPTk931pNnoDISw%2Bda2CKVt8YgawivOKx6h0XiBWHPRNVVJbCQegnEVUPSpCHiZFnTTUphrV4MLuCWzMHy%2FVePCofQrwxecBzSrCg2v%2FyF7AX%2FaHgSI%2BSiuQu5T5hYNMjIW9dhivsDPb7BlJa8W4Wq5wdNnX1lWFyLFBhnCw2f0jf95PQXir%2FYhgosOok5NP2GluGvq78WuvpbWY6S%2Bhve871eb6O0lUoQpg5jXDGsPKC7yh0ujo56VTtH78uctTGWUWpG41vTNHyQD05%2BbqIDIMubBomVr5qTTDINoyVER61zjA517kFRFJ7drd0qRkjcMKGPRuUL2BVwxftBiIQ40jC8ez5IxXVuhhZqlpcfkij4guH5JJHl3Cc5pywwSsera%2BQdu60a%2Bw0IsIjbofcBYUUAg7YhVGCfkbI6AZa6rgmYPrPm2VgkNF%2FbntVRLXON%2FnMW%2B3tfIfoyDxxbJVp1P0X8iisw%2FQSN9Xar%2B0r%2F9rarpmSBL5BODeHAPWh3LxULfoer21jY4K%2BjXvAWe%2FemSmDMDZFtVENWgGWvRu5AO9PqC4LmyTI9N%2F83v7QMD%2F5NPbJyMNtXzXbNiCoruxRtco%2FORiFCpIFOSg%3D%3D&amp;searchVariation=173636587098&amp;highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=eb85adee-7abb-4fdd-ab55-264cf6b14e7e</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>49600</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>45</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_667991-MCO54907943874_042023-V.webp</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>45809.63719193287</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ADATA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Disco sólido SSD interno Adata Ultimate SU650 ASU650SS-512GT-R 512GB</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/disco-solido-ssd-interno-adata-ultimate-su650-asu650ss-512gt-r-512gb/p/MCO35339869?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO35339869&amp;position=6&amp;search_layout=stack&amp;type=product&amp;tracking_id=eb85adee-7abb-4fdd-ab55-264cf6b14e7e&amp;wid=MCO2329119764&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>142900</v>
+      </c>
+      <c r="E4" t="n">
+        <v>299888</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>52% OFF</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>696</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>45809.63719194444</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
           <t>marca</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>titulo</t>
+        </is>
+      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>titulo</t>
+          <t>url</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>url</t>
+          <t>precio</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>precio</t>
+          <t>precio_anterior</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>precio_anterior</t>
+          <t>descuento</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>descuento</t>
+          <t>envio</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>envio</t>
+          <t>envio_gratis</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>envio_gratis</t>
+          <t>rating</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>total_reviews</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>total_reviews</t>
+          <t>imagen</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>imagen</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>fecha_actualizacion</t>
         </is>
@@ -502,178 +708,217 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>lapto</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>Monitor Gamer Xiaomi con pantalla de 34" 180Hz 110V y resolución WQHD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Computador Portatil Laptop Corporativo Promocion Usado</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=%2FteWDOW%2FleiSB2FF9%2BdNlL4T4Qo3T6DDutkHIgD8Yx5xBxfC6QplCKVQ1uVGOtTxpEajBXGloX%2FE7SCQyJhGo9xnIIr72dhXoDek%2BHHuzoUothCKDXBsEudoaU0ulpCiYRvQI%2BHTIWSNE%2BhWzczLyhoTTgYKespsg3q3jKHk33Syf0NQBwXwZL%2FP1wHhsO0YKPArxia1j4OOvZx0oZzLxid12cmF3fQHArtEp1m7jhJiZBr%2BdqRem9mVIikk6%2FNC6kwqgbRLAgh7oC4GqwG1i3N%2Fer9%2BoXZeojjx04edyZpWCJ2Gk60AwgyKHHZSjSLybaTDfJfcDoKxjWtOZ9WN2EjWzr9gD775Mzdc77PUM%2FC2sB9jJmg0oewUJa3xG18fjFDVrbaoqzB0Rm30X8URPQG%2FibvFXmkMSvfWWP2vmkkbHGaUU0Pf2eiLm1aQmkoACgjIOphPBs%2BxQRgMnAf3kcpQlJ2eClc43wK3gifuJ9ZdaYXpOcUUbjQtIsLlwFqyAilUc8OjNSCIp%2Bh5R%2B%2FE5EKV32fSlxYvTB13iZIYVMtjGTDK3W3goMX90m6qdVJPicqXNVEt9EpmknGrceichQJ6GBjDQ3O4PwpeMx%2ByPFilhfl8YmFeaLGXXNKJcezUM%2BusVA%2FJGWf85RWkAy5kmUs4F6q3hl%2F0kF4%2Be2bjKF1w430S9LHlp6UIUxHYlatnuwUCf%2B9KtRWo%2FaJ4g%2B7PA3dHP%2BVCBTFtv9RoyCcmKF0pz2AaEnowFcZlE9eobkLm2qkHIlDIAml1FXUj6ZARYOlnMFeGgqml4aIPEaGAFdJoToKPixCg078dTX2Xkahw28Vb94xQHotV8b9Qkx8zMTiL8Xmx8ApWjntW7bvvrNSncAPOt%2FKCGg%3D%3D&amp;searchVariation=181673730321&amp;highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=6d1f0b94-94af-437e-9b51-a8647a004bfd</t>
-        </is>
+          <t>https://www.mercadolibre.com.co/monitor-gamer-xiaomi-con-pantalla-de-34-180hz-110v-y-resolucion-wqhd/p/MCO43960788?highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO43960788&amp;position=4&amp;search_layout=stack&amp;type=product&amp;tracking_id=1615f080-5283-4342-a0d2-599a57689da2&amp;wid=MCO1518847209&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1513122</v>
       </c>
       <c r="E2" t="n">
-        <v>759999</v>
-      </c>
-      <c r="F2" t="n">
-        <v>999999</v>
+        <v>1949900</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>22% OFF</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>24% OFF</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
           <t>Envío gratis</t>
         </is>
       </c>
-      <c r="I2" t="b">
+      <c r="H2" t="b">
         <v>1</v>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_762946-MCO83338686127_032025-V.webp</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>45809.63341739828</v>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_827699-MLU74975109969_032024-V.webp</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>45809.63902657673</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>lapto</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Monitor LG curvo 32MR50C-B Full HD 32" 1920 px x 1080 px negro 110V</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Laptop Hp I5 Ddr4 8gb Ssd 240gb Windows 11</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=rBE1tT%2BhBOdV1aiCUdqCp%2BJ284SSmHG65dYuVQ4Gm58xYdoBb8Ygv9dfBMflJv%2BJr%2Bnz55gMvHnWgK%2B1k3NX90A6uE%2BVjZDezWjthR1Wmkt0aymXZdivKLT%2BewhVsX6Gnn5T5d%2FScxLjInMP1nCf9QKpW%2FhrW5vdjpl7tsE%2B5F6fqbcxqZ7ZVc%2FNowh4QbQzOjfcEIOor9p16mbTL6iS3VJkTXPpi8rOT0MSXJxTlR1w12n4rYAjlM9KiUZROn%2Bq7ramlmGtNQNJHBOLTCTr9CjWSocjPD0S4xbt5tr9248dbxiQScquMa3hkSXWst9WTZ6gOyVXBJR9G%2FE68V1knb9zHyVOq5mk%2FWDks2S5pKFOB9TKUHNXlnMkDm%2Bwq2aTW9MVM%2B2crskT0AqAHINtL82s1Bb7zZBlSLPeOa98m8yNxK0pxOSvkG4EWdCHf%2BePXGjh12q9%2BYdVKxtFm4OEZb9AT1L2lctqTqlMKlXrDJxn5H8DYSexheaJGV%2FKjNGVTX0SKFdyl7x1C%2Fxcra6mUNu4BnWhqeHl85gTonlD25cNIvpUzLMjSaPoWtRaFfQ9WKn366zrxVBb1B7g0meUC7YsIU9Mo2g8gHBJKes%2BbCWeeWdzL1rzv9qdUvTQeIOKUY%2FSbp2XMMsUD4AP67fX6bvsHtlA%2Bf0MGvuH8QFFvw60TIf4iVQTM%2FNcrqsLkAY5gnhyFaJe8Mc5cKRvEInQkxxRtLXhNFtn1GwAFQ4WqEQ8RgTvgc9stfK0ccFZEHU%2B%2F%2BOSw1n9ZqO%2FCY%2FfaMR0qomvBIv7rTOxVc7emMZ%2BbGPbCPz7nQ5klJD3lr48VLk4F6Zia6Dg%2FWgcdbIRwkw1n0O1YNAdqijZsfM%3D&amp;searchVariation=186865852637&amp;highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=6d1f0b94-94af-437e-9b51-a8647a004bfd</t>
-        </is>
+          <t>https://www.mercadolibre.com.co/monitor-lg-curvo-32mr50c-b-full-hd-32-1920-px-x-1080-px-negro-110v/p/MCO38243621?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO38243621&amp;position=5&amp;search_layout=stack&amp;type=product&amp;tracking_id=1615f080-5283-4342-a0d2-599a57689da2&amp;wid=MCO1578787515&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>780000</v>
       </c>
       <c r="E3" t="n">
-        <v>769999</v>
-      </c>
-      <c r="F3" t="n">
-        <v>999999</v>
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>23% OFF</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
           <t>Envío gratis</t>
         </is>
       </c>
-      <c r="I3" t="b">
+      <c r="H3" t="b">
         <v>1</v>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_966418-MCO84722083030_052025-V.webp</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>45809.63341744232</v>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_663594-MLU77449045398_072024-V.webp</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>45809.63902660412</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>lapto</t>
+          <t>SAMSUNG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ASUS</t>
+          <t>Monitor Gamer Samsung C27R500FHL con pantalla de 27" 60Hz 110V y resolución Full HD Negro</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Portátil Asus Vivobook X1502 Ci5-12500h 24gb Ssd512 Fhd15.6 color Quiet Blue</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://www.mercadolibre.com.co/portatil-asus-vivobook-x1502-ci5-12500h-24gb-ssd512-fhd156-color-quiet-blue/p/MCO47191661?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO47191661&amp;position=10&amp;search_layout=stack&amp;type=product&amp;tracking_id=6d1f0b94-94af-437e-9b51-a8647a004bfd&amp;wid=MCO1569451947&amp;sid=search</t>
-        </is>
+          <t>https://www.mercadolibre.com.co/monitor-gamer-samsung-c27r500fhl-con-pantalla-de-27-60hz-110v-y-resolucion-full-hd-negro/p/MCO43958520?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO43958520&amp;position=6&amp;search_layout=stack&amp;type=product&amp;tracking_id=1615f080-5283-4342-a0d2-599a57689da2&amp;wid=MCO2766968630&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>636800</v>
       </c>
       <c r="E4" t="n">
-        <v>1929900</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2249000</v>
+        <v>1000000</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>36% OFF</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>14% OFF</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
           <t>Envío gratis</t>
         </is>
       </c>
-      <c r="I4" t="b">
+      <c r="H4" t="b">
         <v>1</v>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>616</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
           <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
         </is>
       </c>
-      <c r="M4" s="2" t="n">
-        <v>45809.63341746163</v>
+      <c r="L4" s="2" t="n">
+        <v>45809.63902661313</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Monitor gamer curvo Samsung LED dark blue gray 110V C32R500</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/monitor-gamer-curvo-samsung-led-dark-blue-gray-110v-c32r500/p/MCO43959782?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO43959782&amp;position=7&amp;search_layout=stack&amp;type=product&amp;tracking_id=1615f080-5283-4342-a0d2-599a57689da2&amp;wid=MCO2223865356&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>792900</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>45809.63902662089</v>
       </c>
     </row>
   </sheetData>

--- a/productos_mercadolibre.xlsx
+++ b/productos_mercadolibre.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="almacenamiento" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monitores" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="laptos" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -706,11 +707,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>Monitor Gamer Xiaomi con pantalla de 34" 180Hz 110V y resolución WQHD</t>
@@ -740,15 +737,11 @@
       <c r="H2" t="b">
         <v>1</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4.9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
+      <c r="I2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J2" t="n">
+        <v>58</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -756,7 +749,7 @@
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>45809.63902657673</v>
+        <v>45809.63902657408</v>
       </c>
     </row>
     <row r="3">
@@ -781,11 +774,7 @@
       <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Envío gratis</t>
@@ -794,15 +783,11 @@
       <c r="H3" t="b">
         <v>1</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4.6</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
+      <c r="I3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>65</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -810,7 +795,7 @@
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>45809.63902660412</v>
+        <v>45809.6390266088</v>
       </c>
     </row>
     <row r="4">
@@ -848,15 +833,11 @@
       <c r="H4" t="b">
         <v>1</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4.9</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>616</t>
-        </is>
+      <c r="I4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>616</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -864,7 +845,7 @@
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>45809.63902661313</v>
+        <v>45809.6390266088</v>
       </c>
     </row>
     <row r="5">
@@ -889,36 +870,1249 @@
       <c r="E5" t="n">
         <v>0</v>
       </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>343</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>45809.63902662037</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>titulo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>precio</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>precio_anterior</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>descuento</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>envio</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>envio_gratis</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>envio_full</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>rating</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>total_reviews</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>imagen</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>fecha_actualizacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Portatil Hp 12ava Gen Intel I3 1215u Ssd 512gb Ram 8gb Color Plateado</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=zQFU5BvnvqwRvMq1By5NRGFlzAqpbowk3qmAcnB%2BMJNDDwXDw3blW2x0QBWMcSaSHbHCVFn8z9QnYq1eJ4%2BiIrQdn2pihRo7erq%2FCWpkfyfGrhZe5Q0y9aSLBaAyFrwBVz8pHLUl0v%2BDgI5Z4uNAxCi%2Ftq9munKuJSr3tHuxxID%2FLfS5lpjCKXZf6y5BWLNFa3o8Q9HLMLnEtrWH6sCfv8n9sIlSn%2FxupheY5iO9EiTiB82RqwRYzDEaqFAhTHmbnJTLGJES%2FduL%2BytUQ2CcXDdQ%2FI9qzFtDZuET4I7n7jCACxvJlD0TjaRS%2Bz6FWkNFiVwXpekgIj0EOvfRaJdcptKXGmGbQTHwEt3aIKw8zUwgNEXsM4WAVIvJkEg%2BAOJPiGLcvy9oLbvDE3%2F1Qg1k6L1b07xhQBYOrqJ1Hzw24XIyxvPLHuATlo1tgOMKwmDZj9pNqAuGPVH%2BsxXE8vxGcztIWVIcp8XGXGyr9hpFvVbzfH42HleBpg13sXKRJ5Vjl9lbffaiO5XWuezBmpuJUyoO4DU1nnYNjxCiyUkBOZMsxLHvpEC6G6ifDchjVYhzBo%2BzI2b1%2Fy2r5u9GyQkXGIGRacKYr9hSvlpvLDLPPndYK0kmPApJzRiDE2I1bGnupjy7MbI82xT1KZtDG29siTpEsfBaMpDYtyW2rWqdVzlvBXAmLLiFE%2BRuudIIjRhhVSuQiZjL%2FJMBEUxwP%2FSECQDekZ3LKjkiSN5%2BCqQIABFqmw%2B2FC%2FQwLH5PIoV9jos7xgpGEhBkPSPLSGW8%2Bqjfb5J7hxgYnUIh%2BYWauaZa3Gr9qgWtHoQBjKxT5y5T2Fdbu3oJnCinh1GRNPJn6XClwRyw%2FWXJCAC0F8cbL7vlQWFkgYHjQeiwyUKEVqENuIutnP7QegOWK2gdDux1vQDdxDBQ22FK56BT%2Felqvcnx%2FTeewGBs%2BJX2kTVDc4H4%2BXJehllU62pKGU4tXUI&amp;highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1507088307&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1458900</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1853000</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>21% OFF</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_645989-MLU78944581522_092024-V.webp</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>45809.67502480594</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Notebook Hp 245 G10 R3 7330u 512gb Ssd 8gb Ram Windows 11 Ho</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=P218uynAcTyZmXvon7VW%2BB05NKdbrv2OpL%2FWCxMohF7wPq3pLnEW0GZVqp3NYJ8aqjTMwyMLpfrySzH1v1mRqq6ngqRFHwLD0GDtrD2hSY0Bbq4UZyhV5HSo0i0hX5StFbtvN3LkYOzknOfOMKR8UqMLlNQOoPnvDbE2hsAOTKxYOopK16M9GSZyqp%2FsqCsoexPDq1v3uFyJ2R%2BxHd7bDF%2B%2Fpr2AsZ1aWmUPSw9PmEmdYPzNpvI7e%2FKHVU88pGOs7ril5A2GpEWjzxfdOyqyDWHBjGnHtDHvxZ4UaAlJMaSRpfpUYx0Ys82tyPbnXrrYKowZIIAPGoQiAycX8FMp44x9dJgSxXznOWEL4H1h67ZcwXXtzT5jMyZyVLu5k2rEPbuH795zcKSJnK4qoKYW%2FMtvKs12XgUk0EcC1hjkLRcQ5DcSBTU1wIb1k4aq%2FvbASZYA0%2FU%2FX8LP9fEymdEy9ISan3aB3RD77qskxltzsRMqsxJZOZJ%2B3Ko%2B2W4%2F5DtESs%2FQ1%2Fzm8U4heIk2shJc0s3nRyfwJ7Jp83xnyzlMma7aQFDXhlkDT%2BKTxbWBhOt4nGugEC7PSIHNHtd7jsFocxCzKApEpr93h407loa%2B8FVCzEa%2FSGThzAlC2o6pXSgnbpjmyzBmTyW%2B4Qi9rjbGy94HiUCAJLvvEhh5vMCorTDzHBCJviWXBA0LRp8%2FPHSI8xmQzej%2FW7SLsfuvWeh8j9kMa22oCGt%2FUXpGqymoygpcwDuu2IuUcrxU6uFudy7ubRWqOjw1AYSldcCzfxhEjro2A5SJ5UzP2OvHf4EIB79MguWxk8XDyALruJtEIxE690lkCyLzU6ljjZuAAKD41fnfiGNEygW9uLZJ4Ja41lIEiWKEGc9pSg%2BkH9fM5ZE5Ggo2GeqBKnVNAyY4UDhKPJQZkioHfx6yFWBdDR1r6ayVSDeQW7wIDQtYrJ1CPmXIzA%3D%3D&amp;highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1547113843&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1259900</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1621375</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>22% OFF</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_679019-MLU78080956988_082024-V.webp</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>45809.67502483061</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ASUS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Portátil Asus Vivobook X1502 Ci5-12500h 24gb Ssd512 Fhd15.6 color Quiet Blue</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-asus-vivobook-x1502-ci5-12500h-24gb-ssd512-fhd156-color-quiet-blue/p/MCO47191661?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO47191661&amp;position=5&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1569451947&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1929900</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2249000</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>14% OFF</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>45809.67502484108</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LENOVO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Lenovo Ideapad 1 Ip 1 15igl7 Intel Celeron N4020 15,6 Pulgadas 8 GB Ram</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/lenovo-ideapad-1-ip-1-15igl7-intel-celeron-n4020-156-pulgadas-8-gb-ram/p/MCO40332473?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO40332473&amp;position=18&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO2864083698&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1016900</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1500000</v>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>32% OFF</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>45809.67502484915</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Msi Cyborg 14 A13vf I7 16gb 512gb Ssd Rtx 4060 8gb Color Negro</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/msi-cyborg-14-a13vf-i7-16gb-512gb-ssd-rtx-4060-8gb-color-negro/p/MCO45076522?highlight=false&amp;headerTopBrand=true#polycard_client=search-nordic&amp;searchVariation=MCO45076522&amp;position=10&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1547623157&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4653900</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6999000</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>33% OFF</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>45809.67502485745</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Potátil Portátil 14-dq0533la 14 8gb De Ram - 256gb Ssd - Intel Celeron</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=72GdK%2BpbrTFTM7i1sgjMu%2BbDsZwimgIVsgEMaqQVM80u2lSxiPxIp49lAD5FzvvX7tw%2B3WjmLZh4n%2BWEsTFcMPGWatgq50tuIi838LaR5oQJV5CEEvHbnKXPQACchyTHH0vjIO1%2Fj5c%2FXsO3bZMNq840pE4vh0ds%2Bd%2FwnVC79v072kXMRCGv3qHwC7U14OLGxP1MhOY85quB4Dd%2BoCzJ%2BVTsoBR7e70znoJTiR9qZUrKLyP%2BGL151fg2q%2FjTPcpe0EOWnfesuWGnIbRJ4UtBsHEOeSTUxpPqZKHMg8VjCEq4SmLvT%2BPRSReQB8aIUXznqFgDkSM1AE8omkj%2Fb%2FzxOs6KhMnCGKwZieGHEq6Q1rlE7c5VoFZGbp%2BOdt4PoLgaaqkzDbXOMhYOjXfdXrGgIzF6REZoUczzadV4ktrUlWshAxhwNxeakqcHnzwOFSCVPS4WrphjKzsUv3e3FIITEW1ZLpH%2BijyDAUSqj5BtIwnqZLC0aEfBTEKF086b3De50nkyz%2F1VJd4r2IhpVNLFE3P9mFqfBECnPRa1w%2Bj5TFMNuAMTPGDAZf%2Bp3f9QJMQ%2FrkuqXUtGmXqBcvaJSVoEKarvtyQY9iM9eRVEJGSve0Zvgw66yjF5rAZJXpCXH%2F0SuJqfrP1GZxnDkpeEMHfVYia4j959bA8TrP7ccIlaC37VeVRdDu%2F0329FzL07pGhmr0ABaZML9QGaZrqN7NpZPtdHai42qP5%2BxTxoA%2FgYEARxTAs3Y6XqVCueecJgOI7oc3f14YbulsBtatYNP%2Br%2FoKaJyI184MA5kvfmfDdC2Bfg12W8N6szceKHTo%2FthMXp4IoCP5VQNEK2vH5W%2FqMiPyumd%2FHlHpTXOTabOSyRlb%2BoYDSe4IzEy9SXmvrjE3GZPQi6T7ncDaOr3nL2yy%2BCUGFcYS4jRoUHT7Dr6RSMXBuSjuKMlIz5m2KgbW11LobjxwwP6xE%3D&amp;highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1547113619&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>919900</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1185375</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>22% OFF</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>45809.67502486529</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Portátil Hp 15-fd0026la Intel Core I3 8gb Ram 512gb Ssd</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=QHVRSkMapUYFd0MUsUJK5vva3fHEv%2FyYutnoyKQ309KPVo9qt3PSZ7ic6AU77nHcQz1SOsZVpaNDaqoo3MEy5TX%2Fx6omSlMudceAjcJe7TmVnVv6qgMEKiHF92%2FNwkqZ%2Fj%2FdQYtnH1YCcqK25LLkuC7M8zRZxibPMDqHhDa41LfQzT8c%2Fc2j3NZeddotr4mnhO%2FeiAgvZxsOVd0hkyHjXT6CpYL%2F7XgQFZsNyy%2Fomo3zxEpuqOyS3EuDTHF6K%2FM3k0hGvJK%2BS883r2s0w8NeHtjKUOh9ZDqR7cQneLG4ZVt4OwK51xKgfhII%2BzeCagUquSMbAp76%2FsgtCerLRz9BCuEE0PglxAd%2BjIr3MUL0%2Bgj5YJiP1EmHtBPGfqAY2mHskvzbW06do8Pjn%2BdFMX%2Fea8iyWi3OGOvq0O928uulkF5odhWAmKQcPvs5ZdHf3%2BnV0jb8WXXihcMGhQrADvxvEQH51JoKXOjYkgESygc010gYtqqzT3MiJs9RF%2FWpQr5CgHALRbn32vWyekuFqEFHmObrxqP%2B2mk25JoOhUWUdDpR9saNu0vKbpY8PWF1vyCe3mHfg9nILLA%2FWvCLLxP9da%2FPPyFYxZy%2FxjxaedElM9ABbpyy%2BtCcF7zXQlMoSWf7tTHpbaIhaW6sl4zv%2BsZiLd10R065djXFACsM7VKfZakLbHc0MwB%2FGgyi2RPCmVYd%2Fm5lu4XsHOCpLOCE3ApQF4LXLw6LVwxxpVpuLZb2E5zJRyJ0G9gt5xhE%2Bt1AFun%2BZBBd0X3oyTreYtHLOngjGLwPgPc1GdxghV%2B9wgeQ0zs0dm55nlM6w6DhGNJiRM6uQrAERZrHAAowzsKOY2ELq0Tz0lILYMyZxit0AxnKuccqHqrKCkl7iXonFO5zniizKB87r%2F%2B7DyxH%2B%2FtmdJ%2FoSMSeOcbPA%2BRGQ0Hgxz91UJBNRCeoO0ZHBzk0j4oq&amp;highlight=false&amp;headerTopBrand=true#polycard_client=search-nordic&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO2878894100&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2499900</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>45809.67502487299</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ASUS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Portátil Asus X1605za-mb644 Intel Corei5-12500h 16gb Ram Disco Solido 512ssd 16 Fhd Endless</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-asus-x1605za-mb644-intel-corei5-12500h-16gb-ram-disco-solido-512ssd-16-fhd-endless/p/MCO32161065?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO32161065&amp;position=3&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1523840021&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2029900</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>45809.67502488061</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ASUS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Portatil Asus E1504fa-nj474 Ryzen 5-7520u Ram 16gb Ssd 512gb Color Negro</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-asus-e1504fa-nj474-ryzen-5-7520u-ram-16gb-ssd-512gb-color-negro/p/MCO23498360?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO23498360&amp;position=14&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1541876389&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1725640</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1988778</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>13% OFF</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
         </is>
       </c>
-      <c r="L5" s="2" t="n">
-        <v>45809.63902662089</v>
+      <c r="M10" s="2" t="n">
+        <v>45809.67502488814</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MacBook Air 13.6 M2 256 GB SSD 16 GB Ram Z160000au C/ Nota</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/macbook-air-136-m2-256-gb-ssd-16-gb-ram-z160000au-c-nota/p/MCO26602331?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO26602331&amp;position=8&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO2813970572&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4299299</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5057999</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>15% OFF</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>45809.67502489956</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Portátil HP 15-fd0065la Intel Core i5 16 GB 1 TB SSD 15.6" FHD Windows 11 Home</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=DGWR%2F%2Fegp7TdyCwhdw99a44O2oQgggn7VIYlmeQwtLg8VC08255MGlgaOJG9lbdJKyvhyvI7V5q1aLrsqe%2F4FmXlVusxQNzjHGFm5g0X44I9Dsb6kLzzhEiV4yyhD5iaunlUQefJHzTinDxyR0JqlbymbdlaJx4YYa%2FCdP4FSZgW409zFcLfSsXtpptnSgdJFrIwp86aGz9Uu%2Bd0iXBWcFs6tNefITwdYXIRpyNP1owqQcRMO1yu3x9MLyRXPUjvhwX5W%2ByYCjVFRzjY44o32cMJ1gFNlR5T7n%2BmX84DfqkNTgQkajcL1C4mjGHTtQF%2FhRsBBtUHfcGL0CNVwdGFMTRKj5OsAaex3wfqGTyl8gZ3yMZ3pWHT09upQ8aMymNrlLhYhZNGh6344jbKgSuTxWz2ICbIbPW6fv04fvzdEoEPzoovJO2RozxZhEDGCY0O7OLEkNqLcflDp7pVi2wf3VlmPLVEDFnwMLy1bXZr9kDNHjaskWf88CcTmrMhD3PUgyRWr7K82XAxD7KbQYCmIHWPrqh2tUpU7KUwtNFobF%2FxotC0yF3rHJOEkjYXg2NMxAt2i%2BuCNwQuC8vDNqSnOtqEemigcV%2BS5EvbSJq3wASgw%2BMwI3E4%2BGqWdMjBucyXDOCdLx3dHvUpWfjgAS28SQsLSS1Ibhp3FpUgUelSHlIeeD%2Fury1BdslGa%2F5tx3q95QSGQrmVaiIsNDTuMEc7QhT0%2F0sdRRw3O7tlRj8e54P5EF6Jr%2BnrIjBT3EIsDDDo2vl4XHq6zTCyg2O2ZVGDf0K%2BDoZiDzpwyBm1E5eBuYO2uR9R2NjL91NqgaFVTKAIyOUdFX3x8ou7kmR5%2BlzbnrqYk9tZiILIOGAOgZ7o1oVT4qIHvzVExprTu2ZXRN5kJKv7UdzoUn4k6mdexHYG83G4d810%2BP2GcSek7%2Fu7AWabbdd3B%2FMmqC3tYtvaGMeF6ySSBG9rpBVymR946CS9Jt0rJlOf%2BQ%3D%3D&amp;highlight=false&amp;headerTopBrand=true#polycard_client=search-nordic&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1575797741&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2500939</v>
+      </c>
+      <c r="E12" t="n">
+        <v>4099900</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>39% OFF</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>45809.67502491106</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Portátil Hp 14-em0009la R5 Ram 16gb 512gb Ssd</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=Ui85GGnE61myuhHJSIj0W1rPFgRVo6zApHFyKPftQVLNje9pXasbLvsWHLlFW4MhTRm9ZVeNOrB%2BngajZe8OrVI%2B4nE0K755kqb%2FPICRTgQQEeui%2Bb4erSxuD2POwCn3AK3hEr8UWhN1sDL0bZVt3MHfDnIuEec5gqyaVVoILB185p2wzrsbuOqLXNnou%2FqXgegJBYuVpWHMCXM0%2Fmg1PuPIXlQpqw8Xcppha0utEmiCoygIzCgI51Q%2F3LcsU3Ke9%2BdgGo6cMQ7ACngoSaKyT6l1mvp9EtTdOgAno9qK738ZPQZdqyck1rzjCe6M8v0ViWqCcCkhXpeHhw6ho1tdX3EQU%2B4WDS2OR2gXBKcsK3S3LNiZATtjJxNq2PUOCYaqC9SG1DStQvFywgjF3mM5dLviPgGkFxg9BWvFd9Aa0T47iQZ0hL3L58W0ZzZvjQrHhO93f22Pa4QqGAlTf5BDjt5HY1TCUZclgyI9ARL7IwRLQ5EB4K%2B4J6JGRi%2BWO8jL8U00tNAUDKg%2FmoSvXhNTbdxhaiYyD0mnbxF4wPe5%2BURIe21utXPEWRO69wxZjtT4YWLb0XPYhA7X17bVJq83OmwciLx2fcUb6R%2FvvxVGY0eafDscgnAOnr1ACE08qK0jz5Y4JeSnOh%2Fypcc0Y%2BKB3ENzXJTzKcthsQxXozKrDfDlJIEMVhJzKyi9YpVJ6o8XtAVaF4G5UldPvlRAoUSihWWZaLyHQyICEtWwcaC3h0HuXHOBx0WI%2FFP1EzmtqhecdHo%2Fo1Mel7XBq77HH1ohe37Ti7LTX5Bd2sARF6avfVwT0KF6RDZ%2Fk6U5H9PExFYXGEHR0LBIuGYLgja7vux3NZBgrdEetEylgbMKRvINLvr3azROENAA9eOKRGaOZQuZZEW7rT2CI%2FmkP88zDBvjBNNokaY26yoO0Ox5oAqw8cfh7C8Q&amp;highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO2503419712&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1770900</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2248125</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>21% OFF</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>45809.67502491979</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Notebook 15,6 Hp 250 G9 Intel Celeron 8 Gb Ram 256 Gb Ssd Color Negro</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/notebook-156-hp-250-g9-intel-celeron-8-gb-ram-256-gb-ssd-color-negro/p/MCO24443216?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO24443216&amp;position=21&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1479324193&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>902003</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1094000</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>17% OFF</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>45809.67502492775</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Notebook Hp 245 G10 R3 7330u 512gb Ssd 8gb Ram Windows 11 Ho</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/notebook-hp-245-g10-r3-7330u-512gb-ssd-8gb-ram-windows-11-ho/p/MCO39243137?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO39243137&amp;backend_model=search-backend&amp;position=26&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1547113843&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1259900</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1621375</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>22% OFF</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>45809.67502493539</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Portatil Hp 12ava Gen Intel I3 1215u Ssd 512gb Ram 8gb Color Plateado</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-hp-12ava-gen-intel-i3-1215u-ssd-512gb-ram-8gb-color-plateado/p/MCO29272690?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO29272690&amp;backend_model=search-backend&amp;position=4&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1507088307&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1458900</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1853000</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>21% OFF</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>45809.67502494298</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Portátil 2 en 1 HP Pavilion x360 14-ek1011la Intel Core i5 8 GB RAM 512 GB SSD Windows 11 Home 14" Pantalla táctil FHD</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=2isFgknxOdut9wXlQP0iITpWbs1sARTKTrjHXi%2FMHoczuv2WAdftWVdjPOA74d0RTmEsftMgUsX%2FMM9WXr3j6V%2BAGQ5AG0mIUS5JeEpPBgOTLLj9j8smzhuqpQBQjNLyVlDeYKF07dG00UJvY8tW03dkej5aTdZXNrfk3PmFZbK%2BqlohQF5UEMj%2FIOyKa%2FvLqYa6hoU6ep2lvqBBSycW%2BfOxLR%2Flue%2BMYWuzgRUO3h5oDGDSl7nsWFzlfHPZwOEL%2Brb5r1rvmQo9Owa6Q%2BZ%2FAwSwNAKAcrHhGUR5p7i3Tu35wg5iYCN95AbBBaYXr4nWFHJd9aREV%2B8eyeMpRLOmgihamWbGJfx9kbCvA3ihk8O%2ByWg7SFx5vzw5iA4j5C5uIyyJakoIXATauCzp3YpvOU4Lv%2FzfmwebiBWkcGO%2FpSNO5xV%2FsS4uUp2TekeO7nEfl6FF6Q8xYisLj8K5%2FLruUauzWaCcd6r0EOLnWcMT1VYHzWFp%2FDPpRD%2FM%2BwCTJyD0HLyRaq9o3rX%2BT2OqetnPt4fohuMeVwsb9neAnKOmZ%2B1%2BHU0aIUt%2FA3CPxA64TMmcBTWBUCXloFCybUI9ecZgtWWls40ZEJ6gGaTQSxtaMWf3ZXupuSMAtSGBF3B56W4g5CrbJQHCo1mXQudc%2B6HoSihb1jHSNpKQ05CmNdJZXA2lMG6KyWls2mkEatxNrm100RTtxcZjwjQL%2BRdsR3eo7RuAfrRnkuOwo5ghO%2F9lIq8TVPTszdCJZ6%2B9roXQXQKSqZlExdB2iI1X2ktZkJsAJu96%2BJtFu5U1DSZ%2FHj%2F660BTG0AFaY2iO75lVXam8o6kRrsJgYQlXUz7egDl%2By12SqXEPGquC1RhDls2Vkx9PXBL60XshaTSv8NAPFP6odNk%2BHBUZPdkZ%2FHXBR4dI%2FfemcTtW0L7djFRtZhGfkgQXlOBoyDkaWGqw%2FnF4Vea1ip7RDKPokO%2BIRd752yYsaCXTln0D6jU3vNsoG%2BMiz76COhTZvFRVzbQeb13%2B0BXls2OHFOjgIFgoi4GDdSGTQ%3D%3D&amp;highlight=false&amp;headerTopBrand=true#polycard_client=search-nordic&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO2859705258&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2519937</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3999900</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>37% OFF</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>45809.67502495056</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Portátil HP 15-fc0031la AMD Ryzen 7 16 GB RAM 1 TB SSD 15.6" FHD Windows 11 Home</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=JpCyesSU7FvVnsZ5%2BL%2BzJrom0whIfM9UkilyAkynRPaHNJZmxB99RszVeXnjGIOckALEtIxHh1slZJmJJZoKnNuK5T3uMKFO2fcm3m64QAFDQ9FAFbaB6WT8kFxDzwsYdlwgcNGfhxb700tBs7NQYUX5EX81d6toSPxUzBuoudpAdd73klj7wdkOxsXIBiBduaoOFVwrFMjPui3aDRtdTlfPVgxuMdb6QizMiJWoQL5yg%2BF9SNhtPC7JQuvdGonOsHYJZCrdn%2FacVfMU0rKQQiSAO940mnjoCVoI5e%2BgGu3qnPiZL4TiiZmLWhu8BfionVN263LyNNKcLXtyfzs3rLR8Q25zjk7fIx%2B%2BDOwEEhVyz93nQpLfRyv7o65GvS4mBp5QHYMrX%2BOeDGHZXJO7dC%2Fr68BhGLKnGCvPybClst%2Brq%2BAKwgzeaFF%2Bw5qB4P0zbnzRDg3UTy0tWaJ0psAyyfnH6zS6rOQaigRFvHc%2BaJwaj3z0IONiFeRWi%2BN%2BG1GeecLJQ5Ijf0q2cU7UnVDWH2vZGmkP7WeSIlphoeTggF6D8Bqt%2F44rx2Kn8KGZAx1YM%2Buu4SD34aS%2FsomMNGRnEqUgkB4cnXNAKLAjATKp%2BwGGf8DWBGRxElZ%2FPkzlI7gfKDJyeKG%2BPw8yuMnt%2FvtZ3D0DwkEhj6xZUBksUANEVmwfzk6jxBCHoCfCcxnHLsLd%2FZ%2BqDlRr8LDIQAwUHkmPOgELwi7y0ZGkEKStk0h0MYd0jnjbrev63gap47u4m5c%2FoeDhPyjZ5Iu3%2Fb6myKcEYq8cCOwlmNTwofIUOS8s1aBVwZSXmlKHI4gLMQbGT0tFb5%2FH11Z2ejFEq6FOp9Pgy9REGbBO%2BFIqmpf%2FqYQShEUhzLWeI02lc8Aei%2FVkPhA23v4Qk5kEpNvwwZT9JKOlrY1XBykOUEeSbZUfWluYetUgLeg%2FnpxvJ9omITuzni4YJONdH5MNBlRoeQqVG2vZzo1iTuarHA%3D%3D&amp;highlight=true&amp;headerTopBrand=true#polycard_client=search-nordic&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1575771851&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>4099900</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>45809.67502495806</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>LENOVO</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Portatil Lenovo V14 Core I5-13420h 24gb 512gb Ssd Color Negro</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-lenovo-v14-core-i5-13420h-24gb-512gb-ssd-color-negro/p/MCO44279796?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO44279796&amp;position=13&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1587144125&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1900230</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2176667</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>12% OFF</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H19" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>45809.67502496565</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ASUS</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Portátil Asus Fa506nc Ryzen 5 7535hs Rtx3050 16gb 512gb 15.6 Color Negro</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-asus-fa506nc-ryzen-5-7535hs-rtx3050-16gb-512gb-156-color-negro/p/MCO45003983?highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO45003983&amp;position=9&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1544070727&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2975814</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3199800</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>7% OFF</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>45809.67502497309</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Potátil Portátil 14-dq0533la 14 8gb De Ram - 256gb Ssd - Intel Celeron</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/potatil-portatil-14-dq0533la-14-8gb-de-ram-256gb-ssd-intel-celeron/p/MCO43485439?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO43485439&amp;backend_model=search-backend&amp;position=27&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1547113619&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>919900</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1185375</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>22% OFF</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>45809.67502498048</v>
       </c>
     </row>
   </sheetData>

--- a/productos_mercadolibre.xlsx
+++ b/productos_mercadolibre.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="almacenamiento" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monitores" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="laptos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tablet" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1013,15 +1014,11 @@
       <c r="I2" t="b">
         <v>0</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
+      <c r="J2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K2" t="n">
+        <v>54</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -1029,7 +1026,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>45809.67502480594</v>
+        <v>45809.67502480324</v>
       </c>
     </row>
     <row r="3">
@@ -1070,15 +1067,11 @@
       <c r="I3" t="b">
         <v>0</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>4.6</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="J3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K3" t="n">
+        <v>21</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -1086,7 +1079,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>45809.67502483061</v>
+        <v>45809.67502482639</v>
       </c>
     </row>
     <row r="4">
@@ -1127,15 +1120,11 @@
       <c r="I4" t="b">
         <v>0</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>4.9</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="J4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K4" t="n">
+        <v>14</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -1143,7 +1132,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>45809.67502484108</v>
+        <v>45809.67502483796</v>
       </c>
     </row>
     <row r="5">
@@ -1184,14 +1173,1157 @@
       <c r="I5" t="b">
         <v>0</v>
       </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>45809.67502484954</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Msi Cyborg 14 A13vf I7 16gb 512gb Ssd Rtx 4060 8gb Color Negro</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/msi-cyborg-14-a13vf-i7-16gb-512gb-ssd-rtx-4060-8gb-color-negro/p/MCO45076522?highlight=false&amp;headerTopBrand=true#polycard_client=search-nordic&amp;searchVariation=MCO45076522&amp;position=10&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1547623157&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4653900</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6999000</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>33% OFF</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>45809.67502486111</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Potátil Portátil 14-dq0533la 14 8gb De Ram - 256gb Ssd - Intel Celeron</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=72GdK%2BpbrTFTM7i1sgjMu%2BbDsZwimgIVsgEMaqQVM80u2lSxiPxIp49lAD5FzvvX7tw%2B3WjmLZh4n%2BWEsTFcMPGWatgq50tuIi838LaR5oQJV5CEEvHbnKXPQACchyTHH0vjIO1%2Fj5c%2FXsO3bZMNq840pE4vh0ds%2Bd%2FwnVC79v072kXMRCGv3qHwC7U14OLGxP1MhOY85quB4Dd%2BoCzJ%2BVTsoBR7e70znoJTiR9qZUrKLyP%2BGL151fg2q%2FjTPcpe0EOWnfesuWGnIbRJ4UtBsHEOeSTUxpPqZKHMg8VjCEq4SmLvT%2BPRSReQB8aIUXznqFgDkSM1AE8omkj%2Fb%2FzxOs6KhMnCGKwZieGHEq6Q1rlE7c5VoFZGbp%2BOdt4PoLgaaqkzDbXOMhYOjXfdXrGgIzF6REZoUczzadV4ktrUlWshAxhwNxeakqcHnzwOFSCVPS4WrphjKzsUv3e3FIITEW1ZLpH%2BijyDAUSqj5BtIwnqZLC0aEfBTEKF086b3De50nkyz%2F1VJd4r2IhpVNLFE3P9mFqfBECnPRa1w%2Bj5TFMNuAMTPGDAZf%2Bp3f9QJMQ%2FrkuqXUtGmXqBcvaJSVoEKarvtyQY9iM9eRVEJGSve0Zvgw66yjF5rAZJXpCXH%2F0SuJqfrP1GZxnDkpeEMHfVYia4j959bA8TrP7ccIlaC37VeVRdDu%2F0329FzL07pGhmr0ABaZML9QGaZrqN7NpZPtdHai42qP5%2BxTxoA%2FgYEARxTAs3Y6XqVCueecJgOI7oc3f14YbulsBtatYNP%2Br%2FoKaJyI184MA5kvfmfDdC2Bfg12W8N6szceKHTo%2FthMXp4IoCP5VQNEK2vH5W%2FqMiPyumd%2FHlHpTXOTabOSyRlb%2BoYDSe4IzEy9SXmvrjE3GZPQi6T7ncDaOr3nL2yy%2BCUGFcYS4jRoUHT7Dr6RSMXBuSjuKMlIz5m2KgbW11LobjxwwP6xE%3D&amp;highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1547113619&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>919900</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1185375</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>22% OFF</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K7" t="n">
+        <v>14</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>45809.67502486111</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Portátil Hp 15-fd0026la Intel Core I3 8gb Ram 512gb Ssd</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=QHVRSkMapUYFd0MUsUJK5vva3fHEv%2FyYutnoyKQ309KPVo9qt3PSZ7ic6AU77nHcQz1SOsZVpaNDaqoo3MEy5TX%2Fx6omSlMudceAjcJe7TmVnVv6qgMEKiHF92%2FNwkqZ%2Fj%2FdQYtnH1YCcqK25LLkuC7M8zRZxibPMDqHhDa41LfQzT8c%2Fc2j3NZeddotr4mnhO%2FeiAgvZxsOVd0hkyHjXT6CpYL%2F7XgQFZsNyy%2Fomo3zxEpuqOyS3EuDTHF6K%2FM3k0hGvJK%2BS883r2s0w8NeHtjKUOh9ZDqR7cQneLG4ZVt4OwK51xKgfhII%2BzeCagUquSMbAp76%2FsgtCerLRz9BCuEE0PglxAd%2BjIr3MUL0%2Bgj5YJiP1EmHtBPGfqAY2mHskvzbW06do8Pjn%2BdFMX%2Fea8iyWi3OGOvq0O928uulkF5odhWAmKQcPvs5ZdHf3%2BnV0jb8WXXihcMGhQrADvxvEQH51JoKXOjYkgESygc010gYtqqzT3MiJs9RF%2FWpQr5CgHALRbn32vWyekuFqEFHmObrxqP%2B2mk25JoOhUWUdDpR9saNu0vKbpY8PWF1vyCe3mHfg9nILLA%2FWvCLLxP9da%2FPPyFYxZy%2FxjxaedElM9ABbpyy%2BtCcF7zXQlMoSWf7tTHpbaIhaW6sl4zv%2BsZiLd10R065djXFACsM7VKfZakLbHc0MwB%2FGgyi2RPCmVYd%2Fm5lu4XsHOCpLOCE3ApQF4LXLw6LVwxxpVpuLZb2E5zJRyJ0G9gt5xhE%2Bt1AFun%2BZBBd0X3oyTreYtHLOngjGLwPgPc1GdxghV%2B9wgeQ0zs0dm55nlM6w6DhGNJiRM6uQrAERZrHAAowzsKOY2ELq0Tz0lILYMyZxit0AxnKuccqHqrKCkl7iXonFO5zniizKB87r%2F%2B7DyxH%2B%2FtmdJ%2FoSMSeOcbPA%2BRGQ0Hgxz91UJBNRCeoO0ZHBzk0j4oq&amp;highlight=false&amp;headerTopBrand=true#polycard_client=search-nordic&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO2878894100&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2499900</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>45809.67502487268</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ASUS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Portátil Asus X1605za-mb644 Intel Corei5-12500h 16gb Ram Disco Solido 512ssd 16 Fhd Endless</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-asus-x1605za-mb644-intel-corei5-12500h-16gb-ram-disco-solido-512ssd-16-fhd-endless/p/MCO32161065?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO32161065&amp;position=3&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1523840021&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2029900</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K9" t="n">
+        <v>145</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>45809.67502488426</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ASUS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Portatil Asus E1504fa-nj474 Ryzen 5-7520u Ram 16gb Ssd 512gb Color Negro</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-asus-e1504fa-nj474-ryzen-5-7520u-ram-16gb-ssd-512gb-color-negro/p/MCO23498360?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO23498360&amp;position=14&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1541876389&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1725640</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1988778</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>13% OFF</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K10" t="n">
+        <v>413</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>45809.67502488426</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MacBook Air 13.6 M2 256 GB SSD 16 GB Ram Z160000au C/ Nota</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/macbook-air-136-m2-256-gb-ssd-16-gb-ram-z160000au-c-nota/p/MCO26602331?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO26602331&amp;position=8&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO2813970572&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4299299</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5057999</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>15% OFF</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K11" t="n">
+        <v>131</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>45809.67502489583</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Portátil HP 15-fd0065la Intel Core i5 16 GB 1 TB SSD 15.6" FHD Windows 11 Home</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=DGWR%2F%2Fegp7TdyCwhdw99a44O2oQgggn7VIYlmeQwtLg8VC08255MGlgaOJG9lbdJKyvhyvI7V5q1aLrsqe%2F4FmXlVusxQNzjHGFm5g0X44I9Dsb6kLzzhEiV4yyhD5iaunlUQefJHzTinDxyR0JqlbymbdlaJx4YYa%2FCdP4FSZgW409zFcLfSsXtpptnSgdJFrIwp86aGz9Uu%2Bd0iXBWcFs6tNefITwdYXIRpyNP1owqQcRMO1yu3x9MLyRXPUjvhwX5W%2ByYCjVFRzjY44o32cMJ1gFNlR5T7n%2BmX84DfqkNTgQkajcL1C4mjGHTtQF%2FhRsBBtUHfcGL0CNVwdGFMTRKj5OsAaex3wfqGTyl8gZ3yMZ3pWHT09upQ8aMymNrlLhYhZNGh6344jbKgSuTxWz2ICbIbPW6fv04fvzdEoEPzoovJO2RozxZhEDGCY0O7OLEkNqLcflDp7pVi2wf3VlmPLVEDFnwMLy1bXZr9kDNHjaskWf88CcTmrMhD3PUgyRWr7K82XAxD7KbQYCmIHWPrqh2tUpU7KUwtNFobF%2FxotC0yF3rHJOEkjYXg2NMxAt2i%2BuCNwQuC8vDNqSnOtqEemigcV%2BS5EvbSJq3wASgw%2BMwI3E4%2BGqWdMjBucyXDOCdLx3dHvUpWfjgAS28SQsLSS1Ibhp3FpUgUelSHlIeeD%2Fury1BdslGa%2F5tx3q95QSGQrmVaiIsNDTuMEc7QhT0%2F0sdRRw3O7tlRj8e54P5EF6Jr%2BnrIjBT3EIsDDDo2vl4XHq6zTCyg2O2ZVGDf0K%2BDoZiDzpwyBm1E5eBuYO2uR9R2NjL91NqgaFVTKAIyOUdFX3x8ou7kmR5%2BlzbnrqYk9tZiILIOGAOgZ7o1oVT4qIHvzVExprTu2ZXRN5kJKv7UdzoUn4k6mdexHYG83G4d810%2BP2GcSek7%2Fu7AWabbdd3B%2FMmqC3tYtvaGMeF6ySSBG9rpBVymR946CS9Jt0rJlOf%2BQ%3D%3D&amp;highlight=false&amp;headerTopBrand=true#polycard_client=search-nordic&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1575797741&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2500939</v>
+      </c>
+      <c r="E12" t="n">
+        <v>4099900</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>39% OFF</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>45809.67502490741</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Portátil Hp 14-em0009la R5 Ram 16gb 512gb Ssd</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=Ui85GGnE61myuhHJSIj0W1rPFgRVo6zApHFyKPftQVLNje9pXasbLvsWHLlFW4MhTRm9ZVeNOrB%2BngajZe8OrVI%2B4nE0K755kqb%2FPICRTgQQEeui%2Bb4erSxuD2POwCn3AK3hEr8UWhN1sDL0bZVt3MHfDnIuEec5gqyaVVoILB185p2wzrsbuOqLXNnou%2FqXgegJBYuVpWHMCXM0%2Fmg1PuPIXlQpqw8Xcppha0utEmiCoygIzCgI51Q%2F3LcsU3Ke9%2BdgGo6cMQ7ACngoSaKyT6l1mvp9EtTdOgAno9qK738ZPQZdqyck1rzjCe6M8v0ViWqCcCkhXpeHhw6ho1tdX3EQU%2B4WDS2OR2gXBKcsK3S3LNiZATtjJxNq2PUOCYaqC9SG1DStQvFywgjF3mM5dLviPgGkFxg9BWvFd9Aa0T47iQZ0hL3L58W0ZzZvjQrHhO93f22Pa4QqGAlTf5BDjt5HY1TCUZclgyI9ARL7IwRLQ5EB4K%2B4J6JGRi%2BWO8jL8U00tNAUDKg%2FmoSvXhNTbdxhaiYyD0mnbxF4wPe5%2BURIe21utXPEWRO69wxZjtT4YWLb0XPYhA7X17bVJq83OmwciLx2fcUb6R%2FvvxVGY0eafDscgnAOnr1ACE08qK0jz5Y4JeSnOh%2Fypcc0Y%2BKB3ENzXJTzKcthsQxXozKrDfDlJIEMVhJzKyi9YpVJ6o8XtAVaF4G5UldPvlRAoUSihWWZaLyHQyICEtWwcaC3h0HuXHOBx0WI%2FFP1EzmtqhecdHo%2Fo1Mel7XBq77HH1ohe37Ti7LTX5Bd2sARF6avfVwT0KF6RDZ%2Fk6U5H9PExFYXGEHR0LBIuGYLgja7vux3NZBgrdEetEylgbMKRvINLvr3azROENAA9eOKRGaOZQuZZEW7rT2CI%2FmkP88zDBvjBNNokaY26yoO0Ox5oAqw8cfh7C8Q&amp;highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO2503419712&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1770900</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2248125</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>21% OFF</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>45809.67502491898</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Notebook 15,6 Hp 250 G9 Intel Celeron 8 Gb Ram 256 Gb Ssd Color Negro</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/notebook-156-hp-250-g9-intel-celeron-8-gb-ram-256-gb-ssd-color-negro/p/MCO24443216?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO24443216&amp;position=21&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1479324193&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>902003</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1094000</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>17% OFF</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>22</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>45809.67502493056</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Notebook Hp 245 G10 R3 7330u 512gb Ssd 8gb Ram Windows 11 Ho</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/notebook-hp-245-g10-r3-7330u-512gb-ssd-8gb-ram-windows-11-ho/p/MCO39243137?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO39243137&amp;backend_model=search-backend&amp;position=26&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1547113843&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1259900</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1621375</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>22% OFF</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K15" t="n">
+        <v>21</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>45809.67502493056</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Portatil Hp 12ava Gen Intel I3 1215u Ssd 512gb Ram 8gb Color Plateado</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-hp-12ava-gen-intel-i3-1215u-ssd-512gb-ram-8gb-color-plateado/p/MCO29272690?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO29272690&amp;backend_model=search-backend&amp;position=4&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1507088307&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1458900</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1853000</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>21% OFF</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K16" t="n">
+        <v>54</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>45809.67502494213</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Portátil 2 en 1 HP Pavilion x360 14-ek1011la Intel Core i5 8 GB RAM 512 GB SSD Windows 11 Home 14" Pantalla táctil FHD</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=2isFgknxOdut9wXlQP0iITpWbs1sARTKTrjHXi%2FMHoczuv2WAdftWVdjPOA74d0RTmEsftMgUsX%2FMM9WXr3j6V%2BAGQ5AG0mIUS5JeEpPBgOTLLj9j8smzhuqpQBQjNLyVlDeYKF07dG00UJvY8tW03dkej5aTdZXNrfk3PmFZbK%2BqlohQF5UEMj%2FIOyKa%2FvLqYa6hoU6ep2lvqBBSycW%2BfOxLR%2Flue%2BMYWuzgRUO3h5oDGDSl7nsWFzlfHPZwOEL%2Brb5r1rvmQo9Owa6Q%2BZ%2FAwSwNAKAcrHhGUR5p7i3Tu35wg5iYCN95AbBBaYXr4nWFHJd9aREV%2B8eyeMpRLOmgihamWbGJfx9kbCvA3ihk8O%2ByWg7SFx5vzw5iA4j5C5uIyyJakoIXATauCzp3YpvOU4Lv%2FzfmwebiBWkcGO%2FpSNO5xV%2FsS4uUp2TekeO7nEfl6FF6Q8xYisLj8K5%2FLruUauzWaCcd6r0EOLnWcMT1VYHzWFp%2FDPpRD%2FM%2BwCTJyD0HLyRaq9o3rX%2BT2OqetnPt4fohuMeVwsb9neAnKOmZ%2B1%2BHU0aIUt%2FA3CPxA64TMmcBTWBUCXloFCybUI9ecZgtWWls40ZEJ6gGaTQSxtaMWf3ZXupuSMAtSGBF3B56W4g5CrbJQHCo1mXQudc%2B6HoSihb1jHSNpKQ05CmNdJZXA2lMG6KyWls2mkEatxNrm100RTtxcZjwjQL%2BRdsR3eo7RuAfrRnkuOwo5ghO%2F9lIq8TVPTszdCJZ6%2B9roXQXQKSqZlExdB2iI1X2ktZkJsAJu96%2BJtFu5U1DSZ%2FHj%2F660BTG0AFaY2iO75lVXam8o6kRrsJgYQlXUz7egDl%2By12SqXEPGquC1RhDls2Vkx9PXBL60XshaTSv8NAPFP6odNk%2BHBUZPdkZ%2FHXBR4dI%2FfemcTtW0L7djFRtZhGfkgQXlOBoyDkaWGqw%2FnF4Vea1ip7RDKPokO%2BIRd752yYsaCXTln0D6jU3vNsoG%2BMiz76COhTZvFRVzbQeb13%2B0BXls2OHFOjgIFgoi4GDdSGTQ%3D%3D&amp;highlight=false&amp;headerTopBrand=true#polycard_client=search-nordic&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO2859705258&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2519937</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3999900</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>37% OFF</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>45809.67502495371</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Portátil HP 15-fc0031la AMD Ryzen 7 16 GB RAM 1 TB SSD 15.6" FHD Windows 11 Home</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=JpCyesSU7FvVnsZ5%2BL%2BzJrom0whIfM9UkilyAkynRPaHNJZmxB99RszVeXnjGIOckALEtIxHh1slZJmJJZoKnNuK5T3uMKFO2fcm3m64QAFDQ9FAFbaB6WT8kFxDzwsYdlwgcNGfhxb700tBs7NQYUX5EX81d6toSPxUzBuoudpAdd73klj7wdkOxsXIBiBduaoOFVwrFMjPui3aDRtdTlfPVgxuMdb6QizMiJWoQL5yg%2BF9SNhtPC7JQuvdGonOsHYJZCrdn%2FacVfMU0rKQQiSAO940mnjoCVoI5e%2BgGu3qnPiZL4TiiZmLWhu8BfionVN263LyNNKcLXtyfzs3rLR8Q25zjk7fIx%2B%2BDOwEEhVyz93nQpLfRyv7o65GvS4mBp5QHYMrX%2BOeDGHZXJO7dC%2Fr68BhGLKnGCvPybClst%2Brq%2BAKwgzeaFF%2Bw5qB4P0zbnzRDg3UTy0tWaJ0psAyyfnH6zS6rOQaigRFvHc%2BaJwaj3z0IONiFeRWi%2BN%2BG1GeecLJQ5Ijf0q2cU7UnVDWH2vZGmkP7WeSIlphoeTggF6D8Bqt%2F44rx2Kn8KGZAx1YM%2Buu4SD34aS%2FsomMNGRnEqUgkB4cnXNAKLAjATKp%2BwGGf8DWBGRxElZ%2FPkzlI7gfKDJyeKG%2BPw8yuMnt%2FvtZ3D0DwkEhj6xZUBksUANEVmwfzk6jxBCHoCfCcxnHLsLd%2FZ%2BqDlRr8LDIQAwUHkmPOgELwi7y0ZGkEKStk0h0MYd0jnjbrev63gap47u4m5c%2FoeDhPyjZ5Iu3%2Fb6myKcEYq8cCOwlmNTwofIUOS8s1aBVwZSXmlKHI4gLMQbGT0tFb5%2FH11Z2ejFEq6FOp9Pgy9REGbBO%2BFIqmpf%2FqYQShEUhzLWeI02lc8Aei%2FVkPhA23v4Qk5kEpNvwwZT9JKOlrY1XBykOUEeSbZUfWluYetUgLeg%2FnpxvJ9omITuzni4YJONdH5MNBlRoeQqVG2vZzo1iTuarHA%3D%3D&amp;highlight=true&amp;headerTopBrand=true#polycard_client=search-nordic&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1575771851&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>4099900</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>45809.67502495371</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>LENOVO</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Portatil Lenovo V14 Core I5-13420h 24gb 512gb Ssd Color Negro</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-lenovo-v14-core-i5-13420h-24gb-512gb-ssd-color-negro/p/MCO44279796?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO44279796&amp;position=13&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1587144125&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1900230</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2176667</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>12% OFF</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H19" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K19" t="n">
+        <v>44</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>45809.67502496528</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ASUS</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Portátil Asus Fa506nc Ryzen 5 7535hs Rtx3050 16gb 512gb 15.6 Color Negro</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-asus-fa506nc-ryzen-5-7535hs-rtx3050-16gb-512gb-156-color-negro/p/MCO45003983?highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO45003983&amp;position=9&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1544070727&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2975814</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3199800</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>7% OFF</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>45809.67502497685</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Potátil Portátil 14-dq0533la 14 8gb De Ram - 256gb Ssd - Intel Celeron</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/potatil-portatil-14-dq0533la-14-8gb-de-ram-256gb-ssd-intel-celeron/p/MCO43485439?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO43485439&amp;backend_model=search-backend&amp;position=27&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1547113619&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>919900</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1185375</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>22% OFF</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K21" t="n">
+        <v>14</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>45809.67502497685</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>titulo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>precio</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>precio_anterior</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>descuento</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>envio</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>envio_gratis</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>envio_full</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>rating</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>total_reviews</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>imagen</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>opiniones</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>fecha_actualizacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tablet Android 13 De Última Generación 2024, 128gb+16gb-512g</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=mR3PrLDqSgo6MJmSPfl2dS%2FUo8svLhnfFxnazibKtZXVeLtMP0UoQHj%2BbJpGXNSxlKHqG%2Bz%2BKAOSidbxiQcoTK05NuWlcRvCDD5MjCWB3K4C9HUUZVchWsk7LOwfTerUMIos6E4Bod3tRdbnksNVMvzKRkReGltvzXuQA4OP80tSQ%2FFqfqQAMdprKdOVzOSme4KXR9XX56enzlA9K1TQLedO%2B0F9kFSvph1R7uxsW5MW7jWiRf%2BPoby49x%2BpCOruqv5yj%2B9tHUbJnalH8OJ5XR3voCMNA9kHU8L6y1wqrGWztACnPsDE%2BCasBbrRWN9gchREW0qU9OKv%2BuGLww5%2BSJ36uhWt0xDcy0AGd7wuISgsmjonuu0iuwBYDFDKW3MFXZOYmeDhKdRKt%2Fpi%2Ft%2FK0UIHY9uP3uXwZxAXo07uP69yYoBt%2Belx5HDMuV4quOj1y1sN3ViWFAQW58MtSCxLmVKe%2BrlI0PO8iTBOvOAEmXLqZja66efrwirv2M6UN7GRAiq%2FuJIaJbFGP1RbRHVc9WHBnKgU116FRxUlaU4fqBmxlMHQm5zQUnSaeWuQx5mT9CIGbFbRPMnYbfB7kUYAu4rD5kM6aEZWf3Ni2UVNvIWwwJDfUpaM5BzlLBqz5BBZdXBryopAeHgbuPH0pOiaroIVG4%2FWtkVM71Oo0KPyntc4XJ7fdS29V9Lzr72Sy9fsrUoBNz%2F0wy043vszx3X33tO%2BdhSCxi2xTwVxlfRG%2BulrO5fI6zhEysUKUMoOSBp6FW7L2xHBV6T3rEGW%2FEVfTvOkcfq3enYpcYEgD7xICHEiR3bGSjNrfXW1rRTtjOZEkDD6eHD1V3cNKSMMGgQ1hZU3OCnKXIH9%2F42zw5gQcxTgMfKqjOF2qDFeD%2BffmpGaDFBpLlp9Ol48TnLxRDKW60kFs5OzwPl2j3mh98s4WXRRJUts4%2FaSqxXaZGA869tYGdY%3D&amp;highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=de599f53-e149-4e6e-87ca-312bb77ee567&amp;wid=MCO2840069126&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>907200</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1120000</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>19% OFF</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_942311-MLA82998654053_032025-V.webp</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>45809.67834955709</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HUAWEI</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Tablet Para Niños Huawei Matepad SE 11 Kids Edition Gris 4+128gb + Lápiz</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=47Z74mPwkVy%2F%2BMV8XPeMyih7b4R7yH9gPlALeIw9jt4Itbq4%2BLZgoHGJIOjfh5tnGkwaBBmynXnKO5SQKoDtICbWMU6ADAP9p%2B06BcnngTuLz9t8Sts1JZX%2FEqbMeXKZMumNuLpFVk3z%2B2hga%2BO7ef4VXEAesOLY6d6iof5oFV2n2qV%2Fyjm6P5v%2BCSN76VU8R3p3pncS%2FaaCgwm7Eyt1NIa8lgQKC2iQ9C%2Bls05ZmjXHM0W3FWzNvSLwBwfx31JlMjR%2BQxsCXp1yT1b4A%2F1hJm8W5LCxD4G5Bqmx0IoWP0AF4o4%2FnHu3OY%2F6Feol0Lc4IT%2FWpZOi%2Brefoj7m7hMQD5R9BblTUpbWYlhnfHVZtz8ue5GbWbawmrDAznawKmRKsCBKPB0Sr3AUa0aZLXIZI8wAqblP7OV4%2BC3SqSBPLE9N848u9d1y2l0Re2%2B6PdX4NTx02zi0rHikFGGCBI0o4BZBZQERax2m1rCMmnChGVx3yr1LD%2FPIDy%2FWxeIcVG1AKq6GngTy1JYr%2BReR2sCDsHb7WAmn%2BqKHvCwAJYl6%2F3o5rY%2F2EYQ%2FCl61NKwtsqSjSMlAOpcEuEpSxCc7HuX1GWddDk39LGmfkcgXZ4sRJWzgVBceBkNouFvp2DrcmRzazdJyCH%2FjXY9srSMpdGHteCD6Ebqy%2FVXOanbn4rjy5aTL570xthAX2b0N9ZCSrJgE1vMcurWvuCYOrpL8gFASiNzAI26PD2UrvCJdJeE%2FqtdSdvaXhrmtsuPu0NVgu5W0gm5sEcfYFyPlB65xBVCDfelKwFW2H6xt533wWKDoWxfhq7ugSU4WOQm1WGxGROqz%2FihShH5P1WuEUxEeYigqmPEd6BC2F90Vw20e7K2MZEM9dFJDO1v0YrQeox8mc4v2yqCUeE%2B1xQ6aZx3aA%2Fds0%2B%2BNjH5HZKvYf8rnbiWieZ58VEC3wwD24m4y62PpliSga4%2Fay5oi0F4%3D&amp;highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=de599f53-e149-4e6e-87ca-312bb77ee567&amp;wid=MCO2836671066&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>678932</v>
+      </c>
+      <c r="E3" t="n">
+        <v>999900</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>32% OFF</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '14 may. 2025', 'contenido': 'Realmente pensado para los pequeños.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>45809.67834958383</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Tablet Xiaomi Redmi Pad Se 8gb 256gb Gris</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/tablet-xiaomi-redmi-pad-se-8gb-256gb-gris/p/MCO29219683?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO29219683&amp;position=4&amp;search_layout=stack&amp;type=product&amp;tracking_id=de599f53-e149-4e6e-87ca-312bb77ee567&amp;wid=MCO1567332181&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>709900</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1149900</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>38% OFF</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '26 jul. 2024', 'contenido': 'La tablet es demasiado rápida, corre juegos con facilidad y su pantalla es muy buena. Le verdad me sorprendió lo bueno que corre los juegos y las aplicaciones.', 'votos_utiles': '13'}, {'calificacion': 5, 'fecha': '08 jun. 2024', 'contenido': 'Excelente compra. Una tablet de calidad,buena construcción e increíble apariencia. Definitivamente otro gran producto de xiaomi.', 'votos_utiles': '8'}, {'calificacion': 5, 'fecha': '29 ene. 2025', 'contenido': 'Súper me gustó mucho , apenas para lo que necesito 😊.', 'votos_utiles': '6'}, {'calificacion': 5, 'fecha': '30 dic. 2024', 'contenido': 'Genial.', 'votos_utiles': '3'}, {'calificacion': 5, 'fecha': '17 feb. 2025', 'contenido': '', 'votos_utiles': '3'}]</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>45809.67834959479</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LENOVO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Tablet Lenovo Tab K11 4g Lte 8gb 128gb Teclado + Pen Color Luna Grey</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/tablet-lenovo-tab-k11-4g-lte-8gb-128gb-teclado-pen-color-luna-grey/p/MCO45442884?highlight=true&amp;headerTopBrand=true#polycard_client=search-nordic&amp;searchVariation=MCO45442884&amp;position=5&amp;search_layout=stack&amp;type=product&amp;tracking_id=de599f53-e149-4e6e-87ca-312bb77ee567&amp;wid=MCO1529700467&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1094900</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1899900</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>42% OFF</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1199,37 +2331,42 @@
           <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
         </is>
       </c>
-      <c r="M5" s="2" t="n">
-        <v>45809.67502484915</v>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '15 may. 2025', 'contenido': 'Exelente producto calidad precio. Lo recomiendo totalmente.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '08 may. 2025', 'contenido': 'Bonita y económica.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '30 abr. 2025', 'contenido': 'Muy buena y muy práctica.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '03 mar. 2025', 'contenido': 'Es muy buena.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '10 feb. 2025', 'contenido': 'Excelente!.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>45809.67834960301</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>LENOVO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Tablet Lenovo M11 128gb 8gb Ram + Lapiz 10.9 Pulgadas Color Negro</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/tablet-lenovo-m11-128gb-8gb-ram-lapiz-109-pulgadas-color-negro/p/MCO36109372?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO36109372&amp;position=8&amp;search_layout=stack&amp;type=product&amp;tracking_id=de599f53-e149-4e6e-87ca-312bb77ee567&amp;wid=MCO1501072863&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>874900</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Msi Cyborg 14 A13vf I7 16gb 512gb Ssd Rtx 4060 8gb Color Negro</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.mercadolibre.com.co/msi-cyborg-14-a13vf-i7-16gb-512gb-ssd-rtx-4060-8gb-color-negro/p/MCO45076522?highlight=false&amp;headerTopBrand=true#polycard_client=search-nordic&amp;searchVariation=MCO45076522&amp;position=10&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1547623157&amp;sid=search</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>4653900</v>
-      </c>
-      <c r="E6" t="n">
-        <v>6999000</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>33% OFF</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Envío gratis</t>
@@ -1248,7 +2385,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>167</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1256,863 +2393,13 @@
           <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
         </is>
       </c>
-      <c r="M6" s="2" t="n">
-        <v>45809.67502485745</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Potátil Portátil 14-dq0533la 14 8gb De Ram - 256gb Ssd - Intel Celeron</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=72GdK%2BpbrTFTM7i1sgjMu%2BbDsZwimgIVsgEMaqQVM80u2lSxiPxIp49lAD5FzvvX7tw%2B3WjmLZh4n%2BWEsTFcMPGWatgq50tuIi838LaR5oQJV5CEEvHbnKXPQACchyTHH0vjIO1%2Fj5c%2FXsO3bZMNq840pE4vh0ds%2Bd%2FwnVC79v072kXMRCGv3qHwC7U14OLGxP1MhOY85quB4Dd%2BoCzJ%2BVTsoBR7e70znoJTiR9qZUrKLyP%2BGL151fg2q%2FjTPcpe0EOWnfesuWGnIbRJ4UtBsHEOeSTUxpPqZKHMg8VjCEq4SmLvT%2BPRSReQB8aIUXznqFgDkSM1AE8omkj%2Fb%2FzxOs6KhMnCGKwZieGHEq6Q1rlE7c5VoFZGbp%2BOdt4PoLgaaqkzDbXOMhYOjXfdXrGgIzF6REZoUczzadV4ktrUlWshAxhwNxeakqcHnzwOFSCVPS4WrphjKzsUv3e3FIITEW1ZLpH%2BijyDAUSqj5BtIwnqZLC0aEfBTEKF086b3De50nkyz%2F1VJd4r2IhpVNLFE3P9mFqfBECnPRa1w%2Bj5TFMNuAMTPGDAZf%2Bp3f9QJMQ%2FrkuqXUtGmXqBcvaJSVoEKarvtyQY9iM9eRVEJGSve0Zvgw66yjF5rAZJXpCXH%2F0SuJqfrP1GZxnDkpeEMHfVYia4j959bA8TrP7ccIlaC37VeVRdDu%2F0329FzL07pGhmr0ABaZML9QGaZrqN7NpZPtdHai42qP5%2BxTxoA%2FgYEARxTAs3Y6XqVCueecJgOI7oc3f14YbulsBtatYNP%2Br%2FoKaJyI184MA5kvfmfDdC2Bfg12W8N6szceKHTo%2FthMXp4IoCP5VQNEK2vH5W%2FqMiPyumd%2FHlHpTXOTabOSyRlb%2BoYDSe4IzEy9SXmvrjE3GZPQi6T7ncDaOr3nL2yy%2BCUGFcYS4jRoUHT7Dr6RSMXBuSjuKMlIz5m2KgbW11LobjxwwP6xE%3D&amp;highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1547113619&amp;sid=search</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>919900</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1185375</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>22% OFF</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>4.9</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>45809.67502486529</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Portátil Hp 15-fd0026la Intel Core I3 8gb Ram 512gb Ssd</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=QHVRSkMapUYFd0MUsUJK5vva3fHEv%2FyYutnoyKQ309KPVo9qt3PSZ7ic6AU77nHcQz1SOsZVpaNDaqoo3MEy5TX%2Fx6omSlMudceAjcJe7TmVnVv6qgMEKiHF92%2FNwkqZ%2Fj%2FdQYtnH1YCcqK25LLkuC7M8zRZxibPMDqHhDa41LfQzT8c%2Fc2j3NZeddotr4mnhO%2FeiAgvZxsOVd0hkyHjXT6CpYL%2F7XgQFZsNyy%2Fomo3zxEpuqOyS3EuDTHF6K%2FM3k0hGvJK%2BS883r2s0w8NeHtjKUOh9ZDqR7cQneLG4ZVt4OwK51xKgfhII%2BzeCagUquSMbAp76%2FsgtCerLRz9BCuEE0PglxAd%2BjIr3MUL0%2Bgj5YJiP1EmHtBPGfqAY2mHskvzbW06do8Pjn%2BdFMX%2Fea8iyWi3OGOvq0O928uulkF5odhWAmKQcPvs5ZdHf3%2BnV0jb8WXXihcMGhQrADvxvEQH51JoKXOjYkgESygc010gYtqqzT3MiJs9RF%2FWpQr5CgHALRbn32vWyekuFqEFHmObrxqP%2B2mk25JoOhUWUdDpR9saNu0vKbpY8PWF1vyCe3mHfg9nILLA%2FWvCLLxP9da%2FPPyFYxZy%2FxjxaedElM9ABbpyy%2BtCcF7zXQlMoSWf7tTHpbaIhaW6sl4zv%2BsZiLd10R065djXFACsM7VKfZakLbHc0MwB%2FGgyi2RPCmVYd%2Fm5lu4XsHOCpLOCE3ApQF4LXLw6LVwxxpVpuLZb2E5zJRyJ0G9gt5xhE%2Bt1AFun%2BZBBd0X3oyTreYtHLOngjGLwPgPc1GdxghV%2B9wgeQ0zs0dm55nlM6w6DhGNJiRM6uQrAERZrHAAowzsKOY2ELq0Tz0lILYMyZxit0AxnKuccqHqrKCkl7iXonFO5zniizKB87r%2F%2B7DyxH%2B%2FtmdJ%2FoSMSeOcbPA%2BRGQ0Hgxz91UJBNRCeoO0ZHBzk0j4oq&amp;highlight=false&amp;headerTopBrand=true#polycard_client=search-nordic&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO2878894100&amp;sid=search</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>2499900</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H8" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>45809.67502487299</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ASUS</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Portátil Asus X1605za-mb644 Intel Corei5-12500h 16gb Ram Disco Solido 512ssd 16 Fhd Endless</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://www.mercadolibre.com.co/portatil-asus-x1605za-mb644-intel-corei5-12500h-16gb-ram-disco-solido-512ssd-16-fhd-endless/p/MCO32161065?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO32161065&amp;position=3&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1523840021&amp;sid=search</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>2029900</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H9" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>4.9</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>45809.67502488061</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ASUS</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Portatil Asus E1504fa-nj474 Ryzen 5-7520u Ram 16gb Ssd 512gb Color Negro</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://www.mercadolibre.com.co/portatil-asus-e1504fa-nj474-ryzen-5-7520u-ram-16gb-ssd-512gb-color-negro/p/MCO23498360?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO23498360&amp;position=14&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1541876389&amp;sid=search</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>1725640</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1988778</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>13% OFF</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>413</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>45809.67502488814</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>APPLE</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>MacBook Air 13.6 M2 256 GB SSD 16 GB Ram Z160000au C/ Nota</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>https://www.mercadolibre.com.co/macbook-air-136-m2-256-gb-ssd-16-gb-ram-z160000au-c-nota/p/MCO26602331?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO26602331&amp;position=8&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO2813970572&amp;sid=search</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>4299299</v>
-      </c>
-      <c r="E11" t="n">
-        <v>5057999</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>15% OFF</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>4.9</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>45809.67502489956</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Portátil HP 15-fd0065la Intel Core i5 16 GB 1 TB SSD 15.6" FHD Windows 11 Home</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=DGWR%2F%2Fegp7TdyCwhdw99a44O2oQgggn7VIYlmeQwtLg8VC08255MGlgaOJG9lbdJKyvhyvI7V5q1aLrsqe%2F4FmXlVusxQNzjHGFm5g0X44I9Dsb6kLzzhEiV4yyhD5iaunlUQefJHzTinDxyR0JqlbymbdlaJx4YYa%2FCdP4FSZgW409zFcLfSsXtpptnSgdJFrIwp86aGz9Uu%2Bd0iXBWcFs6tNefITwdYXIRpyNP1owqQcRMO1yu3x9MLyRXPUjvhwX5W%2ByYCjVFRzjY44o32cMJ1gFNlR5T7n%2BmX84DfqkNTgQkajcL1C4mjGHTtQF%2FhRsBBtUHfcGL0CNVwdGFMTRKj5OsAaex3wfqGTyl8gZ3yMZ3pWHT09upQ8aMymNrlLhYhZNGh6344jbKgSuTxWz2ICbIbPW6fv04fvzdEoEPzoovJO2RozxZhEDGCY0O7OLEkNqLcflDp7pVi2wf3VlmPLVEDFnwMLy1bXZr9kDNHjaskWf88CcTmrMhD3PUgyRWr7K82XAxD7KbQYCmIHWPrqh2tUpU7KUwtNFobF%2FxotC0yF3rHJOEkjYXg2NMxAt2i%2BuCNwQuC8vDNqSnOtqEemigcV%2BS5EvbSJq3wASgw%2BMwI3E4%2BGqWdMjBucyXDOCdLx3dHvUpWfjgAS28SQsLSS1Ibhp3FpUgUelSHlIeeD%2Fury1BdslGa%2F5tx3q95QSGQrmVaiIsNDTuMEc7QhT0%2F0sdRRw3O7tlRj8e54P5EF6Jr%2BnrIjBT3EIsDDDo2vl4XHq6zTCyg2O2ZVGDf0K%2BDoZiDzpwyBm1E5eBuYO2uR9R2NjL91NqgaFVTKAIyOUdFX3x8ou7kmR5%2BlzbnrqYk9tZiILIOGAOgZ7o1oVT4qIHvzVExprTu2ZXRN5kJKv7UdzoUn4k6mdexHYG83G4d810%2BP2GcSek7%2Fu7AWabbdd3B%2FMmqC3tYtvaGMeF6ySSBG9rpBVymR946CS9Jt0rJlOf%2BQ%3D%3D&amp;highlight=false&amp;headerTopBrand=true#polycard_client=search-nordic&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1575797741&amp;sid=search</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>2500939</v>
-      </c>
-      <c r="E12" t="n">
-        <v>4099900</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>39% OFF</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H12" t="b">
-        <v>1</v>
-      </c>
-      <c r="I12" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>45809.67502491106</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Portátil Hp 14-em0009la R5 Ram 16gb 512gb Ssd</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=Ui85GGnE61myuhHJSIj0W1rPFgRVo6zApHFyKPftQVLNje9pXasbLvsWHLlFW4MhTRm9ZVeNOrB%2BngajZe8OrVI%2B4nE0K755kqb%2FPICRTgQQEeui%2Bb4erSxuD2POwCn3AK3hEr8UWhN1sDL0bZVt3MHfDnIuEec5gqyaVVoILB185p2wzrsbuOqLXNnou%2FqXgegJBYuVpWHMCXM0%2Fmg1PuPIXlQpqw8Xcppha0utEmiCoygIzCgI51Q%2F3LcsU3Ke9%2BdgGo6cMQ7ACngoSaKyT6l1mvp9EtTdOgAno9qK738ZPQZdqyck1rzjCe6M8v0ViWqCcCkhXpeHhw6ho1tdX3EQU%2B4WDS2OR2gXBKcsK3S3LNiZATtjJxNq2PUOCYaqC9SG1DStQvFywgjF3mM5dLviPgGkFxg9BWvFd9Aa0T47iQZ0hL3L58W0ZzZvjQrHhO93f22Pa4QqGAlTf5BDjt5HY1TCUZclgyI9ARL7IwRLQ5EB4K%2B4J6JGRi%2BWO8jL8U00tNAUDKg%2FmoSvXhNTbdxhaiYyD0mnbxF4wPe5%2BURIe21utXPEWRO69wxZjtT4YWLb0XPYhA7X17bVJq83OmwciLx2fcUb6R%2FvvxVGY0eafDscgnAOnr1ACE08qK0jz5Y4JeSnOh%2Fypcc0Y%2BKB3ENzXJTzKcthsQxXozKrDfDlJIEMVhJzKyi9YpVJ6o8XtAVaF4G5UldPvlRAoUSihWWZaLyHQyICEtWwcaC3h0HuXHOBx0WI%2FFP1EzmtqhecdHo%2Fo1Mel7XBq77HH1ohe37Ti7LTX5Bd2sARF6avfVwT0KF6RDZ%2Fk6U5H9PExFYXGEHR0LBIuGYLgja7vux3NZBgrdEetEylgbMKRvINLvr3azROENAA9eOKRGaOZQuZZEW7rT2CI%2FmkP88zDBvjBNNokaY26yoO0Ox5oAqw8cfh7C8Q&amp;highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO2503419712&amp;sid=search</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>1770900</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2248125</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>21% OFF</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H13" t="b">
-        <v>1</v>
-      </c>
-      <c r="I13" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>45809.67502491979</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Notebook 15,6 Hp 250 G9 Intel Celeron 8 Gb Ram 256 Gb Ssd Color Negro</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>https://www.mercadolibre.com.co/notebook-156-hp-250-g9-intel-celeron-8-gb-ram-256-gb-ssd-color-negro/p/MCO24443216?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO24443216&amp;position=21&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1479324193&amp;sid=search</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>902003</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1094000</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>17% OFF</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H14" t="b">
-        <v>1</v>
-      </c>
-      <c r="I14" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>4.6</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>45809.67502492775</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Notebook Hp 245 G10 R3 7330u 512gb Ssd 8gb Ram Windows 11 Ho</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>https://www.mercadolibre.com.co/notebook-hp-245-g10-r3-7330u-512gb-ssd-8gb-ram-windows-11-ho/p/MCO39243137?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO39243137&amp;backend_model=search-backend&amp;position=26&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1547113843&amp;sid=search</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>1259900</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1621375</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>22% OFF</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I15" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>4.6</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>45809.67502493539</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Portatil Hp 12ava Gen Intel I3 1215u Ssd 512gb Ram 8gb Color Plateado</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>https://www.mercadolibre.com.co/portatil-hp-12ava-gen-intel-i3-1215u-ssd-512gb-ram-8gb-color-plateado/p/MCO29272690?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO29272690&amp;backend_model=search-backend&amp;position=4&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1507088307&amp;sid=search</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>1458900</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1853000</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>21% OFF</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I16" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>45809.67502494298</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Portátil 2 en 1 HP Pavilion x360 14-ek1011la Intel Core i5 8 GB RAM 512 GB SSD Windows 11 Home 14" Pantalla táctil FHD</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=2isFgknxOdut9wXlQP0iITpWbs1sARTKTrjHXi%2FMHoczuv2WAdftWVdjPOA74d0RTmEsftMgUsX%2FMM9WXr3j6V%2BAGQ5AG0mIUS5JeEpPBgOTLLj9j8smzhuqpQBQjNLyVlDeYKF07dG00UJvY8tW03dkej5aTdZXNrfk3PmFZbK%2BqlohQF5UEMj%2FIOyKa%2FvLqYa6hoU6ep2lvqBBSycW%2BfOxLR%2Flue%2BMYWuzgRUO3h5oDGDSl7nsWFzlfHPZwOEL%2Brb5r1rvmQo9Owa6Q%2BZ%2FAwSwNAKAcrHhGUR5p7i3Tu35wg5iYCN95AbBBaYXr4nWFHJd9aREV%2B8eyeMpRLOmgihamWbGJfx9kbCvA3ihk8O%2ByWg7SFx5vzw5iA4j5C5uIyyJakoIXATauCzp3YpvOU4Lv%2FzfmwebiBWkcGO%2FpSNO5xV%2FsS4uUp2TekeO7nEfl6FF6Q8xYisLj8K5%2FLruUauzWaCcd6r0EOLnWcMT1VYHzWFp%2FDPpRD%2FM%2BwCTJyD0HLyRaq9o3rX%2BT2OqetnPt4fohuMeVwsb9neAnKOmZ%2B1%2BHU0aIUt%2FA3CPxA64TMmcBTWBUCXloFCybUI9ecZgtWWls40ZEJ6gGaTQSxtaMWf3ZXupuSMAtSGBF3B56W4g5CrbJQHCo1mXQudc%2B6HoSihb1jHSNpKQ05CmNdJZXA2lMG6KyWls2mkEatxNrm100RTtxcZjwjQL%2BRdsR3eo7RuAfrRnkuOwo5ghO%2F9lIq8TVPTszdCJZ6%2B9roXQXQKSqZlExdB2iI1X2ktZkJsAJu96%2BJtFu5U1DSZ%2FHj%2F660BTG0AFaY2iO75lVXam8o6kRrsJgYQlXUz7egDl%2By12SqXEPGquC1RhDls2Vkx9PXBL60XshaTSv8NAPFP6odNk%2BHBUZPdkZ%2FHXBR4dI%2FfemcTtW0L7djFRtZhGfkgQXlOBoyDkaWGqw%2FnF4Vea1ip7RDKPokO%2BIRd752yYsaCXTln0D6jU3vNsoG%2BMiz76COhTZvFRVzbQeb13%2B0BXls2OHFOjgIFgoi4GDdSGTQ%3D%3D&amp;highlight=false&amp;headerTopBrand=true#polycard_client=search-nordic&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO2859705258&amp;sid=search</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>2519937</v>
-      </c>
-      <c r="E17" t="n">
-        <v>3999900</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>37% OFF</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H17" t="b">
-        <v>1</v>
-      </c>
-      <c r="I17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="n">
-        <v>45809.67502495056</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Portátil HP 15-fc0031la AMD Ryzen 7 16 GB RAM 1 TB SSD 15.6" FHD Windows 11 Home</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=JpCyesSU7FvVnsZ5%2BL%2BzJrom0whIfM9UkilyAkynRPaHNJZmxB99RszVeXnjGIOckALEtIxHh1slZJmJJZoKnNuK5T3uMKFO2fcm3m64QAFDQ9FAFbaB6WT8kFxDzwsYdlwgcNGfhxb700tBs7NQYUX5EX81d6toSPxUzBuoudpAdd73klj7wdkOxsXIBiBduaoOFVwrFMjPui3aDRtdTlfPVgxuMdb6QizMiJWoQL5yg%2BF9SNhtPC7JQuvdGonOsHYJZCrdn%2FacVfMU0rKQQiSAO940mnjoCVoI5e%2BgGu3qnPiZL4TiiZmLWhu8BfionVN263LyNNKcLXtyfzs3rLR8Q25zjk7fIx%2B%2BDOwEEhVyz93nQpLfRyv7o65GvS4mBp5QHYMrX%2BOeDGHZXJO7dC%2Fr68BhGLKnGCvPybClst%2Brq%2BAKwgzeaFF%2Bw5qB4P0zbnzRDg3UTy0tWaJ0psAyyfnH6zS6rOQaigRFvHc%2BaJwaj3z0IONiFeRWi%2BN%2BG1GeecLJQ5Ijf0q2cU7UnVDWH2vZGmkP7WeSIlphoeTggF6D8Bqt%2F44rx2Kn8KGZAx1YM%2Buu4SD34aS%2FsomMNGRnEqUgkB4cnXNAKLAjATKp%2BwGGf8DWBGRxElZ%2FPkzlI7gfKDJyeKG%2BPw8yuMnt%2FvtZ3D0DwkEhj6xZUBksUANEVmwfzk6jxBCHoCfCcxnHLsLd%2FZ%2BqDlRr8LDIQAwUHkmPOgELwi7y0ZGkEKStk0h0MYd0jnjbrev63gap47u4m5c%2FoeDhPyjZ5Iu3%2Fb6myKcEYq8cCOwlmNTwofIUOS8s1aBVwZSXmlKHI4gLMQbGT0tFb5%2FH11Z2ejFEq6FOp9Pgy9REGbBO%2BFIqmpf%2FqYQShEUhzLWeI02lc8Aei%2FVkPhA23v4Qk5kEpNvwwZT9JKOlrY1XBykOUEeSbZUfWluYetUgLeg%2FnpxvJ9omITuzni4YJONdH5MNBlRoeQqVG2vZzo1iTuarHA%3D%3D&amp;highlight=true&amp;headerTopBrand=true#polycard_client=search-nordic&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1575771851&amp;sid=search</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>4099900</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H18" t="b">
-        <v>1</v>
-      </c>
-      <c r="I18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>45809.67502495806</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>LENOVO</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Portatil Lenovo V14 Core I5-13420h 24gb 512gb Ssd Color Negro</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>https://www.mercadolibre.com.co/portatil-lenovo-v14-core-i5-13420h-24gb-512gb-ssd-color-negro/p/MCO44279796?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO44279796&amp;position=13&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1587144125&amp;sid=search</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>1900230</v>
-      </c>
-      <c r="E19" t="n">
-        <v>2176667</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>12% OFF</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I19" t="b">
-        <v>0</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="n">
-        <v>45809.67502496565</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>ASUS</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Portátil Asus Fa506nc Ryzen 5 7535hs Rtx3050 16gb 512gb 15.6 Color Negro</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>https://www.mercadolibre.com.co/portatil-asus-fa506nc-ryzen-5-7535hs-rtx3050-16gb-512gb-156-color-negro/p/MCO45003983?highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO45003983&amp;position=9&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1544070727&amp;sid=search</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>2975814</v>
-      </c>
-      <c r="E20" t="n">
-        <v>3199800</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>7% OFF</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H20" t="b">
-        <v>1</v>
-      </c>
-      <c r="I20" t="b">
-        <v>0</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="n">
-        <v>45809.67502497309</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Potátil Portátil 14-dq0533la 14 8gb De Ram - 256gb Ssd - Intel Celeron</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>https://www.mercadolibre.com.co/potatil-portatil-14-dq0533la-14-8gb-de-ram-256gb-ssd-intel-celeron/p/MCO43485439?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO43485439&amp;backend_model=search-backend&amp;position=27&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1547113619&amp;sid=search</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>919900</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1185375</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>22% OFF</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H21" t="b">
-        <v>1</v>
-      </c>
-      <c r="I21" t="b">
-        <v>0</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>4.9</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="n">
-        <v>45809.67502498048</v>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '10 jun. 2024', 'contenido': 'Me parece muy bien por el precio pero se descarga muy rapido.', 'votos_utiles': '12'}, {'calificacion': 5, 'fecha': '03 sep. 2024', 'contenido': 'Increíble, muy buen precio, excelente calidad. Es rápida la pantalla es muy buena, buena carga, en uso continuo puede durar todo el día.', 'votos_utiles': '9'}, {'calificacion': 5, 'fecha': '26 nov. 2024', 'contenido': 'Vale totalmente la pena por su precio.', 'votos_utiles': '7'}, {'calificacion': 5, 'fecha': '09 may. 2025', 'contenido': 'Un producto, que respecto a la calidad precio, está muy bien.\nPuntos a favor:.\n1. Lapiz para trabajar, cumple perfectamente con la función, con una duracion de su bateria, aceptable, alrededor de una semana con trabajo constante.\n2. Tiene un buen sonido, claro, y con buenos decibeles, no es premium, claro está.\n3. Viene con un buen forro o cubierta, que ayuda a mantenerla seguro, y con mayor comodidad.\n4. Respecto a su software, está bien logrado, fluye con practicamente todo, obviamente no está hecha para jugar aplicativos mayormente exigente, pero para trabajos cotidianos, está excellent. Viene con un aplicativo didactico, para tomar apuntes, y hacer calculos, entre otras opciones.\nPuntos debiles:.\n1. La pantalla, puede mejorar un poco mas, no tiene la mayor iluminación, no es ultra hd, ni nada parecido.\n2. Las camaras no son para realizar videos, imagenes, o videollamadas respectivamente, tienen muy poca resolución, simplemente cumplen.\n3. La bateria si es su punto mas debil, dura muy poco, con trabajo constante, y hay que tener en cuenta, que su carga es lenta, se puede demorar 3 horas en cargar approx.\n4. Llevo alrededor de 6 meses utilizandola, y me ha presentado un par de fallas respecto al sonido, he tenido la obligación de reiniciarle, y se ha solucionado.\nBuen producto, para el que busque algo correcto a buen precio.', 'votos_utiles': '4'}, {'calificacion': 5, 'fecha': '02 dic. 2024', 'contenido': 'Excelente producto en relación precio/calidad. Ha cumplido en las tareas en que la he usado como edición de video y toma de apuntes. El lápiz funciona bastante bien.', 'votos_utiles': '3'}]</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>45809.67834961102</v>
       </c>
     </row>
   </sheetData>

--- a/productos_mercadolibre.xlsx
+++ b/productos_mercadolibre.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monitores" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="laptos" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tablet" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="teclados" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2093,11 +2094,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>Tablet Android 13 De Última Generación 2024, 128gb+16gb-512g</t>
@@ -2130,15 +2127,9 @@
       <c r="I2" t="b">
         <v>0</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>0</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -2151,7 +2142,7 @@
         </is>
       </c>
       <c r="N2" s="2" t="n">
-        <v>45809.67834955709</v>
+        <v>45809.67834956018</v>
       </c>
     </row>
     <row r="3">
@@ -2192,28 +2183,415 @@
       <c r="I3" t="b">
         <v>0</v>
       </c>
+      <c r="J3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '14 may. 2025', 'contenido': 'Realmente pensado para los pequeños.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>45809.67834958334</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Tablet Xiaomi Redmi Pad Se 8gb 256gb Gris</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/tablet-xiaomi-redmi-pad-se-8gb-256gb-gris/p/MCO29219683?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO29219683&amp;position=4&amp;search_layout=stack&amp;type=product&amp;tracking_id=de599f53-e149-4e6e-87ca-312bb77ee567&amp;wid=MCO1567332181&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>709900</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1149900</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>38% OFF</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>298</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '26 jul. 2024', 'contenido': 'La tablet es demasiado rápida, corre juegos con facilidad y su pantalla es muy buena. Le verdad me sorprendió lo bueno que corre los juegos y las aplicaciones.', 'votos_utiles': '13'}, {'calificacion': 5, 'fecha': '08 jun. 2024', 'contenido': 'Excelente compra. Una tablet de calidad,buena construcción e increíble apariencia. Definitivamente otro gran producto de xiaomi.', 'votos_utiles': '8'}, {'calificacion': 5, 'fecha': '29 ene. 2025', 'contenido': 'Súper me gustó mucho , apenas para lo que necesito 😊.', 'votos_utiles': '6'}, {'calificacion': 5, 'fecha': '30 dic. 2024', 'contenido': 'Genial.', 'votos_utiles': '3'}, {'calificacion': 5, 'fecha': '17 feb. 2025', 'contenido': '', 'votos_utiles': '3'}]</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>45809.67834959491</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LENOVO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Tablet Lenovo Tab K11 4g Lte 8gb 128gb Teclado + Pen Color Luna Grey</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/tablet-lenovo-tab-k11-4g-lte-8gb-128gb-teclado-pen-color-luna-grey/p/MCO45442884?highlight=true&amp;headerTopBrand=true#polycard_client=search-nordic&amp;searchVariation=MCO45442884&amp;position=5&amp;search_layout=stack&amp;type=product&amp;tracking_id=de599f53-e149-4e6e-87ca-312bb77ee567&amp;wid=MCO1529700467&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1094900</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1899900</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>42% OFF</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>13</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '15 may. 2025', 'contenido': 'Exelente producto calidad precio. Lo recomiendo totalmente.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '08 may. 2025', 'contenido': 'Bonita y económica.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '30 abr. 2025', 'contenido': 'Muy buena y muy práctica.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '03 mar. 2025', 'contenido': 'Es muy buena.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '10 feb. 2025', 'contenido': 'Excelente!.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>45809.67834960648</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>LENOVO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Tablet Lenovo M11 128gb 8gb Ram + Lapiz 10.9 Pulgadas Color Negro</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/tablet-lenovo-m11-128gb-8gb-ram-lapiz-109-pulgadas-color-negro/p/MCO36109372?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO36109372&amp;position=8&amp;search_layout=stack&amp;type=product&amp;tracking_id=de599f53-e149-4e6e-87ca-312bb77ee567&amp;wid=MCO1501072863&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>874900</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K6" t="n">
+        <v>167</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '10 jun. 2024', 'contenido': 'Me parece muy bien por el precio pero se descarga muy rapido.', 'votos_utiles': '12'}, {'calificacion': 5, 'fecha': '03 sep. 2024', 'contenido': 'Increíble, muy buen precio, excelente calidad. Es rápida la pantalla es muy buena, buena carga, en uso continuo puede durar todo el día.', 'votos_utiles': '9'}, {'calificacion': 5, 'fecha': '26 nov. 2024', 'contenido': 'Vale totalmente la pena por su precio.', 'votos_utiles': '7'}, {'calificacion': 5, 'fecha': '09 may. 2025', 'contenido': 'Un producto, que respecto a la calidad precio, está muy bien.\nPuntos a favor:.\n1. Lapiz para trabajar, cumple perfectamente con la función, con una duracion de su bateria, aceptable, alrededor de una semana con trabajo constante.\n2. Tiene un buen sonido, claro, y con buenos decibeles, no es premium, claro está.\n3. Viene con un buen forro o cubierta, que ayuda a mantenerla seguro, y con mayor comodidad.\n4. Respecto a su software, está bien logrado, fluye con practicamente todo, obviamente no está hecha para jugar aplicativos mayormente exigente, pero para trabajos cotidianos, está excellent. Viene con un aplicativo didactico, para tomar apuntes, y hacer calculos, entre otras opciones.\nPuntos debiles:.\n1. La pantalla, puede mejorar un poco mas, no tiene la mayor iluminación, no es ultra hd, ni nada parecido.\n2. Las camaras no son para realizar videos, imagenes, o videollamadas respectivamente, tienen muy poca resolución, simplemente cumplen.\n3. La bateria si es su punto mas debil, dura muy poco, con trabajo constante, y hay que tener en cuenta, que su carga es lenta, se puede demorar 3 horas en cargar approx.\n4. Llevo alrededor de 6 meses utilizandola, y me ha presentado un par de fallas respecto al sonido, he tenido la obligación de reiniciarle, y se ha solucionado.\nBuen producto, para el que busque algo correcto a buen precio.', 'votos_utiles': '4'}, {'calificacion': 5, 'fecha': '02 dic. 2024', 'contenido': 'Excelente producto en relación precio/calidad. Ha cumplido en las tareas en que la he usado como edición de video y toma de apuntes. El lápiz funciona bastante bien.', 'votos_utiles': '3'}]</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>45809.67834960648</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>titulo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>precio</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>precio_anterior</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>descuento</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>envio</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>envio_gratis</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>envio_full</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>rating</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>total_reviews</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>imagen</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>imagenes</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>opiniones</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>fecha_actualizacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Teclado Mecánico Inalámbrico Newmen Gm610 60% Rgb 61 Teclas</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=6gGtzBLavbK6QT%2FHNpbmv4xJiCt5aKMxBqNom0ChA44NtPEmuvAI%2Bd%2F6wZ5bJEEzHJr5DnaUPSSbXsA27RKEa9B2aGtGEO0TsJfkfy%2BAxjueSxf%2Bb63DYr8jbEaPbuHXO%2B5hpSgqQj9g65y8837ovhh%2FLr824TMjzjtbqPPd1LhEsdCYo22TnDqIeTtfDnpv%2FtmlNqz637XVhPscnSGmouUrSXmqrjeiCPDnf9KVlls8EDsrjF6s%2FERJT5%2BzF0fY%2BttMYUcQwgDnN1mOlZZlKQBr4sMtGrWiG8OFpv3c5EpaylXa%2FBdBvq0jhw70H0oSxSxvb5cuBpONRrhOyv4yPwuTc66azMz98G5fX8C7KZF7EeV99fWGhMOdqwMYvMam8gmrw2AZbdNRtAywmoN06LhUPPXLSsM5kUKroJuLUM3VAkVh5zRqQl%2FQIyXSGPcU5D0nva18v1VGvdIwqwfh0Ibf9JkqBEaIGeZn%2B40QC5od%2Bjf0ozYJOAVdaA8WvEwj%2BOWRrMKdheFNCYVp7FSXsnuyEEYCYT8c%2BbHZ9DLdBMTVctfuHGmPhsO06wVqqTA5Y9fxJHdJBiSPDU5UmhG7ISvZHMV8sxffBRRUzlfKORPzCa8A6pK5AQQRfjBoRFsl6wSRBx8J4hW%2BkAQSay2F6gt1pVQXmsmhXspXlNdWknhJY2OhJ9MCfhbJ91LuskxMN00efWb6svoHLy7UXfl6CJqma5A6SUsiBa%2BKC%2FErjG6jRQrzTjmECxwEUl9YdmtjbYMdwwtDSGKR6Q5JunQwTqCRCplf%2FAWojZHys7g2isSZ2GvCIsWBEAbpoUVJcToj87qK1lwTBs6zEde6g8iRNugxlwcuSepuSFkKENccA3ZAs4Y3wZOlkfOr2xC%2BxxbvOb00Ed6IwFkjIrpK0lfUyePM9tiooSvD8Imm2h7b8Ayff8r0mq9HUCBj%2FrCUw2tA&amp;highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=d5bd1a16-2a63-481d-ab07-d7b9f14f3457&amp;wid=MCO2573729598&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>144415</v>
+      </c>
+      <c r="E2" t="n">
+        <v>169900</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>15% OFF</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_940676-MLU77417106611_072024-V.webp</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_940676-MLU77417106611_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_987647-MLA82113006950_022025-F.jpg', 'https://http2.mlstatic.com/D_NQ_NP_2X_756226-MLU78420919739_082024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_708773-MLA84456438700_052025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '13 sep. 2024', 'contenido': 'Es un producto hermoso, recomiendo instalar el firmware desde la pagina oficial según como indica el manual, arregla un conflicto con varias teclas. También recomiendo poner el idioma del teclado en el pc como ingles us para que no hayan problemas. Siguiendo los pasos que les acabo de mencionar el producto es maravilloso. Lo mejor que se puede conseguir calidad precio. Pdta toca acostumbrarse a dar un comando para usar las flechas y no tiene la tecla ñ.', 'votos_utiles': '8'}, {'calificacion': 5, 'fecha': '09 oct. 2024', 'contenido': 'Extremadamente bueno, una compra que uno no se arrepiente lo recomiendo.', 'votos_utiles': '3'}, {'calificacion': 5, 'fecha': '09 dic. 2024', 'contenido': 'Me gustó, las orientaciones de los usuarios sirvieron mucho … fácil de instalar , dejarlo en opción inglés y para la tilde o ñ se coloca en español … las luces del teclado súper , recomendado !!!.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '31 may. 2025', 'contenido': 'El teclado muy bueno para su precio. La verdad no estaba esperando mucho sino que funcionara bien y fuera cómodo al tacto. A la final ha superado mis expectativas. Muchas gracias.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '27 may. 2025', 'contenido': '', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>45809.68173760112</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Teclado Gamer Mecanico En Español Retroiluminado Con Cable Usb Xtrike Me Gk988 Para Computadora Pc Con Luz</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=f%2F2y0a41zS%2FCSk3LHoy1FmCIOd3IXjkIc4zrxquwe11mnEs31DNrGs4s5WGrbswIcV9mcJMF42%2F%2FNXENqgyu%2FlQzWscGtdgGm5pc%2B4n1Mt2puld%2B2kCs6YlAYLN7ouABMzMjt%2F0MYeuzXcRO5DM9XfBU8IqWp9tAW3BFhiBnyl8%2FEcst8TuhHvi2lI%2BYgB8c9M0z98WMPpnCrYD80Sdi2iGnAb4xjTGp5qvj7foeTG%2FxBA6vSiEBLE7x2UlQ5Ml3lWzVVIV4vKuU%2BhwsQeqCbXkZF352uL4OCafSvy3oYmZxbvVKS4JXJUP3BVDLkKpIWr3Xqhn3LVG6gKoQAPlvIOQsjYpRCm6cg1kks2jGkl8Ww2owqqEFRTdb7EDuWwfZx8mOZeMIAZ4Hg1IxyPhjLXQ%2FdkUJky0iTAWe1OFTOxT1evOPhkW3GPSk721VWfZi84JlxLNJM8j87%2BqEhX5aO7rSB662JU%2BxI9EfURh6WoqdG19xLTWj4WcEVGELrCM7oYoYwyBxEFcuVP9iUiljdTIuHScEneuLOOWeyvSpZ2NoUOEUAikCrQW7X%2FiDWTIZgdyzRusJ%2BIJx3BpsuUWAEbWZoOIQMXAztgzgmtR1AELcUYbBQ7vV9HSAwbZsoj2AJxmLku7N6X1okzof6Fpbdtwe9Hbopr1YSWTf1zWCM6IwMRXXbmsXBZtKQfwi4Pk6KJGj4HXWS02mdU5DGAOgcok5du2bgnYgo8NMgHPAOWvmmlcnd85ssCEg9fKKkcMjGWbETWPSh7xiDsGnSXXwTNNXK8GMp94WkD8bjcDXGq8mL8n1bt717kIG8rEnssoov07dc1xhHx0%2FlVtteyt8LTFvmsiiMpKZzXqV3he5op527UBvZsM2U9QaHewKaBvicFrw%2FTMjgedgArbI43oicXIeLU61Oshp5Tg8FOSkOaz2yD%2FKLgOF86LVMyp%2FsVQ1vs%2FBsIAonsMEK38835kntHbMho%2FMJb2hEARHJajFWEaHs7iZ0y9oh%2Fse2pcNlrw%3D&amp;highlight=true&amp;headerTopBrand=true#polycard_client=search-nordic&amp;tracking_id=d5bd1a16-2a63-481d-ab07-d7b9f14f3457&amp;wid=MCO1560382775&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>104900</v>
+      </c>
+      <c r="E3" t="n">
+        <v>149900</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>30% OFF</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>19</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_973583-MLA83472189647_042025-V.webp</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>[{'calificacion': 5, 'fecha': '14 may. 2025', 'contenido': 'Realmente pensado para los pequeños.', 'votos_utiles': '0'}]</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>45809.67834958383</v>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_973583-MLA83472189647_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_833541-MLA80825743061_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_820938-MLA80563766270_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_760094-MLA80563785792_112024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '01 may. 2025', 'contenido': 'Contento con el producto.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '28 abr. 2025', 'contenido': 'Es una buena opción por el precio, cumple con lo que promete perfectamente, se siente de buena calidad y al responde bien, recomendado.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '31 may. 2025', 'contenido': 'Bastante bien calidad precio:) lo recomiendo!(es algo ruidoso) perfecto para competitivo.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '23 may. 2025', 'contenido': 'Se ve excelente, me gusto mucho.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '22 may. 2025', 'contenido': 'Cumple con todo. Muy buen producto.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>45809.6817376265</v>
       </c>
     </row>
     <row r="4">
@@ -2224,23 +2602,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tablet Xiaomi Redmi Pad Se 8gb 256gb Gris</t>
+          <t>Teclado gamer Redragon Kumara QWERTY Outemu Red español España color negro con luz rainbow</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.mercadolibre.com.co/tablet-xiaomi-redmi-pad-se-8gb-256gb-gris/p/MCO29219683?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO29219683&amp;position=4&amp;search_layout=stack&amp;type=product&amp;tracking_id=de599f53-e149-4e6e-87ca-312bb77ee567&amp;wid=MCO1567332181&amp;sid=search</t>
+          <t>https://www.mercadolibre.com.co/teclado-gamer-redragon-kumara-qwerty-outemu-red-espanol-espana-color-negro-con-luz-rainbow/p/MCO19518470?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO19518470&amp;position=3&amp;search_layout=stack&amp;type=product&amp;tracking_id=d5bd1a16-2a63-481d-ab07-d7b9f14f3457&amp;wid=MCO1347087050&amp;sid=search</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>709900</v>
+        <v>190900</v>
       </c>
       <c r="E4" t="n">
-        <v>1149900</v>
+        <v>199900</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>38% OFF</t>
+          <t>4% OFF</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2261,7 +2639,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -2271,38 +2649,43 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>[{'calificacion': 5, 'fecha': '26 jul. 2024', 'contenido': 'La tablet es demasiado rápida, corre juegos con facilidad y su pantalla es muy buena. Le verdad me sorprendió lo bueno que corre los juegos y las aplicaciones.', 'votos_utiles': '13'}, {'calificacion': 5, 'fecha': '08 jun. 2024', 'contenido': 'Excelente compra. Una tablet de calidad,buena construcción e increíble apariencia. Definitivamente otro gran producto de xiaomi.', 'votos_utiles': '8'}, {'calificacion': 5, 'fecha': '29 ene. 2025', 'contenido': 'Súper me gustó mucho , apenas para lo que necesito 😊.', 'votos_utiles': '6'}, {'calificacion': 5, 'fecha': '30 dic. 2024', 'contenido': 'Genial.', 'votos_utiles': '3'}, {'calificacion': 5, 'fecha': '17 feb. 2025', 'contenido': '', 'votos_utiles': '3'}]</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>45809.67834959479</v>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_636746-MLA52350707355_112022-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_913394-MLA52350707356_112022-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_994079-MLA52350716250_112022-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_912260-MLA52350716251_112022-F.webp']</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '08 may. 2021', 'contenido': 'Panas yo lo veo bien xd, tal vez sería mejor si las luces fueran más brillantes pero de resto llevo 1 mes con el y todo gucci, todo bien todo correcto además me regalaron unas teclas de cambio :) uwu.', 'votos_utiles': '56'}, {'calificacion': 5, 'fecha': '14 jun. 2023', 'contenido': 'Me encantó llevo más o menos 1 año con el producto y no ha presentado problemas, se escucha bien y se ve bien 😎.', 'votos_utiles': '35'}, {'calificacion': 5, 'fecha': '17 ago. 2023', 'contenido': 'El producto es bastante bueno en calidad-precio; cositas que no me acabaron de gustar, pero que son de menor importancia para mi son que algunas partes de las teclas (ej. Bloq mayús) que no se iluminan completamente, no tienen switches brown para comprarlos con el teclado, las patitas de goma antideslizantes no son las mejores, el teclado se tambalea un poquito aunque no se si es mi escritorio o el teclado (con el manual en una esquina se arreglo), de resto es un buen teclado, los materiales en acero para la placa y el "plástico reforzado" están decentes, el cable no es mayado, pero tiene el conector usb en oro chapado (creo que así se le dice xd), es hotswap, por si le quieren poner otros switches, la retroiluminación es decente y algo que me parece vital, pero no tiene, es que el conector no es removible, en general lo recomiendo si no hay mucho dinero para gastar y cuando ya se tenga el set-up bien armado cambiar el teclado o dejarlo.', 'votos_utiles': '12'}, {'calificacion': 5, 'fecha': '26 jun. 2021', 'contenido': 'Bastante bueno, la verdad tanto el tacto como el sonido me gustó demasiado, es bastante bonito gracias al color rojo que arroja el teclado por defecto, es algo pesado lo que hace que sea difícil moverlo sin querer lo cuál es genial, es tenkeyless lo que hace que te quede bastante más espacio del que uno cree que le va a quedar y la verdad estoy tratando de hacer la reseña larga porque es bastante cómodo escribir con este teclado.', 'votos_utiles': '10'}, {'calificacion': 5, 'fecha': '07 sep. 2023', 'contenido': 'Lo recomiendo, excelente producto ☺️ buen material.', 'votos_utiles': '7'}]</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>45809.6817376367</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LENOVO</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tablet Lenovo Tab K11 4g Lte 8gb 128gb Teclado + Pen Color Luna Grey</t>
+          <t>Teclado gamer Redragon Kumara QWERTY Outemu Red español latinoamérica color negro con luz RGB</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.mercadolibre.com.co/tablet-lenovo-tab-k11-4g-lte-8gb-128gb-teclado-pen-color-luna-grey/p/MCO45442884?highlight=true&amp;headerTopBrand=true#polycard_client=search-nordic&amp;searchVariation=MCO45442884&amp;position=5&amp;search_layout=stack&amp;type=product&amp;tracking_id=de599f53-e149-4e6e-87ca-312bb77ee567&amp;wid=MCO1529700467&amp;sid=search</t>
+          <t>https://www.mercadolibre.com.co/teclado-gamer-redragon-kumara-qwerty-outemu-red-espanol-latinoamerica-color-negro-con-luz-rgb/p/MCO19472215?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO19472215&amp;position=4&amp;search_layout=stack&amp;type=product&amp;tracking_id=d5bd1a16-2a63-481d-ab07-d7b9f14f3457&amp;wid=MCO1483729915&amp;sid=search</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1094900</v>
+        <v>190900</v>
       </c>
       <c r="E5" t="n">
-        <v>1899900</v>
+        <v>198000</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>42% OFF</t>
+          <t>3% OFF</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2318,12 +2701,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -2333,31 +2716,36 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>[{'calificacion': 5, 'fecha': '15 may. 2025', 'contenido': 'Exelente producto calidad precio. Lo recomiendo totalmente.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '08 may. 2025', 'contenido': 'Bonita y económica.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '30 abr. 2025', 'contenido': 'Muy buena y muy práctica.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '03 mar. 2025', 'contenido': 'Es muy buena.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '10 feb. 2025', 'contenido': 'Excelente!.', 'votos_utiles': '0'}]</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>45809.67834960301</v>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_864807-MLA77594879101_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_625461-MLA75686545678_042024-F.jpg', 'https://http2.mlstatic.com/D_NQ_NP_2X_867951-MLA77594879095_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_750884-MLA77378571910_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_845414-MLA77378789172_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_901847-MLA77378571898_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_804807-MLA77378808744_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_909019-MLA74488153000_022024-F.jpg']</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '08 may. 2021', 'contenido': 'Panas yo lo veo bien xd, tal vez sería mejor si las luces fueran más brillantes pero de resto llevo 1 mes con el y todo gucci, todo bien todo correcto además me regalaron unas teclas de cambio :) uwu.', 'votos_utiles': '56'}, {'calificacion': 5, 'fecha': '14 jun. 2023', 'contenido': 'Me encantó llevo más o menos 1 año con el producto y no ha presentado problemas, se escucha bien y se ve bien 😎.', 'votos_utiles': '35'}, {'calificacion': 5, 'fecha': '17 ago. 2023', 'contenido': 'El producto es bastante bueno en calidad-precio; cositas que no me acabaron de gustar, pero que son de menor importancia para mi son que algunas partes de las teclas (ej. Bloq mayús) que no se iluminan completamente, no tienen switches brown para comprarlos con el teclado, las patitas de goma antideslizantes no son las mejores, el teclado se tambalea un poquito aunque no se si es mi escritorio o el teclado (con el manual en una esquina se arreglo), de resto es un buen teclado, los materiales en acero para la placa y el "plástico reforzado" están decentes, el cable no es mayado, pero tiene el conector usb en oro chapado (creo que así se le dice xd), es hotswap, por si le quieren poner otros switches, la retroiluminación es decente y algo que me parece vital, pero no tiene, es que el conector no es removible, en general lo recomiendo si no hay mucho dinero para gastar y cuando ya se tenga el set-up bien armado cambiar el teclado o dejarlo.', 'votos_utiles': '12'}, {'calificacion': 5, 'fecha': '26 jun. 2021', 'contenido': 'Bastante bueno, la verdad tanto el tacto como el sonido me gustó demasiado, es bastante bonito gracias al color rojo que arroja el teclado por defecto, es algo pesado lo que hace que sea difícil moverlo sin querer lo cuál es genial, es tenkeyless lo que hace que te quede bastante más espacio del que uno cree que le va a quedar y la verdad estoy tratando de hacer la reseña larga porque es bastante cómodo escribir con este teclado.', 'votos_utiles': '10'}, {'calificacion': 5, 'fecha': '07 sep. 2023', 'contenido': 'Lo recomiendo, excelente producto ☺️ buen material.', 'votos_utiles': '7'}]</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>45809.68173764625</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LENOVO</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tablet Lenovo M11 128gb 8gb Ram + Lapiz 10.9 Pulgadas Color Negro</t>
+          <t>Teclado gamer Redragon Mitra QWERTY Outemu Blue español latinoamérica color negro con luz RGB</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.mercadolibre.com.co/tablet-lenovo-m11-128gb-8gb-ram-lapiz-109-pulgadas-color-negro/p/MCO36109372?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO36109372&amp;position=8&amp;search_layout=stack&amp;type=product&amp;tracking_id=de599f53-e149-4e6e-87ca-312bb77ee567&amp;wid=MCO1501072863&amp;sid=search</t>
+          <t>https://www.mercadolibre.com.co/teclado-gamer-redragon-mitra-qwerty-outemu-blue-espanol-latinoamerica-color-negro-con-luz-rgb/p/MCO15079758?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO15079758&amp;position=9&amp;search_layout=stack&amp;type=product&amp;tracking_id=d5bd1a16-2a63-481d-ab07-d7b9f14f3457&amp;wid=MCO1505508309&amp;sid=search</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>874900</v>
+        <v>279900</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -2385,7 +2773,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -2395,11 +2783,351 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>[{'calificacion': 5, 'fecha': '10 jun. 2024', 'contenido': 'Me parece muy bien por el precio pero se descarga muy rapido.', 'votos_utiles': '12'}, {'calificacion': 5, 'fecha': '03 sep. 2024', 'contenido': 'Increíble, muy buen precio, excelente calidad. Es rápida la pantalla es muy buena, buena carga, en uso continuo puede durar todo el día.', 'votos_utiles': '9'}, {'calificacion': 5, 'fecha': '26 nov. 2024', 'contenido': 'Vale totalmente la pena por su precio.', 'votos_utiles': '7'}, {'calificacion': 5, 'fecha': '09 may. 2025', 'contenido': 'Un producto, que respecto a la calidad precio, está muy bien.\nPuntos a favor:.\n1. Lapiz para trabajar, cumple perfectamente con la función, con una duracion de su bateria, aceptable, alrededor de una semana con trabajo constante.\n2. Tiene un buen sonido, claro, y con buenos decibeles, no es premium, claro está.\n3. Viene con un buen forro o cubierta, que ayuda a mantenerla seguro, y con mayor comodidad.\n4. Respecto a su software, está bien logrado, fluye con practicamente todo, obviamente no está hecha para jugar aplicativos mayormente exigente, pero para trabajos cotidianos, está excellent. Viene con un aplicativo didactico, para tomar apuntes, y hacer calculos, entre otras opciones.\nPuntos debiles:.\n1. La pantalla, puede mejorar un poco mas, no tiene la mayor iluminación, no es ultra hd, ni nada parecido.\n2. Las camaras no son para realizar videos, imagenes, o videollamadas respectivamente, tienen muy poca resolución, simplemente cumplen.\n3. La bateria si es su punto mas debil, dura muy poco, con trabajo constante, y hay que tener en cuenta, que su carga es lenta, se puede demorar 3 horas en cargar approx.\n4. Llevo alrededor de 6 meses utilizandola, y me ha presentado un par de fallas respecto al sonido, he tenido la obligación de reiniciarle, y se ha solucionado.\nBuen producto, para el que busque algo correcto a buen precio.', 'votos_utiles': '4'}, {'calificacion': 5, 'fecha': '02 dic. 2024', 'contenido': 'Excelente producto en relación precio/calidad. Ha cumplido en las tareas en que la he usado como edición de video y toma de apuntes. El lápiz funciona bastante bien.', 'votos_utiles': '3'}]</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>45809.67834961102</v>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_602205-MLA74652847384_022024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_773066-MLA52988770867_122022-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_860664-MLA52988782788_122022-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_944519-MLU73115284216_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_781580-MLU75321470327_032024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_694460-MLU70065260095_062023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_810307-MLU75321420641_032024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_853829-MLU75321391561_032024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_742900-MLU75174250074_032024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_791595-MLU73115624998_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_920640-MLU73115625028_122023-F.webp']</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '07 ago. 2022', 'contenido': 'Feliz con la compra, pedí outemu rojo, que son los clips del teclado. Estos son silenciosos y más suaves que el outemu blue.\nA mí me gusta el teclado silencioso por eso preferí outemu rojo.\nEl teclado tiene retroalimentación de calidad, y se siente la calidad del teclado. Con teclas inborrables porque son de doble inyección.\nMuy feliz con el teclado 100% original. Gracias.', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '20 jun. 2022', 'contenido': 'Es un gran teclado, de muy buena construcción y robusto, sin embargo en la publicación dice que vienen con unos switches outemu blue, y vino con unos switches de color rojo de los cuales no se exactamente la referencia. Aun asi me siento conforme con el funcionamiento de este y lo recomiendo.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '06 ene. 2022', 'contenido': 'Buen producto relación calidad precio.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '09 abr. 2024', 'contenido': 'Se ve de muy buena calidad se nota q es de buena construcción espero q dure.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '14 may. 2025', 'contenido': 'Me gustó mucho el producto, bastante sólido se siente de buena construcción y buena calidad, sensación agradable al momento de pulsar las teclas y buena retroiluminación en cada una de las transiciones, recomiendo el producto totalmente.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>45809.68173765656</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LOGITECH</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Logitech G413 Se, Teclado Gamer Mecánico Retroiluminado Led Color del teclado Grafito Idioma Inglés</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=1%2BmSDuFEjeCjf5EyjYdV5LjMfAU5owNLHEYv3ks1VKpD0Gs0zZTvdlXGVSqVU2xg%2BncfChY%2BC%2BAAHw37%2F7v%2BEifMiSaJ4p17K3K5XrAXV2HEQv4MYSAql9TGf%2BB9VigDzre5GPNO5v%2F6zUHVGeGXBAb0ww3SZNZsWxcpGcVvIrsd%2FB9RcBs9oHxqv3cI0u2A5f1D5XAcqNDhSB9Ee4tEbShrr0kTBMcGviYSNFBtDMz24KVROBy2GoNoJRTiQzllPVlRY7ZFeIEpVsPwAaYH9fjbFmfU1V5gIZRyKCcxbMScmI71XEgfLilHueoqznPDxM7jHKWZ2mZ8aUMBsW1go4M%2BS3pz44v947MELQdtLTgQZmaOj%2BuRTaK%2FwUJXPB8Ry7l5DOsn%2F5jAlDBrvrDctWkiX2gjoBGot4qHPrJUmglwGID9XabLA%2BDt7KHqJGp0hr8VITlYrO%2FPZwzKfHZwjmqHiPz2iCHepwmXYahnElJoJU8vPqD4mYPua4sSpdiVjfFeAJVVaY6dNadGNXQFdg9EFp5qQ70oXeooPtemL%2BeSjOppfN32ZF%2FYvi1VLZj%2FqkJ1I3UrOHMwwK7IKWHRbWo1C%2FEzAIFqJnqtFRB9MBTDNV2sYdKHQUvdBD7M2P5BRlPeLcQwrh%2BFd3iLqI0e3M4c0COGIs3IIRgUI4IqrBkPWIYO9rePq%2FkwQYpAaIKtMU3poo3JeH%2BbjxHSm3nVpXlKa1rtDmwj2QtiGEhfDa6AX5g%2BzB28X5ZI2r9LSLsbjH1sQdIrBOcQd0uL1Uq97ZWs5JnwPo0oxbkLpeoYVi%2BubPo84aEBdcP0PA225XXI8efe9qSlN4UBfKvI3TgcbAYEua9Xjg8StyPoaG0LTgtFNSSiRFv2fJ7sswbMuBh3imQ2D1nexgmFmkMUgmqsQ12vs2iYADEwmMNaRsnWbesp6x1MIVUPFtuV%2FlBIVhkKCsB2wh39b7M9ZBk%2B3ruWNCHYUzP%2Fjs6rP%2F7GdfF5ZEt3OhCbmUVb&amp;highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=d5bd1a16-2a63-481d-ab07-d7b9f14f3457&amp;wid=MCO2855290132&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>357135</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_942664-MLA84857255411_052025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_831940-MLA84724971460_052025-F.jpg']</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '06 mar. 2025', 'contenido': 'Es un 10/10.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '26 dic. 2024', 'contenido': 'Excelente teclado, super rápido paea video juegos muy bueno.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '16 sep. 2024', 'contenido': 'Muy buen teclado, excelente para el gaming.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '11 sep. 2024', 'contenido': 'Con respecto al producto era lo que esperaba, con respecto a la transportadora sé que "envia" es económico pero en muchas áreas del territorio nacional es pésima transportadora, se recomienda cambiar.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '07 jun. 2024', 'contenido': 'Es un buen producto suave silencioso buenas y faciles de combinación del teclado para juegos súper rapido.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>45809.68173766883</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Teclado Mecanico Gaming Premium Tkl Rgb - Blue Switches</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=raxnTiIOfaJGLihafXujD1LfKau1fJt4%2BALVI8%2Bbs57gk4gn%2B0x02l14%2Bit8M7USHQqk8J23Vd7Ela7IruCNXs6Ba7umN1djjbgLKGjPph%2FmF0UKdIhSJWpwIuISvLU34eiNhA2Qz8W8vi%2BClW5rR%2F0zqyi%2BIsWNQ59tjuM%2F8Gy%2F%2F7AcRkW%2BxaQdc52oU37aDBgoxAlqLbTnIYPAkZNeXB2ASeKhGCYMSzORUQFu64NWzbj9X1Ewu69jq6ytRR9tG6BySZ7PqESZlYHXuPWqq3pZy9K740WAlK7N4kMTSHfEht9Pjnm8HkwzsLtvdd1AXZwLRGpirSldH8IrIB29Y6UJlPjl3qcDT%2FHFEV79Rcd7KnS2%2BmNHhRXL9%2F9O03fL4Wur5GvRHtOZPKvRWbWQJLOX595%2FB5tE5CaMf%2BIpmx0rndZOd1aiQMjhEqB0aSnucvngxtVhTqF92xNEu5bSFN5K01hGjQrrYP7qMQ3bmZLdf%2BUzu4wY0qXiYppVcagqcgMKXyyX838k%2FOcuHMCbq7u3O1V%2FbcOqATG8%2FGY909oLtZoV8TvvTOLAV3XjKqNcM%2F1CK83TDb%2FLDBqaYwjB1d3P9dYp0gsnR4jszJnY2jL0ut6oC6Xon8cEjx9jngDpHKfXeKwM%2B6F%2BCFahWXIxzXkcPfV9KIt5nnys%2BEUwxIin993%2FQ4A01WoeagLTABfk2aj2qSMnwP9LIcOvSNEN73fiDov8%2BWR3M%2FCr46AOOfjYcmr2zxiJK7iwJIvoLfyCIzxJWMDPQsihVf6rA2HN6Z6xoDV%2BvzNy7xWBKqOwbxao2uHS%2F8VWRTvzzyA4eZ%2BXuJiTc4eoEDCtpt0VMnnYK0TmNxKNAZr%2FVucsswAhmzh5S%2FYS4gm5wQ3Y33jkQQOIZZUFvSLFK135iqeKhujn19FufKQtndb5FpMSBuhgJ1GVQMMoQb%2FvQ0x9&amp;searchVariation=175176005934&amp;highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=d5bd1a16-2a63-481d-ab07-d7b9f14f3457</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>107920</v>
+      </c>
+      <c r="E8" t="n">
+        <v>134900</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>20% OFF</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_713856-MCO83310185804_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_906560-MCO83311522676_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_629139-MCO83311522714_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_952983-MCO83603556415_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_729467-MCO83603556433_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_862622-MCO83311591058_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_649367-MCO83311591070_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_879923-MCO83327889878_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_835523-MCO83311591120_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_837709-MCO83603556513_042025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '21 may. 2025', 'contenido': 'Suena muy lindo y tiene muchos modos de colores, puedes ponerlo solo rojo y varios colores también tiene multicolor a la vez 🥰🥰.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '13 may. 2025', 'contenido': 'Excelente, recomendado 100%.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '31 may. 2025', 'contenido': 'Es un excelente teclado mecánico, tiene una configuración sencilla de las luces de fondo, también trae para personalizar macros en algunas teclas, tiene un sonido aceptable. Es un poco pesado en comparación con otros, muy estético y trae mucha variedad de configuración de luces.\nLo recomiendo mucho si te gustan los teclados mecánicos al 65% para ahorrar espacios.\nDe muy buena calidad.\nVale la penam por el precio.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '29 may. 2025', 'contenido': 'Tremendo, para su valor. Muy bueno. Eso sí, suena un tris duro.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '28 may. 2025', 'contenido': 'Es sorpréndete la calidad que tiene para lo barato que es, la sensación, las luces, el sonido. Es magnifico! 10 de 10.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>45809.68173768006</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Teclado Gamer T-dagger Arena T-tgk321 Qwerty T-dagger Brown Español Color Negro Con Luz Rainbow</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/teclado-gamer-t-dagger-arena-t-tgk321-qwerty-t-dagger-brown-espanol-color-negro-con-luz-rainbow/p/MCO25354558?highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO25354558&amp;position=13&amp;search_layout=stack&amp;type=product&amp;tracking_id=d5bd1a16-2a63-481d-ab07-d7b9f14f3457&amp;wid=MCO1435132381&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>149900</v>
+      </c>
+      <c r="E9" t="n">
+        <v>214143</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>30% OFF</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_829971-MLU72637468711_112023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_846613-MLA79492165647_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_815620-MLU74161826881_012024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_916860-MLU72566191648_112023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_980831-MLA79491981591_092024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '04 feb. 2025', 'contenido': '', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '25 oct. 2024', 'contenido': 'Muy lindo y comodo.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '22 ene. 2025', 'contenido': 'Me parece un exelente producto precio calidad. Los materiales son bueno y el silencioso, me encantó recomendado.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '22 ene. 2025', 'contenido': '', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '25 abr. 2025', 'contenido': 'Un muy buen producto calidad precio, el teclado es bastante silencioso lo cual es perfecto para mí, también es muy cómodo pero tiene dos cositas que no me gustaron.\n1) entiendo el tema de 60% y la combinación de teclas con el fn pero un teclado de este tamaño necesita por obligación un software de configuración de teclas propio prácticamente no se pueden usar las flechas ya que si das fn + w vas a bloquear wasd como flechas de movimiento pero a su misma vez fn + w es flecha arriba si yo solo quiero ir hacia arriba en un texto voy a tener que darle dos veces por lo que va a subir dos veces el cursor en resumen esa combinación me aprece que está mal y no se puede cambiar.\n2) se escucha un poco el rebote de las teclas cuando se usan muy rápido pero esto puede ser tema de los switches a lo mejor con una lubricada se quite pero de fabrica puede ser un poco molesto.\nPero en general es un muy buen teclado cumple exelente su función ya llevo un mes con el usando todos los días y nunca me deja tirado lo recomiendo.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>45809.68173769186</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Teclado Mecánico Gaming Redragon K636clo Rgb Color del teclado Negro Idioma Inglés US</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/teclado-mecanico-gaming-redragon-k636clo-rgb-color-del-teclado-negro-idioma-ingles-us/p/MCO29039269?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO29039269&amp;position=14&amp;search_layout=stack&amp;type=product&amp;tracking_id=d5bd1a16-2a63-481d-ab07-d7b9f14f3457&amp;wid=MCO2772382820&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>210028</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_674064-MLU73503205759_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_943483-MLU73411990606_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_651951-MLU73411990618_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_758706-MLU73503205777_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_988320-MLU73502811109_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_891015-MLU73502870103_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_742169-MLU73411931788_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_723670-MLU73503225631_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_629594-MLU77910155149_072024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '02 mar. 2024', 'contenido': 'Excelente producto, muy bueno, hace falta revisar las macros pero cómo quedo configurado con solo conectarlo estoy feliz. Todas las teclas funcionan a la perfección.', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '07 nov. 2024', 'contenido': 'Muy bueno, silencioso, suave y práctico, funcionando perfectamente.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '30 abr. 2024', 'contenido': 'Muy bonito exelente producto lo recomiendo 🔥🔥🔥.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '25 may. 2025', 'contenido': 'Justo lo que estaba buscando, por el precio esta muy bien.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '04 abr. 2025', 'contenido': 'Excelente. Viene con las herramientas para cambiar las teclas. Un producto muy completo y estético, sobre todo por el precio!.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>45809.6817377041</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Teclado Mecánico Gamer Gamepower Suki Tkl Switches necánicos 87 teclas antighosting reposamuñecas magnético</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/teclado-mecanico-gamer-gamepower-suki-tkl-switches-necanicos-87-teclas-antighosting-reposamunecas-magnetico/p/MCO45207491?highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO45207491&amp;position=5&amp;search_layout=stack&amp;type=product&amp;tracking_id=d5bd1a16-2a63-481d-ab07-d7b9f14f3457&amp;wid=MCO1542802747&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>127415</v>
+      </c>
+      <c r="E11" t="n">
+        <v>149900</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>15% OFF</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_806430-MLA81431205572_122024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_636597-MLA82479025889_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_752807-MLA82478968071_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_899959-MLA82478941533_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_678323-MLA82478968095_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_762905-MLA82479025859_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_686051-MLA82478941575_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_629643-MLA82478968169_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_848904-MLA84026494874_052025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_614756-MLA84321552659_052025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_959549-MLA84321552663_052025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_739424-MLA84026494876_052025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '08 abr. 2025', 'contenido': 'Excelente , calidad y todo.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '29 may. 2025', 'contenido': 'Excelente teclado para el precio, el recorrido es bastante alto por lo que no es para todo el mundo y los switches no son tan silenciosos, pero en luces y calidad es excelente, sin contar con que permite extraer keycaps fácilmente y el frente es metálico, muy buen producto.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '10 abr. 2025', 'contenido': '', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '05 may. 2025', 'contenido': 'Muy bueno.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '27 abr. 2025', 'contenido': 'Exelente.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>45809.68173771294</v>
       </c>
     </row>
   </sheetData>

--- a/productos_mercadolibre.xlsx
+++ b/productos_mercadolibre.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="almacenamiento" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monitores" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="laptos" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tablet" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="teclados" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tablet" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="teclados" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="laptop" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="celulares" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,6 +498,21 @@
           <t>fecha_actualizacion</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>envio_full</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>imagenes</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>opiniones</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -543,6 +559,9 @@
       <c r="L2" s="2" t="n">
         <v>45809.63719189815</v>
       </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -581,6 +600,9 @@
       <c r="L3" s="2" t="n">
         <v>45809.63719193287</v>
       </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -630,6 +652,1147 @@
       </c>
       <c r="L4" s="2" t="n">
         <v>45809.63719194444</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ADATA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Memoria USB Adata UV240 32GB 2.0 blanco</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/memoria-usb-adata-uv240-32gb-20-blanco/p/MCO9664867?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO9664867&amp;position=10&amp;search_layout=stack&amp;type=product&amp;tracking_id=9e7deede-0473-4d29-95eb-be00dc4fd451&amp;wid=MCO1196438268&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>17600</v>
+      </c>
+      <c r="E5" t="n">
+        <v>21900</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>18% OFF</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>192</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>45809.69471180555</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_694040-MLU75763371779_042024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_985397-MLU70036104461_062023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_654757-MLU75591848261_042024-F.webp']</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '14 feb. 2023', 'contenido': 'De buena calidad lo recomiendo.', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '12 dic. 2024', 'contenido': 'Para un uso doméstico, por el precio adquirido esta muy bien. (algo baja su velocidad a la hora de copiar, pero por lo menos es estable). Un saludo.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '09 abr. 2024', 'contenido': 'Muy bueno pero no trae el tamaño esacto de lo que dice las especificaciones gracias.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '08 abr. 2024', 'contenido': 'Buena calidad. Rápida, la verdad todas las usb funciona bien pero es bonita y la tapa protectora es practica.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '13 mar. 2024', 'contenido': 'Se ven bien.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KINGSTON</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Memoria USB Kingston DTX32GB Exodia DTX/32 32GB 3.2 Gen 1 Liso negro</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/memoria-usb-kingston-dtx32gb-exodia-dtx32-32gb-32-gen-1-liso-negro/p/MCO16227937?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO16227937&amp;position=11&amp;search_layout=stack&amp;type=product&amp;tracking_id=9e7deede-0473-4d29-95eb-be00dc4fd451&amp;wid=MCO1566379885&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>22800</v>
+      </c>
+      <c r="E6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>24% OFF</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>232</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>45809.69471184027</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_913974-MLU74227324811_012024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_920608-MLA74781182461_022024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_844111-MLU70027973115_062023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_664804-MLU70027973117_062023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_713153-MLU78132061832_082024-F.webp']</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '20 ene. 2023', 'contenido': 'Buen producto.\nSi problemas por el momento.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '23 oct. 2022', 'contenido': 'De momento todo bien. Funciona según lo esperado.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '22 oct. 2022', 'contenido': 'Cumple con lo estipulado, 32 gb, kingstone.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '07 sep. 2022', 'contenido': 'Excelente producto funciona a la perfección.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '01 sep. 2022', 'contenido': 'Muy funcional y el ajuste al puerto es bueno.', 'votos_utiles': '1'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ADATA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Memoria USB Adata UV240 32GB 2.0 rojo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/memoria-usb-adata-uv240-32gb-20-rojo/p/MCO9664866?highlight=true&amp;headerTopBrand=true#polycard_client=search-nordic&amp;searchVariation=MCO9664866&amp;position=14&amp;search_layout=stack&amp;type=product&amp;tracking_id=9e7deede-0473-4d29-95eb-be00dc4fd451&amp;wid=MCO880741360&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>17739</v>
+      </c>
+      <c r="E7" t="n">
+        <v>21900</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>19% OFF</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>192</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>45809.69471185185</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_613306-MLU78822813923_082024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_702285-MLU74135785460_012024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_959772-MLU78823066871_082024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_992266-MLU78822813927_082024-F.webp']</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '14 feb. 2023', 'contenido': 'De buena calidad lo recomiendo.', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '12 dic. 2024', 'contenido': 'Para un uso doméstico, por el precio adquirido esta muy bien. (algo baja su velocidad a la hora de copiar, pero por lo menos es estable). Un saludo.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '09 abr. 2024', 'contenido': 'Muy bueno pero no trae el tamaño esacto de lo que dice las especificaciones gracias.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '08 abr. 2024', 'contenido': 'Buena calidad. Rápida, la verdad todas las usb funciona bien pero es bonita y la tapa protectora es practica.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '13 mar. 2024', 'contenido': 'Se ven bien.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KINGSTON</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Memoria USB Kingston DataTraveler 50 DT50 32GB 3.1 Gen 1 plateado y rojo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/memoria-usb-kingston-datatraveler-50-dt50-32gb-31-gen-1-plateado-y-rojo/p/MCO6332945?highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO6332945&amp;position=15&amp;search_layout=stack&amp;type=product&amp;tracking_id=9e7deede-0473-4d29-95eb-be00dc4fd451&amp;wid=MCO1547557493&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>29900</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>23</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>45809.69471186343</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_829050-MLA45993722925_052021-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_617967-MLU73128697932_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_794282-MLU73212738451_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_685969-MLU73128697938_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_946759-MLU73128697944_122023-F.webp']</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '23 ene. 2025', 'contenido': 'Bien.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '30 sep. 2024', 'contenido': 'Excelente producto, muy buena calidad y buen precio.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '02 may. 2023', 'contenido': 'Hasta ahora funciona bien,.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '27 ene. 2023', 'contenido': 'Original de buena calidad.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '12 ene. 2023', 'contenido': 'Excelente.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KINGSTON</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Memoria USB Kingston DataTraveler 100 G3 DT100G3 32GB 3.0 negro</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/memoria-usb-kingston-datatraveler-100-g3-dt100g3-32gb-30-negro/p/MCO6064931?highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO6064931&amp;position=19&amp;search_layout=stack&amp;type=product&amp;tracking_id=9e7deede-0473-4d29-95eb-be00dc4fd451&amp;wid=MCO2875349006&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>19900</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>25</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>45809.694711875</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_993473-MLA74652412874_022024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_703393-MLU72749484146_112023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_675388-MLU78003817199_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_789532-MLU74227173743_012024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_611182-MLU74135831170_012024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_836860-MLU78003817213_072024-F.webp']</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '17 abr. 2024', 'contenido': 'Excelente producto marca y además muy buen precio muvhas gracias.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '15 may. 2025', 'contenido': 'Excelente 👌.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '27 abr. 2025', 'contenido': 'Justo lo que pedí. Compatible para booteo sin problemas.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '27 mar. 2025', 'contenido': 'Buen producto.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '30 may. 2024', 'contenido': 'Very quick delivery , great product.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>KINGSTON</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Memoria USB Kingston DataTraveler Locker+ G3 DTLPG3 32GB 3.0 plateado</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/memoria-usb-kingston-datatraveler-locker-g3-dtlpg3-32gb-30-plateado/p/MCO6334051?highlight=false&amp;headerTopBrand=true#polycard_client=search-nordic&amp;searchVariation=MCO6334051&amp;position=20&amp;search_layout=stack&amp;type=product&amp;tracking_id=9e7deede-0473-4d29-95eb-be00dc4fd451&amp;wid=MCO821874842&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>130900</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>45809.69471188657</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_756945-MLA74651541452_022024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_843436-MLA74652679254_022024-F.webp']</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KINGSTON</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Memoria USB Kingston DataTraveler 70 DT70 32GB 3.2 Gen 1 negro</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/memoria-usb-kingston-datatraveler-70-dt70-32gb-32-gen-1-negro/p/MCO16072105?highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO16072105&amp;position=21&amp;search_layout=stack&amp;type=product&amp;tracking_id=9e7deede-0473-4d29-95eb-be00dc4fd451&amp;wid=MCO1505925889&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>35000</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>45809.69471189815</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_758539-MLA74781169459_022024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_640390-MLA74781979351_022024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_652818-MLA74782717201_022024-F.webp']</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '25 ago. 2023', 'contenido': 'Excelente producto.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '24 ago. 2023', 'contenido': 'Malísima, no sé si es mi unidad, pero solo con un uso se calentó a tal punto en que dejó de funcionar.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ADATA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Memoria Usb Adata Auv240 32 Gb Blanco</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://articulo.mercadolibre.com.co/MCO-608032558-memoria-usb-adata-auv240-32-gb-blanco-_JM?searchVariation=76414034566&amp;highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=76414034566&amp;position=32&amp;search_layout=stack&amp;type=item&amp;tracking_id=9e7deede-0473-4d29-95eb-be00dc4fd451</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>18675</v>
+      </c>
+      <c r="E12" t="n">
+        <v>24900</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>25% OFF</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>45809.69471190972</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_807464-MCO44918470450_022021-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_707724-MCO44918450581_022021-F.webp']</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '18 mar. 2024', 'contenido': 'Funcional para guardar documentos sencillos, uso básico.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '09 oct. 2023', 'contenido': 'Buena calidad.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>KINGSTON</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Memoria Usb Metálica 32gb Kingston Datatraveler 50 Kingston</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://articulo.mercadolibre.com.co/MCO-595358910-memoria-usb-metalica-32gb-kingston-datatraveler-50-kingston-_JM?searchVariation=175782051462&amp;highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=175782051462&amp;position=36&amp;search_layout=stack&amp;type=item&amp;tracking_id=9e7deede-0473-4d29-95eb-be00dc4fd451</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>27900</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>45809.69471192129</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_625876-MCO44125675525_112020-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_669451-MCO44125671585_112020-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_943280-MCO44125677402_112020-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_914099-MCO44125671584_112020-F.webp']</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>KINGSTON</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Memoria Usb Kingston Datatraveler Exodia Dtxon/64 64gb 3.2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://articulo.mercadolibre.com.co/MCO-658653837-memoria-usb-kingston-datatraveler-exodia-dtxon64-64gb-32-_JM?searchVariation=95395796049&amp;highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=95395796049&amp;position=37&amp;search_layout=stack&amp;type=item&amp;tracking_id=9e7deede-0473-4d29-95eb-be00dc4fd451</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>22116</v>
+      </c>
+      <c r="E14" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>26% OFF</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>44</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>45809.69471193287</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_929167-MCO50606651422_072022-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_880847-MCO50606715053_072022-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_782061-MCO50606691200_072022-F.webp']</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '21 may. 2022', 'contenido': 'Excelente producto me gustaria comprar solo negra.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '04 feb. 2024', 'contenido': 'Excelente producto.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '03 feb. 2024', 'contenido': 'Me gustó mucho.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '19 ene. 2024', 'contenido': 'Producto original. Excelente.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '14 dic. 2023', 'contenido': 'Excelente producto, recomendado 100%.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>KINGSTON</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Memoria Usb Metalica 32gb 2.0 Plateada Color Gris Memoria Metalica</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/memoria-usb-metalica-32gb-20-plateada-color-gris-memoria-metalica/p/MCO41275474?highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO41275474&amp;position=26&amp;search_layout=stack&amp;type=product&amp;tracking_id=9e7deede-0473-4d29-95eb-be00dc4fd451&amp;wid=MCO2720082650&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>26640</v>
+      </c>
+      <c r="E15" t="n">
+        <v>29600</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>10% OFF</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>45809.69471195602</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_806970-MLA79385315388_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_799631-MLA79629112941_092024-F.webp']</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '19 abr. 2025', 'contenido': 'Excelente.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '17 feb. 2025', 'contenido': 'Muy rápido el domicilio.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ADATA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Memoria Usb Adata Uv240 32gb 2.0 Rojo</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://articulo.mercadolibre.com.co/MCO-1484377158-memoria-usb-adata-uv240-32gb-20-rojo-_JM?searchVariation=177842822783&amp;highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=177842822783&amp;position=42&amp;search_layout=stack&amp;type=item&amp;tracking_id=9e7deede-0473-4d29-95eb-be00dc4fd451</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>37900</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>45809.69471196759</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_602936-MLA45993881221_052021-F.webp']</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>KINGSTON</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Memoria Kingston 32gb  Usb 3.1/3.0/2.0 Datatraveler G4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://articulo.mercadolibre.com.co/MCO-596222200-memoria-kingston-32gb-usb-313020-datatraveler-g4-_JM?searchVariation=174396094969&amp;highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=174396094969&amp;position=44&amp;search_layout=stack&amp;type=item&amp;tracking_id=9e7deede-0473-4d29-95eb-be00dc4fd451</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>26900</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>45809.69471197917</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_647417-MCO44193087650_112020-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_826168-MCO44193126098_112020-F.webp']</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '27 dic. 2020', 'contenido': 'Excelente producto. Muy buena calidad.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ADATA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Memoria Usb Adata Auv 240 32 Gb Blanco/azul</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://articulo.mercadolibre.com.co/MCO-605756578-memoria-usb-adata-auv-240-32-gb-blancoazul-_JM?searchVariation=75192847444&amp;highlight=false&amp;headerTopBrand=true#polycard_client=search-nordic&amp;searchVariation=75192847444&amp;position=47&amp;search_layout=stack&amp;type=item&amp;tracking_id=9e7deede-0473-4d29-95eb-be00dc4fd451</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>17958</v>
+      </c>
+      <c r="E18" t="n">
+        <v>21900</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>18% OFF</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>33</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>45809.69471199074</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_782363-MCO44795875696_022021-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_979636-MCO44795884405_022021-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_725544-MCO44795877722_022021-F.webp']</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '15 jul. 2021', 'contenido': 'Hasta el momento me funciona bien. Como el uso que le doy es para ver videos en la tv, no me preocupa su voluminosidad, la cual podría estorbar cuando se conectan varios puertos consecutivos en una pc. Es una memoria muy bonita, parece algo frágil el exterior, aunque ya se me cayó una vez y sobrevivió. La tapita es divertida y bonita, pero estorbosa cuando está abierta. Me gustó el detalle de que tiene un agujerito para pasarle un hilito tipo llavero.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '07 ago. 2023', 'contenido': 'Muy buen producto.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '03 jul. 2023', 'contenido': 'Es un buen producto, los materiales son plástico de no muy buena calidad, por lo que hay que tener cuidado con las caídas. Es un usb 2. 0 por lo que no es muy veloz pasando archivos grandes, pero es útil por ese precio para almacenar una buena cantidad de cosas.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '06 abr. 2023', 'contenido': 'Bien.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '15 feb. 2022', 'contenido': 'Excelente, de alta calidad y funciona sin inconvenientes.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>KINGSTON</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Memoria Usb Metalica 32gb Memoria Metalica</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://articulo.mercadolibre.com.co/MCO-2789048870-memoria-usb-metalica-32gb-memoria-metalica-_JM?searchVariation=186617022947&amp;highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=186617022947&amp;position=51&amp;search_layout=stack&amp;type=item&amp;tracking_id=9e7deede-0473-4d29-95eb-be00dc4fd451</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>27900</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>45809.69471200232</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_776293-MCO81489239056_012025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_683150-MCO81489367296_012025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_603981-MCO81489258864_012025-F.webp']</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ADATA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Memoria USB Adata UV240 32GB 2.0 blanco</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/memoria-usb-adata-uv240-32gb-20-blanco/p/MCO9664867?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO9664867&amp;position=8&amp;search_layout=stack&amp;type=product&amp;tracking_id=a21b325d-0046-4731-823c-2f8e38214470&amp;wid=MCO1196438268&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>17600</v>
+      </c>
+      <c r="E20" t="n">
+        <v>21900</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>18% OFF</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J20" t="n">
+        <v>192</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>45809.69471201389</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_694040-MLU75763371779_042024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_985397-MLU70036104461_062023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_654757-MLU75591848261_042024-F.webp']</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '14 feb. 2023', 'contenido': 'De buena calidad lo recomiendo.', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '12 dic. 2024', 'contenido': 'Para un uso doméstico, por el precio adquirido esta muy bien. (algo baja su velocidad a la hora de copiar, pero por lo menos es estable). Un saludo.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '09 abr. 2024', 'contenido': 'Muy bueno pero no trae el tamaño esacto de lo que dice las especificaciones gracias.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '08 abr. 2024', 'contenido': 'Buena calidad. Rápida, la verdad todas las usb funciona bien pero es bonita y la tapa protectora es practica.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '13 mar. 2024', 'contenido': 'Se ven bien.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>KINGSTON</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Memoria USB Kingston DTX32GB Exodia DTX/32 32GB 3.2 Gen 1 Liso negro</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/memoria-usb-kingston-dtx32gb-exodia-dtx32-32gb-32-gen-1-liso-negro/p/MCO16227937?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO16227937&amp;position=11&amp;search_layout=stack&amp;type=product&amp;tracking_id=a21b325d-0046-4731-823c-2f8e38214470&amp;wid=MCO1566379885&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>22800</v>
+      </c>
+      <c r="E21" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>24% OFF</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>232</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>45809.69471202546</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_913974-MLU74227324811_012024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_920608-MLA74781182461_022024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_844111-MLU70027973115_062023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_664804-MLU70027973117_062023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_713153-MLU78132061832_082024-F.webp']</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '20 ene. 2023', 'contenido': 'Buen producto.\nSi problemas por el momento.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '23 oct. 2022', 'contenido': 'De momento todo bien. Funciona según lo esperado.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '22 oct. 2022', 'contenido': 'Cumple con lo estipulado, 32 gb, kingstone.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '07 sep. 2022', 'contenido': 'Excelente producto funciona a la perfección.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '01 sep. 2022', 'contenido': 'Muy funcional y el ajuste al puerto es bueno.', 'votos_utiles': '1'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ADATA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Memoria USB Adata UV240 32GB 2.0 rojo</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/memoria-usb-adata-uv240-32gb-20-rojo/p/MCO9664866?highlight=true&amp;headerTopBrand=true#polycard_client=search-nordic&amp;searchVariation=MCO9664866&amp;position=18&amp;search_layout=stack&amp;type=product&amp;tracking_id=a21b325d-0046-4731-823c-2f8e38214470&amp;wid=MCO880741360&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>17739</v>
+      </c>
+      <c r="E22" t="n">
+        <v>21900</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>19% OFF</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>192</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>45809.69471203704</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_613306-MLU78822813923_082024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_702285-MLU74135785460_012024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_959772-MLU78823066871_082024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_992266-MLU78822813927_082024-F.webp']</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '14 feb. 2023', 'contenido': 'De buena calidad lo recomiendo.', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '12 dic. 2024', 'contenido': 'Para un uso doméstico, por el precio adquirido esta muy bien. (algo baja su velocidad a la hora de copiar, pero por lo menos es estable). Un saludo.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '09 abr. 2024', 'contenido': 'Muy bueno pero no trae el tamaño esacto de lo que dice las especificaciones gracias.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '08 abr. 2024', 'contenido': 'Buena calidad. Rápida, la verdad todas las usb funciona bien pero es bonita y la tapa protectora es practica.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '13 mar. 2024', 'contenido': 'Se ven bien.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>KINGSTON</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Memoria USB Kingston DataTraveler 50 DT50 32GB 3.1 Gen 1 plateado y rojo</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/memoria-usb-kingston-datatraveler-50-dt50-32gb-31-gen-1-plateado-y-rojo/p/MCO6332945?highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO6332945&amp;position=23&amp;search_layout=stack&amp;type=product&amp;tracking_id=a21b325d-0046-4731-823c-2f8e38214470&amp;wid=MCO1547557493&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>29900</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="b">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>23</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>45809.69471204861</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_829050-MLA45993722925_052021-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_617967-MLU73128697932_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_794282-MLU73212738451_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_685969-MLU73128697938_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_946759-MLU73128697944_122023-F.webp']</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '23 ene. 2025', 'contenido': 'Bien.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '30 sep. 2024', 'contenido': 'Excelente producto, muy buena calidad y buen precio.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '02 may. 2023', 'contenido': 'Hasta ahora funciona bien,.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '27 ene. 2023', 'contenido': 'Original de buena calidad.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '12 ene. 2023', 'contenido': 'Excelente.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>KINGSTON</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Memoria USB Kingston DataTraveler 100 G3 DT100G3 32GB 3.0 negro</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/memoria-usb-kingston-datatraveler-100-g3-dt100g3-32gb-30-negro/p/MCO6064931?highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO6064931&amp;position=22&amp;search_layout=stack&amp;type=product&amp;tracking_id=a21b325d-0046-4731-823c-2f8e38214470&amp;wid=MCO2875349006&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>19900</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="b">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J24" t="n">
+        <v>25</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>45809.69471206018</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_993473-MLA74652412874_022024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_703393-MLU72749484146_112023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_675388-MLU78003817199_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_789532-MLU74227173743_012024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_611182-MLU74135831170_012024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_836860-MLU78003817213_072024-F.webp']</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '17 abr. 2024', 'contenido': 'Excelente producto marca y además muy buen precio muvhas gracias.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '15 may. 2025', 'contenido': 'Excelente 👌.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '27 abr. 2025', 'contenido': 'Justo lo que pedí. Compatible para booteo sin problemas.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '27 mar. 2025', 'contenido': 'Buen producto.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '30 may. 2024', 'contenido': 'Very quick delivery , great product.', 'votos_utiles': '0'}]</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -907,7 +2070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -973,35 +2136,36 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>opiniones</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>fecha_actualizacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Portatil Hp 12ava Gen Intel I3 1215u Ssd 512gb Ram 8gb Color Plateado</t>
+          <t>Tablet Android 13 De Última Generación 2024, 128gb+16gb-512g</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=zQFU5BvnvqwRvMq1By5NRGFlzAqpbowk3qmAcnB%2BMJNDDwXDw3blW2x0QBWMcSaSHbHCVFn8z9QnYq1eJ4%2BiIrQdn2pihRo7erq%2FCWpkfyfGrhZe5Q0y9aSLBaAyFrwBVz8pHLUl0v%2BDgI5Z4uNAxCi%2Ftq9munKuJSr3tHuxxID%2FLfS5lpjCKXZf6y5BWLNFa3o8Q9HLMLnEtrWH6sCfv8n9sIlSn%2FxupheY5iO9EiTiB82RqwRYzDEaqFAhTHmbnJTLGJES%2FduL%2BytUQ2CcXDdQ%2FI9qzFtDZuET4I7n7jCACxvJlD0TjaRS%2Bz6FWkNFiVwXpekgIj0EOvfRaJdcptKXGmGbQTHwEt3aIKw8zUwgNEXsM4WAVIvJkEg%2BAOJPiGLcvy9oLbvDE3%2F1Qg1k6L1b07xhQBYOrqJ1Hzw24XIyxvPLHuATlo1tgOMKwmDZj9pNqAuGPVH%2BsxXE8vxGcztIWVIcp8XGXGyr9hpFvVbzfH42HleBpg13sXKRJ5Vjl9lbffaiO5XWuezBmpuJUyoO4DU1nnYNjxCiyUkBOZMsxLHvpEC6G6ifDchjVYhzBo%2BzI2b1%2Fy2r5u9GyQkXGIGRacKYr9hSvlpvLDLPPndYK0kmPApJzRiDE2I1bGnupjy7MbI82xT1KZtDG29siTpEsfBaMpDYtyW2rWqdVzlvBXAmLLiFE%2BRuudIIjRhhVSuQiZjL%2FJMBEUxwP%2FSECQDekZ3LKjkiSN5%2BCqQIABFqmw%2B2FC%2FQwLH5PIoV9jos7xgpGEhBkPSPLSGW8%2Bqjfb5J7hxgYnUIh%2BYWauaZa3Gr9qgWtHoQBjKxT5y5T2Fdbu3oJnCinh1GRNPJn6XClwRyw%2FWXJCAC0F8cbL7vlQWFkgYHjQeiwyUKEVqENuIutnP7QegOWK2gdDux1vQDdxDBQ22FK56BT%2Felqvcnx%2FTeewGBs%2BJX2kTVDc4H4%2BXJehllU62pKGU4tXUI&amp;highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1507088307&amp;sid=search</t>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=mR3PrLDqSgo6MJmSPfl2dS%2FUo8svLhnfFxnazibKtZXVeLtMP0UoQHj%2BbJpGXNSxlKHqG%2Bz%2BKAOSidbxiQcoTK05NuWlcRvCDD5MjCWB3K4C9HUUZVchWsk7LOwfTerUMIos6E4Bod3tRdbnksNVMvzKRkReGltvzXuQA4OP80tSQ%2FFqfqQAMdprKdOVzOSme4KXR9XX56enzlA9K1TQLedO%2B0F9kFSvph1R7uxsW5MW7jWiRf%2BPoby49x%2BpCOruqv5yj%2B9tHUbJnalH8OJ5XR3voCMNA9kHU8L6y1wqrGWztACnPsDE%2BCasBbrRWN9gchREW0qU9OKv%2BuGLww5%2BSJ36uhWt0xDcy0AGd7wuISgsmjonuu0iuwBYDFDKW3MFXZOYmeDhKdRKt%2Fpi%2Ft%2FK0UIHY9uP3uXwZxAXo07uP69yYoBt%2Belx5HDMuV4quOj1y1sN3ViWFAQW58MtSCxLmVKe%2BrlI0PO8iTBOvOAEmXLqZja66efrwirv2M6UN7GRAiq%2FuJIaJbFGP1RbRHVc9WHBnKgU116FRxUlaU4fqBmxlMHQm5zQUnSaeWuQx5mT9CIGbFbRPMnYbfB7kUYAu4rD5kM6aEZWf3Ni2UVNvIWwwJDfUpaM5BzlLBqz5BBZdXBryopAeHgbuPH0pOiaroIVG4%2FWtkVM71Oo0KPyntc4XJ7fdS29V9Lzr72Sy9fsrUoBNz%2F0wy043vszx3X33tO%2BdhSCxi2xTwVxlfRG%2BulrO5fI6zhEysUKUMoOSBp6FW7L2xHBV6T3rEGW%2FEVfTvOkcfq3enYpcYEgD7xICHEiR3bGSjNrfXW1rRTtjOZEkDD6eHD1V3cNKSMMGgQ1hZU3OCnKXIH9%2F42zw5gQcxTgMfKqjOF2qDFeD%2BffmpGaDFBpLlp9Ol48TnLxRDKW60kFs5OzwPl2j3mh98s4WXRRJUts4%2FaSqxXaZGA869tYGdY%3D&amp;highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=de599f53-e149-4e6e-87ca-312bb77ee567&amp;wid=MCO2840069126&amp;sid=search</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1458900</v>
+        <v>907200</v>
       </c>
       <c r="E2" t="n">
-        <v>1853000</v>
+        <v>1120000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>21% OFF</t>
+          <t>19% OFF</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1015,46 +2179,49 @@
       <c r="I2" t="b">
         <v>0</v>
       </c>
-      <c r="J2" t="n">
-        <v>4.8</v>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_645989-MLU78944581522_092024-V.webp</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>45809.67502480324</v>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_942311-MLA82998654053_032025-V.webp</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>45809.67834956018</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>HUAWEI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Notebook Hp 245 G10 R3 7330u 512gb Ssd 8gb Ram Windows 11 Ho</t>
+          <t>Tablet Para Niños Huawei Matepad SE 11 Kids Edition Gris 4+128gb + Lápiz</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=P218uynAcTyZmXvon7VW%2BB05NKdbrv2OpL%2FWCxMohF7wPq3pLnEW0GZVqp3NYJ8aqjTMwyMLpfrySzH1v1mRqq6ngqRFHwLD0GDtrD2hSY0Bbq4UZyhV5HSo0i0hX5StFbtvN3LkYOzknOfOMKR8UqMLlNQOoPnvDbE2hsAOTKxYOopK16M9GSZyqp%2FsqCsoexPDq1v3uFyJ2R%2BxHd7bDF%2B%2Fpr2AsZ1aWmUPSw9PmEmdYPzNpvI7e%2FKHVU88pGOs7ril5A2GpEWjzxfdOyqyDWHBjGnHtDHvxZ4UaAlJMaSRpfpUYx0Ys82tyPbnXrrYKowZIIAPGoQiAycX8FMp44x9dJgSxXznOWEL4H1h67ZcwXXtzT5jMyZyVLu5k2rEPbuH795zcKSJnK4qoKYW%2FMtvKs12XgUk0EcC1hjkLRcQ5DcSBTU1wIb1k4aq%2FvbASZYA0%2FU%2FX8LP9fEymdEy9ISan3aB3RD77qskxltzsRMqsxJZOZJ%2B3Ko%2B2W4%2F5DtESs%2FQ1%2Fzm8U4heIk2shJc0s3nRyfwJ7Jp83xnyzlMma7aQFDXhlkDT%2BKTxbWBhOt4nGugEC7PSIHNHtd7jsFocxCzKApEpr93h407loa%2B8FVCzEa%2FSGThzAlC2o6pXSgnbpjmyzBmTyW%2B4Qi9rjbGy94HiUCAJLvvEhh5vMCorTDzHBCJviWXBA0LRp8%2FPHSI8xmQzej%2FW7SLsfuvWeh8j9kMa22oCGt%2FUXpGqymoygpcwDuu2IuUcrxU6uFudy7ubRWqOjw1AYSldcCzfxhEjro2A5SJ5UzP2OvHf4EIB79MguWxk8XDyALruJtEIxE690lkCyLzU6ljjZuAAKD41fnfiGNEygW9uLZJ4Ja41lIEiWKEGc9pSg%2BkH9fM5ZE5Ggo2GeqBKnVNAyY4UDhKPJQZkioHfx6yFWBdDR1r6ayVSDeQW7wIDQtYrJ1CPmXIzA%3D%3D&amp;highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1547113843&amp;sid=search</t>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=47Z74mPwkVy%2F%2BMV8XPeMyih7b4R7yH9gPlALeIw9jt4Itbq4%2BLZgoHGJIOjfh5tnGkwaBBmynXnKO5SQKoDtICbWMU6ADAP9p%2B06BcnngTuLz9t8Sts1JZX%2FEqbMeXKZMumNuLpFVk3z%2B2hga%2BO7ef4VXEAesOLY6d6iof5oFV2n2qV%2Fyjm6P5v%2BCSN76VU8R3p3pncS%2FaaCgwm7Eyt1NIa8lgQKC2iQ9C%2Bls05ZmjXHM0W3FWzNvSLwBwfx31JlMjR%2BQxsCXp1yT1b4A%2F1hJm8W5LCxD4G5Bqmx0IoWP0AF4o4%2FnHu3OY%2F6Feol0Lc4IT%2FWpZOi%2Brefoj7m7hMQD5R9BblTUpbWYlhnfHVZtz8ue5GbWbawmrDAznawKmRKsCBKPB0Sr3AUa0aZLXIZI8wAqblP7OV4%2BC3SqSBPLE9N848u9d1y2l0Re2%2B6PdX4NTx02zi0rHikFGGCBI0o4BZBZQERax2m1rCMmnChGVx3yr1LD%2FPIDy%2FWxeIcVG1AKq6GngTy1JYr%2BReR2sCDsHb7WAmn%2BqKHvCwAJYl6%2F3o5rY%2F2EYQ%2FCl61NKwtsqSjSMlAOpcEuEpSxCc7HuX1GWddDk39LGmfkcgXZ4sRJWzgVBceBkNouFvp2DrcmRzazdJyCH%2FjXY9srSMpdGHteCD6Ebqy%2FVXOanbn4rjy5aTL570xthAX2b0N9ZCSrJgE1vMcurWvuCYOrpL8gFASiNzAI26PD2UrvCJdJeE%2FqtdSdvaXhrmtsuPu0NVgu5W0gm5sEcfYFyPlB65xBVCDfelKwFW2H6xt533wWKDoWxfhq7ugSU4WOQm1WGxGROqz%2FihShH5P1WuEUxEeYigqmPEd6BC2F90Vw20e7K2MZEM9dFJDO1v0YrQeox8mc4v2yqCUeE%2B1xQ6aZx3aA%2Fds0%2B%2BNjH5HZKvYf8rnbiWieZ58VEC3wwD24m4y62PpliSga4%2Fay5oi0F4%3D&amp;highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=de599f53-e149-4e6e-87ca-312bb77ee567&amp;wid=MCO2836671066&amp;sid=search</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1259900</v>
+        <v>678932</v>
       </c>
       <c r="E3" t="n">
-        <v>1621375</v>
+        <v>999900</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22% OFF</t>
+          <t>32% OFF</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1069,45 +2236,46 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_679019-MLU78080956988_082024-V.webp</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>45809.67502482639</v>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '14 may. 2025', 'contenido': 'Realmente pensado para los pequeños.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>45809.67834958334</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ASUS</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Portátil Asus Vivobook X1502 Ci5-12500h 24gb Ssd512 Fhd15.6 color Quiet Blue</t>
+          <t>Tablet Xiaomi Redmi Pad Se 8gb 256gb Gris</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.mercadolibre.com.co/portatil-asus-vivobook-x1502-ci5-12500h-24gb-ssd512-fhd156-color-quiet-blue/p/MCO47191661?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO47191661&amp;position=5&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1569451947&amp;sid=search</t>
+          <t>https://www.mercadolibre.com.co/tablet-xiaomi-redmi-pad-se-8gb-256gb-gris/p/MCO29219683?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO29219683&amp;position=4&amp;search_layout=stack&amp;type=product&amp;tracking_id=de599f53-e149-4e6e-87ca-312bb77ee567&amp;wid=MCO1567332181&amp;sid=search</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1929900</v>
+        <v>709900</v>
       </c>
       <c r="E4" t="n">
-        <v>2249000</v>
+        <v>1149900</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14% OFF</t>
+          <t>38% OFF</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1122,18 +2290,23 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K4" t="n">
-        <v>14</v>
+        <v>298</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
         </is>
       </c>
-      <c r="M4" s="2" t="n">
-        <v>45809.67502483796</v>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '26 jul. 2024', 'contenido': 'La tablet es demasiado rápida, corre juegos con facilidad y su pantalla es muy buena. Le verdad me sorprendió lo bueno que corre los juegos y las aplicaciones.', 'votos_utiles': '13'}, {'calificacion': 5, 'fecha': '08 jun. 2024', 'contenido': 'Excelente compra. Una tablet de calidad,buena construcción e increíble apariencia. Definitivamente otro gran producto de xiaomi.', 'votos_utiles': '8'}, {'calificacion': 5, 'fecha': '29 ene. 2025', 'contenido': 'Súper me gustó mucho , apenas para lo que necesito 😊.', 'votos_utiles': '6'}, {'calificacion': 5, 'fecha': '30 dic. 2024', 'contenido': 'Genial.', 'votos_utiles': '3'}, {'calificacion': 5, 'fecha': '17 feb. 2025', 'contenido': '', 'votos_utiles': '3'}]</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>45809.67834959491</v>
       </c>
     </row>
     <row r="5">
@@ -1144,23 +2317,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lenovo Ideapad 1 Ip 1 15igl7 Intel Celeron N4020 15,6 Pulgadas 8 GB Ram</t>
+          <t>Tablet Lenovo Tab K11 4g Lte 8gb 128gb Teclado + Pen Color Luna Grey</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.mercadolibre.com.co/lenovo-ideapad-1-ip-1-15igl7-intel-celeron-n4020-156-pulgadas-8-gb-ram/p/MCO40332473?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO40332473&amp;position=18&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO2864083698&amp;sid=search</t>
+          <t>https://www.mercadolibre.com.co/tablet-lenovo-tab-k11-4g-lte-8gb-128gb-teclado-pen-color-luna-grey/p/MCO45442884?highlight=true&amp;headerTopBrand=true#polycard_client=search-nordic&amp;searchVariation=MCO45442884&amp;position=5&amp;search_layout=stack&amp;type=product&amp;tracking_id=de599f53-e149-4e6e-87ca-312bb77ee567&amp;wid=MCO1529700467&amp;sid=search</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1016900</v>
+        <v>1094900</v>
       </c>
       <c r="E5" t="n">
-        <v>1500000</v>
+        <v>1899900</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>32% OFF</t>
+          <t>42% OFF</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1174,42 +2347,49 @@
       <c r="I5" t="b">
         <v>0</v>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>5</v>
+      </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
         </is>
       </c>
-      <c r="M5" s="2" t="n">
-        <v>45809.67502484954</v>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '15 may. 2025', 'contenido': 'Exelente producto calidad precio. Lo recomiendo totalmente.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '08 may. 2025', 'contenido': 'Bonita y económica.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '30 abr. 2025', 'contenido': 'Muy buena y muy práctica.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '03 mar. 2025', 'contenido': 'Es muy buena.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '10 feb. 2025', 'contenido': 'Excelente!.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>45809.67834960648</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>LENOVO</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Msi Cyborg 14 A13vf I7 16gb 512gb Ssd Rtx 4060 8gb Color Negro</t>
+          <t>Tablet Lenovo M11 128gb 8gb Ram + Lapiz 10.9 Pulgadas Color Negro</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.mercadolibre.com.co/msi-cyborg-14-a13vf-i7-16gb-512gb-ssd-rtx-4060-8gb-color-negro/p/MCO45076522?highlight=false&amp;headerTopBrand=true#polycard_client=search-nordic&amp;searchVariation=MCO45076522&amp;position=10&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1547623157&amp;sid=search</t>
+          <t>https://www.mercadolibre.com.co/tablet-lenovo-m11-128gb-8gb-ram-lapiz-109-pulgadas-color-negro/p/MCO36109372?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO36109372&amp;position=8&amp;search_layout=stack&amp;type=product&amp;tracking_id=de599f53-e149-4e6e-87ca-312bb77ee567&amp;wid=MCO1501072863&amp;sid=search</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4653900</v>
+        <v>874900</v>
       </c>
       <c r="E6" t="n">
-        <v>6999000</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>33% OFF</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Envío gratis</t>
@@ -1225,786 +2405,20 @@
         <v>4.9</v>
       </c>
       <c r="K6" t="n">
-        <v>8</v>
+        <v>167</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
         </is>
       </c>
-      <c r="M6" s="2" t="n">
-        <v>45809.67502486111</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Potátil Portátil 14-dq0533la 14 8gb De Ram - 256gb Ssd - Intel Celeron</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=72GdK%2BpbrTFTM7i1sgjMu%2BbDsZwimgIVsgEMaqQVM80u2lSxiPxIp49lAD5FzvvX7tw%2B3WjmLZh4n%2BWEsTFcMPGWatgq50tuIi838LaR5oQJV5CEEvHbnKXPQACchyTHH0vjIO1%2Fj5c%2FXsO3bZMNq840pE4vh0ds%2Bd%2FwnVC79v072kXMRCGv3qHwC7U14OLGxP1MhOY85quB4Dd%2BoCzJ%2BVTsoBR7e70znoJTiR9qZUrKLyP%2BGL151fg2q%2FjTPcpe0EOWnfesuWGnIbRJ4UtBsHEOeSTUxpPqZKHMg8VjCEq4SmLvT%2BPRSReQB8aIUXznqFgDkSM1AE8omkj%2Fb%2FzxOs6KhMnCGKwZieGHEq6Q1rlE7c5VoFZGbp%2BOdt4PoLgaaqkzDbXOMhYOjXfdXrGgIzF6REZoUczzadV4ktrUlWshAxhwNxeakqcHnzwOFSCVPS4WrphjKzsUv3e3FIITEW1ZLpH%2BijyDAUSqj5BtIwnqZLC0aEfBTEKF086b3De50nkyz%2F1VJd4r2IhpVNLFE3P9mFqfBECnPRa1w%2Bj5TFMNuAMTPGDAZf%2Bp3f9QJMQ%2FrkuqXUtGmXqBcvaJSVoEKarvtyQY9iM9eRVEJGSve0Zvgw66yjF5rAZJXpCXH%2F0SuJqfrP1GZxnDkpeEMHfVYia4j959bA8TrP7ccIlaC37VeVRdDu%2F0329FzL07pGhmr0ABaZML9QGaZrqN7NpZPtdHai42qP5%2BxTxoA%2FgYEARxTAs3Y6XqVCueecJgOI7oc3f14YbulsBtatYNP%2Br%2FoKaJyI184MA5kvfmfDdC2Bfg12W8N6szceKHTo%2FthMXp4IoCP5VQNEK2vH5W%2FqMiPyumd%2FHlHpTXOTabOSyRlb%2BoYDSe4IzEy9SXmvrjE3GZPQi6T7ncDaOr3nL2yy%2BCUGFcYS4jRoUHT7Dr6RSMXBuSjuKMlIz5m2KgbW11LobjxwwP6xE%3D&amp;highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1547113619&amp;sid=search</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>919900</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1185375</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>22% OFF</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K7" t="n">
-        <v>14</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>45809.67502486111</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Portátil Hp 15-fd0026la Intel Core I3 8gb Ram 512gb Ssd</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=QHVRSkMapUYFd0MUsUJK5vva3fHEv%2FyYutnoyKQ309KPVo9qt3PSZ7ic6AU77nHcQz1SOsZVpaNDaqoo3MEy5TX%2Fx6omSlMudceAjcJe7TmVnVv6qgMEKiHF92%2FNwkqZ%2Fj%2FdQYtnH1YCcqK25LLkuC7M8zRZxibPMDqHhDa41LfQzT8c%2Fc2j3NZeddotr4mnhO%2FeiAgvZxsOVd0hkyHjXT6CpYL%2F7XgQFZsNyy%2Fomo3zxEpuqOyS3EuDTHF6K%2FM3k0hGvJK%2BS883r2s0w8NeHtjKUOh9ZDqR7cQneLG4ZVt4OwK51xKgfhII%2BzeCagUquSMbAp76%2FsgtCerLRz9BCuEE0PglxAd%2BjIr3MUL0%2Bgj5YJiP1EmHtBPGfqAY2mHskvzbW06do8Pjn%2BdFMX%2Fea8iyWi3OGOvq0O928uulkF5odhWAmKQcPvs5ZdHf3%2BnV0jb8WXXihcMGhQrADvxvEQH51JoKXOjYkgESygc010gYtqqzT3MiJs9RF%2FWpQr5CgHALRbn32vWyekuFqEFHmObrxqP%2B2mk25JoOhUWUdDpR9saNu0vKbpY8PWF1vyCe3mHfg9nILLA%2FWvCLLxP9da%2FPPyFYxZy%2FxjxaedElM9ABbpyy%2BtCcF7zXQlMoSWf7tTHpbaIhaW6sl4zv%2BsZiLd10R065djXFACsM7VKfZakLbHc0MwB%2FGgyi2RPCmVYd%2Fm5lu4XsHOCpLOCE3ApQF4LXLw6LVwxxpVpuLZb2E5zJRyJ0G9gt5xhE%2Bt1AFun%2BZBBd0X3oyTreYtHLOngjGLwPgPc1GdxghV%2B9wgeQ0zs0dm55nlM6w6DhGNJiRM6uQrAERZrHAAowzsKOY2ELq0Tz0lILYMyZxit0AxnKuccqHqrKCkl7iXonFO5zniizKB87r%2F%2B7DyxH%2B%2FtmdJ%2FoSMSeOcbPA%2BRGQ0Hgxz91UJBNRCeoO0ZHBzk0j4oq&amp;highlight=false&amp;headerTopBrand=true#polycard_client=search-nordic&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO2878894100&amp;sid=search</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>2499900</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H8" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>45809.67502487268</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ASUS</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Portátil Asus X1605za-mb644 Intel Corei5-12500h 16gb Ram Disco Solido 512ssd 16 Fhd Endless</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://www.mercadolibre.com.co/portatil-asus-x1605za-mb644-intel-corei5-12500h-16gb-ram-disco-solido-512ssd-16-fhd-endless/p/MCO32161065?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO32161065&amp;position=3&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1523840021&amp;sid=search</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>2029900</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H9" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K9" t="n">
-        <v>145</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>45809.67502488426</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ASUS</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Portatil Asus E1504fa-nj474 Ryzen 5-7520u Ram 16gb Ssd 512gb Color Negro</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://www.mercadolibre.com.co/portatil-asus-e1504fa-nj474-ryzen-5-7520u-ram-16gb-ssd-512gb-color-negro/p/MCO23498360?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO23498360&amp;position=14&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1541876389&amp;sid=search</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>1725640</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1988778</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>13% OFF</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K10" t="n">
-        <v>413</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>45809.67502488426</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>APPLE</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>MacBook Air 13.6 M2 256 GB SSD 16 GB Ram Z160000au C/ Nota</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>https://www.mercadolibre.com.co/macbook-air-136-m2-256-gb-ssd-16-gb-ram-z160000au-c-nota/p/MCO26602331?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO26602331&amp;position=8&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO2813970572&amp;sid=search</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>4299299</v>
-      </c>
-      <c r="E11" t="n">
-        <v>5057999</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>15% OFF</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K11" t="n">
-        <v>131</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>45809.67502489583</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Portátil HP 15-fd0065la Intel Core i5 16 GB 1 TB SSD 15.6" FHD Windows 11 Home</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=DGWR%2F%2Fegp7TdyCwhdw99a44O2oQgggn7VIYlmeQwtLg8VC08255MGlgaOJG9lbdJKyvhyvI7V5q1aLrsqe%2F4FmXlVusxQNzjHGFm5g0X44I9Dsb6kLzzhEiV4yyhD5iaunlUQefJHzTinDxyR0JqlbymbdlaJx4YYa%2FCdP4FSZgW409zFcLfSsXtpptnSgdJFrIwp86aGz9Uu%2Bd0iXBWcFs6tNefITwdYXIRpyNP1owqQcRMO1yu3x9MLyRXPUjvhwX5W%2ByYCjVFRzjY44o32cMJ1gFNlR5T7n%2BmX84DfqkNTgQkajcL1C4mjGHTtQF%2FhRsBBtUHfcGL0CNVwdGFMTRKj5OsAaex3wfqGTyl8gZ3yMZ3pWHT09upQ8aMymNrlLhYhZNGh6344jbKgSuTxWz2ICbIbPW6fv04fvzdEoEPzoovJO2RozxZhEDGCY0O7OLEkNqLcflDp7pVi2wf3VlmPLVEDFnwMLy1bXZr9kDNHjaskWf88CcTmrMhD3PUgyRWr7K82XAxD7KbQYCmIHWPrqh2tUpU7KUwtNFobF%2FxotC0yF3rHJOEkjYXg2NMxAt2i%2BuCNwQuC8vDNqSnOtqEemigcV%2BS5EvbSJq3wASgw%2BMwI3E4%2BGqWdMjBucyXDOCdLx3dHvUpWfjgAS28SQsLSS1Ibhp3FpUgUelSHlIeeD%2Fury1BdslGa%2F5tx3q95QSGQrmVaiIsNDTuMEc7QhT0%2F0sdRRw3O7tlRj8e54P5EF6Jr%2BnrIjBT3EIsDDDo2vl4XHq6zTCyg2O2ZVGDf0K%2BDoZiDzpwyBm1E5eBuYO2uR9R2NjL91NqgaFVTKAIyOUdFX3x8ou7kmR5%2BlzbnrqYk9tZiILIOGAOgZ7o1oVT4qIHvzVExprTu2ZXRN5kJKv7UdzoUn4k6mdexHYG83G4d810%2BP2GcSek7%2Fu7AWabbdd3B%2FMmqC3tYtvaGMeF6ySSBG9rpBVymR946CS9Jt0rJlOf%2BQ%3D%3D&amp;highlight=false&amp;headerTopBrand=true#polycard_client=search-nordic&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1575797741&amp;sid=search</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>2500939</v>
-      </c>
-      <c r="E12" t="n">
-        <v>4099900</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>39% OFF</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H12" t="b">
-        <v>1</v>
-      </c>
-      <c r="I12" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>45809.67502490741</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Portátil Hp 14-em0009la R5 Ram 16gb 512gb Ssd</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=Ui85GGnE61myuhHJSIj0W1rPFgRVo6zApHFyKPftQVLNje9pXasbLvsWHLlFW4MhTRm9ZVeNOrB%2BngajZe8OrVI%2B4nE0K755kqb%2FPICRTgQQEeui%2Bb4erSxuD2POwCn3AK3hEr8UWhN1sDL0bZVt3MHfDnIuEec5gqyaVVoILB185p2wzrsbuOqLXNnou%2FqXgegJBYuVpWHMCXM0%2Fmg1PuPIXlQpqw8Xcppha0utEmiCoygIzCgI51Q%2F3LcsU3Ke9%2BdgGo6cMQ7ACngoSaKyT6l1mvp9EtTdOgAno9qK738ZPQZdqyck1rzjCe6M8v0ViWqCcCkhXpeHhw6ho1tdX3EQU%2B4WDS2OR2gXBKcsK3S3LNiZATtjJxNq2PUOCYaqC9SG1DStQvFywgjF3mM5dLviPgGkFxg9BWvFd9Aa0T47iQZ0hL3L58W0ZzZvjQrHhO93f22Pa4QqGAlTf5BDjt5HY1TCUZclgyI9ARL7IwRLQ5EB4K%2B4J6JGRi%2BWO8jL8U00tNAUDKg%2FmoSvXhNTbdxhaiYyD0mnbxF4wPe5%2BURIe21utXPEWRO69wxZjtT4YWLb0XPYhA7X17bVJq83OmwciLx2fcUb6R%2FvvxVGY0eafDscgnAOnr1ACE08qK0jz5Y4JeSnOh%2Fypcc0Y%2BKB3ENzXJTzKcthsQxXozKrDfDlJIEMVhJzKyi9YpVJ6o8XtAVaF4G5UldPvlRAoUSihWWZaLyHQyICEtWwcaC3h0HuXHOBx0WI%2FFP1EzmtqhecdHo%2Fo1Mel7XBq77HH1ohe37Ti7LTX5Bd2sARF6avfVwT0KF6RDZ%2Fk6U5H9PExFYXGEHR0LBIuGYLgja7vux3NZBgrdEetEylgbMKRvINLvr3azROENAA9eOKRGaOZQuZZEW7rT2CI%2FmkP88zDBvjBNNokaY26yoO0Ox5oAqw8cfh7C8Q&amp;highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO2503419712&amp;sid=search</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>1770900</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2248125</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>21% OFF</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H13" t="b">
-        <v>1</v>
-      </c>
-      <c r="I13" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K13" t="n">
-        <v>20</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>45809.67502491898</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Notebook 15,6 Hp 250 G9 Intel Celeron 8 Gb Ram 256 Gb Ssd Color Negro</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>https://www.mercadolibre.com.co/notebook-156-hp-250-g9-intel-celeron-8-gb-ram-256-gb-ssd-color-negro/p/MCO24443216?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO24443216&amp;position=21&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1479324193&amp;sid=search</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>902003</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1094000</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>17% OFF</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H14" t="b">
-        <v>1</v>
-      </c>
-      <c r="I14" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K14" t="n">
-        <v>22</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>45809.67502493056</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Notebook Hp 245 G10 R3 7330u 512gb Ssd 8gb Ram Windows 11 Ho</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>https://www.mercadolibre.com.co/notebook-hp-245-g10-r3-7330u-512gb-ssd-8gb-ram-windows-11-ho/p/MCO39243137?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO39243137&amp;backend_model=search-backend&amp;position=26&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1547113843&amp;sid=search</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>1259900</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1621375</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>22% OFF</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I15" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K15" t="n">
-        <v>21</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>45809.67502493056</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Portatil Hp 12ava Gen Intel I3 1215u Ssd 512gb Ram 8gb Color Plateado</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>https://www.mercadolibre.com.co/portatil-hp-12ava-gen-intel-i3-1215u-ssd-512gb-ram-8gb-color-plateado/p/MCO29272690?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO29272690&amp;backend_model=search-backend&amp;position=4&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1507088307&amp;sid=search</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>1458900</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1853000</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>21% OFF</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I16" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K16" t="n">
-        <v>54</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>45809.67502494213</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Portátil 2 en 1 HP Pavilion x360 14-ek1011la Intel Core i5 8 GB RAM 512 GB SSD Windows 11 Home 14" Pantalla táctil FHD</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=2isFgknxOdut9wXlQP0iITpWbs1sARTKTrjHXi%2FMHoczuv2WAdftWVdjPOA74d0RTmEsftMgUsX%2FMM9WXr3j6V%2BAGQ5AG0mIUS5JeEpPBgOTLLj9j8smzhuqpQBQjNLyVlDeYKF07dG00UJvY8tW03dkej5aTdZXNrfk3PmFZbK%2BqlohQF5UEMj%2FIOyKa%2FvLqYa6hoU6ep2lvqBBSycW%2BfOxLR%2Flue%2BMYWuzgRUO3h5oDGDSl7nsWFzlfHPZwOEL%2Brb5r1rvmQo9Owa6Q%2BZ%2FAwSwNAKAcrHhGUR5p7i3Tu35wg5iYCN95AbBBaYXr4nWFHJd9aREV%2B8eyeMpRLOmgihamWbGJfx9kbCvA3ihk8O%2ByWg7SFx5vzw5iA4j5C5uIyyJakoIXATauCzp3YpvOU4Lv%2FzfmwebiBWkcGO%2FpSNO5xV%2FsS4uUp2TekeO7nEfl6FF6Q8xYisLj8K5%2FLruUauzWaCcd6r0EOLnWcMT1VYHzWFp%2FDPpRD%2FM%2BwCTJyD0HLyRaq9o3rX%2BT2OqetnPt4fohuMeVwsb9neAnKOmZ%2B1%2BHU0aIUt%2FA3CPxA64TMmcBTWBUCXloFCybUI9ecZgtWWls40ZEJ6gGaTQSxtaMWf3ZXupuSMAtSGBF3B56W4g5CrbJQHCo1mXQudc%2B6HoSihb1jHSNpKQ05CmNdJZXA2lMG6KyWls2mkEatxNrm100RTtxcZjwjQL%2BRdsR3eo7RuAfrRnkuOwo5ghO%2F9lIq8TVPTszdCJZ6%2B9roXQXQKSqZlExdB2iI1X2ktZkJsAJu96%2BJtFu5U1DSZ%2FHj%2F660BTG0AFaY2iO75lVXam8o6kRrsJgYQlXUz7egDl%2By12SqXEPGquC1RhDls2Vkx9PXBL60XshaTSv8NAPFP6odNk%2BHBUZPdkZ%2FHXBR4dI%2FfemcTtW0L7djFRtZhGfkgQXlOBoyDkaWGqw%2FnF4Vea1ip7RDKPokO%2BIRd752yYsaCXTln0D6jU3vNsoG%2BMiz76COhTZvFRVzbQeb13%2B0BXls2OHFOjgIFgoi4GDdSGTQ%3D%3D&amp;highlight=false&amp;headerTopBrand=true#polycard_client=search-nordic&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO2859705258&amp;sid=search</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>2519937</v>
-      </c>
-      <c r="E17" t="n">
-        <v>3999900</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>37% OFF</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H17" t="b">
-        <v>1</v>
-      </c>
-      <c r="I17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="n">
-        <v>45809.67502495371</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Portátil HP 15-fc0031la AMD Ryzen 7 16 GB RAM 1 TB SSD 15.6" FHD Windows 11 Home</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=JpCyesSU7FvVnsZ5%2BL%2BzJrom0whIfM9UkilyAkynRPaHNJZmxB99RszVeXnjGIOckALEtIxHh1slZJmJJZoKnNuK5T3uMKFO2fcm3m64QAFDQ9FAFbaB6WT8kFxDzwsYdlwgcNGfhxb700tBs7NQYUX5EX81d6toSPxUzBuoudpAdd73klj7wdkOxsXIBiBduaoOFVwrFMjPui3aDRtdTlfPVgxuMdb6QizMiJWoQL5yg%2BF9SNhtPC7JQuvdGonOsHYJZCrdn%2FacVfMU0rKQQiSAO940mnjoCVoI5e%2BgGu3qnPiZL4TiiZmLWhu8BfionVN263LyNNKcLXtyfzs3rLR8Q25zjk7fIx%2B%2BDOwEEhVyz93nQpLfRyv7o65GvS4mBp5QHYMrX%2BOeDGHZXJO7dC%2Fr68BhGLKnGCvPybClst%2Brq%2BAKwgzeaFF%2Bw5qB4P0zbnzRDg3UTy0tWaJ0psAyyfnH6zS6rOQaigRFvHc%2BaJwaj3z0IONiFeRWi%2BN%2BG1GeecLJQ5Ijf0q2cU7UnVDWH2vZGmkP7WeSIlphoeTggF6D8Bqt%2F44rx2Kn8KGZAx1YM%2Buu4SD34aS%2FsomMNGRnEqUgkB4cnXNAKLAjATKp%2BwGGf8DWBGRxElZ%2FPkzlI7gfKDJyeKG%2BPw8yuMnt%2FvtZ3D0DwkEhj6xZUBksUANEVmwfzk6jxBCHoCfCcxnHLsLd%2FZ%2BqDlRr8LDIQAwUHkmPOgELwi7y0ZGkEKStk0h0MYd0jnjbrev63gap47u4m5c%2FoeDhPyjZ5Iu3%2Fb6myKcEYq8cCOwlmNTwofIUOS8s1aBVwZSXmlKHI4gLMQbGT0tFb5%2FH11Z2ejFEq6FOp9Pgy9REGbBO%2BFIqmpf%2FqYQShEUhzLWeI02lc8Aei%2FVkPhA23v4Qk5kEpNvwwZT9JKOlrY1XBykOUEeSbZUfWluYetUgLeg%2FnpxvJ9omITuzni4YJONdH5MNBlRoeQqVG2vZzo1iTuarHA%3D%3D&amp;highlight=true&amp;headerTopBrand=true#polycard_client=search-nordic&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1575771851&amp;sid=search</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>4099900</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H18" t="b">
-        <v>1</v>
-      </c>
-      <c r="I18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>5</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>45809.67502495371</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>LENOVO</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Portatil Lenovo V14 Core I5-13420h 24gb 512gb Ssd Color Negro</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>https://www.mercadolibre.com.co/portatil-lenovo-v14-core-i5-13420h-24gb-512gb-ssd-color-negro/p/MCO44279796?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO44279796&amp;position=13&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1587144125&amp;sid=search</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>1900230</v>
-      </c>
-      <c r="E19" t="n">
-        <v>2176667</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>12% OFF</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I19" t="b">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K19" t="n">
-        <v>44</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="n">
-        <v>45809.67502496528</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>ASUS</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Portátil Asus Fa506nc Ryzen 5 7535hs Rtx3050 16gb 512gb 15.6 Color Negro</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>https://www.mercadolibre.com.co/portatil-asus-fa506nc-ryzen-5-7535hs-rtx3050-16gb-512gb-156-color-negro/p/MCO45003983?highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO45003983&amp;position=9&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1544070727&amp;sid=search</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>2975814</v>
-      </c>
-      <c r="E20" t="n">
-        <v>3199800</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>7% OFF</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H20" t="b">
-        <v>1</v>
-      </c>
-      <c r="I20" t="b">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>5</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="n">
-        <v>45809.67502497685</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Potátil Portátil 14-dq0533la 14 8gb De Ram - 256gb Ssd - Intel Celeron</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>https://www.mercadolibre.com.co/potatil-portatil-14-dq0533la-14-8gb-de-ram-256gb-ssd-intel-celeron/p/MCO43485439?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO43485439&amp;backend_model=search-backend&amp;position=27&amp;search_layout=stack&amp;type=product&amp;tracking_id=f57ed311-6736-4ff6-90fb-6463ca5135c1&amp;wid=MCO1547113619&amp;sid=search</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>919900</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1185375</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>22% OFF</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H21" t="b">
-        <v>1</v>
-      </c>
-      <c r="I21" t="b">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K21" t="n">
-        <v>14</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="n">
-        <v>45809.67502497685</v>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '10 jun. 2024', 'contenido': 'Me parece muy bien por el precio pero se descarga muy rapido.', 'votos_utiles': '12'}, {'calificacion': 5, 'fecha': '03 sep. 2024', 'contenido': 'Increíble, muy buen precio, excelente calidad. Es rápida la pantalla es muy buena, buena carga, en uso continuo puede durar todo el día.', 'votos_utiles': '9'}, {'calificacion': 5, 'fecha': '26 nov. 2024', 'contenido': 'Vale totalmente la pena por su precio.', 'votos_utiles': '7'}, {'calificacion': 5, 'fecha': '09 may. 2025', 'contenido': 'Un producto, que respecto a la calidad precio, está muy bien.\nPuntos a favor:.\n1. Lapiz para trabajar, cumple perfectamente con la función, con una duracion de su bateria, aceptable, alrededor de una semana con trabajo constante.\n2. Tiene un buen sonido, claro, y con buenos decibeles, no es premium, claro está.\n3. Viene con un buen forro o cubierta, que ayuda a mantenerla seguro, y con mayor comodidad.\n4. Respecto a su software, está bien logrado, fluye con practicamente todo, obviamente no está hecha para jugar aplicativos mayormente exigente, pero para trabajos cotidianos, está excellent. Viene con un aplicativo didactico, para tomar apuntes, y hacer calculos, entre otras opciones.\nPuntos debiles:.\n1. La pantalla, puede mejorar un poco mas, no tiene la mayor iluminación, no es ultra hd, ni nada parecido.\n2. Las camaras no son para realizar videos, imagenes, o videollamadas respectivamente, tienen muy poca resolución, simplemente cumplen.\n3. La bateria si es su punto mas debil, dura muy poco, con trabajo constante, y hay que tener en cuenta, que su carga es lenta, se puede demorar 3 horas en cargar approx.\n4. Llevo alrededor de 6 meses utilizandola, y me ha presentado un par de fallas respecto al sonido, he tenido la obligación de reiniciarle, y se ha solucionado.\nBuen producto, para el que busque algo correcto a buen precio.', 'votos_utiles': '4'}, {'calificacion': 5, 'fecha': '02 dic. 2024', 'contenido': 'Excelente producto en relación precio/calidad. Ha cumplido en las tareas en que la he usado como edición de video y toma de apuntes. El lápiz funciona bastante bien.', 'votos_utiles': '3'}]</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>45809.67834960648</v>
       </c>
     </row>
   </sheetData>
@@ -2018,7 +2432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2084,10 +2498,15 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>imagenes</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>opiniones</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>fecha_actualizacion</t>
         </is>
@@ -2097,23 +2516,23 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tablet Android 13 De Última Generación 2024, 128gb+16gb-512g</t>
+          <t>Teclado Mecánico Inalámbrico Newmen Gm610 60% Rgb 61 Teclas</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=mR3PrLDqSgo6MJmSPfl2dS%2FUo8svLhnfFxnazibKtZXVeLtMP0UoQHj%2BbJpGXNSxlKHqG%2Bz%2BKAOSidbxiQcoTK05NuWlcRvCDD5MjCWB3K4C9HUUZVchWsk7LOwfTerUMIos6E4Bod3tRdbnksNVMvzKRkReGltvzXuQA4OP80tSQ%2FFqfqQAMdprKdOVzOSme4KXR9XX56enzlA9K1TQLedO%2B0F9kFSvph1R7uxsW5MW7jWiRf%2BPoby49x%2BpCOruqv5yj%2B9tHUbJnalH8OJ5XR3voCMNA9kHU8L6y1wqrGWztACnPsDE%2BCasBbrRWN9gchREW0qU9OKv%2BuGLww5%2BSJ36uhWt0xDcy0AGd7wuISgsmjonuu0iuwBYDFDKW3MFXZOYmeDhKdRKt%2Fpi%2Ft%2FK0UIHY9uP3uXwZxAXo07uP69yYoBt%2Belx5HDMuV4quOj1y1sN3ViWFAQW58MtSCxLmVKe%2BrlI0PO8iTBOvOAEmXLqZja66efrwirv2M6UN7GRAiq%2FuJIaJbFGP1RbRHVc9WHBnKgU116FRxUlaU4fqBmxlMHQm5zQUnSaeWuQx5mT9CIGbFbRPMnYbfB7kUYAu4rD5kM6aEZWf3Ni2UVNvIWwwJDfUpaM5BzlLBqz5BBZdXBryopAeHgbuPH0pOiaroIVG4%2FWtkVM71Oo0KPyntc4XJ7fdS29V9Lzr72Sy9fsrUoBNz%2F0wy043vszx3X33tO%2BdhSCxi2xTwVxlfRG%2BulrO5fI6zhEysUKUMoOSBp6FW7L2xHBV6T3rEGW%2FEVfTvOkcfq3enYpcYEgD7xICHEiR3bGSjNrfXW1rRTtjOZEkDD6eHD1V3cNKSMMGgQ1hZU3OCnKXIH9%2F42zw5gQcxTgMfKqjOF2qDFeD%2BffmpGaDFBpLlp9Ol48TnLxRDKW60kFs5OzwPl2j3mh98s4WXRRJUts4%2FaSqxXaZGA869tYGdY%3D&amp;highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=de599f53-e149-4e6e-87ca-312bb77ee567&amp;wid=MCO2840069126&amp;sid=search</t>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=6gGtzBLavbK6QT%2FHNpbmv4xJiCt5aKMxBqNom0ChA44NtPEmuvAI%2Bd%2F6wZ5bJEEzHJr5DnaUPSSbXsA27RKEa9B2aGtGEO0TsJfkfy%2BAxjueSxf%2Bb63DYr8jbEaPbuHXO%2B5hpSgqQj9g65y8837ovhh%2FLr824TMjzjtbqPPd1LhEsdCYo22TnDqIeTtfDnpv%2FtmlNqz637XVhPscnSGmouUrSXmqrjeiCPDnf9KVlls8EDsrjF6s%2FERJT5%2BzF0fY%2BttMYUcQwgDnN1mOlZZlKQBr4sMtGrWiG8OFpv3c5EpaylXa%2FBdBvq0jhw70H0oSxSxvb5cuBpONRrhOyv4yPwuTc66azMz98G5fX8C7KZF7EeV99fWGhMOdqwMYvMam8gmrw2AZbdNRtAywmoN06LhUPPXLSsM5kUKroJuLUM3VAkVh5zRqQl%2FQIyXSGPcU5D0nva18v1VGvdIwqwfh0Ibf9JkqBEaIGeZn%2B40QC5od%2Bjf0ozYJOAVdaA8WvEwj%2BOWRrMKdheFNCYVp7FSXsnuyEEYCYT8c%2BbHZ9DLdBMTVctfuHGmPhsO06wVqqTA5Y9fxJHdJBiSPDU5UmhG7ISvZHMV8sxffBRRUzlfKORPzCa8A6pK5AQQRfjBoRFsl6wSRBx8J4hW%2BkAQSay2F6gt1pVQXmsmhXspXlNdWknhJY2OhJ9MCfhbJ91LuskxMN00efWb6svoHLy7UXfl6CJqma5A6SUsiBa%2BKC%2FErjG6jRQrzTjmECxwEUl9YdmtjbYMdwwtDSGKR6Q5JunQwTqCRCplf%2FAWojZHys7g2isSZ2GvCIsWBEAbpoUVJcToj87qK1lwTBs6zEde6g8iRNugxlwcuSepuSFkKENccA3ZAs4Y3wZOlkfOr2xC%2BxxbvOb00Ed6IwFkjIrpK0lfUyePM9tiooSvD8Imm2h7b8Ayff8r0mq9HUCBj%2FrCUw2tA&amp;highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=d5bd1a16-2a63-481d-ab07-d7b9f14f3457&amp;wid=MCO2573729598&amp;sid=search</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>907200</v>
+        <v>144415</v>
       </c>
       <c r="E2" t="n">
-        <v>1120000</v>
+        <v>169900</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19% OFF</t>
+          <t>15% OFF</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -2127,49 +2546,52 @@
       <c r="I2" t="b">
         <v>0</v>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>4.9</v>
+      </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_942311-MLA82998654053_032025-V.webp</t>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_940676-MLU77417106611_072024-V.webp</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="n">
-        <v>45809.67834956018</v>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_940676-MLU77417106611_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_987647-MLA82113006950_022025-F.jpg', 'https://http2.mlstatic.com/D_NQ_NP_2X_756226-MLU78420919739_082024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_708773-MLA84456438700_052025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '13 sep. 2024', 'contenido': 'Es un producto hermoso, recomiendo instalar el firmware desde la pagina oficial según como indica el manual, arregla un conflicto con varias teclas. También recomiendo poner el idioma del teclado en el pc como ingles us para que no hayan problemas. Siguiendo los pasos que les acabo de mencionar el producto es maravilloso. Lo mejor que se puede conseguir calidad precio. Pdta toca acostumbrarse a dar un comando para usar las flechas y no tiene la tecla ñ.', 'votos_utiles': '8'}, {'calificacion': 5, 'fecha': '09 oct. 2024', 'contenido': 'Extremadamente bueno, una compra que uno no se arrepiente lo recomiendo.', 'votos_utiles': '3'}, {'calificacion': 5, 'fecha': '09 dic. 2024', 'contenido': 'Me gustó, las orientaciones de los usuarios sirvieron mucho … fácil de instalar , dejarlo en opción inglés y para la tilde o ñ se coloca en español … las luces del teclado súper , recomendado !!!.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '31 may. 2025', 'contenido': 'El teclado muy bueno para su precio. La verdad no estaba esperando mucho sino que funcionara bien y fuera cómodo al tacto. A la final ha superado mis expectativas. Muchas gracias.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '27 may. 2025', 'contenido': '', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>45809.68173760417</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>HUAWEI</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tablet Para Niños Huawei Matepad SE 11 Kids Edition Gris 4+128gb + Lápiz</t>
+          <t>Teclado Gamer Mecanico En Español Retroiluminado Con Cable Usb Xtrike Me Gk988 Para Computadora Pc Con Luz</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=47Z74mPwkVy%2F%2BMV8XPeMyih7b4R7yH9gPlALeIw9jt4Itbq4%2BLZgoHGJIOjfh5tnGkwaBBmynXnKO5SQKoDtICbWMU6ADAP9p%2B06BcnngTuLz9t8Sts1JZX%2FEqbMeXKZMumNuLpFVk3z%2B2hga%2BO7ef4VXEAesOLY6d6iof5oFV2n2qV%2Fyjm6P5v%2BCSN76VU8R3p3pncS%2FaaCgwm7Eyt1NIa8lgQKC2iQ9C%2Bls05ZmjXHM0W3FWzNvSLwBwfx31JlMjR%2BQxsCXp1yT1b4A%2F1hJm8W5LCxD4G5Bqmx0IoWP0AF4o4%2FnHu3OY%2F6Feol0Lc4IT%2FWpZOi%2Brefoj7m7hMQD5R9BblTUpbWYlhnfHVZtz8ue5GbWbawmrDAznawKmRKsCBKPB0Sr3AUa0aZLXIZI8wAqblP7OV4%2BC3SqSBPLE9N848u9d1y2l0Re2%2B6PdX4NTx02zi0rHikFGGCBI0o4BZBZQERax2m1rCMmnChGVx3yr1LD%2FPIDy%2FWxeIcVG1AKq6GngTy1JYr%2BReR2sCDsHb7WAmn%2BqKHvCwAJYl6%2F3o5rY%2F2EYQ%2FCl61NKwtsqSjSMlAOpcEuEpSxCc7HuX1GWddDk39LGmfkcgXZ4sRJWzgVBceBkNouFvp2DrcmRzazdJyCH%2FjXY9srSMpdGHteCD6Ebqy%2FVXOanbn4rjy5aTL570xthAX2b0N9ZCSrJgE1vMcurWvuCYOrpL8gFASiNzAI26PD2UrvCJdJeE%2FqtdSdvaXhrmtsuPu0NVgu5W0gm5sEcfYFyPlB65xBVCDfelKwFW2H6xt533wWKDoWxfhq7ugSU4WOQm1WGxGROqz%2FihShH5P1WuEUxEeYigqmPEd6BC2F90Vw20e7K2MZEM9dFJDO1v0YrQeox8mc4v2yqCUeE%2B1xQ6aZx3aA%2Fds0%2B%2BNjH5HZKvYf8rnbiWieZ58VEC3wwD24m4y62PpliSga4%2Fay5oi0F4%3D&amp;highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=de599f53-e149-4e6e-87ca-312bb77ee567&amp;wid=MCO2836671066&amp;sid=search</t>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=f%2F2y0a41zS%2FCSk3LHoy1FmCIOd3IXjkIc4zrxquwe11mnEs31DNrGs4s5WGrbswIcV9mcJMF42%2F%2FNXENqgyu%2FlQzWscGtdgGm5pc%2B4n1Mt2puld%2B2kCs6YlAYLN7ouABMzMjt%2F0MYeuzXcRO5DM9XfBU8IqWp9tAW3BFhiBnyl8%2FEcst8TuhHvi2lI%2BYgB8c9M0z98WMPpnCrYD80Sdi2iGnAb4xjTGp5qvj7foeTG%2FxBA6vSiEBLE7x2UlQ5Ml3lWzVVIV4vKuU%2BhwsQeqCbXkZF352uL4OCafSvy3oYmZxbvVKS4JXJUP3BVDLkKpIWr3Xqhn3LVG6gKoQAPlvIOQsjYpRCm6cg1kks2jGkl8Ww2owqqEFRTdb7EDuWwfZx8mOZeMIAZ4Hg1IxyPhjLXQ%2FdkUJky0iTAWe1OFTOxT1evOPhkW3GPSk721VWfZi84JlxLNJM8j87%2BqEhX5aO7rSB662JU%2BxI9EfURh6WoqdG19xLTWj4WcEVGELrCM7oYoYwyBxEFcuVP9iUiljdTIuHScEneuLOOWeyvSpZ2NoUOEUAikCrQW7X%2FiDWTIZgdyzRusJ%2BIJx3BpsuUWAEbWZoOIQMXAztgzgmtR1AELcUYbBQ7vV9HSAwbZsoj2AJxmLku7N6X1okzof6Fpbdtwe9Hbopr1YSWTf1zWCM6IwMRXXbmsXBZtKQfwi4Pk6KJGj4HXWS02mdU5DGAOgcok5du2bgnYgo8NMgHPAOWvmmlcnd85ssCEg9fKKkcMjGWbETWPSh7xiDsGnSXXwTNNXK8GMp94WkD8bjcDXGq8mL8n1bt717kIG8rEnssoov07dc1xhHx0%2FlVtteyt8LTFvmsiiMpKZzXqV3he5op527UBvZsM2U9QaHewKaBvicFrw%2FTMjgedgArbI43oicXIeLU61Oshp5Tg8FOSkOaz2yD%2FKLgOF86LVMyp%2FsVQ1vs%2FBsIAonsMEK38835kntHbMho%2FMJb2hEARHJajFWEaHs7iZ0y9oh%2Fse2pcNlrw%3D&amp;highlight=true&amp;headerTopBrand=true#polycard_client=search-nordic&amp;tracking_id=d5bd1a16-2a63-481d-ab07-d7b9f14f3457&amp;wid=MCO1560382775&amp;sid=search</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>678932</v>
+        <v>104900</v>
       </c>
       <c r="E3" t="n">
-        <v>999900</v>
+        <v>149900</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>32% OFF</t>
+          <t>30% OFF</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2184,46 +2606,51 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_973583-MLA83472189647_042025-V.webp</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>[{'calificacion': 5, 'fecha': '14 may. 2025', 'contenido': 'Realmente pensado para los pequeños.', 'votos_utiles': '0'}]</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>45809.67834958334</v>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_973583-MLA83472189647_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_833541-MLA80825743061_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_820938-MLA80563766270_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_760094-MLA80563785792_112024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '01 may. 2025', 'contenido': 'Contento con el producto.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '28 abr. 2025', 'contenido': 'Es una buena opción por el precio, cumple con lo que promete perfectamente, se siente de buena calidad y al responde bien, recomendado.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '31 may. 2025', 'contenido': 'Bastante bien calidad precio:) lo recomiendo!(es algo ruidoso) perfecto para competitivo.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '23 may. 2025', 'contenido': 'Se ve excelente, me gusto mucho.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '22 may. 2025', 'contenido': 'Cumple con todo. Muy buen producto.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>45809.68173762732</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tablet Xiaomi Redmi Pad Se 8gb 256gb Gris</t>
+          <t>Teclado gamer Redragon Kumara QWERTY Outemu Red español España color negro con luz rainbow</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.mercadolibre.com.co/tablet-xiaomi-redmi-pad-se-8gb-256gb-gris/p/MCO29219683?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO29219683&amp;position=4&amp;search_layout=stack&amp;type=product&amp;tracking_id=de599f53-e149-4e6e-87ca-312bb77ee567&amp;wid=MCO1567332181&amp;sid=search</t>
+          <t>https://www.mercadolibre.com.co/teclado-gamer-redragon-kumara-qwerty-outemu-red-espanol-espana-color-negro-con-luz-rainbow/p/MCO19518470?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO19518470&amp;position=3&amp;search_layout=stack&amp;type=product&amp;tracking_id=d5bd1a16-2a63-481d-ab07-d7b9f14f3457&amp;wid=MCO1347087050&amp;sid=search</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>709900</v>
+        <v>190900</v>
       </c>
       <c r="E4" t="n">
-        <v>1149900</v>
+        <v>199900</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>38% OFF</t>
+          <t>4% OFF</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2241,7 +2668,7 @@
         <v>4.8</v>
       </c>
       <c r="K4" t="n">
-        <v>298</v>
+        <v>2285</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -2250,38 +2677,39 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>[{'calificacion': 5, 'fecha': '26 jul. 2024', 'contenido': 'La tablet es demasiado rápida, corre juegos con facilidad y su pantalla es muy buena. Le verdad me sorprendió lo bueno que corre los juegos y las aplicaciones.', 'votos_utiles': '13'}, {'calificacion': 5, 'fecha': '08 jun. 2024', 'contenido': 'Excelente compra. Una tablet de calidad,buena construcción e increíble apariencia. Definitivamente otro gran producto de xiaomi.', 'votos_utiles': '8'}, {'calificacion': 5, 'fecha': '29 ene. 2025', 'contenido': 'Súper me gustó mucho , apenas para lo que necesito 😊.', 'votos_utiles': '6'}, {'calificacion': 5, 'fecha': '30 dic. 2024', 'contenido': 'Genial.', 'votos_utiles': '3'}, {'calificacion': 5, 'fecha': '17 feb. 2025', 'contenido': '', 'votos_utiles': '3'}]</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>45809.67834959491</v>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_636746-MLA52350707355_112022-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_913394-MLA52350707356_112022-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_994079-MLA52350716250_112022-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_912260-MLA52350716251_112022-F.webp']</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '08 may. 2021', 'contenido': 'Panas yo lo veo bien xd, tal vez sería mejor si las luces fueran más brillantes pero de resto llevo 1 mes con el y todo gucci, todo bien todo correcto además me regalaron unas teclas de cambio :) uwu.', 'votos_utiles': '56'}, {'calificacion': 5, 'fecha': '14 jun. 2023', 'contenido': 'Me encantó llevo más o menos 1 año con el producto y no ha presentado problemas, se escucha bien y se ve bien 😎.', 'votos_utiles': '35'}, {'calificacion': 5, 'fecha': '17 ago. 2023', 'contenido': 'El producto es bastante bueno en calidad-precio; cositas que no me acabaron de gustar, pero que son de menor importancia para mi son que algunas partes de las teclas (ej. Bloq mayús) que no se iluminan completamente, no tienen switches brown para comprarlos con el teclado, las patitas de goma antideslizantes no son las mejores, el teclado se tambalea un poquito aunque no se si es mi escritorio o el teclado (con el manual en una esquina se arreglo), de resto es un buen teclado, los materiales en acero para la placa y el "plástico reforzado" están decentes, el cable no es mayado, pero tiene el conector usb en oro chapado (creo que así se le dice xd), es hotswap, por si le quieren poner otros switches, la retroiluminación es decente y algo que me parece vital, pero no tiene, es que el conector no es removible, en general lo recomiendo si no hay mucho dinero para gastar y cuando ya se tenga el set-up bien armado cambiar el teclado o dejarlo.', 'votos_utiles': '12'}, {'calificacion': 5, 'fecha': '26 jun. 2021', 'contenido': 'Bastante bueno, la verdad tanto el tacto como el sonido me gustó demasiado, es bastante bonito gracias al color rojo que arroja el teclado por defecto, es algo pesado lo que hace que sea difícil moverlo sin querer lo cuál es genial, es tenkeyless lo que hace que te quede bastante más espacio del que uno cree que le va a quedar y la verdad estoy tratando de hacer la reseña larga porque es bastante cómodo escribir con este teclado.', 'votos_utiles': '10'}, {'calificacion': 5, 'fecha': '07 sep. 2023', 'contenido': 'Lo recomiendo, excelente producto ☺️ buen material.', 'votos_utiles': '7'}]</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>45809.68173763889</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>LENOVO</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tablet Lenovo Tab K11 4g Lte 8gb 128gb Teclado + Pen Color Luna Grey</t>
+          <t>Teclado gamer Redragon Kumara QWERTY Outemu Red español latinoamérica color negro con luz RGB</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.mercadolibre.com.co/tablet-lenovo-tab-k11-4g-lte-8gb-128gb-teclado-pen-color-luna-grey/p/MCO45442884?highlight=true&amp;headerTopBrand=true#polycard_client=search-nordic&amp;searchVariation=MCO45442884&amp;position=5&amp;search_layout=stack&amp;type=product&amp;tracking_id=de599f53-e149-4e6e-87ca-312bb77ee567&amp;wid=MCO1529700467&amp;sid=search</t>
+          <t>https://www.mercadolibre.com.co/teclado-gamer-redragon-kumara-qwerty-outemu-red-espanol-latinoamerica-color-negro-con-luz-rgb/p/MCO19472215?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO19472215&amp;position=4&amp;search_layout=stack&amp;type=product&amp;tracking_id=d5bd1a16-2a63-481d-ab07-d7b9f14f3457&amp;wid=MCO1483729915&amp;sid=search</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1094900</v>
+        <v>190900</v>
       </c>
       <c r="E5" t="n">
-        <v>1899900</v>
+        <v>198000</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>42% OFF</t>
+          <t>3% OFF</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2296,10 +2724,10 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="K5" t="n">
-        <v>13</v>
+        <v>2285</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -2308,31 +2736,32 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>[{'calificacion': 5, 'fecha': '15 may. 2025', 'contenido': 'Exelente producto calidad precio. Lo recomiendo totalmente.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '08 may. 2025', 'contenido': 'Bonita y económica.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '30 abr. 2025', 'contenido': 'Muy buena y muy práctica.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '03 mar. 2025', 'contenido': 'Es muy buena.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '10 feb. 2025', 'contenido': 'Excelente!.', 'votos_utiles': '0'}]</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>45809.67834960648</v>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_864807-MLA77594879101_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_625461-MLA75686545678_042024-F.jpg', 'https://http2.mlstatic.com/D_NQ_NP_2X_867951-MLA77594879095_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_750884-MLA77378571910_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_845414-MLA77378789172_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_901847-MLA77378571898_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_804807-MLA77378808744_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_909019-MLA74488153000_022024-F.jpg']</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '08 may. 2021', 'contenido': 'Panas yo lo veo bien xd, tal vez sería mejor si las luces fueran más brillantes pero de resto llevo 1 mes con el y todo gucci, todo bien todo correcto además me regalaron unas teclas de cambio :) uwu.', 'votos_utiles': '56'}, {'calificacion': 5, 'fecha': '14 jun. 2023', 'contenido': 'Me encantó llevo más o menos 1 año con el producto y no ha presentado problemas, se escucha bien y se ve bien 😎.', 'votos_utiles': '35'}, {'calificacion': 5, 'fecha': '17 ago. 2023', 'contenido': 'El producto es bastante bueno en calidad-precio; cositas que no me acabaron de gustar, pero que son de menor importancia para mi son que algunas partes de las teclas (ej. Bloq mayús) que no se iluminan completamente, no tienen switches brown para comprarlos con el teclado, las patitas de goma antideslizantes no son las mejores, el teclado se tambalea un poquito aunque no se si es mi escritorio o el teclado (con el manual en una esquina se arreglo), de resto es un buen teclado, los materiales en acero para la placa y el "plástico reforzado" están decentes, el cable no es mayado, pero tiene el conector usb en oro chapado (creo que así se le dice xd), es hotswap, por si le quieren poner otros switches, la retroiluminación es decente y algo que me parece vital, pero no tiene, es que el conector no es removible, en general lo recomiendo si no hay mucho dinero para gastar y cuando ya se tenga el set-up bien armado cambiar el teclado o dejarlo.', 'votos_utiles': '12'}, {'calificacion': 5, 'fecha': '26 jun. 2021', 'contenido': 'Bastante bueno, la verdad tanto el tacto como el sonido me gustó demasiado, es bastante bonito gracias al color rojo que arroja el teclado por defecto, es algo pesado lo que hace que sea difícil moverlo sin querer lo cuál es genial, es tenkeyless lo que hace que te quede bastante más espacio del que uno cree que le va a quedar y la verdad estoy tratando de hacer la reseña larga porque es bastante cómodo escribir con este teclado.', 'votos_utiles': '10'}, {'calificacion': 5, 'fecha': '07 sep. 2023', 'contenido': 'Lo recomiendo, excelente producto ☺️ buen material.', 'votos_utiles': '7'}]</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>45809.68173765046</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>LENOVO</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tablet Lenovo M11 128gb 8gb Ram + Lapiz 10.9 Pulgadas Color Negro</t>
+          <t>Teclado gamer Redragon Mitra QWERTY Outemu Blue español latinoamérica color negro con luz RGB</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.mercadolibre.com.co/tablet-lenovo-m11-128gb-8gb-ram-lapiz-109-pulgadas-color-negro/p/MCO36109372?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO36109372&amp;position=8&amp;search_layout=stack&amp;type=product&amp;tracking_id=de599f53-e149-4e6e-87ca-312bb77ee567&amp;wid=MCO1501072863&amp;sid=search</t>
+          <t>https://www.mercadolibre.com.co/teclado-gamer-redragon-mitra-qwerty-outemu-blue-espanol-latinoamerica-color-negro-con-luz-rgb/p/MCO15079758?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO15079758&amp;position=9&amp;search_layout=stack&amp;type=product&amp;tracking_id=d5bd1a16-2a63-481d-ab07-d7b9f14f3457&amp;wid=MCO1505508309&amp;sid=search</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>874900</v>
+        <v>279900</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -2353,7 +2782,7 @@
         <v>4.9</v>
       </c>
       <c r="K6" t="n">
-        <v>167</v>
+        <v>68</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -2362,11 +2791,307 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>[{'calificacion': 5, 'fecha': '10 jun. 2024', 'contenido': 'Me parece muy bien por el precio pero se descarga muy rapido.', 'votos_utiles': '12'}, {'calificacion': 5, 'fecha': '03 sep. 2024', 'contenido': 'Increíble, muy buen precio, excelente calidad. Es rápida la pantalla es muy buena, buena carga, en uso continuo puede durar todo el día.', 'votos_utiles': '9'}, {'calificacion': 5, 'fecha': '26 nov. 2024', 'contenido': 'Vale totalmente la pena por su precio.', 'votos_utiles': '7'}, {'calificacion': 5, 'fecha': '09 may. 2025', 'contenido': 'Un producto, que respecto a la calidad precio, está muy bien.\nPuntos a favor:.\n1. Lapiz para trabajar, cumple perfectamente con la función, con una duracion de su bateria, aceptable, alrededor de una semana con trabajo constante.\n2. Tiene un buen sonido, claro, y con buenos decibeles, no es premium, claro está.\n3. Viene con un buen forro o cubierta, que ayuda a mantenerla seguro, y con mayor comodidad.\n4. Respecto a su software, está bien logrado, fluye con practicamente todo, obviamente no está hecha para jugar aplicativos mayormente exigente, pero para trabajos cotidianos, está excellent. Viene con un aplicativo didactico, para tomar apuntes, y hacer calculos, entre otras opciones.\nPuntos debiles:.\n1. La pantalla, puede mejorar un poco mas, no tiene la mayor iluminación, no es ultra hd, ni nada parecido.\n2. Las camaras no son para realizar videos, imagenes, o videollamadas respectivamente, tienen muy poca resolución, simplemente cumplen.\n3. La bateria si es su punto mas debil, dura muy poco, con trabajo constante, y hay que tener en cuenta, que su carga es lenta, se puede demorar 3 horas en cargar approx.\n4. Llevo alrededor de 6 meses utilizandola, y me ha presentado un par de fallas respecto al sonido, he tenido la obligación de reiniciarle, y se ha solucionado.\nBuen producto, para el que busque algo correcto a buen precio.', 'votos_utiles': '4'}, {'calificacion': 5, 'fecha': '02 dic. 2024', 'contenido': 'Excelente producto en relación precio/calidad. Ha cumplido en las tareas en que la he usado como edición de video y toma de apuntes. El lápiz funciona bastante bien.', 'votos_utiles': '3'}]</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>45809.67834960648</v>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_602205-MLA74652847384_022024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_773066-MLA52988770867_122022-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_860664-MLA52988782788_122022-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_944519-MLU73115284216_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_781580-MLU75321470327_032024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_694460-MLU70065260095_062023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_810307-MLU75321420641_032024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_853829-MLU75321391561_032024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_742900-MLU75174250074_032024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_791595-MLU73115624998_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_920640-MLU73115625028_122023-F.webp']</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '07 ago. 2022', 'contenido': 'Feliz con la compra, pedí outemu rojo, que son los clips del teclado. Estos son silenciosos y más suaves que el outemu blue.\nA mí me gusta el teclado silencioso por eso preferí outemu rojo.\nEl teclado tiene retroalimentación de calidad, y se siente la calidad del teclado. Con teclas inborrables porque son de doble inyección.\nMuy feliz con el teclado 100% original. Gracias.', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '20 jun. 2022', 'contenido': 'Es un gran teclado, de muy buena construcción y robusto, sin embargo en la publicación dice que vienen con unos switches outemu blue, y vino con unos switches de color rojo de los cuales no se exactamente la referencia. Aun asi me siento conforme con el funcionamiento de este y lo recomiendo.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '06 ene. 2022', 'contenido': 'Buen producto relación calidad precio.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '09 abr. 2024', 'contenido': 'Se ve de muy buena calidad se nota q es de buena construcción espero q dure.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '14 may. 2025', 'contenido': 'Me gustó mucho el producto, bastante sólido se siente de buena construcción y buena calidad, sensación agradable al momento de pulsar las teclas y buena retroiluminación en cada una de las transiciones, recomiendo el producto totalmente.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>45809.68173766204</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LOGITECH</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Logitech G413 Se, Teclado Gamer Mecánico Retroiluminado Led Color del teclado Grafito Idioma Inglés</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=1%2BmSDuFEjeCjf5EyjYdV5LjMfAU5owNLHEYv3ks1VKpD0Gs0zZTvdlXGVSqVU2xg%2BncfChY%2BC%2BAAHw37%2F7v%2BEifMiSaJ4p17K3K5XrAXV2HEQv4MYSAql9TGf%2BB9VigDzre5GPNO5v%2F6zUHVGeGXBAb0ww3SZNZsWxcpGcVvIrsd%2FB9RcBs9oHxqv3cI0u2A5f1D5XAcqNDhSB9Ee4tEbShrr0kTBMcGviYSNFBtDMz24KVROBy2GoNoJRTiQzllPVlRY7ZFeIEpVsPwAaYH9fjbFmfU1V5gIZRyKCcxbMScmI71XEgfLilHueoqznPDxM7jHKWZ2mZ8aUMBsW1go4M%2BS3pz44v947MELQdtLTgQZmaOj%2BuRTaK%2FwUJXPB8Ry7l5DOsn%2F5jAlDBrvrDctWkiX2gjoBGot4qHPrJUmglwGID9XabLA%2BDt7KHqJGp0hr8VITlYrO%2FPZwzKfHZwjmqHiPz2iCHepwmXYahnElJoJU8vPqD4mYPua4sSpdiVjfFeAJVVaY6dNadGNXQFdg9EFp5qQ70oXeooPtemL%2BeSjOppfN32ZF%2FYvi1VLZj%2FqkJ1I3UrOHMwwK7IKWHRbWo1C%2FEzAIFqJnqtFRB9MBTDNV2sYdKHQUvdBD7M2P5BRlPeLcQwrh%2BFd3iLqI0e3M4c0COGIs3IIRgUI4IqrBkPWIYO9rePq%2FkwQYpAaIKtMU3poo3JeH%2BbjxHSm3nVpXlKa1rtDmwj2QtiGEhfDa6AX5g%2BzB28X5ZI2r9LSLsbjH1sQdIrBOcQd0uL1Uq97ZWs5JnwPo0oxbkLpeoYVi%2BubPo84aEBdcP0PA225XXI8efe9qSlN4UBfKvI3TgcbAYEua9Xjg8StyPoaG0LTgtFNSSiRFv2fJ7sswbMuBh3imQ2D1nexgmFmkMUgmqsQ12vs2iYADEwmMNaRsnWbesp6x1MIVUPFtuV%2FlBIVhkKCsB2wh39b7M9ZBk%2B3ruWNCHYUzP%2Fjs6rP%2F7GdfF5ZEt3OhCbmUVb&amp;highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=d5bd1a16-2a63-481d-ab07-d7b9f14f3457&amp;wid=MCO2855290132&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>357135</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K7" t="n">
+        <v>11</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_942664-MLA84857255411_052025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_831940-MLA84724971460_052025-F.jpg']</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '06 mar. 2025', 'contenido': 'Es un 10/10.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '26 dic. 2024', 'contenido': 'Excelente teclado, super rápido paea video juegos muy bueno.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '16 sep. 2024', 'contenido': 'Muy buen teclado, excelente para el gaming.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '11 sep. 2024', 'contenido': 'Con respecto al producto era lo que esperaba, con respecto a la transportadora sé que "envia" es económico pero en muchas áreas del territorio nacional es pésima transportadora, se recomienda cambiar.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '07 jun. 2024', 'contenido': 'Es un buen producto suave silencioso buenas y faciles de combinación del teclado para juegos súper rapido.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>45809.68173767361</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Teclado Mecanico Gaming Premium Tkl Rgb - Blue Switches</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=raxnTiIOfaJGLihafXujD1LfKau1fJt4%2BALVI8%2Bbs57gk4gn%2B0x02l14%2Bit8M7USHQqk8J23Vd7Ela7IruCNXs6Ba7umN1djjbgLKGjPph%2FmF0UKdIhSJWpwIuISvLU34eiNhA2Qz8W8vi%2BClW5rR%2F0zqyi%2BIsWNQ59tjuM%2F8Gy%2F%2F7AcRkW%2BxaQdc52oU37aDBgoxAlqLbTnIYPAkZNeXB2ASeKhGCYMSzORUQFu64NWzbj9X1Ewu69jq6ytRR9tG6BySZ7PqESZlYHXuPWqq3pZy9K740WAlK7N4kMTSHfEht9Pjnm8HkwzsLtvdd1AXZwLRGpirSldH8IrIB29Y6UJlPjl3qcDT%2FHFEV79Rcd7KnS2%2BmNHhRXL9%2F9O03fL4Wur5GvRHtOZPKvRWbWQJLOX595%2FB5tE5CaMf%2BIpmx0rndZOd1aiQMjhEqB0aSnucvngxtVhTqF92xNEu5bSFN5K01hGjQrrYP7qMQ3bmZLdf%2BUzu4wY0qXiYppVcagqcgMKXyyX838k%2FOcuHMCbq7u3O1V%2FbcOqATG8%2FGY909oLtZoV8TvvTOLAV3XjKqNcM%2F1CK83TDb%2FLDBqaYwjB1d3P9dYp0gsnR4jszJnY2jL0ut6oC6Xon8cEjx9jngDpHKfXeKwM%2B6F%2BCFahWXIxzXkcPfV9KIt5nnys%2BEUwxIin993%2FQ4A01WoeagLTABfk2aj2qSMnwP9LIcOvSNEN73fiDov8%2BWR3M%2FCr46AOOfjYcmr2zxiJK7iwJIvoLfyCIzxJWMDPQsihVf6rA2HN6Z6xoDV%2BvzNy7xWBKqOwbxao2uHS%2F8VWRTvzzyA4eZ%2BXuJiTc4eoEDCtpt0VMnnYK0TmNxKNAZr%2FVucsswAhmzh5S%2FYS4gm5wQ3Y33jkQQOIZZUFvSLFK135iqeKhujn19FufKQtndb5FpMSBuhgJ1GVQMMoQb%2FvQ0x9&amp;searchVariation=175176005934&amp;highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=d5bd1a16-2a63-481d-ab07-d7b9f14f3457</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>107920</v>
+      </c>
+      <c r="E8" t="n">
+        <v>134900</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>20% OFF</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>9</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_713856-MCO83310185804_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_906560-MCO83311522676_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_629139-MCO83311522714_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_952983-MCO83603556415_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_729467-MCO83603556433_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_862622-MCO83311591058_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_649367-MCO83311591070_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_879923-MCO83327889878_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_835523-MCO83311591120_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_837709-MCO83603556513_042025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '21 may. 2025', 'contenido': 'Suena muy lindo y tiene muchos modos de colores, puedes ponerlo solo rojo y varios colores también tiene multicolor a la vez 🥰🥰.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '13 may. 2025', 'contenido': 'Excelente, recomendado 100%.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '31 may. 2025', 'contenido': 'Es un excelente teclado mecánico, tiene una configuración sencilla de las luces de fondo, también trae para personalizar macros en algunas teclas, tiene un sonido aceptable. Es un poco pesado en comparación con otros, muy estético y trae mucha variedad de configuración de luces.\nLo recomiendo mucho si te gustan los teclados mecánicos al 65% para ahorrar espacios.\nDe muy buena calidad.\nVale la penam por el precio.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '29 may. 2025', 'contenido': 'Tremendo, para su valor. Muy bueno. Eso sí, suena un tris duro.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '28 may. 2025', 'contenido': 'Es sorpréndete la calidad que tiene para lo barato que es, la sensación, las luces, el sonido. Es magnifico! 10 de 10.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>45809.68173768518</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Teclado Gamer T-dagger Arena T-tgk321 Qwerty T-dagger Brown Español Color Negro Con Luz Rainbow</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/teclado-gamer-t-dagger-arena-t-tgk321-qwerty-t-dagger-brown-espanol-color-negro-con-luz-rainbow/p/MCO25354558?highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO25354558&amp;position=13&amp;search_layout=stack&amp;type=product&amp;tracking_id=d5bd1a16-2a63-481d-ab07-d7b9f14f3457&amp;wid=MCO1435132381&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>149900</v>
+      </c>
+      <c r="E9" t="n">
+        <v>214143</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>30% OFF</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K9" t="n">
+        <v>111</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_829971-MLU72637468711_112023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_846613-MLA79492165647_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_815620-MLU74161826881_012024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_916860-MLU72566191648_112023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_980831-MLA79491981591_092024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '04 feb. 2025', 'contenido': '', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '25 oct. 2024', 'contenido': 'Muy lindo y comodo.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '22 ene. 2025', 'contenido': 'Me parece un exelente producto precio calidad. Los materiales son bueno y el silencioso, me encantó recomendado.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '22 ene. 2025', 'contenido': '', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '25 abr. 2025', 'contenido': 'Un muy buen producto calidad precio, el teclado es bastante silencioso lo cual es perfecto para mí, también es muy cómodo pero tiene dos cositas que no me gustaron.\n1) entiendo el tema de 60% y la combinación de teclas con el fn pero un teclado de este tamaño necesita por obligación un software de configuración de teclas propio prácticamente no se pueden usar las flechas ya que si das fn + w vas a bloquear wasd como flechas de movimiento pero a su misma vez fn + w es flecha arriba si yo solo quiero ir hacia arriba en un texto voy a tener que darle dos veces por lo que va a subir dos veces el cursor en resumen esa combinación me aprece que está mal y no se puede cambiar.\n2) se escucha un poco el rebote de las teclas cuando se usan muy rápido pero esto puede ser tema de los switches a lo mejor con una lubricada se quite pero de fabrica puede ser un poco molesto.\nPero en general es un muy buen teclado cumple exelente su función ya llevo un mes con el usando todos los días y nunca me deja tirado lo recomiendo.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>45809.68173769676</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Teclado Mecánico Gaming Redragon K636clo Rgb Color del teclado Negro Idioma Inglés US</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/teclado-mecanico-gaming-redragon-k636clo-rgb-color-del-teclado-negro-idioma-ingles-us/p/MCO29039269?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO29039269&amp;position=14&amp;search_layout=stack&amp;type=product&amp;tracking_id=d5bd1a16-2a63-481d-ab07-d7b9f14f3457&amp;wid=MCO2772382820&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>210028</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K10" t="n">
+        <v>137</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_674064-MLU73503205759_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_943483-MLU73411990606_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_651951-MLU73411990618_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_758706-MLU73503205777_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_988320-MLU73502811109_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_891015-MLU73502870103_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_742169-MLU73411931788_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_723670-MLU73503225631_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_629594-MLU77910155149_072024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '02 mar. 2024', 'contenido': 'Excelente producto, muy bueno, hace falta revisar las macros pero cómo quedo configurado con solo conectarlo estoy feliz. Todas las teclas funcionan a la perfección.', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '07 nov. 2024', 'contenido': 'Muy bueno, silencioso, suave y práctico, funcionando perfectamente.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '30 abr. 2024', 'contenido': 'Muy bonito exelente producto lo recomiendo 🔥🔥🔥.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '25 may. 2025', 'contenido': 'Justo lo que estaba buscando, por el precio esta muy bien.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '04 abr. 2025', 'contenido': 'Excelente. Viene con las herramientas para cambiar las teclas. Un producto muy completo y estético, sobre todo por el precio!.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>45809.68173770834</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Teclado Mecánico Gamer Gamepower Suki Tkl Switches necánicos 87 teclas antighosting reposamuñecas magnético</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/teclado-mecanico-gamer-gamepower-suki-tkl-switches-necanicos-87-teclas-antighosting-reposamunecas-magnetico/p/MCO45207491?highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO45207491&amp;position=5&amp;search_layout=stack&amp;type=product&amp;tracking_id=d5bd1a16-2a63-481d-ab07-d7b9f14f3457&amp;wid=MCO1542802747&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>127415</v>
+      </c>
+      <c r="E11" t="n">
+        <v>149900</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>15% OFF</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>11</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_806430-MLA81431205572_122024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_636597-MLA82479025889_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_752807-MLA82478968071_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_899959-MLA82478941533_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_678323-MLA82478968095_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_762905-MLA82479025859_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_686051-MLA82478941575_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_629643-MLA82478968169_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_848904-MLA84026494874_052025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_614756-MLA84321552659_052025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_959549-MLA84321552663_052025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_739424-MLA84026494876_052025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '08 abr. 2025', 'contenido': 'Excelente , calidad y todo.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '29 may. 2025', 'contenido': 'Excelente teclado para el precio, el recorrido es bastante alto por lo que no es para todo el mundo y los switches no son tan silenciosos, pero en luces y calidad es excelente, sin contar con que permite extraer keycaps fácilmente y el frente es metálico, muy buen producto.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '10 abr. 2025', 'contenido': '', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '05 may. 2025', 'contenido': 'Muy bueno.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '27 abr. 2025', 'contenido': 'Exelente.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>45809.68173770834</v>
       </c>
     </row>
   </sheetData>
@@ -2380,7 +3105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2463,28 +3188,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Teclado Mecánico Inalámbrico Newmen Gm610 60% Rgb 61 Teclas</t>
+          <t>Portatil Hp 12ava Gen Intel I3 1215u Ssd 512gb Ram 8gb Color Plateado</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=6gGtzBLavbK6QT%2FHNpbmv4xJiCt5aKMxBqNom0ChA44NtPEmuvAI%2Bd%2F6wZ5bJEEzHJr5DnaUPSSbXsA27RKEa9B2aGtGEO0TsJfkfy%2BAxjueSxf%2Bb63DYr8jbEaPbuHXO%2B5hpSgqQj9g65y8837ovhh%2FLr824TMjzjtbqPPd1LhEsdCYo22TnDqIeTtfDnpv%2FtmlNqz637XVhPscnSGmouUrSXmqrjeiCPDnf9KVlls8EDsrjF6s%2FERJT5%2BzF0fY%2BttMYUcQwgDnN1mOlZZlKQBr4sMtGrWiG8OFpv3c5EpaylXa%2FBdBvq0jhw70H0oSxSxvb5cuBpONRrhOyv4yPwuTc66azMz98G5fX8C7KZF7EeV99fWGhMOdqwMYvMam8gmrw2AZbdNRtAywmoN06LhUPPXLSsM5kUKroJuLUM3VAkVh5zRqQl%2FQIyXSGPcU5D0nva18v1VGvdIwqwfh0Ibf9JkqBEaIGeZn%2B40QC5od%2Bjf0ozYJOAVdaA8WvEwj%2BOWRrMKdheFNCYVp7FSXsnuyEEYCYT8c%2BbHZ9DLdBMTVctfuHGmPhsO06wVqqTA5Y9fxJHdJBiSPDU5UmhG7ISvZHMV8sxffBRRUzlfKORPzCa8A6pK5AQQRfjBoRFsl6wSRBx8J4hW%2BkAQSay2F6gt1pVQXmsmhXspXlNdWknhJY2OhJ9MCfhbJ91LuskxMN00efWb6svoHLy7UXfl6CJqma5A6SUsiBa%2BKC%2FErjG6jRQrzTjmECxwEUl9YdmtjbYMdwwtDSGKR6Q5JunQwTqCRCplf%2FAWojZHys7g2isSZ2GvCIsWBEAbpoUVJcToj87qK1lwTBs6zEde6g8iRNugxlwcuSepuSFkKENccA3ZAs4Y3wZOlkfOr2xC%2BxxbvOb00Ed6IwFkjIrpK0lfUyePM9tiooSvD8Imm2h7b8Ayff8r0mq9HUCBj%2FrCUw2tA&amp;highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=d5bd1a16-2a63-481d-ab07-d7b9f14f3457&amp;wid=MCO2573729598&amp;sid=search</t>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=dku4jdiAcXRE4Py1V8DoDDrtydxMZpVo3FGxDxGIPUG02cgOmoyBduDaFQYIV9jdoGSdLxtpAIKmGkGpuZGVorajxGxUlkHDfQvH2tgSM0H5UwNcuIJjKRMJbh1MPAOFvWOEOO%2BoDAuiN0cgM96fDsQDaXOGnxux6Weki4J%2B%2FSxlYW36%2FirEObipRCSuKoRyOA5CyAzcXLUx5QWoFyCNcF69qXe69EPfVERqNbCZiOAz%2BiSADI55VH1ra4h%2FVjJJ73tV65zNzlGSIR4C%2Bf%2Br16uNwYh54ecpvQvg9sfGqBhiNwnVvunYBAMsrM6CyOZq6D%2BX0ima8Lb8fFqSDzLRYifZL0VrdrZ10vWPcoZB01yes%2FYPbtHqDe1u1vqlZwmu053DAJC8lbQsv3cGSPFD10%2B8cyBA1ZpsY%2Bi0JiYJePgB2l6LBueahbuBVEtmAxzNU18GlKOa%2BubI7E7iaKbzrEMx7j7%2BGzprdjAxEcCdh5Sqh28%2FBDrGrBCRmDn2fksZJcdHWTd5Fm3LaZLFyCuifrUTz0GZBBa%2BpIlsQ7oai90nuEBjNLvzI7XSTOmMghBrmcKqDeu8XGB2g3q7phl5%2FBqPt4P1hrpBoJe39qbl2fQZIKE9czB7llEz9Kww99yZDZXf9Mu7WWEL078tnmwYIPXYifleY5t%2FiyO3SlqON7BdTnFRtm9QslStkg%2FXvitYQgN%2Fsljrw43VBqfowRMnjNdpjjrlZBmb8L%2FtDhIXuwaozNYifxQjKBOkf9LAASI52ZAGlJUCgMf11KxLgXukvtyr8sQSWzpHGsw2r2QwzoAzSHqFbJ1QLCPteG9UPUSb3mOTfsA69rKCa30rkyAJc1db6rxXnZJPOxYNsda7z81CBVS4vN4WJRO1IK%2Fy04Dn6Zop%2F0t%2ByMuFsbNiN10pdgxCd29udyXX5N%2BUg2jVs8L7i6xdxyHLr6XLfTcvffotzeqsw%2FOS%2B44iMw%3D%3D&amp;highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO1507088307&amp;sid=search</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>144415</v>
+        <v>1458900</v>
       </c>
       <c r="E2" t="n">
-        <v>169900</v>
+        <v>1853000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>15% OFF</t>
+          <t>21% OFF</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -2498,60 +3223,56 @@
       <c r="I2" t="b">
         <v>0</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>4.9</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="J2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K2" t="n">
+        <v>54</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_940676-MLU77417106611_072024-V.webp</t>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_645989-MLU78944581522_092024-V.webp</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_940676-MLU77417106611_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_987647-MLA82113006950_022025-F.jpg', 'https://http2.mlstatic.com/D_NQ_NP_2X_756226-MLU78420919739_082024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_708773-MLA84456438700_052025-F.webp']</t>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_645989-MLU78944581522_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_605957-MLU79183304451_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_641148-MLU78944551828_092024-F.webp']</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>[{'calificacion': 5, 'fecha': '13 sep. 2024', 'contenido': 'Es un producto hermoso, recomiendo instalar el firmware desde la pagina oficial según como indica el manual, arregla un conflicto con varias teclas. También recomiendo poner el idioma del teclado en el pc como ingles us para que no hayan problemas. Siguiendo los pasos que les acabo de mencionar el producto es maravilloso. Lo mejor que se puede conseguir calidad precio. Pdta toca acostumbrarse a dar un comando para usar las flechas y no tiene la tecla ñ.', 'votos_utiles': '8'}, {'calificacion': 5, 'fecha': '09 oct. 2024', 'contenido': 'Extremadamente bueno, una compra que uno no se arrepiente lo recomiendo.', 'votos_utiles': '3'}, {'calificacion': 5, 'fecha': '09 dic. 2024', 'contenido': 'Me gustó, las orientaciones de los usuarios sirvieron mucho … fácil de instalar , dejarlo en opción inglés y para la tilde o ñ se coloca en español … las luces del teclado súper , recomendado !!!.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '31 may. 2025', 'contenido': 'El teclado muy bueno para su precio. La verdad no estaba esperando mucho sino que funcionara bien y fuera cómodo al tacto. A la final ha superado mis expectativas. Muchas gracias.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '27 may. 2025', 'contenido': '', 'votos_utiles': '0'}]</t>
+          <t>[{'calificacion': 5, 'fecha': '16 jul. 2024', 'contenido': 'Excelente producto muy recomendado.', 'votos_utiles': '6'}, {'calificacion': 5, 'fecha': '26 feb. 2025', 'contenido': '', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '21 dic. 2024', 'contenido': 'Me pareció un producto muy bueno y de excelente calidad 😃.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '06 may. 2025', 'contenido': 'Excelente, corresponde la descripción. Satisfecho con la compra.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '24 may. 2025', 'contenido': 'Excelente equipo.', 'votos_utiles': '0'}]</t>
         </is>
       </c>
       <c r="O2" s="2" t="n">
-        <v>45809.68173760112</v>
+        <v>45809.69780228009</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Teclado Gamer Mecanico En Español Retroiluminado Con Cable Usb Xtrike Me Gk988 Para Computadora Pc Con Luz</t>
+          <t>Notebook Hp 245 G10 R3 7330u 512gb Ssd 8gb Ram Windows 11 Ho</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=f%2F2y0a41zS%2FCSk3LHoy1FmCIOd3IXjkIc4zrxquwe11mnEs31DNrGs4s5WGrbswIcV9mcJMF42%2F%2FNXENqgyu%2FlQzWscGtdgGm5pc%2B4n1Mt2puld%2B2kCs6YlAYLN7ouABMzMjt%2F0MYeuzXcRO5DM9XfBU8IqWp9tAW3BFhiBnyl8%2FEcst8TuhHvi2lI%2BYgB8c9M0z98WMPpnCrYD80Sdi2iGnAb4xjTGp5qvj7foeTG%2FxBA6vSiEBLE7x2UlQ5Ml3lWzVVIV4vKuU%2BhwsQeqCbXkZF352uL4OCafSvy3oYmZxbvVKS4JXJUP3BVDLkKpIWr3Xqhn3LVG6gKoQAPlvIOQsjYpRCm6cg1kks2jGkl8Ww2owqqEFRTdb7EDuWwfZx8mOZeMIAZ4Hg1IxyPhjLXQ%2FdkUJky0iTAWe1OFTOxT1evOPhkW3GPSk721VWfZi84JlxLNJM8j87%2BqEhX5aO7rSB662JU%2BxI9EfURh6WoqdG19xLTWj4WcEVGELrCM7oYoYwyBxEFcuVP9iUiljdTIuHScEneuLOOWeyvSpZ2NoUOEUAikCrQW7X%2FiDWTIZgdyzRusJ%2BIJx3BpsuUWAEbWZoOIQMXAztgzgmtR1AELcUYbBQ7vV9HSAwbZsoj2AJxmLku7N6X1okzof6Fpbdtwe9Hbopr1YSWTf1zWCM6IwMRXXbmsXBZtKQfwi4Pk6KJGj4HXWS02mdU5DGAOgcok5du2bgnYgo8NMgHPAOWvmmlcnd85ssCEg9fKKkcMjGWbETWPSh7xiDsGnSXXwTNNXK8GMp94WkD8bjcDXGq8mL8n1bt717kIG8rEnssoov07dc1xhHx0%2FlVtteyt8LTFvmsiiMpKZzXqV3he5op527UBvZsM2U9QaHewKaBvicFrw%2FTMjgedgArbI43oicXIeLU61Oshp5Tg8FOSkOaz2yD%2FKLgOF86LVMyp%2FsVQ1vs%2FBsIAonsMEK38835kntHbMho%2FMJb2hEARHJajFWEaHs7iZ0y9oh%2Fse2pcNlrw%3D&amp;highlight=true&amp;headerTopBrand=true#polycard_client=search-nordic&amp;tracking_id=d5bd1a16-2a63-481d-ab07-d7b9f14f3457&amp;wid=MCO1560382775&amp;sid=search</t>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=%2BguJVvqHQV%2FYie73icpk4wBmcxN%2BwLIpWJMDL3%2B4s2u%2B94pS%2BNE26JdD3OYn%2BU5%2FHfTf0RIG2nwgOcyR5fixIxf78VopB085Wwp1LziVOA%2BWShvcpw6OUXZs%2F1JFAIfLxF3vFgvx0WT4v9TRg4JeqDqTeSEBR12bSQMfPw%2FeOwLlxEUmFRQ3KWmEeLtjRo1sAXCKw7gPq2p6BfPo43ff1%2Bm7%2FbLTH2dNFvxt46oSKPMLsXrjaa4n8P9O649bOjCuaUqV%2FFL6cfb%2Bfx5%2BSENn1OI9tO8QpprKoit1dOr6zYjr0AkZHL535iJ9FXS0HnzvMCD8ZRAv1caHsIMhQLfrzyhelo8fqsIGQPcHF91HKMJYUCoCFW%2FWLUUKApQ0SE9pHRgwG4HzEWQQsx3PrGcma8vfSVeBzwAgAyq77xLiidr0eyhRZZPbKKkK1y2zkxb7AsVIRD6Lu9G6%2BdfPZDzp0jN4h%2BorTTz7O2coTuy0GG3klsycylDhfgw3ga4hCo0uuObGY7vTZ%2FSdENZxi1mZPJfQeoMbaJCK%2Bd1YVqw5nf%2BnwfuPC%2FAQAF0LuqxtR1ogUkzAADu0txX2BN4vg2hd3ra7LoVHItTKChTOstSKj1rXw7SM2rXeX8j7qHPXx0l2XmO1GuwUwYpaPFICuQO8Bwr6ivIypNzhrn9z%2FVPpjqrr%2F6lSI0st53L6TLsNbEXIpfp1Ol8g42ojfGbz1xtF93Vz9n1RJUUw7n3O7s%2FCg2zAt%2FxAxNqyE%2FFICJG0wVEztkjMrUa2wWHyta70WmLC2ww0xckfmyKDgh26mXqggrMJOz0mZtdpymugXz9lwffes01hiWYqjf74h2oTdyO1JK2O3HUW2IFF2TZ%2BlF1z6R0y82VQReABYYzV5Iz7ssTU2x59eEdfS0Yt%2BV49DCIYK%2B8T5%2F%2FlOztNXJtSiXLzHv0e7LRh%2FvuKspY7z3fUiBQdTr0%3D&amp;highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO1547113843&amp;sid=search</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>104900</v>
+        <v>1259900</v>
       </c>
       <c r="E3" t="n">
-        <v>149900</v>
+        <v>1621375</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30% OFF</t>
+          <t>22% OFF</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2565,60 +3286,56 @@
       <c r="I3" t="b">
         <v>0</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="J3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K3" t="n">
+        <v>21</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_973583-MLA83472189647_042025-V.webp</t>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_679019-MLU78080956988_082024-V.webp</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_973583-MLA83472189647_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_833541-MLA80825743061_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_820938-MLA80563766270_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_760094-MLA80563785792_112024-F.webp']</t>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_679019-MLU78080956988_082024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_630529-MLU78080779350_082024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_880233-MLU78307689171_082024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_860704-MLU78080957006_082024-F.webp']</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>[{'calificacion': 5, 'fecha': '01 may. 2025', 'contenido': 'Contento con el producto.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '28 abr. 2025', 'contenido': 'Es una buena opción por el precio, cumple con lo que promete perfectamente, se siente de buena calidad y al responde bien, recomendado.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '31 may. 2025', 'contenido': 'Bastante bien calidad precio:) lo recomiendo!(es algo ruidoso) perfecto para competitivo.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '23 may. 2025', 'contenido': 'Se ve excelente, me gusto mucho.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '22 may. 2025', 'contenido': 'Cumple con todo. Muy buen producto.', 'votos_utiles': '0'}]</t>
+          <t>[{'calificacion': 5, 'fecha': '27 may. 2025', 'contenido': 'Buena opcion.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '24 may. 2025', 'contenido': 'Muy bueno.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '19 may. 2025', 'contenido': 'Buen producto calidad - precio.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '13 may. 2025', 'contenido': 'Buen producto unue no veo mucho cambio en el brillo de la pantalla.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '06 may. 2025', 'contenido': 'Excelente.', 'votos_utiles': '0'}]</t>
         </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>45809.6817376265</v>
+        <v>45809.69780230324</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ASUS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Teclado gamer Redragon Kumara QWERTY Outemu Red español España color negro con luz rainbow</t>
+          <t>Portátil Asus Vivobook X1502 Ci5-12500h 24gb Ssd512 Fhd15.6 color Quiet Blue</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.mercadolibre.com.co/teclado-gamer-redragon-kumara-qwerty-outemu-red-espanol-espana-color-negro-con-luz-rainbow/p/MCO19518470?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO19518470&amp;position=3&amp;search_layout=stack&amp;type=product&amp;tracking_id=d5bd1a16-2a63-481d-ab07-d7b9f14f3457&amp;wid=MCO1347087050&amp;sid=search</t>
+          <t>https://www.mercadolibre.com.co/portatil-asus-vivobook-x1502-ci5-12500h-24gb-ssd512-fhd156-color-quiet-blue/p/MCO47191661?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO47191661&amp;position=22&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO1569451947&amp;sid=search</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>190900</v>
+        <v>1929900</v>
       </c>
       <c r="E4" t="n">
-        <v>199900</v>
+        <v>2249000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4% OFF</t>
+          <t>14% OFF</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2632,15 +3349,11 @@
       <c r="I4" t="b">
         <v>0</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2285</t>
-        </is>
+      <c r="J4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K4" t="n">
+        <v>14</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -2649,43 +3362,43 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_636746-MLA52350707355_112022-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_913394-MLA52350707356_112022-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_994079-MLA52350716250_112022-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_912260-MLA52350716251_112022-F.webp']</t>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_877811-MLA83102329491_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_703080-MLA82814024258_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_805571-MLA83102329495_032025-F.webp']</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>[{'calificacion': 5, 'fecha': '08 may. 2021', 'contenido': 'Panas yo lo veo bien xd, tal vez sería mejor si las luces fueran más brillantes pero de resto llevo 1 mes con el y todo gucci, todo bien todo correcto además me regalaron unas teclas de cambio :) uwu.', 'votos_utiles': '56'}, {'calificacion': 5, 'fecha': '14 jun. 2023', 'contenido': 'Me encantó llevo más o menos 1 año con el producto y no ha presentado problemas, se escucha bien y se ve bien 😎.', 'votos_utiles': '35'}, {'calificacion': 5, 'fecha': '17 ago. 2023', 'contenido': 'El producto es bastante bueno en calidad-precio; cositas que no me acabaron de gustar, pero que son de menor importancia para mi son que algunas partes de las teclas (ej. Bloq mayús) que no se iluminan completamente, no tienen switches brown para comprarlos con el teclado, las patitas de goma antideslizantes no son las mejores, el teclado se tambalea un poquito aunque no se si es mi escritorio o el teclado (con el manual en una esquina se arreglo), de resto es un buen teclado, los materiales en acero para la placa y el "plástico reforzado" están decentes, el cable no es mayado, pero tiene el conector usb en oro chapado (creo que así se le dice xd), es hotswap, por si le quieren poner otros switches, la retroiluminación es decente y algo que me parece vital, pero no tiene, es que el conector no es removible, en general lo recomiendo si no hay mucho dinero para gastar y cuando ya se tenga el set-up bien armado cambiar el teclado o dejarlo.', 'votos_utiles': '12'}, {'calificacion': 5, 'fecha': '26 jun. 2021', 'contenido': 'Bastante bueno, la verdad tanto el tacto como el sonido me gustó demasiado, es bastante bonito gracias al color rojo que arroja el teclado por defecto, es algo pesado lo que hace que sea difícil moverlo sin querer lo cuál es genial, es tenkeyless lo que hace que te quede bastante más espacio del que uno cree que le va a quedar y la verdad estoy tratando de hacer la reseña larga porque es bastante cómodo escribir con este teclado.', 'votos_utiles': '10'}, {'calificacion': 5, 'fecha': '07 sep. 2023', 'contenido': 'Lo recomiendo, excelente producto ☺️ buen material.', 'votos_utiles': '7'}]</t>
+          <t>[{'calificacion': 5, 'fecha': '24 may. 2025', 'contenido': 'Hasta el momento ha funcionado super bien y es bastante rápido, su diseño es muy funcional y práctico para la manipulación. Tiene una buena calidad de imagen y es cómodo para la vista.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '21 may. 2025', 'contenido': 'Excelente.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '19 may. 2025', 'contenido': 'Buen producto.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '19 may. 2025', 'contenido': 'Un super equipo, en relación precio-calidad, muy rápido y bonito.', 'votos_utiles': '0'}]</t>
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>45809.6817376367</v>
+        <v>45809.69780231481</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LENOVO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Teclado gamer Redragon Kumara QWERTY Outemu Red español latinoamérica color negro con luz RGB</t>
+          <t>Lenovo Ideapad 1 Ip 1 15igl7 Intel Celeron N4020 15,6 Pulgadas 8 GB Ram</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.mercadolibre.com.co/teclado-gamer-redragon-kumara-qwerty-outemu-red-espanol-latinoamerica-color-negro-con-luz-rgb/p/MCO19472215?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO19472215&amp;position=4&amp;search_layout=stack&amp;type=product&amp;tracking_id=d5bd1a16-2a63-481d-ab07-d7b9f14f3457&amp;wid=MCO1483729915&amp;sid=search</t>
+          <t>https://www.mercadolibre.com.co/lenovo-ideapad-1-ip-1-15igl7-intel-celeron-n4020-156-pulgadas-8-gb-ram/p/MCO40332473?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO40332473&amp;position=26&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO2864083698&amp;sid=search</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>190900</v>
+        <v>1016900</v>
       </c>
       <c r="E5" t="n">
-        <v>198000</v>
+        <v>1500000</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3% OFF</t>
+          <t>32% OFF</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2699,15 +3412,9 @@
       <c r="I5" t="b">
         <v>0</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2285</t>
-        </is>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>0</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -2716,43 +3423,43 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_864807-MLA77594879101_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_625461-MLA75686545678_042024-F.jpg', 'https://http2.mlstatic.com/D_NQ_NP_2X_867951-MLA77594879095_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_750884-MLA77378571910_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_845414-MLA77378789172_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_901847-MLA77378571898_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_804807-MLA77378808744_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_909019-MLA74488153000_022024-F.jpg']</t>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_698989-MLU78765589152_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_861837-MLU78765589158_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_797157-MLU79001804755_092024-F.webp']</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>[{'calificacion': 5, 'fecha': '08 may. 2021', 'contenido': 'Panas yo lo veo bien xd, tal vez sería mejor si las luces fueran más brillantes pero de resto llevo 1 mes con el y todo gucci, todo bien todo correcto además me regalaron unas teclas de cambio :) uwu.', 'votos_utiles': '56'}, {'calificacion': 5, 'fecha': '14 jun. 2023', 'contenido': 'Me encantó llevo más o menos 1 año con el producto y no ha presentado problemas, se escucha bien y se ve bien 😎.', 'votos_utiles': '35'}, {'calificacion': 5, 'fecha': '17 ago. 2023', 'contenido': 'El producto es bastante bueno en calidad-precio; cositas que no me acabaron de gustar, pero que son de menor importancia para mi son que algunas partes de las teclas (ej. Bloq mayús) que no se iluminan completamente, no tienen switches brown para comprarlos con el teclado, las patitas de goma antideslizantes no son las mejores, el teclado se tambalea un poquito aunque no se si es mi escritorio o el teclado (con el manual en una esquina se arreglo), de resto es un buen teclado, los materiales en acero para la placa y el "plástico reforzado" están decentes, el cable no es mayado, pero tiene el conector usb en oro chapado (creo que así se le dice xd), es hotswap, por si le quieren poner otros switches, la retroiluminación es decente y algo que me parece vital, pero no tiene, es que el conector no es removible, en general lo recomiendo si no hay mucho dinero para gastar y cuando ya se tenga el set-up bien armado cambiar el teclado o dejarlo.', 'votos_utiles': '12'}, {'calificacion': 5, 'fecha': '26 jun. 2021', 'contenido': 'Bastante bueno, la verdad tanto el tacto como el sonido me gustó demasiado, es bastante bonito gracias al color rojo que arroja el teclado por defecto, es algo pesado lo que hace que sea difícil moverlo sin querer lo cuál es genial, es tenkeyless lo que hace que te quede bastante más espacio del que uno cree que le va a quedar y la verdad estoy tratando de hacer la reseña larga porque es bastante cómodo escribir con este teclado.', 'votos_utiles': '10'}, {'calificacion': 5, 'fecha': '07 sep. 2023', 'contenido': 'Lo recomiendo, excelente producto ☺️ buen material.', 'votos_utiles': '7'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="O5" s="2" t="n">
-        <v>45809.68173764625</v>
+        <v>45809.69780231481</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Teclado gamer Redragon Mitra QWERTY Outemu Blue español latinoamérica color negro con luz RGB</t>
+          <t>Portátil HP 15-fd0065la Intel Core i5 16 GB 1 TB SSD 15.6" FHD Windows 11 Home</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.mercadolibre.com.co/teclado-gamer-redragon-mitra-qwerty-outemu-blue-espanol-latinoamerica-color-negro-con-luz-rgb/p/MCO15079758?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO15079758&amp;position=9&amp;search_layout=stack&amp;type=product&amp;tracking_id=d5bd1a16-2a63-481d-ab07-d7b9f14f3457&amp;wid=MCO1505508309&amp;sid=search</t>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=23xU%2F%2FNVjqICOy5bgG4de3phADouskiAFKa2T5lIUE1evPFLwdWiJr05FIff7KgtDX85ZPtqoqFz%2F5dxSvVxw2I0YWCYZfjsqy5fC9vZ54GupRcAYWGC1WD0y1YatU5NwJySaKD%2Fyt8aEwf7B%2BmiqJsFf71IHk67ZOWS7e500Wz98FO924DMxd3WpP2b%2FHqqLU%2B2qo6FPriUs7r8HtaMFY1qnLxIs%2BpKXymgp97Hr%2BvX7ydKWRQQusuAQaSv8qfNcN9318ydrDeL6C%2FGO7XnP2cIVGuFmWZkoqFi8vnWcLoVjIQn9RlGdHF5O1RLNZRKTOIXo8%2FHN1GLKkcXDlCSGnvd0qKwHFE%2F6otOnmwOowBfWl%2FK5p1CJEjHHjIZFIVwH6ucXZdszT4T86RfXDEgDXVwSp3OdKM6xHQMvlShdHwVg0aH0FN%2FbThO4Xp1KBlO80ju4onU4wULeJ9xiyP2U3ydKbSRDl9ON5nTR1EO3AINmU7M743JCNSosb8Lw75undRDstJiHZwcBflL%2FTBu1k7d1xJHTu9coE2S1FiWHnyeMaeFGaLE5InwZnghdGa09Pny5cvYZgT%2BUAsoZX3VXwnfZVm2wGzcFI5bLSo8N4oCoF9JmIZ7umnUKtGhxpt9DhcEkN9M%2FGdPzppOnNw6fwP4DhGtHfiNC6tsLkwngCZD4KHpmA3Gn9ew%2FAkmdqU7pmcq%2F4yrtEGZv3J%2F5oNUFc6cHVjs5If3JBLdadGR2rt%2BaO5nAWAkE6sOgjJ4zOg4R%2BFW7tC9VGzgXYq8xT1kYSi0nSDlEZkVkx54bfdcKJdjzCPQty4p0%2FwJxXrJp0gy%2B3uezDxPHWcrBAbXe40%2B6OuNpIw7BcewGpDUplYNVbb6IfJI0WqYx0sGUN1q4RJAh%2Bhvgi51BdOJFJ83yLyIER4FSzp%2BB9Vco3%2Fn%2FLyeoDTZccg%2BkdsA9ngsrx%2FYNQ5ghnKS87NK3E2Q1QgOpobBrP0LzgU%3D&amp;highlight=false&amp;headerTopBrand=true#polycard_client=search-nordic&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO1575797741&amp;sid=search</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>279900</v>
+        <v>2500939</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>4099900</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>39% OFF</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2766,15 +3473,11 @@
       <c r="I6" t="b">
         <v>0</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>4.9</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
+      <c r="J6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -2783,45 +3486,41 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_602205-MLA74652847384_022024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_773066-MLA52988770867_122022-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_860664-MLA52988782788_122022-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_944519-MLU73115284216_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_781580-MLU75321470327_032024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_694460-MLU70065260095_062023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_810307-MLU75321420641_032024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_853829-MLU75321391561_032024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_742900-MLU75174250074_032024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_791595-MLU73115624998_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_920640-MLU73115625028_122023-F.webp']</t>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_873079-MLA82669520756_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_879656-MLA84247887703_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_745543-MLA82956543925_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_831985-MLA82956572471_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_847818-MLA83952780706_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_930561-MLA84247761613_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_984171-MLA84247838835_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_904741-MLA84247761629_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_606436-MLA84247887717_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_875651-MLA84247838847_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_707448-MLA84247887737_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_729925-MLA84247887743_042025-F.webp']</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>[{'calificacion': 5, 'fecha': '07 ago. 2022', 'contenido': 'Feliz con la compra, pedí outemu rojo, que son los clips del teclado. Estos son silenciosos y más suaves que el outemu blue.\nA mí me gusta el teclado silencioso por eso preferí outemu rojo.\nEl teclado tiene retroalimentación de calidad, y se siente la calidad del teclado. Con teclas inborrables porque son de doble inyección.\nMuy feliz con el teclado 100% original. Gracias.', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '20 jun. 2022', 'contenido': 'Es un gran teclado, de muy buena construcción y robusto, sin embargo en la publicación dice que vienen con unos switches outemu blue, y vino con unos switches de color rojo de los cuales no se exactamente la referencia. Aun asi me siento conforme con el funcionamiento de este y lo recomiendo.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '06 ene. 2022', 'contenido': 'Buen producto relación calidad precio.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '09 abr. 2024', 'contenido': 'Se ve de muy buena calidad se nota q es de buena construcción espero q dure.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '14 may. 2025', 'contenido': 'Me gustó mucho el producto, bastante sólido se siente de buena construcción y buena calidad, sensación agradable al momento de pulsar las teclas y buena retroiluminación en cada una de las transiciones, recomiendo el producto totalmente.', 'votos_utiles': '0'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="O6" s="2" t="n">
-        <v>45809.68173765656</v>
+        <v>45809.69780232639</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LOGITECH</t>
+          <t>ASUS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Logitech G413 Se, Teclado Gamer Mecánico Retroiluminado Led Color del teclado Grafito Idioma Inglés</t>
+          <t>Portátil Asus X1605za-mb644 Intel Corei5-12500h 16gb Ram Disco Solido 512ssd 16 Fhd Endless</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=1%2BmSDuFEjeCjf5EyjYdV5LjMfAU5owNLHEYv3ks1VKpD0Gs0zZTvdlXGVSqVU2xg%2BncfChY%2BC%2BAAHw37%2F7v%2BEifMiSaJ4p17K3K5XrAXV2HEQv4MYSAql9TGf%2BB9VigDzre5GPNO5v%2F6zUHVGeGXBAb0ww3SZNZsWxcpGcVvIrsd%2FB9RcBs9oHxqv3cI0u2A5f1D5XAcqNDhSB9Ee4tEbShrr0kTBMcGviYSNFBtDMz24KVROBy2GoNoJRTiQzllPVlRY7ZFeIEpVsPwAaYH9fjbFmfU1V5gIZRyKCcxbMScmI71XEgfLilHueoqznPDxM7jHKWZ2mZ8aUMBsW1go4M%2BS3pz44v947MELQdtLTgQZmaOj%2BuRTaK%2FwUJXPB8Ry7l5DOsn%2F5jAlDBrvrDctWkiX2gjoBGot4qHPrJUmglwGID9XabLA%2BDt7KHqJGp0hr8VITlYrO%2FPZwzKfHZwjmqHiPz2iCHepwmXYahnElJoJU8vPqD4mYPua4sSpdiVjfFeAJVVaY6dNadGNXQFdg9EFp5qQ70oXeooPtemL%2BeSjOppfN32ZF%2FYvi1VLZj%2FqkJ1I3UrOHMwwK7IKWHRbWo1C%2FEzAIFqJnqtFRB9MBTDNV2sYdKHQUvdBD7M2P5BRlPeLcQwrh%2BFd3iLqI0e3M4c0COGIs3IIRgUI4IqrBkPWIYO9rePq%2FkwQYpAaIKtMU3poo3JeH%2BbjxHSm3nVpXlKa1rtDmwj2QtiGEhfDa6AX5g%2BzB28X5ZI2r9LSLsbjH1sQdIrBOcQd0uL1Uq97ZWs5JnwPo0oxbkLpeoYVi%2BubPo84aEBdcP0PA225XXI8efe9qSlN4UBfKvI3TgcbAYEua9Xjg8StyPoaG0LTgtFNSSiRFv2fJ7sswbMuBh3imQ2D1nexgmFmkMUgmqsQ12vs2iYADEwmMNaRsnWbesp6x1MIVUPFtuV%2FlBIVhkKCsB2wh39b7M9ZBk%2B3ruWNCHYUzP%2Fjs6rP%2F7GdfF5ZEt3OhCbmUVb&amp;highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=d5bd1a16-2a63-481d-ab07-d7b9f14f3457&amp;wid=MCO2855290132&amp;sid=search</t>
+          <t>https://www.mercadolibre.com.co/portatil-asus-x1605za-mb644-intel-corei5-12500h-16gb-ram-disco-solido-512ssd-16-fhd-endless/p/MCO32161065?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO32161065&amp;position=5&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO1523840021&amp;sid=search</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>357135</v>
+        <v>2029900</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Envío gratis</t>
@@ -2833,15 +3532,11 @@
       <c r="I7" t="b">
         <v>0</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>4.9</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="J7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K7" t="n">
+        <v>145</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -2850,43 +3545,43 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_942664-MLA84857255411_052025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_831940-MLA84724971460_052025-F.jpg']</t>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_822592-MLU74290609668_022024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_961011-MLU74290777838_022024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_769942-MLU74406002007_022024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_995013-MLU74406002009_022024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_838170-MLU74406002013_022024-F.webp']</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>[{'calificacion': 5, 'fecha': '06 mar. 2025', 'contenido': 'Es un 10/10.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '26 dic. 2024', 'contenido': 'Excelente teclado, super rápido paea video juegos muy bueno.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '16 sep. 2024', 'contenido': 'Muy buen teclado, excelente para el gaming.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '11 sep. 2024', 'contenido': 'Con respecto al producto era lo que esperaba, con respecto a la transportadora sé que "envia" es económico pero en muchas áreas del territorio nacional es pésima transportadora, se recomienda cambiar.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '07 jun. 2024', 'contenido': 'Es un buen producto suave silencioso buenas y faciles de combinación del teclado para juegos súper rapido.', 'votos_utiles': '0'}]</t>
+          <t>[{'calificacion': 5, 'fecha': '25 mar. 2025', 'contenido': 'Sus 12 nucleos y 16 procesadores lógicos lo hacen ideal en toda la cantidad de archivos, páginas y programas que debo usar. Es un exclente equipo. Tarda menos de 15 segundos en encender y apagar.\nExcelente refrigeración y su tiempo de carga es rápido. Buena duración de la batería dependiendo del trabajo que se este realizando. La pantalla es super amplia.\nEstoy muy satisfecho con la compra.', 'votos_utiles': '9'}, {'calificacion': 5, 'fecha': '03 may. 2025', 'contenido': 'Muy buen equipo, es bastante rápido y me corre bien varias ventanas a la vez y juegos pesaditos y exigentes gráficamente, el único contra que le encontré es que la batería se desaparece con nada 😭, lo cual hace que toque estarlo cargando o tenerlo conectado, me gustó que no se calienta demasiado, yo si recomiendo el equipo 👌.', 'votos_utiles': '5'}, {'calificacion': 5, 'fecha': '11 abr. 2024', 'contenido': 'Producto de acuerdo a lo esperado, buena calidad.', 'votos_utiles': '5'}, {'calificacion': 5, 'fecha': '24 jun. 2024', 'contenido': 'Muy buen equipo, trabaja a la perfección.', 'votos_utiles': '3'}, {'calificacion': 5, 'fecha': '16 mar. 2025', 'contenido': '', 'votos_utiles': '2'}]</t>
         </is>
       </c>
       <c r="O7" s="2" t="n">
-        <v>45809.68173766883</v>
+        <v>45809.69780233796</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ASUS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Teclado Mecanico Gaming Premium Tkl Rgb - Blue Switches</t>
+          <t>Portátil Asus Fa506nc Ryzen 5 7535hs Rtx3050 16gb 512gb 15.6 Color Negro</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=raxnTiIOfaJGLihafXujD1LfKau1fJt4%2BALVI8%2Bbs57gk4gn%2B0x02l14%2Bit8M7USHQqk8J23Vd7Ela7IruCNXs6Ba7umN1djjbgLKGjPph%2FmF0UKdIhSJWpwIuISvLU34eiNhA2Qz8W8vi%2BClW5rR%2F0zqyi%2BIsWNQ59tjuM%2F8Gy%2F%2F7AcRkW%2BxaQdc52oU37aDBgoxAlqLbTnIYPAkZNeXB2ASeKhGCYMSzORUQFu64NWzbj9X1Ewu69jq6ytRR9tG6BySZ7PqESZlYHXuPWqq3pZy9K740WAlK7N4kMTSHfEht9Pjnm8HkwzsLtvdd1AXZwLRGpirSldH8IrIB29Y6UJlPjl3qcDT%2FHFEV79Rcd7KnS2%2BmNHhRXL9%2F9O03fL4Wur5GvRHtOZPKvRWbWQJLOX595%2FB5tE5CaMf%2BIpmx0rndZOd1aiQMjhEqB0aSnucvngxtVhTqF92xNEu5bSFN5K01hGjQrrYP7qMQ3bmZLdf%2BUzu4wY0qXiYppVcagqcgMKXyyX838k%2FOcuHMCbq7u3O1V%2FbcOqATG8%2FGY909oLtZoV8TvvTOLAV3XjKqNcM%2F1CK83TDb%2FLDBqaYwjB1d3P9dYp0gsnR4jszJnY2jL0ut6oC6Xon8cEjx9jngDpHKfXeKwM%2B6F%2BCFahWXIxzXkcPfV9KIt5nnys%2BEUwxIin993%2FQ4A01WoeagLTABfk2aj2qSMnwP9LIcOvSNEN73fiDov8%2BWR3M%2FCr46AOOfjYcmr2zxiJK7iwJIvoLfyCIzxJWMDPQsihVf6rA2HN6Z6xoDV%2BvzNy7xWBKqOwbxao2uHS%2F8VWRTvzzyA4eZ%2BXuJiTc4eoEDCtpt0VMnnYK0TmNxKNAZr%2FVucsswAhmzh5S%2FYS4gm5wQ3Y33jkQQOIZZUFvSLFK135iqeKhujn19FufKQtndb5FpMSBuhgJ1GVQMMoQb%2FvQ0x9&amp;searchVariation=175176005934&amp;highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=d5bd1a16-2a63-481d-ab07-d7b9f14f3457</t>
+          <t>https://www.mercadolibre.com.co/portatil-asus-fa506nc-ryzen-5-7535hs-rtx3050-16gb-512gb-156-color-negro/p/MCO45003983?highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO45003983&amp;position=10&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO1544070727&amp;sid=search</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>107920</v>
+        <v>2975814</v>
       </c>
       <c r="E8" t="n">
-        <v>134900</v>
+        <v>3199800</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20% OFF</t>
+          <t>7% OFF</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2900,15 +3595,11 @@
       <c r="I8" t="b">
         <v>0</v>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="J8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -2917,43 +3608,43 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_713856-MCO83310185804_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_906560-MCO83311522676_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_629139-MCO83311522714_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_952983-MCO83603556415_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_729467-MCO83603556433_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_862622-MCO83311591058_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_649367-MCO83311591070_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_879923-MCO83327889878_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_835523-MCO83311591120_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_837709-MCO83603556513_042025-F.webp']</t>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_680616-MLA81284061462_122024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_978440-MLA81284061466_122024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_957941-MLA81284061468_122024-F.webp']</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>[{'calificacion': 5, 'fecha': '21 may. 2025', 'contenido': 'Suena muy lindo y tiene muchos modos de colores, puedes ponerlo solo rojo y varios colores también tiene multicolor a la vez 🥰🥰.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '13 may. 2025', 'contenido': 'Excelente, recomendado 100%.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '31 may. 2025', 'contenido': 'Es un excelente teclado mecánico, tiene una configuración sencilla de las luces de fondo, también trae para personalizar macros en algunas teclas, tiene un sonido aceptable. Es un poco pesado en comparación con otros, muy estético y trae mucha variedad de configuración de luces.\nLo recomiendo mucho si te gustan los teclados mecánicos al 65% para ahorrar espacios.\nDe muy buena calidad.\nVale la penam por el precio.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '29 may. 2025', 'contenido': 'Tremendo, para su valor. Muy bueno. Eso sí, suena un tris duro.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '28 may. 2025', 'contenido': 'Es sorpréndete la calidad que tiene para lo barato que es, la sensación, las luces, el sonido. Es magnifico! 10 de 10.', 'votos_utiles': '0'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>45809.68173768006</v>
+        <v>45809.69780233796</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ASUS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Teclado Gamer T-dagger Arena T-tgk321 Qwerty T-dagger Brown Español Color Negro Con Luz Rainbow</t>
+          <t>Portatil Asus E1504fa-nj474 Ryzen 5-7520u Ram 16gb Ssd 512gb Color Negro</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.mercadolibre.com.co/teclado-gamer-t-dagger-arena-t-tgk321-qwerty-t-dagger-brown-espanol-color-negro-con-luz-rainbow/p/MCO25354558?highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO25354558&amp;position=13&amp;search_layout=stack&amp;type=product&amp;tracking_id=d5bd1a16-2a63-481d-ab07-d7b9f14f3457&amp;wid=MCO1435132381&amp;sid=search</t>
+          <t>https://www.mercadolibre.com.co/portatil-asus-e1504fa-nj474-ryzen-5-7520u-ram-16gb-ssd-512gb-color-negro/p/MCO23498360?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO23498360&amp;position=3&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO1541876389&amp;sid=search</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>149900</v>
+        <v>1725640</v>
       </c>
       <c r="E9" t="n">
-        <v>214143</v>
+        <v>1988778</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30% OFF</t>
+          <t>13% OFF</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2967,15 +3658,11 @@
       <c r="I9" t="b">
         <v>0</v>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
+      <c r="J9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K9" t="n">
+        <v>413</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -2984,43 +3671,43 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_829971-MLU72637468711_112023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_846613-MLA79492165647_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_815620-MLU74161826881_012024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_916860-MLU72566191648_112023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_980831-MLA79491981591_092024-F.webp']</t>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_785588-MLU73109363362_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_726659-MLU73193255159_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_765061-MLU74154709735_012024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_794132-MLU71686123628_092023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_870312-MLU73981577884_012024-F.webp']</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>[{'calificacion': 5, 'fecha': '04 feb. 2025', 'contenido': '', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '25 oct. 2024', 'contenido': 'Muy lindo y comodo.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '22 ene. 2025', 'contenido': 'Me parece un exelente producto precio calidad. Los materiales son bueno y el silencioso, me encantó recomendado.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '22 ene. 2025', 'contenido': '', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '25 abr. 2025', 'contenido': 'Un muy buen producto calidad precio, el teclado es bastante silencioso lo cual es perfecto para mí, también es muy cómodo pero tiene dos cositas que no me gustaron.\n1) entiendo el tema de 60% y la combinación de teclas con el fn pero un teclado de este tamaño necesita por obligación un software de configuración de teclas propio prácticamente no se pueden usar las flechas ya que si das fn + w vas a bloquear wasd como flechas de movimiento pero a su misma vez fn + w es flecha arriba si yo solo quiero ir hacia arriba en un texto voy a tener que darle dos veces por lo que va a subir dos veces el cursor en resumen esa combinación me aprece que está mal y no se puede cambiar.\n2) se escucha un poco el rebote de las teclas cuando se usan muy rápido pero esto puede ser tema de los switches a lo mejor con una lubricada se quite pero de fabrica puede ser un poco molesto.\nPero en general es un muy buen teclado cumple exelente su función ya llevo un mes con el usando todos los días y nunca me deja tirado lo recomiendo.', 'votos_utiles': '0'}]</t>
+          <t>[{'calificacion': 5, 'fecha': '27 jun. 2023', 'contenido': 'Excelente producto, la pantalla se me hace que le falta un poco de brillo, por lo demás no se encuentra ningún otro pc con esas características a un mejor precio.', 'votos_utiles': '30'}, {'calificacion': 5, 'fecha': '08 abr. 2024', 'contenido': 'En un principio, cuando recibí el equipo, la caja ya había sido abierta. Luego me di cuenta de que lo hicieron para instalar windows 11 de cortesía. Esto me genero desconfianza. Aunque lo revisé y todo parecía estar bien y nuevo, recomiendo que, al realizar la compra, pidan el producto totalmente sellado. Después, pueden instalar el sistema operativo usando un pendrive. Lo ideal es que sea windows 11, ya que es el más estable para este modelo.\nReinstalé windows 11 pro en inglés usando mi cuenta de microsoft. En un principio, la resolución de la imagen era de muy mala calidad, el sonido se distorsionaba y la batería duraba muy poco, lo cual me preocupó. Sin embargo, luego de las actualizaciones automáticas de windows, todo esto se corrigió.\nEl equipo viene por defecto con linux, es decir, no tiene licencia de windows. Pero se puede comprar una licencia oem en internet. Normalmente no supera los 15 dólares y es vitalicia.\nLlevo poco más de un mes usándolo para programar y usar photoshop, y el rendimiento esta muy bien, tambien corre algunos juegos pero no es gamer.\nCompra recomendada.', 'votos_utiles': '15'}, {'calificacion': 5, 'fecha': '06 sep. 2023', 'contenido': 'Me parecio excelente el computador. Es rapido, cuenta con buenas caracteristicas y en mi caso venia con windows 11. El precio es justo a su rendimiento. Estuve buscando otros laptops en otras paginas y en mercadolibre pero definitivamente esta maquina es muy buena para su bajo costo y sin decir que asus es una buena marca. En si me siento contento por la compra se los recomiendo 💯/💯.', 'votos_utiles': '12'}, {'calificacion': 5, 'fecha': '19 sep. 2023', 'contenido': 'Hasta ahora muy buen rendimiento, vino sin sistema operativo así que toco instalarle windows 11.', 'votos_utiles': '9'}, {'calificacion': 5, 'fecha': '26 sep. 2023', 'contenido': 'Hasta el momento no he tenido problemas con el equipo, corre todo muy bien, soy programador y trabajo con programas pesados y bien, también tengo un emulador de play 2 y también corre bien.', 'votos_utiles': '8'}]</t>
         </is>
       </c>
       <c r="O9" s="2" t="n">
-        <v>45809.68173769186</v>
+        <v>45809.69780234954</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Teclado Mecánico Gaming Redragon K636clo Rgb Color del teclado Negro Idioma Inglés US</t>
+          <t>Portátil Hp 14-em0009la R5 Ram 16gb 512gb Ssd</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.mercadolibre.com.co/teclado-mecanico-gaming-redragon-k636clo-rgb-color-del-teclado-negro-idioma-ingles-us/p/MCO29039269?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO29039269&amp;position=14&amp;search_layout=stack&amp;type=product&amp;tracking_id=d5bd1a16-2a63-481d-ab07-d7b9f14f3457&amp;wid=MCO2772382820&amp;sid=search</t>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=tyTYKpzlgRnMLVeSPPYpkn80O67AYEXoCcecd95T2pOZjixqfUeYO6g2BnM9ovUMBc7lELHt%2BhJFUV6EDF8FrMZx1gm56eXjwYu7fju548XoFhX%2Fse2sGG2bWc2hA%2Blqsnur2s22FM6qvFlT5Sr%2Fyzbx%2BGKSc6ngRfyotCpTldAmuoBRIioGf8B2xOT84gBMof5Q6giy%2BjXGuB3k%2BNA9lUQp5eKv2CILA%2Be1yU8xpppwLPmUXv7tnQrZR85nc9ncb9lDQAoQEnUIJA1KEqg5jFOqFr%2FvNSgEPBA%2F9rpW6vHcdWOFDG4aOKEmxw%2F3YnhnCWt3bAyd0%2Bx8eSE1Be4FSj%2FvfJFaZF5zxLi8hCbNtEdwEuMYnBl67bZTC3Qzf6ZbIfeNKJoVIzOWQbcbxhIsY2xMhW%2F%2B0gvQLcpOWSp0Z4fRJhoEetAutOXdB5wTQ4wrYOHjbqy1m86m1%2FnQLCqpzDdMvuzfRlynQnyPT9AlZ39z1%2B4kAJKs882d%2FzRo59Y3kQnP0OEnQ6ZyO5%2BP0KFU8ZxsdO0eZuAxseEN9A4zIJevVd0bLkyD3f30dCM%2BQcyLnH4XSE3svRfTf7PaKC9mGQCRsJpF%2FD2uwTm76Vfs0%2F8BG5G%2F5oYNajLmJ7FMZF0c%2F5Omj2eLYBDOXm5Hj58caHace7i3UE1FMadLmHf6TAfj9N4j5QOOygqWD%2FHKI7KA2gEoYCK4fYa36wwVTTbGeV0PpZG6Hvk0wTF%2FjnjgBkOgaoRI6DCrpVxidEqZ9hynkjIVHDXCPNiv5TEk8PK2y%2Bhizjslvj3hQx%2BsjyS%2Bzr6xMpxTmUPlp6SutYfTND77QDW7farwViCsePn3gzfct7ZJruwCpMx7RikGf0wRj8xamGsbpp04f3uaMyzGH%2BiWdaxA2TjltrSsyPp4CqA74fg01SCTssfjfyOvcLhxTJHWQEPU&amp;highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO2503419712&amp;sid=search</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>210028</v>
+        <v>1770900</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>2248125</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>21% OFF</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3034,15 +3721,11 @@
       <c r="I10" t="b">
         <v>0</v>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>4.9</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
+      <c r="J10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -3051,83 +3734,6021 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_674064-MLU73503205759_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_943483-MLU73411990606_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_651951-MLU73411990618_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_758706-MLU73503205777_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_988320-MLU73502811109_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_891015-MLU73502870103_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_742169-MLU73411931788_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_723670-MLU73503225631_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_629594-MLU77910155149_072024-F.webp']</t>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_971993-MLU72165226628_102023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_895690-MLU72226746163_102023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_971777-MLU72165196948_102023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_716188-MLU75004584385_032024-F.webp']</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>[{'calificacion': 5, 'fecha': '02 mar. 2024', 'contenido': 'Excelente producto, muy bueno, hace falta revisar las macros pero cómo quedo configurado con solo conectarlo estoy feliz. Todas las teclas funcionan a la perfección.', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '07 nov. 2024', 'contenido': 'Muy bueno, silencioso, suave y práctico, funcionando perfectamente.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '30 abr. 2024', 'contenido': 'Muy bonito exelente producto lo recomiendo 🔥🔥🔥.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '25 may. 2025', 'contenido': 'Justo lo que estaba buscando, por el precio esta muy bien.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '04 abr. 2025', 'contenido': 'Excelente. Viene con las herramientas para cambiar las teclas. Un producto muy completo y estético, sobre todo por el precio!.', 'votos_utiles': '0'}]</t>
+          <t>[{'calificacion': 5, 'fecha': '21 dic. 2024', 'contenido': 'Excelente producto.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '31 oct. 2024', 'contenido': 'Por el momento cumple con lo prometido 👍🏽👍🏽.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '29 oct. 2024', 'contenido': 'Me pareció muy bueno en rendimiento y durabilidad de la batería.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '10 oct. 2024', 'contenido': 'Muy bueno, necesitaba un dispositivo para mí estudio y trabajo eficiente y asequible. Está máquina se ha comportado muy bien, muchas gracias 🫂.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '09 oct. 2024', 'contenido': 'Venía con windows 11 pre instalado pero le instalamos windows 10. Hp oficialmente solo da soporte para windows 11 sin embargo los drivers funcionan sin problema en windows 10.\nEl equipo nos pareció excelente por el precio es bastante fluido, el color es un plateado dorado que lo hace ver elegante y es muy ligero y silencioso, la batería nos duró más de 2 horas y aún tenía la mitad de la carga.\nInstalamos photoshop 2024 y corre sin problema las 16 gb de ram permiten tener varios programas abiertos sin que el equipo sufra en rendimiento.\nEstamos muy satisfechos con la compra, esperemos a ver cuánto dura el equipo en buenas condiciones.', 'votos_utiles': '0'}]</t>
         </is>
       </c>
       <c r="O10" s="2" t="n">
-        <v>45809.6817377041</v>
+        <v>45809.69780236111</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Teclado Mecánico Gamer Gamepower Suki Tkl Switches necánicos 87 teclas antighosting reposamuñecas magnético</t>
+          <t>Portátil 2 en 1 HP Pavilion x360 14-ek1011la Intel Core i5 8 GB RAM 512 GB SSD Windows 11 Home 14" Pantalla táctil FHD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.mercadolibre.com.co/teclado-mecanico-gamer-gamepower-suki-tkl-switches-necanicos-87-teclas-antighosting-reposamunecas-magnetico/p/MCO45207491?highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO45207491&amp;position=5&amp;search_layout=stack&amp;type=product&amp;tracking_id=d5bd1a16-2a63-481d-ab07-d7b9f14f3457&amp;wid=MCO1542802747&amp;sid=search</t>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=gAJhe5EaqsLLEBHVD24euXY7TbCgDx10UvhSmhYX7cMyvWMunfWO4cpPh7DH%2FrGx6nBEdDy2CqoVYr%2FbZZasPtXST%2FWc%2BRJEVBB9RFByNu%2FgvTA9r540KDeosoFlp35iz2VbBxIARI4Lkq9GRfC%2BFDPFoWyxUhOCvOIizzVKtoY2glKb88bWETKBRskQqqees5lWEKZOLZofkL0Rqly%2FSJgdDXkfMlvTNoZUlSYbM%2BI%2BcujX413ckQn3xaU7ym%2Bgrxs4aKs3o82eueAc7ae86RzqWxXKVaBeEuUH3jSQkYVs68NrftH5YHD5LJwfVA0QUmakWJRaI5yyWCBQ6TIflvAQCsmgPOEjmC7WsiM5SipNo4da3ygdYrJMhpYhqVkAdjlkEtw8%2FaBJo5EkYWiH5cWsnuOgxe279T7WnaPYEKmi8cwu%2FXeAf4RwoGT%2FWiPpBHF0ca7FUjePTWVAWkpqrM8jLx4DE3i%2BMUa1sIqo%2BJk1e4gj2iW735mBi4196U27R8tjEB0y61b1xxff%2BvXicrdxLYYb1TZQ1Bd2TGmXMbHLxPr4JK8g9CD%2FcBzJq%2BNNA2BHYUMkWivQNIG31AllfucJf9fwKfUozZwQaHLlKRa50sLqhWWmpwK9vPi3jVkeD2uLc3ZKH8Ex61M%2B%2FPq8CDl2UL469wsraGfoVYs8ipW%2FR338kGtwlktZvWGFdHGFJATq2%2BsnsL19gYg0Wry1Pr9ixxRrhlEkTsDVFPwuYqZgc%2BZ4aC%2FS1YxRroWpFqLNKIvUI4OAnRUnHB1Y1NYIFAxv1ra6uOREM%2BvHM5SHEsCk5nqFPX4s3WmdF2elGaeEfUlJlAE27JQfptRx8g55X1ZePj61hVes23iF9DD%2BLgpLEExGUS6I7u3DzPrvyvJ4hS7SbAvrOl24NLmHhlYd9%2BjteLK3WyGSnW9oRgyFnkprzvTc5aJnwQToJ%2Fj1bSmw33TIoQuuoU8D8gkcTXo%2B0bMuVuysKRCWaQab5Z1AYtR%2BP9Esb7CbyxGBAGOxGctOZROaUpKkB4%2Bs1SO9098%3D&amp;highlight=false&amp;headerTopBrand=true#polycard_client=search-nordic&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO2859705258&amp;sid=search</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>127415</v>
+        <v>2519937</v>
       </c>
       <c r="E11" t="n">
-        <v>149900</v>
+        <v>3999900</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>37% OFF</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_988735-MLA83130332646_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_794568-MLA84319057304_052025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_727216-MLA83130332652_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_759584-MLA83421014329_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_929368-MLA84319028858_052025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_675179-MLA84318904618_052025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_928766-MLA84319028882_052025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_652583-MLA84616214019_052025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_789295-MLA84318904640_052025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_731357-MLA84616214037_052025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_629484-MLA84616214041_052025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>45809.69780236111</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MacBook Air 13.6 M2 256 GB SSD 16 GB Ram Z160000au C/ Nota</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/macbook-air-136-m2-256-gb-ssd-16-gb-ram-z160000au-c-nota/p/MCO26602331?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO26602331&amp;position=8&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO1547152627&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4266374</v>
+      </c>
+      <c r="E12" t="n">
+        <v>4960900</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>14% OFF</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K12" t="n">
+        <v>131</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_708839-MLA51356236557_082022-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_613040-MLA51356222696_082022-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_889912-MLA51356222738_082022-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_619023-MLA51356202957_082022-F.webp']</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '16 jun. 2023', 'contenido': 'Excelente elección la que hice, un gran pc para trabajar, soy dba y la verdad es que para desarrollo es muy bueno, la batería le dura un montón, el procesador es muy bueno, el sonido, la pantalla están a otro nivel, super recomendado.', 'votos_utiles': '28'}, {'calificacion': 5, 'fecha': '01 dic. 2023', 'contenido': '¡me encanta! esperé a probarla en todo lo que hago para comprobar si me serviría y ha sido una buena decisión de compra. La uso para diseño gráfico, edición de video, animación, modelado 3d y me va super bien. La mía es de 8gb de ram, si la van a usar para edición en after effects recomiendo la de 16gb, porque con 8 a veces se traban un poquito los fotogramas, nada grave, pero si es muy pesado puede que sufra. Del resto todo va genial.', 'votos_utiles': '17'}, {'calificacion': 5, 'fecha': '17 feb. 2024', 'contenido': 'Excelente, es la versión de 8 cores cpu y 8 cores gpu.', 'votos_utiles': '5'}, {'calificacion': 5, 'fecha': '08 nov. 2024', 'contenido': 'Excelente, viene sellado y nuevo probado en desarrollo de aplicaciones los emuladores con m2 corre perfectamente en simultáneo 👍.', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '17 ago. 2024', 'contenido': 'El producto está excelente, no me gusto que den una descripción errada su chip no es de 10 nuclueos.', 'votos_utiles': '2'}]</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>45809.69780237268</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Notebook 15,6 Hp 250 G9 Intel Celeron 8 Gb Ram 256 Gb Ssd Color Negro</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/notebook-156-hp-250-g9-intel-celeron-8-gb-ram-256-gb-ssd-color-negro/p/MCO24443216?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO24443216&amp;position=15&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO1479324193&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>902003</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1094000</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>17% OFF</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K13" t="n">
+        <v>22</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_669596-MLA72666764739_112023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_997141-MLA72594738346_112023-F.webp']</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '02 mar. 2025', 'contenido': 'Muy bueno, económico y lo recibí rápidamente.', 'votos_utiles': '4'}, {'calificacion': 5, 'fecha': '15 may. 2025', 'contenido': 'Me encanto y el precio espectacular.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '18 may. 2025', 'contenido': 'Increíble todo presentable y bonito.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '13 may. 2025', 'contenido': 'Excelente equipo.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '21 may. 2025', 'contenido': 'Excelente muy bonito.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>45809.69780238426</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Portátil HP 14-ep0027la Intel Core i3 8 GB 512 GB SSD 14" HD Windows 11 Home</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=J6wCQzz9ca7Z8ssBYlfsliXBnMwOsvQrPpRYhyY4BrhcqpLxDd%2FYQKtf2HKrMKYp5JuWlTSZbTrzsO6UAPyoiFL9xRXD7vKtyn7zUMKcGnX3TgfPLPofGBvXbbujtvinOUKs0uGy1axwacVCrR4oLiKwZnUTqL%2F3Qz%2B%2B35%2FdmRUBEWL%2BYtgWaFZIc2QC6EK6BOKLzWT1yQI4fpivXNd01wNPGRWROopcp8NqzCxikMY7mew39s7yMbGjp21prwmC7NBVidPWmbG5EYgU865unKwNqzwkWjd7dlbQAS3xIGc9kcCwQfce5LURhgJrtLjejLNMRz%2BNtrQaTKxUCFu0jLG6KsB3hvG%2BlTyUdqxt1x4dUdBV04kKIpafibVP4ndAu3VyX7Ch%2BXBzeuylCJjqizlmU6ry6T32rNo6hEeDKr6qXQOdarQt7xmc47BdLkgS4j6b9uKHkJk%2Bz%2FEWW3F8vUwFSSr1B2QIipDUXqyJ6HHYkb2ALgTutatA9uw3T8%2BIxHcLGT132mF%2FgOXBoY%2Bj7Hv784uHbVGDudchJvzqhZAw4FIqLfpeRHz%2F3GQNP9gdUqUUM2sreES%2BExvxGvctrzTBj5zlZxVpGrXVEUaeUXTaAKNie4%2BuP0hrtAjQnt0RQckLoyCGmEqekx2VMfseEA%2FuXLsLxQZSUdKDv9xVgs4Ges4uSEV2Vuu%2Fto7z4NaG85Cga%2F8DyKiidML2rmtc4AsRQE%2F8MqfCIcDojul26i7nT1IsbxNgVJ83EmHipC9%2BXujXSoiiLoFCsYUxPQ2yhg6MbhTJQgOOEuEbJLOdBGmWSf7n8n8DqDvmHe5NS5ykN3hsyFXoF7Rc6QHTj1WMrvlbnYeZs2MSVMgyYt%2Beb%2BNGYgnr20iN1DvimPkn3V130Wv%2FDb1%2Fwo7HmTzVH5ztaARI%2BZy%2BiyXHNNfnVqS%2FKvtntE5asapj7QaWbUL%2F1BR%2Fc8YwXCrCb6viB%2BfkXVayTH3wpg%3D%3D&amp;highlight=false&amp;headerTopBrand=true#polycard_client=search-nordic&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO2840103620&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1679940</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2799900</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>40% OFF</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_681699-MLA83021702514_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_964132-MLA83021702532_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_768910-MLA81628910116_012025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_739151-MLA81900796165_012025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_692347-MLA83311634715_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_713509-MLA83021731670_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_795311-MLA83311634733_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_817317-MLA83311590217_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_783345-MLA83311590261_032025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>45809.69780239584</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Portátil HP 15-fc0031la AMD Ryzen 7 16 GB RAM 1 TB SSD 15.6" FHD Windows 11 Home</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=JksAp4c8Kuaazb%2FxPnfb8r7C2iC%2FHkog3Lj6cmynep1pmByig3qyGReWBSRa8M2dNTDCAd2aZza%2B95mHkjKmnJDtwb1P6W0EB7M8Fzj2ilN%2FyVHnQj4OyrNXlw4kr5ENQwNhWMbQtINE5rP74fGKAdb9mrvPFaKDJg3Qgr0a4%2BUpYyjkVyMIhNai%2FGvBXZGkUlutbSxUZd16kjSRDkBK7Ew%2BQuMuz8ny1U9i%2BhAjRZIGqXum48tzPt4CnMbuHvJqm59aKQXf6xfbt5n6Ksyki1yqwXelUk9aVZfR1Vd0YJelUB6ri%2Fxeh4%2BOIGx%2FN5x1h6ZwFxOSaIWGMUig23A0dV2zfzsMnfy59r6NMDnceeiZYatK5ESIi%2FlTU4TnPzJqWm9VfuCGHm2xtmYtk5cMH65feJqdgZ%2F4hre8h89IDXQ9WgLReq6FyRd5aYKUUQQf0hpi5Gbm%2BOZJseJQndOz7d5qTv0NcxOeao4WJPZv%2Bnasy8EP4juCy9kvbVxQ0lMbULxzDrzXALEfjPpp%2BLvwRQymbosSb1G1YoNzK%2FRCMEL7eR8nbgRVbd9E5znFaZe8CNAEkfa7%2FIeOtWGGM5AmLZX5qNF1YbN4tYWUma7Xq7mVhWPSi%2ByEsVAu5O%2B7lb8kehgdoemg2YS4p2I01IGWByTdqY4mDL4718KuCfWuGO0POgmXN82be9Db7NNRIY9CJBpewpxHwA1iG5fLVz1Pgqd9rKfl1aYFDpSMGJfvi7jqwOJjvsoH84hcYHsbBMVqGKKPsD2b7N58QjMa03lgiUbb2Us0LlCXIlIuj7ioXd5TQfVUSU%2F4CWqu6KC4mQ3WUZfHrfsCgez6wf53ZHzk0AUC%2F6cbYVPVrU8Z4JxnS527XJ5JSQZqe8SiJR3rRpObHFWrDM8oArsI0vUqJri0FSFvfUlInqSuDhAfAMLJxHQTmNQBAWBM6xGGWNAPsh9tDoRiLm0kX%2B6%2BKETh7I0LShcFgIiI&amp;highlight=true&amp;headerTopBrand=true#polycard_client=search-nordic&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO1575771851&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4099900</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_815916-MLA82945757783_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_874654-MLA84247757623_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_625769-MLA82945757787_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_660337-MLA82945757789_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_632767-MLA83952776642_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_952877-MLA83952474652_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_743470-MLA83952484392_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_832640-MLA83952474656_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_693165-MLA83952513586_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_900626-MLA83952484400_042025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '29 may. 2025', 'contenido': 'Excelente, tal como lo esperaba, totalmente empacado y con protección en la caja. Encantado.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>45809.69780240741</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LENOVO</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Potátil Lenovo Ideapad Slim 3 15IAH8 15.6" color abyss blue 16GB de Ram 512GB SSD Intel Core i5</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/potatil-lenovo-ideapad-slim-3-15iah8-156-color-abyss-blue-16gb-de-ram-512gb-ssd-intel-core-i5/p/MCO28604720?highlight=true&amp;headerTopBrand=true#polycard_client=search-nordic&amp;searchVariation=MCO28604720&amp;position=4&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO1480376745&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1939900</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2499000</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>22% OFF</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K16" t="n">
+        <v>51</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_795161-MLU73180411829_112023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_602068-MLU78543909026_082024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_837841-MLU73097256104_112023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_816754-MLU73097236384_112023-F.webp']</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '30 abr. 2025', 'contenido': 'Todo excelente excepto que la caja vino abierta y la pc ya estaba inicializada.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '05 mar. 2025', 'contenido': 'Un producto muy bueno, se comporta de manera esperada y se puede trabajar muy bien en él.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '24 oct. 2024', 'contenido': 'Excelente producto era lo que quería.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '28 may. 2025', 'contenido': 'Excelente.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '24 may. 2025', 'contenido': 'Bien fiel a la descripción del producto, para poder usar el desbloqueo con huella debes instalarlo un windows diferente al que trae.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>45809.69780241898</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Notebook Hp 245 G10 R3 7330u 512gb Ssd 8gb Ram Windows 11 Ho</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/notebook-hp-245-g10-r3-7330u-512gb-ssd-8gb-ram-windows-11-ho/p/MCO39243137?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO39243137&amp;backend_model=search-backend&amp;position=14&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO1547113843&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1259900</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1621375</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>22% OFF</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K17" t="n">
+        <v>21</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_679019-MLU78080956988_082024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_630529-MLU78080779350_082024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_880233-MLU78307689171_082024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_860704-MLU78080957006_082024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '27 may. 2025', 'contenido': 'Buena opcion.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '24 may. 2025', 'contenido': 'Muy bueno.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '19 may. 2025', 'contenido': 'Buen producto calidad - precio.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '13 may. 2025', 'contenido': 'Buen producto unue no veo mucho cambio en el brillo de la pantalla.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '06 may. 2025', 'contenido': 'Excelente.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>45809.69780243056</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Portatil Hp 12ava Gen Intel I3 1215u Ssd 512gb Ram 8gb Color Plateado</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-hp-12ava-gen-intel-i3-1215u-ssd-512gb-ram-8gb-color-plateado/p/MCO29272690?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO29272690&amp;backend_model=search-backend&amp;position=20&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO1507088307&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1458900</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1853000</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>21% OFF</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K18" t="n">
+        <v>54</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_645989-MLU78944581522_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_605957-MLU79183304451_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_641148-MLU78944551828_092024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '16 jul. 2024', 'contenido': 'Excelente producto muy recomendado.', 'votos_utiles': '6'}, {'calificacion': 5, 'fecha': '26 feb. 2025', 'contenido': '', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '21 dic. 2024', 'contenido': 'Me pareció un producto muy bueno y de excelente calidad 😃.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '06 may. 2025', 'contenido': 'Excelente, corresponde la descripción. Satisfecho con la compra.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '24 may. 2025', 'contenido': 'Excelente equipo.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>45809.69780244213</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>LENOVO</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Portatil Lenovo V14 Core I5-13420h 24gb 512gb Ssd Color Negro</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-lenovo-v14-core-i5-13420h-24gb-512gb-ssd-color-negro/p/MCO44279796?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO44279796&amp;position=9&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO1587144125&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1900230</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2176667</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>12% OFF</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H19" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K19" t="n">
+        <v>44</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_634636-MLA81072483529_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_664825-MLA81072531241_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_812999-MLA81072493673_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_699921-MLA81072493687_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_986563-MLA80807408510_112024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '26 dic. 2024', 'contenido': 'Al parecer de fabrica el producto viene de 8gb pero lo expanden a 16 gb con capacidad para que corran a 3200mt/s. En general muy bien, el windows que trae se debe activar pero esto lo decía en la descripción. Cumple las expectativas es muy buen equipo por el precio.', 'votos_utiles': '5'}, {'calificacion': 5, 'fecha': '08 mar. 2025', 'contenido': 'Muy buena pinta.', 'votos_utiles': '3'}, {'calificacion': 5, 'fecha': '21 feb. 2025', 'contenido': 'El producto vienes con windows 10 de prueba, tiene tapada la camara tapada con una cinta imperceptible, el color no es negro, sino gris claro. Me disguste al comienzo por el windows, pero lo logré solucionar, reinstalando desde cero y después actualizando al windows 11.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '04 feb. 2025', 'contenido': 'Buen equipo.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '08 ene. 2025', 'contenido': 'Nos gusta mucho. Excelente producto.', 'votos_utiles': '1'}]</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>45809.6978024537</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ASUS</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Computador Portatil Asus X1504za-nj227 Core I5 24gb 512gb Azul</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/computador-portatil-asus-x1504za-nj227-core-i5-24gb-512gb-azul/p/MCO34194456?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO34194456&amp;position=35&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO1434617549&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1999900</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>33</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_688334-MLU74956004603_032024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_935244-MLU74956073831_032024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_785486-MLU74956073833_032024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_881132-MLU74956220031_032024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '22 jul. 2024', 'contenido': 'Rápido para llegar, y producto 100% original.', 'votos_utiles': '3'}, {'calificacion': 5, 'fecha': '07 ago. 2024', 'contenido': 'Excelente producto, lo malo es que la batería dura 2 horas.', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '04 abr. 2025', 'contenido': 'Llevo usandolo 7 meses y no se queda pegado ni trabado, tiene buena imagen, buen sonido, la duración de la batería si no es mucha, pero abro muchas ventanas dos navegadores, word excel, whatsapp, canva. Y funciona super bien.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '10 oct. 2024', 'contenido': 'Super bueno el computador.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '02 oct. 2024', 'contenido': 'Excelente producto.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>45809.6978024537</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ACER</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Portátil Acer Nitro V Amd 7535hs Rtx 2050 Ram 16gb M.2 512gb Color Negro</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-acer-nitro-v-amd-7535hs-rtx-2050-ram-16gb-m2-512gb-color-negro/p/MCO45180899?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO45180899&amp;position=27&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO2855376486&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3964360</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K21" t="n">
+        <v>43</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_741891-MLA82198647484_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_832363-MLA81683562665_122024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_639895-MLA81683572115_122024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_833177-MLA81683562669_122024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_975584-MLA81414345144_122024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_803507-MLA82482205935_022025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '08 feb. 2025', 'contenido': 'Excelente producto, muy bonito y de buena calidad, lo probe y me dejo sorprendido, muchisimas gracias.', 'votos_utiles': '6'}, {'calificacion': 5, 'fecha': '19 feb. 2025', 'contenido': 'Es un computador que ha cumplido de más con las expectativas que tenia antes de comprarlo.\nPor el momento llevo dos semanas con el computador y me ha gustado que la duración de la batería es mayor a lo que pensé que duraba aproximadamente 4 horas si no estas jugando o usando programas exigentes. Lo único que no me ha gustado es la cuestión del brillo de la pantalla que en los juegos se baja un poco pero no se si será algo que tenga que ver con el plan de energía o con los ajustes de algunos juegos, los componentes parece que son duraderos hasta el momento.', 'votos_utiles': '4'}, {'calificacion': 5, 'fecha': '19 feb. 2025', 'contenido': '', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '19 mar. 2025', 'contenido': 'Un producto exelente y eficaz.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '20 may. 2025', 'contenido': 'El producto a funcionado bien los primeros 2 meses, la pantalla es excelente ybel funcionamiento para juegos y trabajo es muy bueno. Lo unico es que al momento de suspender el equipo este no se suspende bien, sin embargo con el modo hinbernar trabaja ok. Por lo demas un 10.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>45809.69780246528</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ASUS</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Portatil Asus Vivobook X1504za-nj372 Corei5 1235u 20gb 512gb Azul</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-asus-vivobook-x1504za-nj372-corei5-1235u-20gb-512gb-azul/p/MCO28710903?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO28710903&amp;position=28&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO2219873382&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2049900</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H22" t="b">
+        <v>1</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K22" t="n">
+        <v>325</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_676134-MLU74074108678_012024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_803354-MLU73981459906_012024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_785021-MLU74126725721_012024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_696570-MLU74965214543_032024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '10 mar. 2024', 'contenido': 'Buen producto. Buenas calidad, full rápido y me parece que esta bien calidad precio.\nLo único que no me gusta es que la batería dura como 3 horas y adicional así tengo uno las manos limpias quedan las huellas. Pero todo bien del portátil los recomiendo ya que está bien por su precio full rápido.', 'votos_utiles': '34'}, {'calificacion': 5, 'fecha': '08 mar. 2024', 'contenido': 'En general un muy buen equipo, lo único negativo hasta ahora es la duración de la batería, máximo 4 horas, lo que lo obliga estar conectado todo el día. Lo uso para correr photoshop, lightroom e ilustrator y los corre sin esfuerzo.', 'votos_utiles': '25'}, {'calificacion': 5, 'fecha': '24 mar. 2024', 'contenido': 'Muy potente, algo pesada pero acorde a lo comprado. Bastante contento con el pc. Algo q si me pone pensativo es el trackpad que a ratos se bugea. No sé si será problema de hardware o controladores.', 'votos_utiles': '7'}, {'calificacion': 5, 'fecha': '07 may. 2024', 'contenido': 'El equipo cuenta con una buena configuración, pero se debe tener en cuenta que el procesador arranca con 1. 3 gh y no con 3. 3 gh cómo aparece en las características del equipo.', 'votos_utiles': '7'}, {'calificacion': 5, 'fecha': '28 jul. 2024', 'contenido': 'Viene con windows 11 pirata y office pirata.\nTrackpad se traba mucho. Me toco inhabilitar y usar un mouse externo.', 'votos_utiles': '6'}]</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>45809.69780247685</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Laptop Hp 240 G9 Intel Celeron N4500 8gb 256gb Ssd 14 Black Color Plateado</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/laptop-hp-240-g9-intel-celeron-n4500-8gb-256gb-ssd-14-black-color-plateado/p/MCO33774175?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO33774175&amp;position=21&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO1479423655&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1140000</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H23" t="b">
+        <v>1</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K23" t="n">
+        <v>126</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_760560-MLU74476868512_022024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_705247-MLU74476670886_022024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_851843-MLU74476533280_022024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_871087-MLU74476670900_022024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_976018-MLU77494129899_072024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '26 ago. 2024', 'contenido': 'Excelente producto muy rápido, me parece muy bueno de verdad ,estoy muy contento seguiré usándolo y les contaré más adelante. !lo recomiendo ¡.', 'votos_utiles': '18'}, {'calificacion': 5, 'fecha': '29 ago. 2024', 'contenido': 'Excelente producto de muy buena calidad.', 'votos_utiles': '7'}, {'calificacion': 5, 'fecha': '23 nov. 2024', 'contenido': 'Buen producto.', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '23 ene. 2025', 'contenido': 'Buen producto, buen precio.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '15 dic. 2024', 'contenido': 'Buen equipo.', 'votos_utiles': '1'}]</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>45809.69780248842</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DELL</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Portátil Dell Inspiron 7MPHP de 15,6" con procesador Intel Core i3 1215U 8 GB de RAM SSD de 512 GB gráficos Intel UHD Windows 11 Home</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-dell-inspiron-7mphp-de-156-con-procesador-intel-core-i3-1215u-8-gb-de-ram-ssd-de-512-gb-graficos-intel-uhd-windows-11-home/p/MCO29241815?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO29241815&amp;position=29&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO2878763932&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1542900</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H24" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K24" t="n">
+        <v>12</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_974186-MLU73493739646_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_707745-MLU73493749390_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_881227-MLA82482550187_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_948197-MLA82482550195_022025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '02 nov. 2024', 'contenido': 'En un principio tuvo un problema con la batería por lo cual casi tengo que devolverlo, pero con una actualización de bios mejoro totalmente, ahora funciona perfectamente y ganó rendimiento.\nActualización: el equipo definitivamente presenta problemas con la batería, básicamente es un equipo de mesa porque tiene que estar al cargador, sino, se apaga.', 'votos_utiles': '5'}, {'calificacion': 5, 'fecha': '26 may. 2025', 'contenido': 'Buen equipo. Recomendado.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '14 sep. 2024', 'contenido': 'Me gustó mucho.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>45809.69780248842</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LENOVO</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Portatil Lenovo V14 Core I5-13420h 16gb 512gb Ssd Color Negro</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-lenovo-v14-core-i5-13420h-16gb-512gb-ssd-color-negro/p/MCO44291281?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO44291281&amp;position=38&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO1587242933&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1822630</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2087778</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>12% OFF</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H25" t="b">
+        <v>1</v>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K25" t="n">
+        <v>44</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_879967-MLA82146207764_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_805132-MLA82146235530_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_651506-MLA82146235542_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_766303-MLA82146235560_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_894436-MLA80807769694_112024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '26 dic. 2024', 'contenido': 'Al parecer de fabrica el producto viene de 8gb pero lo expanden a 16 gb con capacidad para que corran a 3200mt/s. En general muy bien, el windows que trae se debe activar pero esto lo decía en la descripción. Cumple las expectativas es muy buen equipo por el precio.', 'votos_utiles': '5'}, {'calificacion': 5, 'fecha': '08 mar. 2025', 'contenido': 'Muy buena pinta.', 'votos_utiles': '3'}, {'calificacion': 5, 'fecha': '21 feb. 2025', 'contenido': 'El producto vienes con windows 10 de prueba, tiene tapada la camara tapada con una cinta imperceptible, el color no es negro, sino gris claro. Me disguste al comienzo por el windows, pero lo logré solucionar, reinstalando desde cero y después actualizando al windows 11.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '04 feb. 2025', 'contenido': 'Buen equipo.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '08 ene. 2025', 'contenido': 'Nos gusta mucho. Excelente producto.', 'votos_utiles': '1'}]</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>45809.6978025</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Apple MacBook Air M1 A2337 Oro 8GB RAM 256GB 13´´</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/apple-macbook-air-m1-a2337-oro-8gb-ram-256gb-13/p/MCO17828522?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO17828522&amp;position=25&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO808606084&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>3290119</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3963999</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>17% OFF</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H26" t="b">
+        <v>1</v>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K26" t="n">
+        <v>382</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_951282-MLU75274695601_032024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_600571-MLA46516512357_062021-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_927851-MLA46516517294_062021-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_779467-MLU70045246870_062023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_851876-MLU70045142548_062023-F.webp']</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '20 ene. 2022', 'contenido': 'Excelente, no estaba confiada de comprar este tipo de productos en una página que no fuera mac o apple, pero realmente vale la pena, 100% recomendado.', 'votos_utiles': '25'}, {'calificacion': 5, 'fecha': '20 oct. 2023', 'contenido': 'La mejor compra que pude haber hecho! me ahorre un montón comprándolo con ellos, todo fue muy seguro y confiable, el equipo es brutal, mejor de lo que pensé a decir verdad y pude actualizar la garantía de apple, para que la vigencia de la garantía iniciara desde el momento en que tuve el computador sin ningún problema.', 'votos_utiles': '18'}, {'calificacion': 5, 'fecha': '27 sep. 2021', 'contenido': 'Viene con el empaque original, es una belleza xd. Super recomendado!!!.', 'votos_utiles': '14'}, {'calificacion': 5, 'fecha': '01 dic. 2023', 'contenido': 'Con un mes de uso les puedo decir que fue una buena compra, corren súper bien los programas, la suite de adobe, ¡muy bueno!.\nDe pronto recomendaría que al enviarlo se protegiera un poco más, enviarlo en una caja adicional y no envuelto en vinipel, pero no hay queja es un buen producto.', 'votos_utiles': '9'}, {'calificacion': 5, 'fecha': '17 may. 2022', 'contenido': 'Muy bueno. El procesador m1 de apple es silencioso, no se calienta y realmente hace que la batería dure, con un trabajo fuerte, unas 6 horas continuas. Si se usa moderadamente, puede llegar hasta las 10 horas. El tamaño es perfecto y la pantalla muy descansada.', 'votos_utiles': '7'}]</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>45809.69780251157</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Apple MacBook Air A2337 (13 pulgadas, 2020, Chip M1, 256 GB de SSD, 8 GB de RAM) - Gris espacial</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/apple-macbook-air-a2337-13-pulgadas-2020-chip-m1-256-gb-de-ssd-8-gb-de-ram-gris-espacial/p/MCO17828518?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO17828518&amp;position=19&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO2882533476&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>3179900</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H27" t="b">
+        <v>1</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K27" t="n">
+        <v>382</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_801112-MLA46516512347_062021-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_945128-MLU78157079171_082024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_845099-MLU78156774309_082024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_970152-MLU75333668768_032024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_651876-MLU70045054836_062023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_812414-MLU74227330835_012024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_634442-MLU77934175580_082024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '20 ene. 2022', 'contenido': 'Excelente, no estaba confiada de comprar este tipo de productos en una página que no fuera mac o apple, pero realmente vale la pena, 100% recomendado.', 'votos_utiles': '25'}, {'calificacion': 5, 'fecha': '20 oct. 2023', 'contenido': 'La mejor compra que pude haber hecho! me ahorre un montón comprándolo con ellos, todo fue muy seguro y confiable, el equipo es brutal, mejor de lo que pensé a decir verdad y pude actualizar la garantía de apple, para que la vigencia de la garantía iniciara desde el momento en que tuve el computador sin ningún problema.', 'votos_utiles': '18'}, {'calificacion': 5, 'fecha': '27 sep. 2021', 'contenido': 'Viene con el empaque original, es una belleza xd. Super recomendado!!!.', 'votos_utiles': '14'}, {'calificacion': 5, 'fecha': '01 dic. 2023', 'contenido': 'Con un mes de uso les puedo decir que fue una buena compra, corren súper bien los programas, la suite de adobe, ¡muy bueno!.\nDe pronto recomendaría que al enviarlo se protegiera un poco más, enviarlo en una caja adicional y no envuelto en vinipel, pero no hay queja es un buen producto.', 'votos_utiles': '9'}, {'calificacion': 5, 'fecha': '17 may. 2022', 'contenido': 'Muy bueno. El procesador m1 de apple es silencioso, no se calienta y realmente hace que la batería dure, con un trabajo fuerte, unas 6 horas continuas. Si se usa moderadamente, puede llegar hasta las 10 horas. El tamaño es perfecto y la pantalla muy descansada.', 'votos_utiles': '7'}]</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>45809.69780252315</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>LENOVO</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Portátil Lenovo Ideapad Slim 3 Intel Ci 5 16gb 512gb Touch Color Artic Grey</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-lenovo-ideapad-slim-3-intel-ci-5-16gb-512gb-touch-color-artic-grey/p/MCO44598331?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO44598331&amp;position=30&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO1561982735&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2640900</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H28" t="b">
+        <v>1</v>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_963696-MLA81226959531_122024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_977405-MLA81775119705_012025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_887519-MLA81505007442_012025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_964742-MLA83676357824_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_623826-MLA83969533867_042025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>45809.69780252315</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>LENOVO</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Portátil Lenovo Ideapad Slim 3 Amd Ryzen 7 16gb 512gb 15.6 Color Arctic Grey</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-lenovo-ideapad-slim-3-amd-ryzen-7-16gb-512gb-156-color-arctic-grey/p/MCO37810549?highlight=true&amp;headerTopBrand=true#polycard_client=search-nordic&amp;searchVariation=MCO37810549&amp;position=34&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO2779010778&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2089900</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2499000</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>16% OFF</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K29" t="n">
+        <v>15</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_909281-MLU77515509327_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_677423-MLU77126524991_062024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_635914-MLU77515154279_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_971628-MLU77300455380_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_633279-MLU76917265854_062024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '03 ene. 2025', 'contenido': 'Acabo de recibirlo. Todo en orden hasta el momento.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '30 may. 2025', 'contenido': 'Es muy lindo, hasta el momento se ve todo muy bien, es rápido y cumple con lo descrito.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '14 abr. 2025', 'contenido': 'Excelente producto como esperaba, muy buena mi compra.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '06 feb. 2025', 'contenido': 'Excelente equipo para tareas no tan exigentes. Funciona correcto.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>45809.69780253472</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>LENOVO</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Portatil Lenovo V14 Ryzen 5-7520u 16gb 512gb Ssd 14 Fhd W11 Color Gris</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-lenovo-v14-ryzen-5-7520u-16gb-512gb-ssd-14-fhd-w11-color-gris/p/MCO45053079?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO45053079&amp;position=36&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO2871737532&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1563436</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1799889</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>13% OFF</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H30" t="b">
+        <v>1</v>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K30" t="n">
+        <v>67</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_973188-MLA81586990965_122024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_835175-MLA81317920492_122024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_739569-MLA81318127024_122024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '09 may. 2024', 'contenido': 'Cómo lo dice la descripción si necesitan editar no es recomendable por la tarjeta de video que trae de resto bien.', 'votos_utiles': '4'}, {'calificacion': 5, 'fecha': '20 sep. 2024', 'contenido': '', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '06 abr. 2024', 'contenido': 'Tuve problemas ,pero le dieron soporte técnico.\nNo funcionó para un juego.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '28 dic. 2024', 'contenido': 'Es excelente, igual a la descripción, aunque apenas lo empezamos a usar tenemos una buena impresión de él y por su precio es magnífico.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '11 feb. 2024', 'contenido': 'Excelente producto 👌🏻.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>45809.6978025463</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Notebook Gamer Hp Victus Geforce Rtx 3050 Intel Core I5 12450h Ram 8gb 512gb Ssd 15.6 Windows 11 Home Teclado En Ingles</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/notebook-gamer-hp-victus-geforce-rtx-3050-intel-core-i5-12450h-ram-8gb-512gb-ssd-156-windows-11-home-teclado-en-ingles/p/MCO38663805?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO38663805&amp;position=24&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO2806196396&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2859287</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H31" t="b">
+        <v>1</v>
+      </c>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K31" t="n">
+        <v>9</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_641788-MLU77760151986_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_819035-MLU77980686613_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_898014-MLU77980513409_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_603791-MLU77980609361_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_688727-MLU77980686653_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_964238-MLU77980513423_072024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '16 abr. 2025', 'contenido': '', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '17 may. 2025', 'contenido': 'Funciona bien hasta ahora.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '24 abr. 2025', 'contenido': 'Oportuno y de calidad.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>45809.6978025463</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>LENOVO</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Laptop Lenovo V14 G3 Core I7 Ram 16gb Ssd 512gb Windows 11p Color Gris</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/laptop-lenovo-v14-g3-core-i7-ram-16gb-ssd-512gb-windows-11p-color-gris/p/MCO26889377?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO26889377&amp;position=31&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO2862177114&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2822111</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H32" t="b">
+        <v>1</v>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>5</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_738596-MLU77745865439_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_790574-MLU77745865443_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_711353-MLU71542677954_092023-F.webp']</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>45809.69780255787</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Portátil HP Pavilion 15-eg2502la Intel Core i5, 8GB RAM, 512GB SSD FHD Windows 11 Home Single Language 15.6"</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-hp-pavilion-15-eg2502la-intel-core-i5-8gb-ram-512gb-ssd-fhd-windows-11-home-single-language-156/p/MCO43617108?highlight=true&amp;headerTopBrand=true#polycard_client=search-nordic&amp;searchVariation=MCO43617108&amp;position=37&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO1533188369&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1999900</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3999900</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>50% OFF</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H33" t="b">
+        <v>1</v>
+      </c>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>5</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_869128-MLA82657660240_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_604498-MLA82657699012_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_847044-MLA80907670179_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_990362-MLA80644182686_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_745759-MLA82657660244_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_711980-MLA80644326096_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_815064-MLA80907728731_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_772797-MLA82657612892_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_705589-MLA82657688828_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_736084-MLA82657660248_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_687884-MLA82657660252_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_779975-MLA82944618805_032025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>45809.69780256945</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>LENOVO</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Laptop Lenovo V15 G4 15.6 Fhd, Amd Ryzen 5 7520u 16gb 512gb Color Gris Oscuro</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/laptop-lenovo-v15-g4-156-fhd-amd-ryzen-5-7520u-16gb-512gb-color-gris-oscuro/p/MCO38471251?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO38471251&amp;position=23&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO2847347768&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1799000</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2599000</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>30% OFF</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H34" t="b">
+        <v>1</v>
+      </c>
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>5</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_985927-MLA83785959761_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_652695-MLA83493369896_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_864036-MLA83493369908_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_869464-MLA83786028359_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_859104-MLU77594784568_072024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>45809.69780258102</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ASUS</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Asus X1504ZA-NJ Portatil Vivobook Core I3 1215u 12gb Ssd 512gb Color Gris</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/asus-x1504za-nj-portatil-vivobook-core-i3-1215u-12gb-ssd-512gb-color-gris/p/MCO41209434?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO41209434&amp;position=41&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO2855495740&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1789900</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H35" t="b">
+        <v>1</v>
+      </c>
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K35" t="n">
+        <v>155</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_810314-MLA79572310599_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_759250-MLA79572181493_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_980329-MLA79328451606_092024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '04 feb. 2025', 'contenido': 'Buen diseño y rendimiento, mal por no traer windows con una licencia válida.', 'votos_utiles': '4'}, {'calificacion': 5, 'fecha': '12 mar. 2025', 'contenido': 'El portátil me parece excelente pero lo malo es que dice tener teclado retroiluminado fue una de las razones por la que lo compre pero después de tanto buscar resulta que no tiene mi única petición es que por favor pongan correctamente las especificaciones para evitar molestias por parte de los compradores muchas gracias.', 'votos_utiles': '3'}, {'calificacion': 5, 'fecha': '05 feb. 2025', 'contenido': 'Excelente producto, muy buena calidad, excelente precio.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '29 mar. 2025', 'contenido': 'El producto está bien, todo correcto excepto que el windows venía preactivado con un programa se terceros lo que podria haber comprometido la seguridad del sistema. Dejen que cada cliente se encargue de activar el windows si es que el equipo no lo trae preactivado de fabrica, pero no le metan esos programas de terceros para activar, mal ahi con ese tema.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '22 ene. 2025', 'contenido': 'Excelente.', 'votos_utiles': '1'}]</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>45809.69780259259</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Portátil Hp 14-em0009la R5 Ram 16gb 512gb Ssd</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-hp-14-em0009la-r5-ram-16gb-512gb-ssd/p/MCO27712926?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO27712926&amp;backend_model=search-backend&amp;position=44&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO2503419712&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1770900</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2248125</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>21% OFF</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H36" t="b">
+        <v>1</v>
+      </c>
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K36" t="n">
+        <v>20</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_971993-MLU72165226628_102023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_895690-MLU72226746163_102023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_971777-MLU72165196948_102023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_716188-MLU75004584385_032024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '21 dic. 2024', 'contenido': 'Excelente producto.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '31 oct. 2024', 'contenido': 'Por el momento cumple con lo prometido 👍🏽👍🏽.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '29 oct. 2024', 'contenido': 'Me pareció muy bueno en rendimiento y durabilidad de la batería.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '10 oct. 2024', 'contenido': 'Muy bueno, necesitaba un dispositivo para mí estudio y trabajo eficiente y asequible. Está máquina se ha comportado muy bien, muchas gracias 🫂.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '09 oct. 2024', 'contenido': 'Venía con windows 11 pre instalado pero le instalamos windows 10. Hp oficialmente solo da soporte para windows 11 sin embargo los drivers funcionan sin problema en windows 10.\nEl equipo nos pareció excelente por el precio es bastante fluido, el color es un plateado dorado que lo hace ver elegante y es muy ligero y silencioso, la batería nos duró más de 2 horas y aún tenía la mitad de la carga.\nInstalamos photoshop 2024 y corre sin problema las 16 gb de ram permiten tener varios programas abiertos sin que el equipo sufra en rendimiento.\nEstamos muy satisfechos con la compra, esperemos a ver cuánto dura el equipo en buenas condiciones.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>45809.69780260417</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MacBook Air Apple Plateada Chip M1 - 13.3'' 256gb + 8gb Ram Color Plata</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/macbook-air-apple-plateada-chip-m1-133-256gb-8gb-ram-color-plata/p/MCO23897874?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO23897874&amp;position=52&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO1542965083&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>3136711</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3336927</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>6% OFF</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H37" t="b">
+        <v>1</v>
+      </c>
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K37" t="n">
+        <v>7</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_927163-MLA48622311771_122021-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_877821-MLA48622311780_122021-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_895758-MLU75330635714_032024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_613244-MLA52006428745_102022-F.webp']</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '04 may. 2022', 'contenido': 'La verdad es que es una super máquina, super fluido para casi todo los programas que uso, excelente para edición de video e imagines, la pantalla es una belleza, para programación 10 de 10. Un portátil que le puede funcionar a cualquiera para trabajar o estudiar, la autonomía es increíble nunca había tenido un portátil que le durará tanto la batería. Aguanta todo un día sin cargar. Eso sí para juegos no es tan bueno, por la refrigeración y el tema de los puertos tipo usb c si es algo molesto, pero con un convertidor se soluciona sin ningún problema. En mi opinión es el mejor portátil relación precio calidad y si tienes un ipad compatible es una experiencia única trabajar con los 2 dispositivos. Estéticamente también es una belleza. Sin duda alguna es una excelente inversion.', 'votos_utiles': '16'}, {'calificacion': 5, 'fecha': '28 oct. 2023', 'contenido': 'Excelente. La única observación es que el teclado no está en español, como dice la descripción del producto. De resto, todo perfecto.', 'votos_utiles': '5'}, {'calificacion': 5, 'fecha': '21 ene. 2023', 'contenido': 'Ese mac es muy bueno la verdad quede encantado, lo malo es que casi no trae para conectarle cosas y todo toca compralo por aparte y obviamente costoso.', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '22 ene. 2025', 'contenido': 'Excelente producto muy rápido y excelente rendimiento.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '25 ago. 2022', 'contenido': 'Muy buen producto, es original y funciona muy bien.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>45809.69780260417</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>LENOVO</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Portátil Lenovo Loq I5 12450hx Rtx 3050 Ram 24gb M.2 512gb Color Gris</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-lenovo-loq-i5-12450hx-rtx-3050-ram-24gb-m2-512gb-color-gris/p/MCO45171417?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO45171417&amp;position=32&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO2330572176&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>3391900</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3999000</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>15% OFF</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Envío gratis</t>
-        </is>
-      </c>
-      <c r="H11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_806430-MLA81431205572_122024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_636597-MLA82479025889_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_752807-MLA82478968071_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_899959-MLA82478941533_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_678323-MLA82478968095_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_762905-MLA82479025859_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_686051-MLA82478941575_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_629643-MLA82478968169_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_848904-MLA84026494874_052025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_614756-MLA84321552659_052025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_959549-MLA84321552663_052025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_739424-MLA84026494876_052025-F.webp']</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>[{'calificacion': 5, 'fecha': '08 abr. 2025', 'contenido': 'Excelente , calidad y todo.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '29 may. 2025', 'contenido': 'Excelente teclado para el precio, el recorrido es bastante alto por lo que no es para todo el mundo y los switches no son tan silenciosos, pero en luces y calidad es excelente, sin contar con que permite extraer keycaps fácilmente y el frente es metálico, muy buen producto.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '10 abr. 2025', 'contenido': '', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '05 may. 2025', 'contenido': 'Muy bueno.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '27 abr. 2025', 'contenido': 'Exelente.', 'votos_utiles': '0'}]</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="n">
-        <v>45809.68173771294</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H38" t="b">
+        <v>1</v>
+      </c>
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_987364-MLA81403229692_122024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_974590-MLA81672868677_122024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '14 ene. 2025', 'contenido': 'La verdad el mejor portátil calidad precio para este 2025, teniendo en cuenta el precio considero la pantalla, diseño, potencia y en general el equipo lo mejor de lo mejor, lo único medio flojo es el audio pero bueno con ese precio que más podemos pedir, recomendado 100% para estudio y trabajo,superó mis expectativas!.', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '12 ene. 2025', 'contenido': 'Muy buen producto, aunque tiene fugas de luz la pantalla, es normal en pantallas ips pero son equipos muy costosos para que tengan estos problemas.', 'votos_utiles': '2'}]</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>45809.69780261574</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>DELL</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Portátil Computador Dell Intel Core I3 Ssd 512gb Ram 16gb Color Plateado</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-computador-dell-intel-core-i3-ssd-512gb-ram-16gb-color-plateado/p/MCO36040434?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO36040434&amp;position=40&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO1590497761&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1539900</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H39" t="b">
+        <v>1</v>
+      </c>
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>5</v>
+      </c>
+      <c r="K39" t="n">
+        <v>12</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_770176-MLU75931401003_042024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_831397-MLU75931450311_042024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_756128-MLU75931489827_042024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_968122-MLU75931401031_042024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '09 oct. 2024', 'contenido': 'Hasta hora todo bien cumple su función.', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '30 abr. 2025', 'contenido': 'Excelente!! muy bonito el portatil, viene bien empacado. Recomendado.\nBeneficio calidad/precio 10/10.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '03 abr. 2025', 'contenido': 'Excelente.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '28 feb. 2025', 'contenido': 'Excelente producto, vale la pena la compra.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '09 ene. 2025', 'contenido': 'Excelente.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="n">
+        <v>45809.69780262731</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Portátil HP 15-fc0031la AMD Ryzen 7 16 GB RAM 1 TB SSD 15.6" FHD Windows 11 Home</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-hp-15-fc0031la-amd-ryzen-7-16-gb-ram-1-tb-ssd-156-fhd-windows-11-home/p/MCO46955411?highlight=true&amp;headerTopBrand=true#polycard_client=search-nordic&amp;searchVariation=MCO46955411&amp;backend_model=search-backend&amp;position=33&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO1575771851&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>4099900</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H40" t="b">
+        <v>1</v>
+      </c>
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>5</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_815916-MLA82945757783_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_874654-MLA84247757623_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_625769-MLA82945757787_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_660337-MLA82945757789_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_632767-MLA83952776642_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_952877-MLA83952474652_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_743470-MLA83952484392_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_832640-MLA83952474656_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_693165-MLA83952513586_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_900626-MLA83952484400_042025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '29 may. 2025', 'contenido': 'Excelente, tal como lo esperaba, totalmente empacado y con protección en la caja. Encantado.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="n">
+        <v>45809.69780263889</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ACER</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Portátil Acer A314 Core I3 N305 Ram 8gb / 512gb Ssd Pant 14 Color Plateado</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-acer-a314-core-i3-n305-ram-8gb-512gb-ssd-pant-14-color-plateado/p/MCO26314505?highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO26314505&amp;position=51&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO1507994095&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1441900</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1699000</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>15% OFF</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H41" t="b">
+        <v>1</v>
+      </c>
+      <c r="I41" t="b">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>5</v>
+      </c>
+      <c r="K41" t="n">
+        <v>5</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_604376-MLU71250039543_082023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_672975-MLU71250039539_082023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_906856-MLU71250039513_082023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_671038-MLU71250039531_082023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_923047-MLU71250039519_082023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_979669-MLU75008026861_032024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="n">
+        <v>45809.69780263889</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>DELL</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Portatil Dell 12ava Gen Intel I5 1235u Ram 16g Ssd 512gb Fhd</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://articulo.mercadolibre.com.co/MCO-2195229740-portatil-dell-12ava-gen-intel-i5-1235u-ram-16g-ssd-512gb-fhd-_JM?searchVariation=185116985227&amp;highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=185116985227&amp;position=58&amp;search_layout=stack&amp;type=item&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1788288</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2714143</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>34% OFF</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H42" t="b">
+        <v>1</v>
+      </c>
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K42" t="n">
+        <v>47</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_904912-MCO83799180877_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_622595-MCO79584034437_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_779638-MCO79340867374_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_962550-MCO79340837530_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_644458-MCO79583984351_092024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '02 ene. 2025', 'contenido': 'El equipo es de buena marca y sus características son buenas, hasta el momento no hay nada que resolver,.', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '25 ene. 2025', 'contenido': 'Los productos que contienen lo de mercadolibre son muy buenos.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '06 sep. 2024', 'contenido': 'Me pareció perfecto, tiene dos slots para aumentarle la ram en un futuro. Velocidad buena.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '15 jul. 2024', 'contenido': 'Computador calidad precio fluido para trabajar y estudiar. Una semana de uso.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '10 abr. 2024', 'contenido': 'Bien.', 'votos_utiles': '1'}]</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>45809.69780265047</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ACER</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Portatil Acer Anv15-core I7-13620h-16gb 512gbssd-rtx4060 W11 Color Negro</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-acer-anv15-core-i7-13620h-16gb-512gbssd-rtx4060-w11-color-negro/p/MCO40349136?highlight=true&amp;headerTopBrand=true#polycard_client=search-nordic&amp;searchVariation=MCO40349136&amp;position=39&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO2838784016&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>4599900</v>
+      </c>
+      <c r="E43" t="n">
+        <v>5499000</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>16% OFF</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H43" t="b">
+        <v>1</v>
+      </c>
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>5</v>
+      </c>
+      <c r="K43" t="n">
+        <v>5</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_666931-MLA84520656400_052025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_959367-MLA84520656408_052025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="n">
+        <v>45809.69780266203</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Portátil HP 14-em0021la AMD Ryzen 5 16 GB RAM 512 GB SSD 14" FHD Windows 11 Home</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-hp-14-em0021la-amd-ryzen-5-16-gb-ram-512-gb-ssd-14-fhd-windows-11-home/p/MCO40677703?highlight=true&amp;headerTopBrand=true#polycard_client=search-nordic&amp;searchVariation=MCO40677703&amp;position=46&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO2839966264&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>3769900</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H44" t="b">
+        <v>1</v>
+      </c>
+      <c r="I44" t="b">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_885614-MLA80402372726_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_985307-MLA83016946286_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_766946-MLA80661827215_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_653332-MLA80661827223_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_825145-MLA83016946296_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_960757-MLA83306630973_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_729130-MLA83306715903_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_822188-MLA83016946340_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_975250-MLA83306621309_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_669244-MLA83306650235_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_669468-MLA83306631061_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_854122-MLA83306650311_032025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="n">
+        <v>45809.69780267361</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>DELL</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Potátil Inspiron 3520 15.6" color plateado 24GB de Ram - 1TB SSD - Intel Core i5</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/potatil-inspiron-3520-156-color-plateado-24gb-de-ram-1tb-ssd-intel-core-i5/p/MCO28036809?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO28036809&amp;position=42&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO2877609362&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2224671</v>
+      </c>
+      <c r="E45" t="n">
+        <v>3370714</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>34% OFF</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H45" t="b">
+        <v>1</v>
+      </c>
+      <c r="I45" t="b">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K45" t="n">
+        <v>61</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_614295-MLA83382157596_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_699565-MLA83382224918_042025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '28 may. 2024', 'contenido': 'Excelente equipo, con una excelente pantalla 1080p a 120hz, buen procesador y buena ram por el precio comparado con otros equipos del mismo rango.', 'votos_utiles': '3'}, {'calificacion': 5, 'fecha': '27 ago. 2024', 'contenido': 'Muy buen portátil, enciende y apaga muy rápido, programas de edición de fotos como photoshop y corel funcionan muy bien, al igual que programas de edición de vídeo y autocad, la imagen se ve muy bien y es muy liviano.', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '05 ene. 2024', 'contenido': '', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '22 feb. 2025', 'contenido': 'Super bueno, me encantó.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '04 sep. 2024', 'contenido': 'Bastante minimalista el diseño y los materiales, pero parece bueno, habrá que esperar.', 'votos_utiles': '1'}]</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="n">
+        <v>45809.69780267361</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>LENOVO</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Portátil Lenovo Loq 15iax9e Intel Core i5-12450HX 16 GB 512 GB SSD Rtx 3050 Linux 15.6 - 83 mes00000 Luna Grey</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-lenovo-loq-15iax9e-intel-core-i5-12450hx-16-gb-512-gb-ssd-rtx-3050-linux-156-83-mes00000-luna-grey/p/MCO46041404?highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO46041404&amp;position=48&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO1565833163&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>3259900</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H46" t="b">
+        <v>1</v>
+      </c>
+      <c r="I46" t="b">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K46" t="n">
+        <v>4</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_616917-MLA82397783055_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_964751-MLA82397753819_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_611356-MLA82115164154_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_633128-MLA82397783073_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_896739-MLA82115164168_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_842018-MLA82397916241_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_612272-MLA82397879409_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_928102-MLA82397783113_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_968942-MLA82115164238_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_892696-MLA82397753943_022025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '12 may. 2025', 'contenido': 'Aún lo estoy probando, de momento se comporta bien, la batería no dura nada, alrededor de una 1,3 hora.', 'votos_utiles': '1'}]</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="n">
+        <v>45809.69780268519</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>LENOVO</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Potátil V-Series V14 14" color gris 24GB de Ram - 512GB SSD - Intel Core i5</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/potatil-v-series-v14-14-color-gris-24gb-de-ram-512gb-ssd-intel-core-i5/p/MCO36489354?highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO36489354&amp;position=43&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO2865692140&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2070000</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H47" t="b">
+        <v>1</v>
+      </c>
+      <c r="I47" t="b">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K47" t="n">
+        <v>166</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_891965-MLA76136106233_052024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_774211-MLA76135753897_052024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_687923-MLA76135753913_052024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_761956-MLA76136115989_052024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_964160-MLA76136115991_052024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_695480-MLA76136106261_052024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_716461-MLA76136115995_052024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '30 ago. 2024', 'contenido': 'Melo, lo que si queda corto es la definición de la pantalla, pero por el precio está bien.', 'votos_utiles': '8'}, {'calificacion': 5, 'fecha': '16 sep. 2024', 'contenido': 'Me parece que la beteria le dura muy poco y me parece que se caliente bastante usándolo para cosas que no deberían su ponerle problemas como ver un directo twitch.', 'votos_utiles': '7'}, {'calificacion': 5, 'fecha': '12 ago. 2024', 'contenido': 'Muy bueno en cuanto a calidad/precio, se siente de materiales de calidad y muy liviano, respecto a la batería no dura mucho pero carga bastante rápido. Se siente fluido y trabaja de manera eficiente, no es ruidoso ni se calienta en exceso.', 'votos_utiles': '3'}, {'calificacion': 5, 'fecha': '31 ago. 2024', 'contenido': 'Execelente producto, potente y rápido.', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '28 nov. 2024', 'contenido': 'Excelente equipo !!!.', 'votos_utiles': '2'}]</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="n">
+        <v>45809.69780269676</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ASUS</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Laptop Asus Tuf Ryzen 5 7535hs 8gb 512gb 15.6 4gb Color Negro</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/laptop-asus-tuf-ryzen-5-7535hs-8gb-512gb-156-4gb-color-negro/p/MCO37560222?highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO37560222&amp;position=49&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO2822482712&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>3146900</v>
+      </c>
+      <c r="E48" t="n">
+        <v>3599000</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>12% OFF</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H48" t="b">
+        <v>1</v>
+      </c>
+      <c r="I48" t="b">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>5</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_632438-MLU76685957420_062024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_602733-MLU76685869256_062024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_774402-MLU76685821260_062024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_764964-MLU76889306417_062024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_662416-MLU76889306427_062024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="n">
+        <v>45809.69780270833</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ASUS</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Portatil Gamer Asus Tuf Ryzen 5 7535h Ram 24gb Ssd 512 Rtx 2050 4gb</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-gamer-asus-tuf-ryzen-5-7535h-ram-24gb-ssd-512-rtx-2050-4gb/p/MCO37325847?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO37325847&amp;position=45&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO2882510508&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>2980000</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H49" t="b">
+        <v>1</v>
+      </c>
+      <c r="I49" t="b">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K49" t="n">
+        <v>39</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_963857-MLU76731619781_052024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_966626-MLU76532971772_052024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_898773-MLU76532961934_052024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_978495-MLU76731454031_052024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_720531-MLU76532971808_052024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_961833-MLU76533000928_052024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_797769-MLU76731454073_052024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_710973-MLU76731454119_052024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_600399-MLU76731619919_052024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '09 oct. 2024', 'contenido': 'Pues la verdad muy contento pero pues temas de batería es compresible la perdida media de carga.\nConsejo descargar la app myasus hay automáticamente actualiza cosillas para que se armonice todo.\nOtra app para mirar graficas y estado del equipo es armony crate, tiene bastante funcionalidades. Pero para mejor equilibrio y evitar apagados repentinos borrar armony e instalar ghelper poderosa y super funcional mejora en creces hasta la temperatura. La opción esta en sus manos.', 'votos_utiles': '14'}, {'calificacion': 5, 'fecha': '06 dic. 2024', 'contenido': 'Muy bueno , rápido.\nNo me gustó que estuviera modificado y no se diga en la descripción nada de eso. Tenía unas manchas de grasa de mano en el teclado.\nNo es nuevo. Ya la caja había sido abierta. Pero es bueno el producto y por eso no lo devolví. Muy rápido y tiene licencia de windows. Hasta ahora todo bien con el producto.', 'votos_utiles': '4'}, {'calificacion': 5, 'fecha': '16 dic. 2024', 'contenido': 'Llevo unas cuantas semanas con el y puedo decir que no me arrepiento de comprarlo, las puesto pruebas que le e hecho las pasa muy bien con sola una excepción y es la duración de la batería. Lo recomiendo si buscas una laptop confiable.', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '07 ene. 2025', 'contenido': 'Excelente, muy buen rendimiento, me corre todo y con muy buena calidad gráfica, consejo adicional que me salvó el de armory crate, puede hacer que no detecte la gpu o se apague de repente, mejor buscar alternativas.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '17 ene. 2025', 'contenido': '', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="n">
+        <v>45809.69780270833</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Apple MacBook Air 2020 13 pulgadas Chip M1 256 GB de SSD 8 GB de RAM Color Plata</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/apple-macbook-air-2020-13-pulgadas-chip-m1-256-gb-de-ssd-8-gb-de-ram-color-plata/p/MCO17828520?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO17828520&amp;position=47&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO1575243473&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>3115500</v>
+      </c>
+      <c r="E50" t="n">
+        <v>3350000</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>7% OFF</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H50" t="b">
+        <v>1</v>
+      </c>
+      <c r="I50" t="b">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K50" t="n">
+        <v>382</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_648428-MLA46516517286_062021-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_895726-MLU75293694793_032024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_961511-MLA46516517289_062021-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_769401-MLU75147183330_032024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_981204-MLU70064738229_062023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_671110-MLU70064738261_062023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_894288-MLU70064738283_062023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_990274-MLU70064710555_062023-F.webp']</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '20 ene. 2022', 'contenido': 'Excelente, no estaba confiada de comprar este tipo de productos en una página que no fuera mac o apple, pero realmente vale la pena, 100% recomendado.', 'votos_utiles': '25'}, {'calificacion': 5, 'fecha': '20 oct. 2023', 'contenido': 'La mejor compra que pude haber hecho! me ahorre un montón comprándolo con ellos, todo fue muy seguro y confiable, el equipo es brutal, mejor de lo que pensé a decir verdad y pude actualizar la garantía de apple, para que la vigencia de la garantía iniciara desde el momento en que tuve el computador sin ningún problema.', 'votos_utiles': '18'}, {'calificacion': 5, 'fecha': '27 sep. 2021', 'contenido': 'Viene con el empaque original, es una belleza xd. Super recomendado!!!.', 'votos_utiles': '14'}, {'calificacion': 5, 'fecha': '01 dic. 2023', 'contenido': 'Con un mes de uso les puedo decir que fue una buena compra, corren súper bien los programas, la suite de adobe, ¡muy bueno!.\nDe pronto recomendaría que al enviarlo se protegiera un poco más, enviarlo en una caja adicional y no envuelto en vinipel, pero no hay queja es un buen producto.', 'votos_utiles': '9'}, {'calificacion': 5, 'fecha': '17 may. 2022', 'contenido': 'Muy bueno. El procesador m1 de apple es silencioso, no se calienta y realmente hace que la batería dure, con un trabajo fuerte, unas 6 horas continuas. Si se usa moderadamente, puede llegar hasta las 10 horas. El tamaño es perfecto y la pantalla muy descansada.', 'votos_utiles': '7'}]</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="n">
+        <v>45809.69780271991</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Portátil HP 14-ep1001la Intel Core Ultra 5 8GB RAM 512GB SSD FHD Windows 11 Home Single Language 14"</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-hp-14-ep1001la-intel-core-ultra-5-8gb-ram-512gb-ssd-fhd-windows-11-home-single-language-14/p/MCO39104210?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO39104210&amp;position=50&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO1573232957&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2374900</v>
+      </c>
+      <c r="E51" t="n">
+        <v>3599000</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>34% OFF</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H51" t="b">
+        <v>1</v>
+      </c>
+      <c r="I51" t="b">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K51" t="n">
+        <v>9</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_891264-MLA82657660270_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_849962-MLU77996429170_082024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_731493-MLU78221428597_082024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_738184-MLU77996360028_082024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_683780-MLU77996605068_082024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_793058-MLU77996605044_082024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_939224-MLA82657699054_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_767580-MLA78990180702_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_637994-MLA78990239604_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_721348-MLA82657660276_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_718870-MLA78990200374_092024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '02 mar. 2025', 'contenido': 'Muy bueno, y aún buen precio.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '25 feb. 2025', 'contenido': 'La imagen no es tan buena y la batería no dura mucho.\nQué lástima la inversión.', 'votos_utiles': '2'}]</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="n">
+        <v>45809.69780273148</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Notebook Hp Victus Gamer Amd Ryzen 5-8645hs Nvidia Geforce Rtx 4050 8gb Ddr5 512gb Ssd 15.6 Inch Fhd Ips 144hz Gaming</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/notebook-hp-victus-gamer-amd-ryzen-5-8645hs-nvidia-geforce-rtx-4050-8gb-ddr5-512gb-ssd-156-inch-fhd-ips-144hz-gaming/p/MCO38292652?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO38292652&amp;position=53&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO2566409674&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>3685030</v>
+      </c>
+      <c r="E52" t="n">
+        <v>3799000</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>3% OFF</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H52" t="b">
+        <v>1</v>
+      </c>
+      <c r="I52" t="b">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>5</v>
+      </c>
+      <c r="K52" t="n">
+        <v>14</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_648973-MLA79440868945_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_866568-MLA79198224468_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_703876-MLA79198515124_092024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '16 oct. 2024', 'contenido': 'El producto llega en su caja original, el rendimiento es excelente, tiene una sola memoria ram de 8gb, recomendable comprar la otra para mejorar aún más, el cargador que incluye es el de 200w mide aproximadamente 3 mtrs y tener en cuenta que el teclado no tiene la ñ es tipo inglés, todo me ha salido bien con el pc, sin problemas.', 'votos_utiles': '8'}, {'calificacion': 5, 'fecha': '02 sep. 2024', 'contenido': 'Excelente, la batería en modo eco dura hasta 8 horas de trabajo continuo y conectado es excelente para jugar.', 'votos_utiles': '5'}, {'calificacion': 5, 'fecha': '10 oct. 2024', 'contenido': 'Me encantó la máquina, muchos computadores se centran demasiado en lo estético y descuidan para lo que realmente se va a usar.\nEl rendimiento ha sido muy bueno.', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '07 nov. 2024', 'contenido': 'De momento todo en perfecto estado. Al revisar los componentes todo es exactamente como se anuncia. Muy satisfecho con el producto, gracias.\nComo pequeña recomendación, sería bueno que la caja la envuelvan en plastico de burbujas para evitar problemas con la transportadora y golpes.', 'votos_utiles': '1'}]</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="n">
+        <v>45809.69780274305</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ASUS</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Laptop Asus Vivobook X1605va I9-13900h Ram 16gb Ssd 1tb Color Negro</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/laptop-asus-vivobook-x1605va-i9-13900h-ram-16gb-ssd-1tb-color-negro/p/MCO25584449?highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO25584449&amp;position=54&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO1426529711&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H53" t="b">
+        <v>1</v>
+      </c>
+      <c r="I53" t="b">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K53" t="n">
+        <v>12</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_732063-MLU78704454934_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_825976-MLU78704405212_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_751240-MLA75983733505_042024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '07 oct. 2024', 'contenido': 'Batería 3.\nVelocidad 4.\nImagen 5.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '14 abr. 2025', 'contenido': 'Muy bueno!.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '29 mar. 2025', 'contenido': 'Llevo 1 mes y el equipo se ha comportado bien. Buen precio y calidad.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '15 nov. 2024', 'contenido': 'Muy buen equipo, rápido.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '05 feb. 2025', 'contenido': 'Se recalienta mucho el portátil, y el cargador más. La batería no dura nada.', 'votos_utiles': '3'}]</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="n">
+        <v>45809.69780274305</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Apple Macbook Air 13.6 256gb Ssd / 16gb M3 Chip - Midnight</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/apple-macbook-air-136-256gb-ssd-16gb-m3-chip-midnight/p/MCO44961636?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO44961636&amp;position=55&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO1569020689&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>4749799</v>
+      </c>
+      <c r="E54" t="n">
+        <v>5587999</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>15% OFF</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H54" t="b">
+        <v>1</v>
+      </c>
+      <c r="I54" t="b">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>5</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_766778-MLA82142235314_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_947233-MLA81245110590_122024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_975109-MLA81245129904_122024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_652674-MLA81245110594_122024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="n">
+        <v>45809.69780275463</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ACER</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Computador Portatil Gamer Acer Nitro V 15 Negro Intel Core I9 13900h 16gb De Ram 512gb Ssd Nvidia Geforce Rtx 4060 8gb 144 Hz 1920x1080px Windows 11 Home</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/computador-portatil-gamer-acer-nitro-v-15-negro-intel-core-i9-13900h-16gb-de-ram-512gb-ssd-nvidia-geforce-rtx-4060-8gb-144-hz-1920x1080px-windows-11-home/p/MCO46514886?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO46514886&amp;position=56&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO2831701728&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>5549149</v>
+      </c>
+      <c r="E55" t="n">
+        <v>6234999</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>11% OFF</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H55" t="b">
+        <v>1</v>
+      </c>
+      <c r="I55" t="b">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K55" t="n">
+        <v>5</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_887040-MLA82770467139_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_682918-MLA82770419211_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_861262-MLA82484322004_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_934348-MLA82484322006_022025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '07 may. 2025', 'contenido': 'Excelente todo. Yo le meti todas las 64 de ram y un tb adicional ssd m2, y para mi trabajo y gamer al pelo.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '16 abr. 2025', 'contenido': 'Independientemente de los componentes que traiga la contruccion del v15 esta algo mal pensada, la mayoria del aire caliente sale en direccion a la pantalla calentandola.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="n">
+        <v>45809.6978027662</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Laptop Gamer Hp Victus 15.6 144hz Ryzen 5 8645hs 16 Ram 512 Ssd Nvidia Geforce Rtx 4050 6 Gb</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/laptop-gamer-hp-victus-156-144hz-ryzen-5-8645hs-16-ram-512-ssd-nvidia-geforce-rtx-4050-6-gb/p/MCO38762807?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO38762807&amp;position=57&amp;search_layout=stack&amp;type=product&amp;tracking_id=c1118f62-c899-4a8e-856a-abe30fb24cc2&amp;wid=MCO2843445534&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>3959120</v>
+      </c>
+      <c r="E56" t="n">
+        <v>4499000</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>12% OFF</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H56" t="b">
+        <v>1</v>
+      </c>
+      <c r="I56" t="b">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>5</v>
+      </c>
+      <c r="K56" t="n">
+        <v>14</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_716074-MLU78067607047_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_964822-MLU78067394135_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_785280-MLU78067394139_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_747408-MLU78067685245_072024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '16 oct. 2024', 'contenido': 'El producto llega en su caja original, el rendimiento es excelente, tiene una sola memoria ram de 8gb, recomendable comprar la otra para mejorar aún más, el cargador que incluye es el de 200w mide aproximadamente 3 mtrs y tener en cuenta que el teclado no tiene la ñ es tipo inglés, todo me ha salido bien con el pc, sin problemas.', 'votos_utiles': '8'}, {'calificacion': 5, 'fecha': '02 sep. 2024', 'contenido': 'Excelente, la batería en modo eco dura hasta 8 horas de trabajo continuo y conectado es excelente para jugar.', 'votos_utiles': '5'}, {'calificacion': 5, 'fecha': '10 oct. 2024', 'contenido': 'Me encantó la máquina, muchos computadores se centran demasiado en lo estético y descuidan para lo que realmente se va a usar.\nEl rendimiento ha sido muy bueno.', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '07 nov. 2024', 'contenido': 'De momento todo en perfecto estado. Al revisar los componentes todo es exactamente como se anuncia. Muy satisfecho con el producto, gracias.\nComo pequeña recomendación, sería bueno que la caja la envuelvan en plastico de burbujas para evitar problemas con la transportadora y golpes.', 'votos_utiles': '1'}]</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="n">
+        <v>45809.6978027662</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Portatil Hp 12ava Gen Intel I3 1215u Ssd 512gb Ram 8gb Color Plateado</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=3zk5x4q31HqIsLjewiEl2XhGoTTZBkbtYeWG7ZF3XYFKcVDUaUADHDECIpLJmEvxCMOWNAJ6hznDitILLplhrzEHA3ZiJzB7fjlNIRNsfHJx3AnqNRDfZY%2FVl%2B7KS1S6jgcr4Uw9fqcR31GT3E1%2B2MpAGt23BKfqoLVp8WMzxbTS2aBwVLfP0dT19iaHx5mX6seajZ6evES4a8Gulidh0tOHZo9qylIOPFh8YpdGrTP9vaFlMVVZPniEZQOcr1r6O%2F05mE2PytzONo2e%2FQPj7vvYdqjGkUa3JAqvlknEf4eXjhlcdakvmBatUt8j0wzBZMhSNFbqObl6HOk8Yz2VCcnZevUXxvT0E3RcZ237903ajvXc7sQMrPkDuRqgQisFpYhR5tripnvFRABPepKbT7wuB5%2B8GlzLUlFgZP4kj1p4GALzbyZYs1kT7lrru6RfwM6FA18%2FdYpFXmqtJYGy8nj3JJR1hd5AUgmp51CAzLz%2F2zlCegf9UojOfa0GXmy%2FMIV%2BuHIWzcy2boi89i4TcFslXeYKJXVoz0SBnAijGuZbyPW4NRB6TxAXbuOO%2BkB5%2FmXhD390zEsiO%2BAuuVm9ONxCvxlLCkVzP9KMSaLidaJSppEKoXsFn2GmYHUtf9cK4WaRQNGEImCkgWjZE0F3kGf4GRPnAC5k1V1719oK1C8HfoFS7OOkxnFlpcAb859v9xy6UxcBx8hwOAh28ilP8irHD5FipBgFGco7Di0rVpgpxkotGfB0IYlY7K9BQpmA4PFifiZRbjHV2xj5ilBFo54Ux4a5hQ4esSEa61VhYFg%2FayWWE9i5RSJSQqm3TIKuzVq182t8eUHbTYGA9CB6DZMeWEMHBLQ6UH2mIz8RZ%2Bfwo%2BxhFjj23r4q6PgZs7sRjMnAnBNf4YhQHXIMkz54GYiIcnkRy2fUA46KgNzYEjPkE1zM6JUwRVQa7g2hqo4xaEqNdoHWwAaMtgs%3D&amp;highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO1507088307&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1458900</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1853000</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>21% OFF</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H57" t="b">
+        <v>1</v>
+      </c>
+      <c r="I57" t="b">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K57" t="n">
+        <v>54</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_645989-MLU78944581522_092024-V.webp</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_645989-MLU78944581522_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_605957-MLU79183304451_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_641148-MLU78944551828_092024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '16 jul. 2024', 'contenido': 'Excelente producto muy recomendado.', 'votos_utiles': '6'}, {'calificacion': 5, 'fecha': '26 feb. 2025', 'contenido': '', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '21 dic. 2024', 'contenido': 'Me pareció un producto muy bueno y de excelente calidad 😃.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '06 may. 2025', 'contenido': 'Excelente, corresponde la descripción. Satisfecho con la compra.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '24 may. 2025', 'contenido': 'Excelente equipo.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="n">
+        <v>45809.69780278935</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Notebook Hp 245 G10 R3 7330u 512gb Ssd 8gb Ram Windows 11 Ho</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=7aPxKdLlVLYJVAkbZrPExN4riYF3ybbL0HnY2Z0KaA7knmIPiTLNnIYPihzEj60%2FsP2THkFcfnuUj8zP7LN%2FOOI0v%2BXP7vaHbvLzc3cCwYuHOY4Bmpanj%2FkJ%2Fi253XKv6ySOdrZvL4OOPzoaaTzW7PzPS5uHZzUcdlzFgBM8IMAIYxj%2BiSFWwKHAfRYiWyRxIpVpUncbL6JY4L92Rk96bgHFjJWP5hDd2OyMs%2BA%2BN32pPv5bT%2B0waPwBb6VVQJMuAP7V7r0OV1ZebfSktAzRAnsrRFZ20eRHSbBiyxhc4F0Yw8snQAWCPxgYRAVpzwaPk%2Bkjx48KhLjmTf7EKQW5wyzOJ5M6XOCi1Sk8yVvdmpauEKoYd7U4wo9WuBmUJbwrYz8q8c1T6qLD0V%2F943FLke1BaB18KOMGQCbJxabujtnXOANavZHBc%2BNSwxjaBvH90zCFrdpusmB9JyDobFsZOv9zdNimkamqSGxi%2Fc6ytKVqQp8ykz5z2N4o31dUF4FHOdrNKWHscYd8DupNtoAHjdDeySHkdxRvxVC7nKhgj2GpTAJnuNn3u8r8pRf%2BY%2Fd33aABanlXt99l7T3p7fLcYYv9INhC1l12zDrvU7LMZ%2FrVwHSr66eW38ExiGfWd%2BY%2FMpwK1zTdAuRtEf9T3hrjtCZXfCg7U9NMH27lnQZy4E9zJ6FJKg%2BN62CkzfWbire%2B3V2UqeD8%2BhC4DjGQl2DufEvLxpeN9VCghOwFHUo1IEiVY573MRBtFavDOYdNajo93Qm%2BApY20KyzDzKiwefrYVHDhin%2FWBLHm0%2FtHJxggl6IN3feXVUEBKhz8e1V%2FtaM7%2BbSv6LElyh43o3p5DG10nry6QkeFmwHqIQXTNBgnOSp%2BdirVvJFHjrJtP7wQLk1W78Q5GfxBg%2BP4y2ZgU32cFMYalqGtPERS89nkUqXzQ%2Fj7w3EZApaPptqosvQCvyg&amp;highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO1547113843&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1259900</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1621375</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>22% OFF</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H58" t="b">
+        <v>1</v>
+      </c>
+      <c r="I58" t="b">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K58" t="n">
+        <v>21</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_679019-MLU78080956988_082024-V.webp</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_679019-MLU78080956988_082024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_630529-MLU78080779350_082024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_880233-MLU78307689171_082024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_860704-MLU78080957006_082024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '27 may. 2025', 'contenido': 'Buena opcion.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '24 may. 2025', 'contenido': 'Muy bueno.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '19 may. 2025', 'contenido': 'Buen producto calidad - precio.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '13 may. 2025', 'contenido': 'Buen producto unue no veo mucho cambio en el brillo de la pantalla.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '06 may. 2025', 'contenido': 'Excelente.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="n">
+        <v>45809.69780280093</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ASUS</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Portátil Asus Vivobook X1502 Ci5-12500h 24gb Ssd512 Fhd15.6 color Quiet Blue</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-asus-vivobook-x1502-ci5-12500h-24gb-ssd512-fhd156-color-quiet-blue/p/MCO47191661?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO47191661&amp;position=8&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO1569451947&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1929900</v>
+      </c>
+      <c r="E59" t="n">
+        <v>2249000</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>14% OFF</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H59" t="b">
+        <v>1</v>
+      </c>
+      <c r="I59" t="b">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K59" t="n">
+        <v>14</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_877811-MLA83102329491_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_703080-MLA82814024258_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_805571-MLA83102329495_032025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '24 may. 2025', 'contenido': 'Hasta el momento ha funcionado super bien y es bastante rápido, su diseño es muy funcional y práctico para la manipulación. Tiene una buena calidad de imagen y es cómodo para la vista.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '21 may. 2025', 'contenido': 'Excelente.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '19 may. 2025', 'contenido': 'Buen producto.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '19 may. 2025', 'contenido': 'Un super equipo, en relación precio-calidad, muy rápido y bonito.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="n">
+        <v>45809.69780280093</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>LENOVO</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Lenovo Ideapad 1 Ip 1 15igl7 Intel Celeron N4020 15,6 Pulgadas 8 GB Ram</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/lenovo-ideapad-1-ip-1-15igl7-intel-celeron-n4020-156-pulgadas-8-gb-ram/p/MCO40332473?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO40332473&amp;position=4&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO2864083698&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1016900</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>32% OFF</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H60" t="b">
+        <v>1</v>
+      </c>
+      <c r="I60" t="b">
+        <v>0</v>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_698989-MLU78765589152_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_861837-MLU78765589158_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_797157-MLU79001804755_092024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="n">
+        <v>45809.6978028125</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Portátil Hp 15-fd0026la Intel Core I3 8gb Ram 512gb Ssd</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=7rxKWQ7YebPIwTcMe%2FVbKlY8dDNATsSwhM%2FkKA%2B2rOFG3CiZocK7Dg0dUE8iVnMMEYts5i9Kx6Pr81OU0LJuVl3wPUzQoEVit%2BxB%2BgUh1V2VxlsLsGXS1j%2BaIscsiGoulCVgpWDCEuAIWQQgEIoKHs7%2FLf0Fqt3n6afoPRozUTuIIfuTgFkM3tT0mMioh7nnz%2FOeBVkGs%2BeY%2BgCDdzUaYG8nUsUHvzJcuhJX1tiCjX3239baoclmSZUcX6YOqQ1k4UIKeawpMGY%2FnYUPoaoc2J0hqPWn6mfc5nTmEedHFZmIcD5o8xPDV%2FQl%2FC1rLh3tGl8r6QgYUnJddsTf%2FYJXz6JNxjaO1f0Y5bIFD%2BqHEdPf%2F9CPQo0J5P3BjygeP2zH5%2FCs61dxD3rRtbBo2tGm5Wa6OxypF4CNglxFhLmwmUgh7MsICgH9254Sw4cqqiIEpXQgJCc5zy2uAs0sWRCC8NkZ%2FswBJGlZtJbUNCXuihow1Y6E16UOLYI2MDHzM8bm3bHGsZZsuZkp5JxbAxzMdEVZNT8BIIkdc5nN4u4ZlRKuQ8Qlw%2F7v6234s%2FPJYy23QeKfeKDwPbctL1A%2B5sUs4iOJUYlesT01ZhAPptEKwxGy6tHrWstIWIaPJaF6vOPyhZPmBWGj2p%2BDjoAbqsEqs2TMVmpwnlGMS8rARTZGj%2B3BTN5waZPLHhei8Tg3g%2BRJbmepmslxUaa1gHnZCUlYD3rULCes7D8lYXnMkdOZcJ%2B2dxMscWn%2BjnB3cDJTzwf66KIP8BKiATjX7HfpA3Cu1aoo9P7B1rxHBC3iMLTIU8ctUN%2FreQ3jUuy2qhodZnYwXZ2Bto0Q5ttagBrVuGN7e6OW7DXY093GGZgHjFQDIhEOLQxxm5nm5rgJqVIzdw31Lcqa9o%2FfGWMgW2KQd4zqBrX8%2FSo5u6w8j9qcBFNal7wCSEZsS8BWR8n%2BqH075g%3D%3D&amp;highlight=false&amp;headerTopBrand=true#polycard_client=search-nordic&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO2878894100&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>2499900</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I61" t="b">
+        <v>0</v>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_692884-MLU76223208770_052024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_782590-MLU76223139428_052024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_986836-MLU76412455875_052024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_773714-MLU76223139436_052024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="n">
+        <v>45809.69780282408</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ASUS</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Portátil Asus X1605za-mb644 Intel Corei5-12500h 16gb Ram Disco Solido 512ssd 16 Fhd Endless</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-asus-x1605za-mb644-intel-corei5-12500h-16gb-ram-disco-solido-512ssd-16-fhd-endless/p/MCO32161065?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO32161065&amp;position=3&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO1523840021&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>2029900</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H62" t="b">
+        <v>1</v>
+      </c>
+      <c r="I62" t="b">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K62" t="n">
+        <v>145</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_822592-MLU74290609668_022024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_961011-MLU74290777838_022024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_769942-MLU74406002007_022024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_995013-MLU74406002009_022024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_838170-MLU74406002013_022024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '25 mar. 2025', 'contenido': 'Sus 12 nucleos y 16 procesadores lógicos lo hacen ideal en toda la cantidad de archivos, páginas y programas que debo usar. Es un exclente equipo. Tarda menos de 15 segundos en encender y apagar.\nExcelente refrigeración y su tiempo de carga es rápido. Buena duración de la batería dependiendo del trabajo que se este realizando. La pantalla es super amplia.\nEstoy muy satisfecho con la compra.', 'votos_utiles': '9'}, {'calificacion': 5, 'fecha': '03 may. 2025', 'contenido': 'Muy buen equipo, es bastante rápido y me corre bien varias ventanas a la vez y juegos pesaditos y exigentes gráficamente, el único contra que le encontré es que la batería se desaparece con nada 😭, lo cual hace que toque estarlo cargando o tenerlo conectado, me gustó que no se calienta demasiado, yo si recomiendo el equipo 👌.', 'votos_utiles': '5'}, {'calificacion': 5, 'fecha': '11 abr. 2024', 'contenido': 'Producto de acuerdo a lo esperado, buena calidad.', 'votos_utiles': '5'}, {'calificacion': 5, 'fecha': '24 jun. 2024', 'contenido': 'Muy buen equipo, trabaja a la perfección.', 'votos_utiles': '3'}, {'calificacion': 5, 'fecha': '16 mar. 2025', 'contenido': '', 'votos_utiles': '2'}]</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="n">
+        <v>45809.69780283565</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ASUS</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Portátil Asus Fa506nc Ryzen 5 7535hs Rtx3050 16gb 512gb 15.6 Color Negro</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-asus-fa506nc-ryzen-5-7535hs-rtx3050-16gb-512gb-156-color-negro/p/MCO45003983?highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO45003983&amp;position=10&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO1544070727&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>2975814</v>
+      </c>
+      <c r="E63" t="n">
+        <v>3199800</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>7% OFF</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H63" t="b">
+        <v>1</v>
+      </c>
+      <c r="I63" t="b">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>5</v>
+      </c>
+      <c r="K63" t="n">
+        <v>3</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_680616-MLA81284061462_122024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_978440-MLA81284061466_122024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_957941-MLA81284061468_122024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="n">
+        <v>45809.69780283565</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ASUS</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Portatil Asus E1504fa-nj474 Ryzen 5-7520u Ram 16gb Ssd 512gb Color Negro</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-asus-e1504fa-nj474-ryzen-5-7520u-ram-16gb-ssd-512gb-color-negro/p/MCO23498360?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO23498360&amp;position=14&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO1541876389&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1725640</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1988778</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>13% OFF</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H64" t="b">
+        <v>1</v>
+      </c>
+      <c r="I64" t="b">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K64" t="n">
+        <v>413</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_785588-MLU73109363362_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_726659-MLU73193255159_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_765061-MLU74154709735_012024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_794132-MLU71686123628_092023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_870312-MLU73981577884_012024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '27 jun. 2023', 'contenido': 'Excelente producto, la pantalla se me hace que le falta un poco de brillo, por lo demás no se encuentra ningún otro pc con esas características a un mejor precio.', 'votos_utiles': '30'}, {'calificacion': 5, 'fecha': '08 abr. 2024', 'contenido': 'En un principio, cuando recibí el equipo, la caja ya había sido abierta. Luego me di cuenta de que lo hicieron para instalar windows 11 de cortesía. Esto me genero desconfianza. Aunque lo revisé y todo parecía estar bien y nuevo, recomiendo que, al realizar la compra, pidan el producto totalmente sellado. Después, pueden instalar el sistema operativo usando un pendrive. Lo ideal es que sea windows 11, ya que es el más estable para este modelo.\nReinstalé windows 11 pro en inglés usando mi cuenta de microsoft. En un principio, la resolución de la imagen era de muy mala calidad, el sonido se distorsionaba y la batería duraba muy poco, lo cual me preocupó. Sin embargo, luego de las actualizaciones automáticas de windows, todo esto se corrigió.\nEl equipo viene por defecto con linux, es decir, no tiene licencia de windows. Pero se puede comprar una licencia oem en internet. Normalmente no supera los 15 dólares y es vitalicia.\nLlevo poco más de un mes usándolo para programar y usar photoshop, y el rendimiento esta muy bien, tambien corre algunos juegos pero no es gamer.\nCompra recomendada.', 'votos_utiles': '15'}, {'calificacion': 5, 'fecha': '06 sep. 2023', 'contenido': 'Me parecio excelente el computador. Es rapido, cuenta con buenas caracteristicas y en mi caso venia con windows 11. El precio es justo a su rendimiento. Estuve buscando otros laptops en otras paginas y en mercadolibre pero definitivamente esta maquina es muy buena para su bajo costo y sin decir que asus es una buena marca. En si me siento contento por la compra se los recomiendo 💯/💯.', 'votos_utiles': '12'}, {'calificacion': 5, 'fecha': '19 sep. 2023', 'contenido': 'Hasta ahora muy buen rendimiento, vino sin sistema operativo así que toco instalarle windows 11.', 'votos_utiles': '9'}, {'calificacion': 5, 'fecha': '26 sep. 2023', 'contenido': 'Hasta el momento no he tenido problemas con el equipo, corre todo muy bien, soy programador y trabajo con programas pesados y bien, también tengo un emulador de play 2 y también corre bien.', 'votos_utiles': '8'}]</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="n">
+        <v>45809.69780284722</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Portátil Hp 14-em0009la R5 Ram 16gb 512gb Ssd</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=N%2BKLmv2nrsjDYHSu4f8Poo1UY3A5cx58HwmjCwRaT4xwPin3NUxoHuz3m4dgJABTIq8UjvhPlZonGZKTQeM8S0y8S9r6k%2BZ3kbMm%2BW7QrYpOC0JMuByGAEhCK%2Bmt05miMzykoubcCelC2GWgfjFYMl1JxUJm8jpgVqT%2FQIEXNjhPOvKsF81anLzwcALL6EK3WMo1L5JhGk%2BAkV51IY8%2Bhn%2BDpuUnDkUBxYHO76284Do6fMPYhKI3G4%2FUrPJZGdcH%2Fx1lxC%2FSSgw4%2FCxxsG4NtDz40IURyKSqAA4P2kmMaNLK2VYUEI%2FU%2FJuN6ssDPDgGKjosnu7q%2FdAHlXpfAMGAbvRD0K3E%2F4sOwPZGTbtjI09H4AhXoFLGORRtfLgVofJ%2F2M22L%2BGKGheLPSvPLvMf4Q93rTkQY2Xa60UL1M0e%2FyV6YEHOd9FoymSy%2B7jY1Ehe82TayWGjahghoG75obfh4O%2B5GjDSELZxtDbfVehp4Emw98KwIfeyuJ8Qh0fB1dVqnDUct%2BcYTNgGjd3mMW9imiYDhNbQwp4e5x3qB9oeg6eo0iNge6AcDTa4EXUxzUH%2FCM%2BOjN2Ei2O4Msrfz9WhPIFPRZJXAXU%2FZv3HmrEZinnxsRAYxFhmyX%2F9nQ2xTlmyiC1OAngVMOmFsOUCrcsP8QS6kslCYPJBxWCDDOpZjf%2BPsrkjBjHduku0qyFpJumcuAbIVIf2mhiBaC7ElvjxqCCL8oC%2BP4Lsd6H9PMlQdG35ysmbL8vfXT6LdtewAUWtGJeSfFdu7Hsuz54vkA4dxepEQpVxBp3K%2BL4TaxawZw%2BVNLg9fjsyoAReN7KUahlWBa9G99t6RxKyk2CvXdB5gq1nxLz78CgKckv0Z6kZ8g2%2BClis9L0woqIQv1nHqJcjKGgt0PHclVz2wQNY05SZrtYai8psRODpPdlJstg%2BLCkn35Z7&amp;highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO2503419712&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1770900</v>
+      </c>
+      <c r="E65" t="n">
+        <v>2248125</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>21% OFF</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H65" t="b">
+        <v>1</v>
+      </c>
+      <c r="I65" t="b">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K65" t="n">
+        <v>20</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_971993-MLU72165226628_102023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_895690-MLU72226746163_102023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_971777-MLU72165196948_102023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_716188-MLU75004584385_032024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '21 dic. 2024', 'contenido': 'Excelente producto.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '31 oct. 2024', 'contenido': 'Por el momento cumple con lo prometido 👍🏽👍🏽.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '29 oct. 2024', 'contenido': 'Me pareció muy bueno en rendimiento y durabilidad de la batería.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '10 oct. 2024', 'contenido': 'Muy bueno, necesitaba un dispositivo para mí estudio y trabajo eficiente y asequible. Está máquina se ha comportado muy bien, muchas gracias 🫂.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '09 oct. 2024', 'contenido': 'Venía con windows 11 pre instalado pero le instalamos windows 10. Hp oficialmente solo da soporte para windows 11 sin embargo los drivers funcionan sin problema en windows 10.\nEl equipo nos pareció excelente por el precio es bastante fluido, el color es un plateado dorado que lo hace ver elegante y es muy ligero y silencioso, la batería nos duró más de 2 horas y aún tenía la mitad de la carga.\nInstalamos photoshop 2024 y corre sin problema las 16 gb de ram permiten tener varios programas abiertos sin que el equipo sufra en rendimiento.\nEstamos muy satisfechos con la compra, esperemos a ver cuánto dura el equipo en buenas condiciones.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="n">
+        <v>45809.6978028588</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Portátil HP 15-fd0065la Intel Core i5 16 GB 1 TB SSD 15.6" FHD Windows 11 Home</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=zrEQFkwo%2Bha2jUzCOjN6%2Fj93YsV5%2F%2BKkGo3%2Bycsw1DNsAOb%2BFCn8lbEjV5vuACF%2FqiLsfRlXFQg94mH80yDFnEofFyRMSW4JNWgiiqNRDfA8NS%2BmrmIAJgdB4MptnbYfmRRg4kY6A4k6HGfpiQfvF9GFnCGrCQy018QVrOytrsBoLrqpFp8gYEhDlySWCVq1jE50i6o5cTCnc%2FeXNC58LCwMOcHsIaqup2%2FF0PobtLbiq7diJGjq9bDIXalKvVX87%2BfzrAXSWWPdWKBFQme5vFz8PQCH0KaRBG%2FKRq%2FcDFDC7Rrg4%2BBVPtoWGYEfDghyOkXZhVxk3VcSedTZ55yD5YfgjFgyaW9l7t0Cj8GHhtmR8b2ejbNO%2B3GBY8DafcH90c33xycb84DIDxx7mnz6v6lqSS6HMo6DCN34ODEEsqDqvDPcRkFQN18T15lMBaL5vz8bvjfDCEDfWuISMMZzKhcFNbpmMcV1E3CmH724ZEYZh4utkArKbrW9a6rcdOqq6%2B%2Fm8Wxhg%2FNP6txUUp%2BnB3tXyc9BQyqFICL%2F9c6VdnWc5BZFJ6Z8VyQ5RxMNpqetwaOEG%2BW93wfnjFvHkSby9PT2xgy0Bn90axEUk7F2zyAQEieDV0NwHQxhc0t9MpkA5jHuX2gnViLta%2BuI%2FVKJm1nbuZxiAJQ6ZXDSEDmZKVJxgtUR0mnqyvl8Sn%2BmLrDkmR8k6RYgmetNTSNZr3SU5Wj84k2dZKF9B%2FZW21DQIUX7LYghmqduTnSXxpDv%2BkZ6%2BMT7aAv4yJBtY7X5H8Kyo5DJmwxZP11viUPgpH1EK%2BB72DAt3W0GEqj55152zd53zDBWGNTrTzMqmkRH7ve8lY0eTRueFMtiiiOLbN8qP%2FoC6agFLUfQTO4HS3ApHtwBNN6Dshz5gW%2FMuK30%2FB5q%2BlIShWE%2BjYGTcrvax1t9LTZYzzsvqR0dmGdrzcEMjOpixS6IO5GJJ5ldmxWOEAWikrqMYcio&amp;highlight=false&amp;headerTopBrand=true#polycard_client=search-nordic&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO1575797741&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>2500939</v>
+      </c>
+      <c r="E66" t="n">
+        <v>4099900</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>39% OFF</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H66" t="b">
+        <v>1</v>
+      </c>
+      <c r="I66" t="b">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>5</v>
+      </c>
+      <c r="K66" t="n">
+        <v>2</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_873079-MLA82669520756_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_879656-MLA84247887703_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_745543-MLA82956543925_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_831985-MLA82956572471_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_847818-MLA83952780706_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_930561-MLA84247761613_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_984171-MLA84247838835_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_904741-MLA84247761629_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_606436-MLA84247887717_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_875651-MLA84247838847_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_707448-MLA84247887737_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_729925-MLA84247887743_042025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="n">
+        <v>45809.69780287037</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>MacBook Air 13.6 M2 256 GB SSD 16 GB Ram Z160000au C/ Nota</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/macbook-air-136-m2-256-gb-ssd-16-gb-ram-z160000au-c-nota/p/MCO26602331?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO26602331&amp;position=18&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO1547152627&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>4266374</v>
+      </c>
+      <c r="E67" t="n">
+        <v>4960900</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>14% OFF</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H67" t="b">
+        <v>1</v>
+      </c>
+      <c r="I67" t="b">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K67" t="n">
+        <v>131</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_708839-MLA51356236557_082022-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_613040-MLA51356222696_082022-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_889912-MLA51356222738_082022-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_619023-MLA51356202957_082022-F.webp']</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '16 jun. 2023', 'contenido': 'Excelente elección la que hice, un gran pc para trabajar, soy dba y la verdad es que para desarrollo es muy bueno, la batería le dura un montón, el procesador es muy bueno, el sonido, la pantalla están a otro nivel, super recomendado.', 'votos_utiles': '28'}, {'calificacion': 5, 'fecha': '01 dic. 2023', 'contenido': '¡me encanta! esperé a probarla en todo lo que hago para comprobar si me serviría y ha sido una buena decisión de compra. La uso para diseño gráfico, edición de video, animación, modelado 3d y me va super bien. La mía es de 8gb de ram, si la van a usar para edición en after effects recomiendo la de 16gb, porque con 8 a veces se traban un poquito los fotogramas, nada grave, pero si es muy pesado puede que sufra. Del resto todo va genial.', 'votos_utiles': '17'}, {'calificacion': 5, 'fecha': '17 feb. 2024', 'contenido': 'Excelente, es la versión de 8 cores cpu y 8 cores gpu.', 'votos_utiles': '5'}, {'calificacion': 5, 'fecha': '08 nov. 2024', 'contenido': 'Excelente, viene sellado y nuevo probado en desarrollo de aplicaciones los emuladores con m2 corre perfectamente en simultáneo 👍.', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '17 ago. 2024', 'contenido': 'El producto está excelente, no me gusto que den una descripción errada su chip no es de 10 nuclueos.', 'votos_utiles': '2'}]</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="n">
+        <v>45809.69780288194</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Notebook 15,6 Hp 250 G9 Intel Celeron 8 Gb Ram 256 Gb Ssd Color Negro</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/notebook-156-hp-250-g9-intel-celeron-8-gb-ram-256-gb-ssd-color-negro/p/MCO24443216?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO24443216&amp;position=22&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO1479324193&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>902003</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1094000</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>17% OFF</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H68" t="b">
+        <v>1</v>
+      </c>
+      <c r="I68" t="b">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K68" t="n">
+        <v>22</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_669596-MLA72666764739_112023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_997141-MLA72594738346_112023-F.webp']</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '02 mar. 2025', 'contenido': 'Muy bueno, económico y lo recibí rápidamente.', 'votos_utiles': '4'}, {'calificacion': 5, 'fecha': '15 may. 2025', 'contenido': 'Me encanto y el precio espectacular.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '18 may. 2025', 'contenido': 'Increíble todo presentable y bonito.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '13 may. 2025', 'contenido': 'Excelente equipo.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '21 may. 2025', 'contenido': 'Excelente muy bonito.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="n">
+        <v>45809.69780288194</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Portátil 2 en 1 HP Pavilion x360 14-ek1011la Intel Core i5 8 GB RAM 512 GB SSD Windows 11 Home 14" Pantalla táctil FHD</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=%2BSe3mbHnUq3o5K5Ma4QG0e7Tbp8jVrEVndktNi2II%2FpEKKIIrzy6DKHLEQXwHmjsCP7fB6w6fMaejUzoWHWm14QbIJeVF6ZIGZpNkbPxm4KERMOhjBSKovolnzHjPBMOTfnUEr6tvv7fXSNIGiEfy7hC7PGBcGWhh8ABNS%2B8LCy97wuSpo099prP7aEVPEsTdiJGgX4lwlv56sx7vIao9B%2Ba9VdPJKDs94pmiyRx1PQNeNSP5D3Rlv%2BBbBlE2uPGCOfxf4pHnMWAQsJ5jTGqKzazOEB4ihJUrrBNTSHFcEmcJtXN2inM4Xhhu7KhnTbkJsMGZY4uDsr5CdwQO%2BP4EtTydJQtRdz24R%2B4UjrlPdlh26au3A4f0Cc%2BJl8nmNyxR4x5NIcps2ItYXWIkpa%2FfZJui3DFzE%2Fjddacgzd5VKSxrVNlRfA1tqqhrk63noLLBbXi6V%2FhOWSWUS8zonybALg%2BzxnRhCIYle6OCqJpzNsnLpYpi2GonQ8wB8PsfrR8uCAGjuybjmX1Ntx4x%2Fb2BrzVDBRiW3UuPJs9TuJVqcvkUpEuLnJvdXKJh8dohuxispnFaGkMyj7AQaCWjGMVkH%2BZy%2FhHKqPbfN9of%2B1zaUcUBdXmsMsewyZas5p8i%2FUiO6UltUhLqrYHffhM%2BI9VJX6zV%2BEOujUZPd%2FC%2F1a5DGUfX4VKnyPmMDvc8rGchBRd56Bei7O4PHxkXfeiA%2BFf1UxY%2BjRwnLT6TBFEECu2aK1%2F1DuWxfeJZx%2BJgLG3pUk%2B30QuKUT8k9WMzqt0mLl13bXxCNJEYSH3sL8GFp07NsTEaUDa9CMu1oswwhezldZ5EbYfZ3k1R7GIVFHseWonEbXP5m6xJCy%2BmsnLgqiKAuzbR4LhufGRbRiZ9bEDmuWOSScPsc%2BS3r%2BZORUYZvnx7Dq4BDP84IKg872%2FAWOCoM7CMxQ%2BJYqcSNKT%2Bw4Iw%2BaaTQW%2B%2Fmt585gkMpMsiirwBnGyyQEoaLpXvinN6blOoEkPm4LzfF71n3euWxSJkq7RFHiulGhXZC9lvxE4og%3D%3D&amp;highlight=false&amp;headerTopBrand=true#polycard_client=search-nordic&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO2859705258&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>2519937</v>
+      </c>
+      <c r="E69" t="n">
+        <v>3999900</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>37% OFF</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H69" t="b">
+        <v>1</v>
+      </c>
+      <c r="I69" t="b">
+        <v>0</v>
+      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_988735-MLA83130332646_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_794568-MLA84319057304_052025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_727216-MLA83130332652_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_759584-MLA83421014329_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_929368-MLA84319028858_052025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_675179-MLA84318904618_052025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_928766-MLA84319028882_052025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_652583-MLA84616214019_052025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_789295-MLA84318904640_052025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_731357-MLA84616214037_052025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_629484-MLA84616214041_052025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="n">
+        <v>45809.69780289352</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Portátil HP 15-fc0031la AMD Ryzen 7 16 GB RAM 1 TB SSD 15.6" FHD Windows 11 Home</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=fqAwV4T57cb34rd3Kqf2SGHtlfmHWtNC5CmZC23EPLpRCRRU8LdOIFuTRkKJhln6yJ55FRcEVw9z4vy5OWr9%2BmugkiOHxgO4TJMOTQD9d7jie1Nae2FT9kp4M52dJd8Bww1a4E8XFz%2B46qzk4t2IwUZaOQgSW6OtknvJNgcO7aqLNTVL%2F1CT%2Fwd7D%2BA%2B8QqcP%2BnolVDjI%2F3kpgjl8G3CRoKy4hdKNFelLpDVpKMEt6Svzpes3Nd1E0OvnMdtfiTkMOhE1oQ5XdtYDuUuY9ZvBUiYn5f%2F6dw1a0eToukVczdkkvtcH536SqcchJWxiUZaFHiNREuXtXbdL458Nbnvgew8fztzme7bnXE0WorNiHSZglAqyojldD5mEasByCgiXU8vlSr7bDAIbV1WDygYuX2YcXu5rHJDhC%2BLW2srMxWzgmYmkjRZEOtHoQBtTsazd9CvLeNBy7M5%2BYERS%2Fn82nWspqKZct2YBV9C5pCLrt4GEBlGpJNc84TNqyorjXnTMKmcTIz1TcSGvXVLWnzVtNYxEPilqLWc3sTvnRKhEDtcJInxS6izgyG%2BV2V6Od%2Fs0hd7d%2FNBCbA%2BpYtgR4pXROxp5icHjWc9IasDn7DhxitifFjPoL6QQumBYN8Shw30ruo%2FvYKI5c9RuJdEwRatW8IpgF0CTi%2BOd%2FiiWQINzICm2ReoD63ClcQVXR%2Fs1UvyYr%2Bke36XMA3YI4cxcmnQgidnqn96Fo2jd%2BfUeQSQDnoAgKSHAaJ9vVVVYNdeKhgTfw8PJZTn2l1EHN0Ek1lOCI53he%2FEsMIg6oePL7OXdBhDubl9f6KwTc3KQSms43uVKoS5VtVJ0rTFtDLX%2FjNM65Ahhsf9LfqpDjfmP6IX%2FEzTKEsezvP1R9kYCbeFQuwhX6vPEClUcCVRAzhEZtcyd0sG1ertd0UMMW7zpzEkz7eJxXizI9jgrLHTeIH%2FWvz%2BlbC3F088VahYgxN33YxvvBoHyM0%3D&amp;highlight=true&amp;headerTopBrand=true#polycard_client=search-nordic&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO1575771851&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>4099900</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H70" t="b">
+        <v>1</v>
+      </c>
+      <c r="I70" t="b">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>5</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_815916-MLA82945757783_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_874654-MLA84247757623_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_625769-MLA82945757787_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_660337-MLA82945757789_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_632767-MLA83952776642_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_952877-MLA83952474652_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_743470-MLA83952484392_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_832640-MLA83952474656_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_693165-MLA83952513586_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_900626-MLA83952484400_042025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '29 may. 2025', 'contenido': 'Excelente, tal como lo esperaba, totalmente empacado y con protección en la caja. Encantado.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="n">
+        <v>45809.6978029051</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>LENOVO</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Potátil Lenovo Ideapad Slim 3 15IAH8 15.6" color abyss blue 16GB de Ram 512GB SSD Intel Core i5</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/potatil-lenovo-ideapad-slim-3-15iah8-156-color-abyss-blue-16gb-de-ram-512gb-ssd-intel-core-i5/p/MCO28604720?highlight=true&amp;headerTopBrand=true#polycard_client=search-nordic&amp;searchVariation=MCO28604720&amp;position=9&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO1480376745&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1939900</v>
+      </c>
+      <c r="E71" t="n">
+        <v>2499000</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>22% OFF</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H71" t="b">
+        <v>1</v>
+      </c>
+      <c r="I71" t="b">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K71" t="n">
+        <v>51</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_795161-MLU73180411829_112023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_602068-MLU78543909026_082024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_837841-MLU73097256104_112023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_816754-MLU73097236384_112023-F.webp']</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '30 abr. 2025', 'contenido': 'Todo excelente excepto que la caja vino abierta y la pc ya estaba inicializada.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '05 mar. 2025', 'contenido': 'Un producto muy bueno, se comporta de manera esperada y se puede trabajar muy bien en él.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '24 oct. 2024', 'contenido': 'Excelente producto era lo que quería.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '28 may. 2025', 'contenido': 'Excelente.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '24 may. 2025', 'contenido': 'Bien fiel a la descripción del producto, para poder usar el desbloqueo con huella debes instalarlo un windows diferente al que trae.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="n">
+        <v>45809.69780291666</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Notebook Hp 245 G10 R3 7330u 512gb Ssd 8gb Ram Windows 11 Ho</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/notebook-hp-245-g10-r3-7330u-512gb-ssd-8gb-ram-windows-11-ho/p/MCO39243137?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO39243137&amp;backend_model=search-backend&amp;position=15&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO1547113843&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1259900</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1621375</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>22% OFF</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H72" t="b">
+        <v>1</v>
+      </c>
+      <c r="I72" t="b">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K72" t="n">
+        <v>21</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_679019-MLU78080956988_082024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_630529-MLU78080779350_082024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_880233-MLU78307689171_082024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_860704-MLU78080957006_082024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '27 may. 2025', 'contenido': 'Buena opcion.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '24 may. 2025', 'contenido': 'Muy bueno.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '19 may. 2025', 'contenido': 'Buen producto calidad - precio.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '13 may. 2025', 'contenido': 'Buen producto unue no veo mucho cambio en el brillo de la pantalla.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '06 may. 2025', 'contenido': 'Excelente.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="n">
+        <v>45809.69780291666</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Portatil Hp 12ava Gen Intel I3 1215u Ssd 512gb Ram 8gb Color Plateado</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-hp-12ava-gen-intel-i3-1215u-ssd-512gb-ram-8gb-color-plateado/p/MCO29272690?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO29272690&amp;backend_model=search-backend&amp;position=19&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO1507088307&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1458900</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1853000</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>21% OFF</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H73" t="b">
+        <v>1</v>
+      </c>
+      <c r="I73" t="b">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K73" t="n">
+        <v>54</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_645989-MLU78944581522_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_605957-MLU79183304451_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_641148-MLU78944551828_092024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '16 jul. 2024', 'contenido': 'Excelente producto muy recomendado.', 'votos_utiles': '6'}, {'calificacion': 5, 'fecha': '26 feb. 2025', 'contenido': '', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '21 dic. 2024', 'contenido': 'Me pareció un producto muy bueno y de excelente calidad 😃.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '06 may. 2025', 'contenido': 'Excelente, corresponde la descripción. Satisfecho con la compra.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '24 may. 2025', 'contenido': 'Excelente equipo.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="n">
+        <v>45809.69780292824</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>LENOVO</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Portatil Lenovo V14 Core I5-13420h 24gb 512gb Ssd Color Negro</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-lenovo-v14-core-i5-13420h-24gb-512gb-ssd-color-negro/p/MCO44279796?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO44279796&amp;position=21&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO1587144125&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1900230</v>
+      </c>
+      <c r="E74" t="n">
+        <v>2176667</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>12% OFF</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H74" t="b">
+        <v>1</v>
+      </c>
+      <c r="I74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K74" t="n">
+        <v>44</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_634636-MLA81072483529_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_664825-MLA81072531241_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_812999-MLA81072493673_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_699921-MLA81072493687_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_986563-MLA80807408510_112024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '26 dic. 2024', 'contenido': 'Al parecer de fabrica el producto viene de 8gb pero lo expanden a 16 gb con capacidad para que corran a 3200mt/s. En general muy bien, el windows que trae se debe activar pero esto lo decía en la descripción. Cumple las expectativas es muy buen equipo por el precio.', 'votos_utiles': '5'}, {'calificacion': 5, 'fecha': '08 mar. 2025', 'contenido': 'Muy buena pinta.', 'votos_utiles': '3'}, {'calificacion': 5, 'fecha': '21 feb. 2025', 'contenido': 'El producto vienes con windows 10 de prueba, tiene tapada la camara tapada con una cinta imperceptible, el color no es negro, sino gris claro. Me disguste al comienzo por el windows, pero lo logré solucionar, reinstalando desde cero y después actualizando al windows 11.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '04 feb. 2025', 'contenido': 'Buen equipo.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '08 ene. 2025', 'contenido': 'Nos gusta mucho. Excelente producto.', 'votos_utiles': '1'}]</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="n">
+        <v>45809.69780293982</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ASUS</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Computador Portatil Asus X1504za-nj227 Core I5 24gb 512gb Azul</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/computador-portatil-asus-x1504za-nj227-core-i5-24gb-512gb-azul/p/MCO34194456?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO34194456&amp;position=13&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO1434617549&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1999900</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H75" t="b">
+        <v>1</v>
+      </c>
+      <c r="I75" t="b">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K75" t="n">
+        <v>33</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_688334-MLU74956004603_032024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_935244-MLU74956073831_032024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_785486-MLU74956073833_032024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_881132-MLU74956220031_032024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '22 jul. 2024', 'contenido': 'Rápido para llegar, y producto 100% original.', 'votos_utiles': '3'}, {'calificacion': 5, 'fecha': '07 ago. 2024', 'contenido': 'Excelente producto, lo malo es que la batería dura 2 horas.', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '04 abr. 2025', 'contenido': 'Llevo usandolo 7 meses y no se queda pegado ni trabado, tiene buena imagen, buen sonido, la duración de la batería si no es mucha, pero abro muchas ventanas dos navegadores, word excel, whatsapp, canva. Y funciona super bien.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '10 oct. 2024', 'contenido': 'Super bueno el computador.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '02 oct. 2024', 'contenido': 'Excelente producto.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="n">
+        <v>45809.69780293982</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ACER</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Portátil Acer Nitro V Amd 7535hs Rtx 2050 Ram 16gb M.2 512gb Color Negro</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-acer-nitro-v-amd-7535hs-rtx-2050-ram-16gb-m2-512gb-color-negro/p/MCO45180899?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO45180899&amp;position=25&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO2855376486&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>3964360</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H76" t="b">
+        <v>1</v>
+      </c>
+      <c r="I76" t="b">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K76" t="n">
+        <v>43</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_741891-MLA82198647484_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_832363-MLA81683562665_122024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_639895-MLA81683572115_122024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_833177-MLA81683562669_122024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_975584-MLA81414345144_122024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_803507-MLA82482205935_022025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '08 feb. 2025', 'contenido': 'Excelente producto, muy bonito y de buena calidad, lo probe y me dejo sorprendido, muchisimas gracias.', 'votos_utiles': '6'}, {'calificacion': 5, 'fecha': '19 feb. 2025', 'contenido': 'Es un computador que ha cumplido de más con las expectativas que tenia antes de comprarlo.\nPor el momento llevo dos semanas con el computador y me ha gustado que la duración de la batería es mayor a lo que pensé que duraba aproximadamente 4 horas si no estas jugando o usando programas exigentes. Lo único que no me ha gustado es la cuestión del brillo de la pantalla que en los juegos se baja un poco pero no se si será algo que tenga que ver con el plan de energía o con los ajustes de algunos juegos, los componentes parece que son duraderos hasta el momento.', 'votos_utiles': '4'}, {'calificacion': 5, 'fecha': '19 feb. 2025', 'contenido': '', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '19 mar. 2025', 'contenido': 'Un producto exelente y eficaz.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '20 may. 2025', 'contenido': 'El producto a funcionado bien los primeros 2 meses, la pantalla es excelente ybel funcionamiento para juegos y trabajo es muy bueno. Lo unico es que al momento de suspender el equipo este no se suspende bien, sin embargo con el modo hinbernar trabaja ok. Por lo demas un 10.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="n">
+        <v>45809.69780295139</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ASUS</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Portatil Asus Vivobook X1504za-nj372 Corei5 1235u 20gb 512gb Azul</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-asus-vivobook-x1504za-nj372-corei5-1235u-20gb-512gb-azul/p/MCO28710903?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO28710903&amp;position=28&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO2219873382&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>2049900</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H77" t="b">
+        <v>1</v>
+      </c>
+      <c r="I77" t="b">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K77" t="n">
+        <v>325</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_676134-MLU74074108678_012024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_803354-MLU73981459906_012024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_785021-MLU74126725721_012024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_696570-MLU74965214543_032024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '10 mar. 2024', 'contenido': 'Buen producto. Buenas calidad, full rápido y me parece que esta bien calidad precio.\nLo único que no me gusta es que la batería dura como 3 horas y adicional así tengo uno las manos limpias quedan las huellas. Pero todo bien del portátil los recomiendo ya que está bien por su precio full rápido.', 'votos_utiles': '34'}, {'calificacion': 5, 'fecha': '08 mar. 2024', 'contenido': 'En general un muy buen equipo, lo único negativo hasta ahora es la duración de la batería, máximo 4 horas, lo que lo obliga estar conectado todo el día. Lo uso para correr photoshop, lightroom e ilustrator y los corre sin esfuerzo.', 'votos_utiles': '25'}, {'calificacion': 5, 'fecha': '24 mar. 2024', 'contenido': 'Muy potente, algo pesada pero acorde a lo comprado. Bastante contento con el pc. Algo q si me pone pensativo es el trackpad que a ratos se bugea. No sé si será problema de hardware o controladores.', 'votos_utiles': '7'}, {'calificacion': 5, 'fecha': '07 may. 2024', 'contenido': 'El equipo cuenta con una buena configuración, pero se debe tener en cuenta que el procesador arranca con 1. 3 gh y no con 3. 3 gh cómo aparece en las características del equipo.', 'votos_utiles': '7'}, {'calificacion': 5, 'fecha': '28 jul. 2024', 'contenido': 'Viene con windows 11 pirata y office pirata.\nTrackpad se traba mucho. Me toco inhabilitar y usar un mouse externo.', 'votos_utiles': '6'}]</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="n">
+        <v>45809.69780296296</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Laptop Hp 240 G9 Intel Celeron N4500 8gb 256gb Ssd 14 Black Color Plateado</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/laptop-hp-240-g9-intel-celeron-n4500-8gb-256gb-ssd-14-black-color-plateado/p/MCO33774175?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO33774175&amp;position=31&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO1479423655&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1140000</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H78" t="b">
+        <v>1</v>
+      </c>
+      <c r="I78" t="b">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K78" t="n">
+        <v>126</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_760560-MLU74476868512_022024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_705247-MLU74476670886_022024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_851843-MLU74476533280_022024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_871087-MLU74476670900_022024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_976018-MLU77494129899_072024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '26 ago. 2024', 'contenido': 'Excelente producto muy rápido, me parece muy bueno de verdad ,estoy muy contento seguiré usándolo y les contaré más adelante. !lo recomiendo ¡.', 'votos_utiles': '18'}, {'calificacion': 5, 'fecha': '29 ago. 2024', 'contenido': 'Excelente producto de muy buena calidad.', 'votos_utiles': '7'}, {'calificacion': 5, 'fecha': '23 nov. 2024', 'contenido': 'Buen producto.', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '23 ene. 2025', 'contenido': 'Buen producto, buen precio.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '15 dic. 2024', 'contenido': 'Buen equipo.', 'votos_utiles': '1'}]</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="n">
+        <v>45809.69780297454</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>DELL</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Portátil Dell Inspiron 7MPHP de 15,6" con procesador Intel Core i3 1215U 8 GB de RAM SSD de 512 GB gráficos Intel UHD Windows 11 Home</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-dell-inspiron-7mphp-de-156-con-procesador-intel-core-i3-1215u-8-gb-de-ram-ssd-de-512-gb-graficos-intel-uhd-windows-11-home/p/MCO29241815?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO29241815&amp;position=34&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO2878763932&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1542900</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H79" t="b">
+        <v>1</v>
+      </c>
+      <c r="I79" t="b">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K79" t="n">
+        <v>12</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_974186-MLU73493739646_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_707745-MLU73493749390_122023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_881227-MLA82482550187_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_948197-MLA82482550195_022025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '02 nov. 2024', 'contenido': 'En un principio tuvo un problema con la batería por lo cual casi tengo que devolverlo, pero con una actualización de bios mejoro totalmente, ahora funciona perfectamente y ganó rendimiento.\nActualización: el equipo definitivamente presenta problemas con la batería, básicamente es un equipo de mesa porque tiene que estar al cargador, sino, se apaga.', 'votos_utiles': '5'}, {'calificacion': 5, 'fecha': '26 may. 2025', 'contenido': 'Buen equipo. Recomendado.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '14 sep. 2024', 'contenido': 'Me gustó mucho.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="n">
+        <v>45809.69780298611</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>LENOVO</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Portatil Lenovo V14 Core I5-13420h 16gb 512gb Ssd Color Negro</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-lenovo-v14-core-i5-13420h-16gb-512gb-ssd-color-negro/p/MCO44291281?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO44291281&amp;position=37&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO1587242933&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1822630</v>
+      </c>
+      <c r="E80" t="n">
+        <v>2087778</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>12% OFF</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H80" t="b">
+        <v>1</v>
+      </c>
+      <c r="I80" t="b">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K80" t="n">
+        <v>44</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_879967-MLA82146207764_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_805132-MLA82146235530_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_651506-MLA82146235542_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_766303-MLA82146235560_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_894436-MLA80807769694_112024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '26 dic. 2024', 'contenido': 'Al parecer de fabrica el producto viene de 8gb pero lo expanden a 16 gb con capacidad para que corran a 3200mt/s. En general muy bien, el windows que trae se debe activar pero esto lo decía en la descripción. Cumple las expectativas es muy buen equipo por el precio.', 'votos_utiles': '5'}, {'calificacion': 5, 'fecha': '08 mar. 2025', 'contenido': 'Muy buena pinta.', 'votos_utiles': '3'}, {'calificacion': 5, 'fecha': '21 feb. 2025', 'contenido': 'El producto vienes con windows 10 de prueba, tiene tapada la camara tapada con una cinta imperceptible, el color no es negro, sino gris claro. Me disguste al comienzo por el windows, pero lo logré solucionar, reinstalando desde cero y después actualizando al windows 11.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '04 feb. 2025', 'contenido': 'Buen equipo.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '08 ene. 2025', 'contenido': 'Nos gusta mucho. Excelente producto.', 'votos_utiles': '1'}]</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="n">
+        <v>45809.69780299768</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Apple MacBook Air M1 A2337 Oro 8GB RAM 256GB 13´´</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/apple-macbook-air-m1-a2337-oro-8gb-ram-256gb-13/p/MCO17828522?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO17828522&amp;position=47&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO808606084&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>3290119</v>
+      </c>
+      <c r="E81" t="n">
+        <v>3963999</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>17% OFF</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H81" t="b">
+        <v>1</v>
+      </c>
+      <c r="I81" t="b">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K81" t="n">
+        <v>382</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_951282-MLU75274695601_032024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_600571-MLA46516512357_062021-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_927851-MLA46516517294_062021-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_779467-MLU70045246870_062023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_851876-MLU70045142548_062023-F.webp']</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '20 ene. 2022', 'contenido': 'Excelente, no estaba confiada de comprar este tipo de productos en una página que no fuera mac o apple, pero realmente vale la pena, 100% recomendado.', 'votos_utiles': '25'}, {'calificacion': 5, 'fecha': '20 oct. 2023', 'contenido': 'La mejor compra que pude haber hecho! me ahorre un montón comprándolo con ellos, todo fue muy seguro y confiable, el equipo es brutal, mejor de lo que pensé a decir verdad y pude actualizar la garantía de apple, para que la vigencia de la garantía iniciara desde el momento en que tuve el computador sin ningún problema.', 'votos_utiles': '18'}, {'calificacion': 5, 'fecha': '27 sep. 2021', 'contenido': 'Viene con el empaque original, es una belleza xd. Super recomendado!!!.', 'votos_utiles': '14'}, {'calificacion': 5, 'fecha': '01 dic. 2023', 'contenido': 'Con un mes de uso les puedo decir que fue una buena compra, corren súper bien los programas, la suite de adobe, ¡muy bueno!.\nDe pronto recomendaría que al enviarlo se protegiera un poco más, enviarlo en una caja adicional y no envuelto en vinipel, pero no hay queja es un buen producto.', 'votos_utiles': '9'}, {'calificacion': 5, 'fecha': '17 may. 2022', 'contenido': 'Muy bueno. El procesador m1 de apple es silencioso, no se calienta y realmente hace que la batería dure, con un trabajo fuerte, unas 6 horas continuas. Si se usa moderadamente, puede llegar hasta las 10 horas. El tamaño es perfecto y la pantalla muy descansada.', 'votos_utiles': '7'}]</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="n">
+        <v>45809.69780299768</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Apple MacBook Air A2337 (13 pulgadas, 2020, Chip M1, 256 GB de SSD, 8 GB de RAM) - Gris espacial</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/apple-macbook-air-a2337-13-pulgadas-2020-chip-m1-256-gb-de-ssd-8-gb-de-ram-gris-espacial/p/MCO17828518?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO17828518&amp;position=40&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO2882533476&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>3179900</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H82" t="b">
+        <v>1</v>
+      </c>
+      <c r="I82" t="b">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K82" t="n">
+        <v>382</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_801112-MLA46516512347_062021-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_945128-MLU78157079171_082024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_845099-MLU78156774309_082024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_970152-MLU75333668768_032024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_651876-MLU70045054836_062023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_812414-MLU74227330835_012024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_634442-MLU77934175580_082024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '20 ene. 2022', 'contenido': 'Excelente, no estaba confiada de comprar este tipo de productos en una página que no fuera mac o apple, pero realmente vale la pena, 100% recomendado.', 'votos_utiles': '25'}, {'calificacion': 5, 'fecha': '20 oct. 2023', 'contenido': 'La mejor compra que pude haber hecho! me ahorre un montón comprándolo con ellos, todo fue muy seguro y confiable, el equipo es brutal, mejor de lo que pensé a decir verdad y pude actualizar la garantía de apple, para que la vigencia de la garantía iniciara desde el momento en que tuve el computador sin ningún problema.', 'votos_utiles': '18'}, {'calificacion': 5, 'fecha': '27 sep. 2021', 'contenido': 'Viene con el empaque original, es una belleza xd. Super recomendado!!!.', 'votos_utiles': '14'}, {'calificacion': 5, 'fecha': '01 dic. 2023', 'contenido': 'Con un mes de uso les puedo decir que fue una buena compra, corren súper bien los programas, la suite de adobe, ¡muy bueno!.\nDe pronto recomendaría que al enviarlo se protegiera un poco más, enviarlo en una caja adicional y no envuelto en vinipel, pero no hay queja es un buen producto.', 'votos_utiles': '9'}, {'calificacion': 5, 'fecha': '17 may. 2022', 'contenido': 'Muy bueno. El procesador m1 de apple es silencioso, no se calienta y realmente hace que la batería dure, con un trabajo fuerte, unas 6 horas continuas. Si se usa moderadamente, puede llegar hasta las 10 horas. El tamaño es perfecto y la pantalla muy descansada.', 'votos_utiles': '7'}]</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="n">
+        <v>45809.69780300926</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>LENOVO</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Portátil Lenovo Ideapad Slim 3 Intel Ci 5 16gb 512gb Touch Color Artic Grey</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-lenovo-ideapad-slim-3-intel-ci-5-16gb-512gb-touch-color-artic-grey/p/MCO44598331?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO44598331&amp;position=42&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO1561982735&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>2640900</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H83" t="b">
+        <v>1</v>
+      </c>
+      <c r="I83" t="b">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>5</v>
+      </c>
+      <c r="K83" t="n">
+        <v>4</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_963696-MLA81226959531_122024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_977405-MLA81775119705_012025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_887519-MLA81505007442_012025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_964742-MLA83676357824_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_623826-MLA83969533867_042025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="n">
+        <v>45809.69780302083</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>LENOVO</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Portátil Lenovo Ideapad Slim 3 Amd Ryzen 7 16gb 512gb 15.6 Color Arctic Grey</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-lenovo-ideapad-slim-3-amd-ryzen-7-16gb-512gb-156-color-arctic-grey/p/MCO37810549?highlight=true&amp;headerTopBrand=true#polycard_client=search-nordic&amp;searchVariation=MCO37810549&amp;position=44&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO2779010778&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>2089900</v>
+      </c>
+      <c r="E84" t="n">
+        <v>2499000</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>16% OFF</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H84" t="b">
+        <v>1</v>
+      </c>
+      <c r="I84" t="b">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K84" t="n">
+        <v>15</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_909281-MLU77515509327_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_677423-MLU77126524991_062024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_635914-MLU77515154279_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_971628-MLU77300455380_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_633279-MLU76917265854_062024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '03 ene. 2025', 'contenido': 'Acabo de recibirlo. Todo en orden hasta el momento.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '30 may. 2025', 'contenido': 'Es muy lindo, hasta el momento se ve todo muy bien, es rápido y cumple con lo descrito.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '14 abr. 2025', 'contenido': 'Excelente producto como esperaba, muy buena mi compra.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '06 feb. 2025', 'contenido': 'Excelente equipo para tareas no tan exigentes. Funciona correcto.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="n">
+        <v>45809.69780302083</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>LENOVO</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Portatil Lenovo V14 Ryzen 5-7520u 16gb 512gb Ssd 14 Fhd W11 Color Gris</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-lenovo-v14-ryzen-5-7520u-16gb-512gb-ssd-14-fhd-w11-color-gris/p/MCO45053079?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO45053079&amp;position=23&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO2871737532&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1563436</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1799889</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>13% OFF</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H85" t="b">
+        <v>1</v>
+      </c>
+      <c r="I85" t="b">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K85" t="n">
+        <v>67</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_973188-MLA81586990965_122024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_835175-MLA81317920492_122024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_739569-MLA81318127024_122024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '09 may. 2024', 'contenido': 'Cómo lo dice la descripción si necesitan editar no es recomendable por la tarjeta de video que trae de resto bien.', 'votos_utiles': '4'}, {'calificacion': 5, 'fecha': '20 sep. 2024', 'contenido': '', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '06 abr. 2024', 'contenido': 'Tuve problemas ,pero le dieron soporte técnico.\nNo funcionó para un juego.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '28 dic. 2024', 'contenido': 'Es excelente, igual a la descripción, aunque apenas lo empezamos a usar tenemos una buena impresión de él y por su precio es magnífico.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '11 feb. 2024', 'contenido': 'Excelente producto 👌🏻.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="n">
+        <v>45809.69780303241</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Notebook Gamer Hp Victus Geforce Rtx 3050 Intel Core I5 12450h Ram 8gb 512gb Ssd 15.6 Windows 11 Home Teclado En Ingles</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/notebook-gamer-hp-victus-geforce-rtx-3050-intel-core-i5-12450h-ram-8gb-512gb-ssd-156-windows-11-home-teclado-en-ingles/p/MCO38663805?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO38663805&amp;position=29&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO2806196396&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>2859287</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H86" t="b">
+        <v>1</v>
+      </c>
+      <c r="I86" t="b">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K86" t="n">
+        <v>9</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_641788-MLU77760151986_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_819035-MLU77980686613_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_898014-MLU77980513409_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_603791-MLU77980609361_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_688727-MLU77980686653_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_964238-MLU77980513423_072024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '16 abr. 2025', 'contenido': '', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '17 may. 2025', 'contenido': 'Funciona bien hasta ahora.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '24 abr. 2025', 'contenido': 'Oportuno y de calidad.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="n">
+        <v>45809.69780304398</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>LENOVO</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Laptop Lenovo V14 G3 Core I7 Ram 16gb Ssd 512gb Windows 11p Color Gris</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/laptop-lenovo-v14-g3-core-i7-ram-16gb-ssd-512gb-windows-11p-color-gris/p/MCO26889377?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO26889377&amp;position=32&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO2862177114&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>2822111</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H87" t="b">
+        <v>1</v>
+      </c>
+      <c r="I87" t="b">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>5</v>
+      </c>
+      <c r="K87" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_738596-MLU77745865439_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_790574-MLU77745865443_072024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_711353-MLU71542677954_092023-F.webp']</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="n">
+        <v>45809.69780305555</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Portátil HP Pavilion 15-eg2502la Intel Core i5, 8GB RAM, 512GB SSD FHD Windows 11 Home Single Language 15.6"</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-hp-pavilion-15-eg2502la-intel-core-i5-8gb-ram-512gb-ssd-fhd-windows-11-home-single-language-156/p/MCO43617108?highlight=true&amp;headerTopBrand=true#polycard_client=search-nordic&amp;searchVariation=MCO43617108&amp;position=35&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO1533188369&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1999900</v>
+      </c>
+      <c r="E88" t="n">
+        <v>3999900</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>50% OFF</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H88" t="b">
+        <v>1</v>
+      </c>
+      <c r="I88" t="b">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>5</v>
+      </c>
+      <c r="K88" t="n">
+        <v>2</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_869128-MLA82657660240_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_604498-MLA82657699012_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_847044-MLA80907670179_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_990362-MLA80644182686_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_745759-MLA82657660244_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_711980-MLA80644326096_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_815064-MLA80907728731_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_772797-MLA82657612892_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_705589-MLA82657688828_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_736084-MLA82657660248_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_687884-MLA82657660252_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_779975-MLA82944618805_032025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="n">
+        <v>45809.69780305555</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>LENOVO</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Laptop Lenovo V15 G4 15.6 Fhd, Amd Ryzen 5 7520u 16gb 512gb Color Gris Oscuro</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/laptop-lenovo-v15-g4-156-fhd-amd-ryzen-5-7520u-16gb-512gb-color-gris-oscuro/p/MCO38471251?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO38471251&amp;position=38&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO2847347768&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>1799000</v>
+      </c>
+      <c r="E89" t="n">
+        <v>2599000</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>30% OFF</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H89" t="b">
+        <v>1</v>
+      </c>
+      <c r="I89" t="b">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>5</v>
+      </c>
+      <c r="K89" t="n">
+        <v>1</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_985927-MLA83785959761_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_652695-MLA83493369896_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_864036-MLA83493369908_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_869464-MLA83786028359_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_859104-MLU77594784568_072024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="n">
+        <v>45809.69780306713</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ASUS</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Asus X1504ZA-NJ Portatil Vivobook Core I3 1215u 12gb Ssd 512gb Color Gris</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/asus-x1504za-nj-portatil-vivobook-core-i3-1215u-12gb-ssd-512gb-color-gris/p/MCO41209434?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO41209434&amp;position=41&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO2855495740&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1789900</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H90" t="b">
+        <v>1</v>
+      </c>
+      <c r="I90" t="b">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K90" t="n">
+        <v>155</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_810314-MLA79572310599_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_759250-MLA79572181493_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_980329-MLA79328451606_092024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '04 feb. 2025', 'contenido': 'Buen diseño y rendimiento, mal por no traer windows con una licencia válida.', 'votos_utiles': '4'}, {'calificacion': 5, 'fecha': '12 mar. 2025', 'contenido': 'El portátil me parece excelente pero lo malo es que dice tener teclado retroiluminado fue una de las razones por la que lo compre pero después de tanto buscar resulta que no tiene mi única petición es que por favor pongan correctamente las especificaciones para evitar molestias por parte de los compradores muchas gracias.', 'votos_utiles': '3'}, {'calificacion': 5, 'fecha': '05 feb. 2025', 'contenido': 'Excelente producto, muy buena calidad, excelente precio.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '29 mar. 2025', 'contenido': 'El producto está bien, todo correcto excepto que el windows venía preactivado con un programa se terceros lo que podria haber comprometido la seguridad del sistema. Dejen que cada cliente se encargue de activar el windows si es que el equipo no lo trae preactivado de fabrica, pero no le metan esos programas de terceros para activar, mal ahi con ese tema.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '22 ene. 2025', 'contenido': 'Excelente.', 'votos_utiles': '1'}]</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="n">
+        <v>45809.69780307871</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Portátil Hp 14-em0009la R5 Ram 16gb 512gb Ssd</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-hp-14-em0009la-r5-ram-16gb-512gb-ssd/p/MCO27712926?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO27712926&amp;backend_model=search-backend&amp;position=27&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO2503419712&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>1770900</v>
+      </c>
+      <c r="E91" t="n">
+        <v>2248125</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>21% OFF</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H91" t="b">
+        <v>1</v>
+      </c>
+      <c r="I91" t="b">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K91" t="n">
+        <v>20</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_971993-MLU72165226628_102023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_895690-MLU72226746163_102023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_971777-MLU72165196948_102023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_716188-MLU75004584385_032024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '21 dic. 2024', 'contenido': 'Excelente producto.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '31 oct. 2024', 'contenido': 'Por el momento cumple con lo prometido 👍🏽👍🏽.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '29 oct. 2024', 'contenido': 'Me pareció muy bueno en rendimiento y durabilidad de la batería.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '10 oct. 2024', 'contenido': 'Muy bueno, necesitaba un dispositivo para mí estudio y trabajo eficiente y asequible. Está máquina se ha comportado muy bien, muchas gracias 🫂.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '09 oct. 2024', 'contenido': 'Venía con windows 11 pre instalado pero le instalamos windows 10. Hp oficialmente solo da soporte para windows 11 sin embargo los drivers funcionan sin problema en windows 10.\nEl equipo nos pareció excelente por el precio es bastante fluido, el color es un plateado dorado que lo hace ver elegante y es muy ligero y silencioso, la batería nos duró más de 2 horas y aún tenía la mitad de la carga.\nInstalamos photoshop 2024 y corre sin problema las 16 gb de ram permiten tener varios programas abiertos sin que el equipo sufra en rendimiento.\nEstamos muy satisfechos con la compra, esperemos a ver cuánto dura el equipo en buenas condiciones.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="n">
+        <v>45809.69780307871</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>MacBook Air Apple Plateada Chip M1 - 13.3'' 256gb + 8gb Ram Color Plata</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/macbook-air-apple-plateada-chip-m1-133-256gb-8gb-ram-color-plata/p/MCO23897874?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO23897874&amp;position=26&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO1542965083&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>3136711</v>
+      </c>
+      <c r="E92" t="n">
+        <v>3336927</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>6% OFF</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H92" t="b">
+        <v>1</v>
+      </c>
+      <c r="I92" t="b">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K92" t="n">
+        <v>7</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_927163-MLA48622311771_122021-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_877821-MLA48622311780_122021-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_895758-MLU75330635714_032024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_613244-MLA52006428745_102022-F.webp']</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '04 may. 2022', 'contenido': 'La verdad es que es una super máquina, super fluido para casi todo los programas que uso, excelente para edición de video e imagines, la pantalla es una belleza, para programación 10 de 10. Un portátil que le puede funcionar a cualquiera para trabajar o estudiar, la autonomía es increíble nunca había tenido un portátil que le durará tanto la batería. Aguanta todo un día sin cargar. Eso sí para juegos no es tan bueno, por la refrigeración y el tema de los puertos tipo usb c si es algo molesto, pero con un convertidor se soluciona sin ningún problema. En mi opinión es el mejor portátil relación precio calidad y si tienes un ipad compatible es una experiencia única trabajar con los 2 dispositivos. Estéticamente también es una belleza. Sin duda alguna es una excelente inversion.', 'votos_utiles': '16'}, {'calificacion': 5, 'fecha': '28 oct. 2023', 'contenido': 'Excelente. La única observación es que el teclado no está en español, como dice la descripción del producto. De resto, todo perfecto.', 'votos_utiles': '5'}, {'calificacion': 5, 'fecha': '21 ene. 2023', 'contenido': 'Ese mac es muy bueno la verdad quede encantado, lo malo es que casi no trae para conectarle cosas y todo toca compralo por aparte y obviamente costoso.', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '22 ene. 2025', 'contenido': 'Excelente producto muy rápido y excelente rendimiento.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '25 ago. 2022', 'contenido': 'Muy buen producto, es original y funciona muy bien.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="n">
+        <v>45809.69780309028</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>LENOVO</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Portátil Lenovo Loq I5 12450hx Rtx 3050 Ram 24gb M.2 512gb Color Gris</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-lenovo-loq-i5-12450hx-rtx-3050-ram-24gb-m2-512gb-color-gris/p/MCO45171417?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO45171417&amp;position=30&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO2330572176&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>3391900</v>
+      </c>
+      <c r="E93" t="n">
+        <v>3999000</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>15% OFF</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H93" t="b">
+        <v>1</v>
+      </c>
+      <c r="I93" t="b">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K93" t="n">
+        <v>4</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_987364-MLA81403229692_122024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_974590-MLA81672868677_122024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '14 ene. 2025', 'contenido': 'La verdad el mejor portátil calidad precio para este 2025, teniendo en cuenta el precio considero la pantalla, diseño, potencia y en general el equipo lo mejor de lo mejor, lo único medio flojo es el audio pero bueno con ese precio que más podemos pedir, recomendado 100% para estudio y trabajo,superó mis expectativas!.', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '12 ene. 2025', 'contenido': 'Muy buen producto, aunque tiene fugas de luz la pantalla, es normal en pantallas ips pero son equipos muy costosos para que tengan estos problemas.', 'votos_utiles': '2'}]</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="n">
+        <v>45809.69780310185</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>DELL</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Portátil Computador Dell Intel Core I3 Ssd 512gb Ram 16gb Color Plateado</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-computador-dell-intel-core-i3-ssd-512gb-ram-16gb-color-plateado/p/MCO36040434?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO36040434&amp;position=33&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO1590497761&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>1539900</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H94" t="b">
+        <v>1</v>
+      </c>
+      <c r="I94" t="b">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>5</v>
+      </c>
+      <c r="K94" t="n">
+        <v>12</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_770176-MLU75931401003_042024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_831397-MLU75931450311_042024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_756128-MLU75931489827_042024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_968122-MLU75931401031_042024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '09 oct. 2024', 'contenido': 'Hasta hora todo bien cumple su función.', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '30 abr. 2025', 'contenido': 'Excelente!! muy bonito el portatil, viene bien empacado. Recomendado.\nBeneficio calidad/precio 10/10.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '03 abr. 2025', 'contenido': 'Excelente.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '28 feb. 2025', 'contenido': 'Excelente producto, vale la pena la compra.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '09 ene. 2025', 'contenido': 'Excelente.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="n">
+        <v>45809.69780311343</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Portátil HP 15-fc0031la AMD Ryzen 7 16 GB RAM 1 TB SSD 15.6" FHD Windows 11 Home</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-hp-15-fc0031la-amd-ryzen-7-16-gb-ram-1-tb-ssd-156-fhd-windows-11-home/p/MCO46955411?highlight=true&amp;headerTopBrand=true#polycard_client=search-nordic&amp;searchVariation=MCO46955411&amp;backend_model=search-backend&amp;position=24&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO1575771851&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>4099900</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H95" t="b">
+        <v>1</v>
+      </c>
+      <c r="I95" t="b">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>5</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_815916-MLA82945757783_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_874654-MLA84247757623_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_625769-MLA82945757787_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_660337-MLA82945757789_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_632767-MLA83952776642_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_952877-MLA83952474652_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_743470-MLA83952484392_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_832640-MLA83952474656_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_693165-MLA83952513586_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_900626-MLA83952484400_042025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '29 may. 2025', 'contenido': 'Excelente, tal como lo esperaba, totalmente empacado y con protección en la caja. Encantado.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="n">
+        <v>45809.69780311343</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>ACER</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Portátil Acer A314 Core I3 N305 Ram 8gb / 512gb Ssd Pant 14 Color Plateado</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-acer-a314-core-i3-n305-ram-8gb-512gb-ssd-pant-14-color-plateado/p/MCO26314505?highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO26314505&amp;position=36&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO1507994095&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>1441900</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1699000</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>15% OFF</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H96" t="b">
+        <v>1</v>
+      </c>
+      <c r="I96" t="b">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>5</v>
+      </c>
+      <c r="K96" t="n">
+        <v>5</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_604376-MLU71250039543_082023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_672975-MLU71250039539_082023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_906856-MLU71250039513_082023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_671038-MLU71250039531_082023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_923047-MLU71250039519_082023-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_979669-MLU75008026861_032024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="n">
+        <v>45809.697803125</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>DELL</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Portatil Dell 12ava Gen Intel I5 1235u Ram 16g Ssd 512gb Fhd</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>https://articulo.mercadolibre.com.co/MCO-2195229740-portatil-dell-12ava-gen-intel-i5-1235u-ram-16g-ssd-512gb-fhd-_JM?searchVariation=185116985227&amp;highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=185116985227&amp;position=58&amp;search_layout=stack&amp;type=item&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>1788288</v>
+      </c>
+      <c r="E97" t="n">
+        <v>2714143</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>34% OFF</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H97" t="b">
+        <v>1</v>
+      </c>
+      <c r="I97" t="b">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K97" t="n">
+        <v>47</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_904912-MCO83799180877_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_622595-MCO79584034437_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_779638-MCO79340867374_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_962550-MCO79340837530_092024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_644458-MCO79583984351_092024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '02 ene. 2025', 'contenido': 'El equipo es de buena marca y sus características son buenas, hasta el momento no hay nada que resolver,.', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '25 ene. 2025', 'contenido': 'Los productos que contienen lo de mercadolibre son muy buenos.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '06 sep. 2024', 'contenido': 'Me pareció perfecto, tiene dos slots para aumentarle la ram en un futuro. Velocidad buena.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '15 jul. 2024', 'contenido': 'Computador calidad precio fluido para trabajar y estudiar. Una semana de uso.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '10 abr. 2024', 'contenido': 'Bien.', 'votos_utiles': '1'}]</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="n">
+        <v>45809.69780313657</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>ACER</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Portatil Acer Anv15-core I7-13620h-16gb 512gbssd-rtx4060 W11 Color Negro</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-acer-anv15-core-i7-13620h-16gb-512gbssd-rtx4060-w11-color-negro/p/MCO40349136?highlight=true&amp;headerTopBrand=true#polycard_client=search-nordic&amp;searchVariation=MCO40349136&amp;position=39&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO2838784016&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>4599900</v>
+      </c>
+      <c r="E98" t="n">
+        <v>5499000</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>16% OFF</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H98" t="b">
+        <v>1</v>
+      </c>
+      <c r="I98" t="b">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>5</v>
+      </c>
+      <c r="K98" t="n">
+        <v>5</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_666931-MLA84520656400_052025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_959367-MLA84520656408_052025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="n">
+        <v>45809.69780314815</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Portátil HP 14-em0021la AMD Ryzen 5 16 GB RAM 512 GB SSD 14" FHD Windows 11 Home</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-hp-14-em0021la-amd-ryzen-5-16-gb-ram-512-gb-ssd-14-fhd-windows-11-home/p/MCO40677703?highlight=true&amp;headerTopBrand=true#polycard_client=search-nordic&amp;searchVariation=MCO40677703&amp;position=43&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO2839966264&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>3769900</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H99" t="b">
+        <v>1</v>
+      </c>
+      <c r="I99" t="b">
+        <v>0</v>
+      </c>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_885614-MLA80402372726_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_985307-MLA83016946286_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_766946-MLA80661827215_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_653332-MLA80661827223_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_825145-MLA83016946296_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_960757-MLA83306630973_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_729130-MLA83306715903_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_822188-MLA83016946340_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_975250-MLA83306621309_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_669244-MLA83306650235_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_669468-MLA83306631061_032025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_854122-MLA83306650311_032025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="n">
+        <v>45809.69780314815</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>DELL</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Potátil Inspiron 3520 15.6" color plateado 24GB de Ram - 1TB SSD - Intel Core i5</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/potatil-inspiron-3520-156-color-plateado-24gb-de-ram-1tb-ssd-intel-core-i5/p/MCO28036809?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO28036809&amp;position=46&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO2877609362&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>2224671</v>
+      </c>
+      <c r="E100" t="n">
+        <v>3370714</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>34% OFF</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H100" t="b">
+        <v>1</v>
+      </c>
+      <c r="I100" t="b">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K100" t="n">
+        <v>61</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_614295-MLA83382157596_042025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_699565-MLA83382224918_042025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '28 may. 2024', 'contenido': 'Excelente equipo, con una excelente pantalla 1080p a 120hz, buen procesador y buena ram por el precio comparado con otros equipos del mismo rango.', 'votos_utiles': '3'}, {'calificacion': 5, 'fecha': '27 ago. 2024', 'contenido': 'Muy buen portátil, enciende y apaga muy rápido, programas de edición de fotos como photoshop y corel funcionan muy bien, al igual que programas de edición de vídeo y autocad, la imagen se ve muy bien y es muy liviano.', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '05 ene. 2024', 'contenido': '', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '22 feb. 2025', 'contenido': 'Super bueno, me encantó.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '04 sep. 2024', 'contenido': 'Bastante minimalista el diseño y los materiales, pero parece bueno, habrá que esperar.', 'votos_utiles': '1'}]</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="n">
+        <v>45809.69780315972</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>LENOVO</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Portátil Lenovo Loq 15iax9e Intel Core i5-12450HX 16 GB 512 GB SSD Rtx 3050 Linux 15.6 - 83 mes00000 Luna Grey</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/portatil-lenovo-loq-15iax9e-intel-core-i5-12450hx-16-gb-512-gb-ssd-rtx-3050-linux-156-83-mes00000-luna-grey/p/MCO46041404?highlight=false&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO46041404&amp;position=45&amp;search_layout=stack&amp;type=product&amp;tracking_id=850fc68e-18cd-4d4d-8a4c-275c4dbd0805&amp;wid=MCO1565833163&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>3259900</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H101" t="b">
+        <v>1</v>
+      </c>
+      <c r="I101" t="b">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K101" t="n">
+        <v>4</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_616917-MLA82397783055_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_964751-MLA82397753819_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_611356-MLA82115164154_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_633128-MLA82397783073_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_896739-MLA82115164168_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_842018-MLA82397916241_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_612272-MLA82397879409_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_928102-MLA82397783113_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_968942-MLA82115164238_022025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_892696-MLA82397753943_022025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '12 may. 2025', 'contenido': 'Aún lo estoy probando, de momento se comporta bien, la batería no dura nada, alrededor de una 1,3 hora.', 'votos_utiles': '1'}]</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="n">
+        <v>45809.69780317129</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>titulo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>precio</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>precio_anterior</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>descuento</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>envio</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>envio_gratis</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>envio_full</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>rating</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>total_reviews</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>imagen</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>imagenes</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>opiniones</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>fecha_actualizacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MOTOROLA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Celular Motorola Moto G35 5g, 256 GB, 4 GB RAM + 8 GB RAM Boost y cámara de 50 MP con pantalla Ai NFC 6.7 con superbrillo, gris</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/celular-motorola-moto-g35-5g-256-gb-4-gb-ram-8-gb-ram-boost-y-camara-de-50-mp-con-pantalla-ai-nfc-67-con-superbrillo-gris/p/MCO41998152?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO41998152&amp;position=2&amp;search_layout=stack&amp;type=product&amp;tracking_id=4aae2b86-3cd4-480d-91c3-208ac8209887&amp;wid=MCO2868956904&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>669933</v>
+      </c>
+      <c r="E2" t="n">
+        <v>999900</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>33% OFF</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_722812-MLA79743301446_102024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '22 may. 2025', 'contenido': 'Genial.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '02 mar. 2025', 'contenido': 'Excelente producto.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '22 feb. 2025', 'contenido': 'Buen producto.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>45809.70020177693</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MOTOROLA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Smartphone Moto G35 5g 256gb - Coral - Cuero vegano</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/smartphone-moto-g35-5g-256gb-coral-cuero-vegano/p/MCO41540860?highlight=true&amp;headerTopBrand=true#polycard_client=search-nordic&amp;searchVariation=MCO41540860&amp;position=18&amp;search_layout=stack&amp;type=product&amp;tracking_id=4aae2b86-3cd4-480d-91c3-208ac8209887&amp;wid=MCO2809026642&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>699900</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1399900</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>50% OFF</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_867628-MLA80145052363_102024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_894817-MLA79891797742_102024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_632925-MLA80145033167_102024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_873550-MLA80145120367_102024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_789890-MLA80145052421_102024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_711117-MLA80145033199_102024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_981646-MLA80145052445_102024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_945243-MLA80145120417_102024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_853004-MLA80145167017_102024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '22 may. 2025', 'contenido': 'Genial.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '02 mar. 2025', 'contenido': 'Excelente producto.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '22 feb. 2025', 'contenido': 'Buen producto.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>45809.70020180252</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TECNO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Smartphone Tecno Spark 30  256+8gb + Audifonos Tecno Es1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=0JQWJee0m5aMyzEJWchcSXlPR02GTk%2BP42vE6rSie3h27pvvUduiuQ0pLzmAPDEOS%2Bg0dhkdFFM3WQbmmRnx7P8jRV27LnZa70P%2FR3YVGAvA1fLjvo2u5HstIahYWt45wqGMGo47Ska5jOMgWUxgKjspeJHuPEnDRVN0YeU2PXDAngq32hBA8h1yiPgYhlinTiul0SwTu2OC2Q8nbpb2VWyI%2FXv6xcRbMpxryaDA6AK7jspzf%2BDJ7EpgY6AjpwQpV8uQM%2BM%2FRVIagoPAMnRkQn%2BDluPP70kTZxfJOIFH0cDrkAFjsXFZR65Q4qxIK7FMoXd5ZIxBxz6F27sOSkJ2yiE9rMK4%2FCtIjL2SsIZFAZ4TxBT6COo%2Fr1NBKyIzIBXMUSZ346x8GF0iEBrwiHRIpLXQyCSl5xPskPJihPCsfTZqqh1NCWsaFD003j2QrI9inenWuH%2BhsqBxY6RjE23uYqltmFXVTzAZCMVj4W%2FeaRn4nm1uMzHGd9RXpeKFHkAty%2BJfnnf87iWy1K8%2BBgf3eENtW4ySNP3R%2BVdv1ktJAxa34fIeoChJYH7BpgJGV8OK7SbosYHjF7CDttt8DJyxUTpJ2p7YKK5gktfJreTyRxJ8o5HWEtxNbCUzSSZ4TbJYBp8oCk3mBFFNVw1TBv5i1hrYa3dBIL1I2qVg9EfXhXDntPsRoadPlJWfPE%2BSDModA4ildIc09sgn%2BHCbwfyeoMPIvUXbA1sXDAeLhvoHxCdnP7ZSKHMFm0XcgcINGYGFseoWqWiSo4c8TWm90q93WNC8QXDvvZToyqM3x%2Bsm3cDikQfdsAV%2Bi0CjOtFjKnYAqcgBu%2FMlYDnpwJrbXQF7XAw8yDFIb%2BYNWxy44aLcyXLeW%2Bf5xkVkQQiOqxBufmRMDeuIErwCGkw26cQR%2BT9XYa4rPHU8aVa2PaFEfik%2FrrQhYB38PGQ%3D&amp;searchVariation=182256254638&amp;highlight=false&amp;headerTopBrand=true#polycard_client=search-nordic&amp;tracking_id=4aae2b86-3cd4-480d-91c3-208ac8209887</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>729900</v>
+      </c>
+      <c r="E4" t="n">
+        <v>999900</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>27% OFF</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_771556-MCO80511739690_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_658889-MCO80772862203_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_898101-MCO80511739710_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_946960-MCO80511956156_112024-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_705947-MCO80511887110_112024-F.webp']</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '02 may. 2025', 'contenido': 'Excelente producto recomendado muchachos.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '16 abr. 2025', 'contenido': 'En 2 meses de uso ha sido un buen equipo, tiene excelente cámara y una buena relación precio va calidad.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>45809.70020182443</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TECNO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Smartphone Tecno Spark 30c 128+4gb</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://click1.mercadolibre.com.co/mclics/clicks/external/MCO/count?a=%2FmJR5aUBOtmmWTfyyXulz5gNt%2FbBG7aAcgvKt2Yrwu1QPb65nMvFJB9XjWthJfJ7o5hxg8YyITzj8E%2B8UIKJ2i8DXHikQlzU%2BhmOx5PeyEuHaLQsXX0ftBuR26HKyK7%2FCdq1uIj9pi1MZVpPnw1fCYcIzzqqWkdwCZ7QYeuwPeHzOiUhGkyVFeH7%2Fjy35bw7GzLrq%2FhkfSd6wsEbyLTeRpmexoDJ2pg2M1EfLKFzpdNe1j%2B%2BWbYoj10WQNkX8%2FfAb48NWaoa60KuocgOt5GFv0t7Wua5G3ZdGJ%2FeTUBSmbVLIRZ0xi%2B9MZJJe4o8CRjS0oFGR6mCbjtsUfLrAV2pZA%2B060WW0QCHWgnyIWgMP9nutiuCp9G%2BbClOyl27b3m1ZqvvtvRG5msDha3wcv0eOJdFq%2BwhWdNaudx%2F0XX8qZkZazM7AMx87%2BmwaeR6o6q%2FQmfJY%2BRIGF0G1M3RysgCH%2B63aqReaimzHJySEdsVu6ExwwzW%2BhzCWUH%2FLSd%2BPOOpCpwbYLBqKZrXeby7Ashj39cXMJqfu5zvc76G2Guuvxf7n%2FLreLHgxTxIIsd1xGWzKyMdllcOjA7wVJueIVC0dHe9%2BDtjPG7sdhQ0RsTyLzDe60CFZJe%2BTaQEVt2rU8ruwlco2UvMkEKIOkIi7ekD7XxgBEVF27rdrXB2e9Te9agWpIcqNVjKMiahBJNKlyzKMx7oVnXnvi8q2EDaLg1E04cZovdY6Sjg8x5bQxgXupPnphIR6fCktCxDL3xXrG%2F%2FAypkcoG9fhtzWMUYEoAKtD2Hhzdu0%2FnFmeo8FKup2hDWR7dlVklaYTPLrawWCeSX9qA8UXficCzarMozhIxYlEB7A7bzsM0otCRSZZI8Wp6%2BZ3uxwR1ZvoRyn0o12RCzjCC84xkIdNxO5LfHO9xT7mS0CA%3D%3D&amp;searchVariation=182732098342&amp;highlight=false&amp;headerTopBrand=true#polycard_client=search-nordic&amp;tracking_id=4aae2b86-3cd4-480d-91c3-208ac8209887</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>479900</v>
+      </c>
+      <c r="E5" t="n">
+        <v>859900</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>44% OFF</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_640848-MCO81602345120_012025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_667188-MCO81873558503_012025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_870410-MCO81873558509_012025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_620882-MCO81873578323_012025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '29 abr. 2025', 'contenido': 'Muy bueno por ese precio más que satisfecho.', 'votos_utiles': '0'}, {'calificacion': 5, 'fecha': '06 may. 2025', 'contenido': 'Fue una verdadera sorpresa cuando se apagó de la nada y luego prendió a los 15 días como si se hubiese formateado solo.\nY la empresa no tiene canales efectivos para reclamos.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>45809.70020184437</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MOTOROLA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Celular Motorola Moto G55 256gb 8gb RAM 5G Negro</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.co/celular-motorola-moto-g55-256gb-8gb-ram-5g-negro/p/MCO42830499?highlight=true&amp;headerTopBrand=false#polycard_client=search-nordic&amp;searchVariation=MCO42830499&amp;position=24&amp;search_layout=stack&amp;type=product&amp;tracking_id=4aae2b86-3cd4-480d-91c3-208ac8209887&amp;wid=MCO1583511721&amp;sid=search</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>718003</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1399900</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>45% OFF</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Envío gratis</t>
+        </is>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>['https://http2.mlstatic.com/D_NQ_NP_2X_799287-MLA82052499865_012025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_829046-MLA82052471101_012025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_881518-MLA82052509561_012025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_654188-MLA82052471121_012025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_926424-MLA82052499909_012025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_731942-MLA82052461041_012025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_787445-MLA82052499941_012025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_602041-MLA82052471161_012025-F.webp', 'https://http2.mlstatic.com/D_NQ_NP_2X_916614-MLA82052471177_012025-F.webp']</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>[{'calificacion': 5, 'fecha': '05 mar. 2025', 'contenido': 'Excelente celular, buen desempeño, pantalla con buena resolución, viene con cargador y buena duración de batería, carga rápida. Excelente opción de compra a cuotas sin interés.', 'votos_utiles': '4'}, {'calificacion': 5, 'fecha': '08 abr. 2025', 'contenido': 'Por el precio es más de lo que esperaba es hermoso tiene una imagen superior la duración de la batería es buena y el almacenamiento más de lo que uno espera estéticamente muy lindo.', 'votos_utiles': '2'}, {'calificacion': 5, 'fecha': '22 mar. 2025', 'contenido': 'Recomiendo al 100%.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '19 mar. 2025', 'contenido': 'Excelente teléfono su relación calidad y precio.', 'votos_utiles': '1'}, {'calificacion': 5, 'fecha': '30 may. 2025', 'contenido': 'Excelente.', 'votos_utiles': '0'}]</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>45809.70020186302</v>
       </c>
     </row>
   </sheetData>
